--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,219 +492,219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1467</v>
+        <v>5.1445</v>
       </c>
       <c r="C2" t="n">
-        <v>1.02934</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.343400433740389</v>
+        <v>1.6569</v>
       </c>
       <c r="E2" t="n">
-        <v>41.7878</v>
+        <v>5.1445</v>
       </c>
       <c r="F2" t="n">
-        <v>4.771607325114059</v>
+        <v>2.0291</v>
       </c>
       <c r="G2" t="n">
-        <v>37.01620162053675</v>
+        <v>3.1154</v>
       </c>
       <c r="H2" t="n">
-        <v>4.771607325114059</v>
+        <v>2.0291</v>
       </c>
       <c r="I2" t="n">
-        <v>4.694146167238831</v>
+        <v>1.6447</v>
       </c>
       <c r="J2" t="n">
-        <v>37.01620162053675</v>
+        <v>3.1154</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>41.7103</v>
+        <v>4.7601</v>
       </c>
       <c r="N2" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6516</v>
+        <v>5.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93032</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.150056083818442</v>
+        <v>1.6066</v>
       </c>
       <c r="E3" t="n">
-        <v>35.7736</v>
+        <v>5.02</v>
       </c>
       <c r="F3" t="n">
-        <v>20.64848009456676</v>
+        <v>4.1713</v>
       </c>
       <c r="G3" t="n">
-        <v>15.12516021428822</v>
+        <v>0.8487</v>
       </c>
       <c r="H3" t="n">
-        <v>21.1807665516224</v>
+        <v>4.2216</v>
       </c>
       <c r="I3" t="n">
-        <v>23.10629078358807</v>
+        <v>3.4218</v>
       </c>
       <c r="J3" t="n">
-        <v>15.12516021428822</v>
+        <v>0.8487</v>
       </c>
       <c r="K3" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="L3" t="n">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>38.2315</v>
+        <v>4.2705</v>
       </c>
       <c r="N3" t="n">
-        <v>259</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6152</v>
+        <v>4.9177</v>
       </c>
       <c r="C4" t="n">
-        <v>0.92304</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.13649552210478</v>
+        <v>1.5653</v>
       </c>
       <c r="E4" t="n">
-        <v>35.3518</v>
+        <v>4.9177</v>
       </c>
       <c r="F4" t="n">
-        <v>6.307332771352982</v>
+        <v>3.7926</v>
       </c>
       <c r="G4" t="n">
-        <v>29.04449275476558</v>
+        <v>1.1251</v>
       </c>
       <c r="H4" t="n">
-        <v>6.307332771352982</v>
+        <v>3.7926</v>
       </c>
       <c r="I4" t="n">
-        <v>6.450681243429186</v>
+        <v>3.074</v>
       </c>
       <c r="J4" t="n">
-        <v>29.04449275476558</v>
+        <v>1.1251</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L4" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M4" t="n">
-        <v>35.4952</v>
+        <v>4.1991</v>
       </c>
       <c r="N4" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2376</v>
+        <v>4.5864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8475199999999999</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.000684755960739</v>
+        <v>1.4314</v>
       </c>
       <c r="E5" t="n">
-        <v>31.1273</v>
+        <v>4.5864</v>
       </c>
       <c r="F5" t="n">
-        <v>7.052748371537242</v>
+        <v>1.5062</v>
       </c>
       <c r="G5" t="n">
-        <v>24.0745479629476</v>
+        <v>3.0802</v>
       </c>
       <c r="H5" t="n">
-        <v>7.052748371537242</v>
+        <v>1.5062</v>
       </c>
       <c r="I5" t="n">
-        <v>7.693907314404264</v>
+        <v>1.5132</v>
       </c>
       <c r="J5" t="n">
-        <v>24.0745479629476</v>
+        <v>3.0802</v>
       </c>
       <c r="K5" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>31.7685</v>
+        <v>4.5934</v>
       </c>
       <c r="N5" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0699</v>
+        <v>4.4351</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8139799999999999</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9431823543614812</v>
+        <v>1.3703</v>
       </c>
       <c r="E6" t="n">
-        <v>29.3386</v>
+        <v>4.4351</v>
       </c>
       <c r="F6" t="n">
-        <v>14.77273828003327</v>
+        <v>1.3587</v>
       </c>
       <c r="G6" t="n">
-        <v>14.56588856202366</v>
+        <v>3.0764</v>
       </c>
       <c r="H6" t="n">
-        <v>14.77273828003327</v>
+        <v>1.3587</v>
       </c>
       <c r="I6" t="n">
-        <v>15.10848233185221</v>
+        <v>1.365</v>
       </c>
       <c r="J6" t="n">
-        <v>14.56588856202366</v>
+        <v>3.0764</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -725,7 +713,7 @@
         <v>150</v>
       </c>
       <c r="M6" t="n">
-        <v>29.6744</v>
+        <v>4.4414</v>
       </c>
       <c r="N6" t="n">
         <v>255</v>
@@ -734,737 +722,737 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8915</v>
+        <v>4.1209</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7783000000000001</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.883836213598943</v>
+        <v>1.2434</v>
       </c>
       <c r="E7" t="n">
-        <v>27.4926</v>
+        <v>4.1209</v>
       </c>
       <c r="F7" t="n">
-        <v>21.95848463953661</v>
+        <v>1.3328</v>
       </c>
       <c r="G7" t="n">
-        <v>5.534121366467873</v>
+        <v>2.7881</v>
       </c>
       <c r="H7" t="n">
-        <v>22.94537826203932</v>
+        <v>1.3328</v>
       </c>
       <c r="I7" t="n">
-        <v>21.45541863463416</v>
+        <v>1.3328</v>
       </c>
       <c r="J7" t="n">
-        <v>5.534121366467873</v>
+        <v>2.7881</v>
       </c>
       <c r="K7" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M7" t="n">
-        <v>26.9895</v>
+        <v>4.1209</v>
       </c>
       <c r="N7" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9607</v>
+        <v>3.7879</v>
       </c>
       <c r="C8" t="n">
-        <v>0.59214</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6022769272889148</v>
+        <v>1.1089</v>
       </c>
       <c r="E8" t="n">
-        <v>18.7344</v>
+        <v>3.7879</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.100234261044625</v>
+        <v>3.4908</v>
       </c>
       <c r="G8" t="n">
-        <v>23.83465814376496</v>
+        <v>0.2971</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.100234261044625</v>
+        <v>3.4908</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.017438250313381</v>
+        <v>2.8294</v>
       </c>
       <c r="J8" t="n">
-        <v>23.83465814376496</v>
+        <v>0.2971</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L8" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>18.8172</v>
+        <v>3.1265</v>
       </c>
       <c r="N8" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4536</v>
+        <v>3.7249</v>
       </c>
       <c r="C9" t="n">
-        <v>0.49072</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4670206074408195</v>
+        <v>1.0834</v>
       </c>
       <c r="E9" t="n">
-        <v>14.5271</v>
+        <v>3.7249</v>
       </c>
       <c r="F9" t="n">
-        <v>19.2901438042139</v>
+        <v>4.5556</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.763002508687</v>
+        <v>-0.8307</v>
       </c>
       <c r="H9" t="n">
-        <v>19.49422240703643</v>
+        <v>5.7676</v>
       </c>
       <c r="I9" t="n">
-        <v>21.26642444403974</v>
+        <v>4.6748</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.763002508687</v>
+        <v>-0.8307</v>
       </c>
       <c r="K9" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="L9" t="n">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>16.5034</v>
+        <v>3.8441</v>
       </c>
       <c r="N9" t="n">
-        <v>259</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0535</v>
+        <v>2.8066</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4107000000000001</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3684198044685483</v>
+        <v>0.7124</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4601</v>
+        <v>2.8066</v>
       </c>
       <c r="F10" t="n">
-        <v>31.73663269158155</v>
+        <v>1.6129</v>
       </c>
       <c r="G10" t="n">
-        <v>-20.27656761027097</v>
+        <v>1.1937</v>
       </c>
       <c r="H10" t="n">
-        <v>41.69682397801593</v>
+        <v>1.6129</v>
       </c>
       <c r="I10" t="n">
-        <v>38.98923800541749</v>
+        <v>1.6129</v>
       </c>
       <c r="J10" t="n">
-        <v>-20.27656761027097</v>
+        <v>1.1937</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M10" t="n">
-        <v>18.7127</v>
+        <v>2.8066</v>
       </c>
       <c r="N10" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0421</v>
+        <v>2.6674</v>
       </c>
       <c r="C11" t="n">
-        <v>0.40842</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3657115494229891</v>
+        <v>0.6562</v>
       </c>
       <c r="E11" t="n">
-        <v>11.3758</v>
+        <v>2.6674</v>
       </c>
       <c r="F11" t="n">
-        <v>22.12518271659159</v>
+        <v>0.6102</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.74936060675662</v>
+        <v>2.0572</v>
       </c>
       <c r="H11" t="n">
-        <v>23.18022304518638</v>
+        <v>0.6102</v>
       </c>
       <c r="I11" t="n">
-        <v>22.80392072302427</v>
+        <v>0.613</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.74936060675662</v>
+        <v>2.0572</v>
       </c>
       <c r="K11" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
-        <v>12.0546</v>
+        <v>2.6702</v>
       </c>
       <c r="N11" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9741</v>
+        <v>2.566</v>
       </c>
       <c r="C12" t="n">
-        <v>0.39482</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.349653133287941</v>
+        <v>0.6152</v>
       </c>
       <c r="E12" t="n">
-        <v>10.8763</v>
+        <v>2.566</v>
       </c>
       <c r="F12" t="n">
-        <v>10.87630907666378</v>
+        <v>2.4204</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1456</v>
       </c>
       <c r="H12" t="n">
-        <v>10.87630907666378</v>
+        <v>2.4204</v>
       </c>
       <c r="I12" t="n">
-        <v>10.38193139136088</v>
+        <v>2.4204</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.1456</v>
       </c>
       <c r="K12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M12" t="n">
-        <v>10.3819</v>
+        <v>2.566</v>
       </c>
       <c r="N12" t="n">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9374</v>
+        <v>2.0219</v>
       </c>
       <c r="C13" t="n">
-        <v>0.38748</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3410586908473928</v>
+        <v>0.3954</v>
       </c>
       <c r="E13" t="n">
-        <v>10.609</v>
+        <v>2.0219</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.137921873092</v>
+        <v>2.0219</v>
       </c>
       <c r="G13" t="n">
-        <v>31.74689225484405</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-21.82359221058382</v>
+        <v>2.0219</v>
       </c>
       <c r="I13" t="n">
-        <v>-23.80755513881871</v>
+        <v>2.0219</v>
       </c>
       <c r="J13" t="n">
-        <v>31.74689225484405</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L13" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>7.9393</v>
+        <v>2.0219</v>
       </c>
       <c r="N13" t="n">
-        <v>259</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5869</v>
+        <v>1.9313</v>
       </c>
       <c r="C14" t="n">
-        <v>0.31738</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2617593710715774</v>
+        <v>0.3588</v>
       </c>
       <c r="E14" t="n">
-        <v>8.142300000000001</v>
+        <v>1.9313</v>
       </c>
       <c r="F14" t="n">
-        <v>8.142286032778385</v>
+        <v>2.0288</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0975</v>
       </c>
       <c r="H14" t="n">
-        <v>8.142286032778385</v>
+        <v>2.0288</v>
       </c>
       <c r="I14" t="n">
-        <v>8.406645968907553</v>
+        <v>2.0288</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0975</v>
       </c>
       <c r="K14" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>8.406599999999999</v>
+        <v>1.9313</v>
       </c>
       <c r="N14" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5226</v>
+        <v>1.9054</v>
       </c>
       <c r="C15" t="n">
-        <v>0.30452</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2477200070387384</v>
+        <v>0.3484</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7056</v>
+        <v>1.9054</v>
       </c>
       <c r="F15" t="n">
-        <v>11.58595336617771</v>
+        <v>1.9054</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.88037573931316</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>11.58595336617771</v>
+        <v>1.9054</v>
       </c>
       <c r="I15" t="n">
-        <v>11.39786970763587</v>
+        <v>1.9054</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.88037573931316</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7.5175</v>
+        <v>1.9054</v>
       </c>
       <c r="N15" t="n">
-        <v>249</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4927</v>
+        <v>1.7076</v>
       </c>
       <c r="C16" t="n">
-        <v>0.29854</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2412467993225417</v>
+        <v>0.2685</v>
       </c>
       <c r="E16" t="n">
-        <v>7.5042</v>
+        <v>1.7076</v>
       </c>
       <c r="F16" t="n">
-        <v>9.674222878245441</v>
+        <v>1.7076</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.170000826767146</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.674222878245441</v>
+        <v>1.7076</v>
       </c>
       <c r="I16" t="n">
-        <v>9.517173805546651</v>
+        <v>1.7076</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.170000826767146</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.3472</v>
+        <v>1.7076</v>
       </c>
       <c r="N16" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4268</v>
+        <v>1.6762</v>
       </c>
       <c r="C17" t="n">
-        <v>0.28536</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2271180306249246</v>
+        <v>0.2558</v>
       </c>
       <c r="E17" t="n">
-        <v>7.0647</v>
+        <v>1.6762</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.319415644500066</v>
+        <v>1.6762</v>
       </c>
       <c r="G17" t="n">
-        <v>10.38414826889112</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.319415644500066</v>
+        <v>1.6762</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.394856909147795</v>
+        <v>1.6762</v>
       </c>
       <c r="J17" t="n">
-        <v>10.38414826889112</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6.9893</v>
+        <v>1.6762</v>
       </c>
       <c r="N17" t="n">
-        <v>255</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4112</v>
+        <v>1.6414</v>
       </c>
       <c r="C18" t="n">
-        <v>0.28224</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2237912277398316</v>
+        <v>0.2417</v>
       </c>
       <c r="E18" t="n">
-        <v>6.9612</v>
+        <v>1.6414</v>
       </c>
       <c r="F18" t="n">
-        <v>6.961249106096336</v>
+        <v>0.1477</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.4937</v>
       </c>
       <c r="H18" t="n">
-        <v>6.961249106096336</v>
+        <v>0.1477</v>
       </c>
       <c r="I18" t="n">
-        <v>7.458481185103216</v>
+        <v>0.1484</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.4937</v>
       </c>
       <c r="K18" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M18" t="n">
-        <v>7.4585</v>
+        <v>1.6421</v>
       </c>
       <c r="N18" t="n">
-        <v>110</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1578</v>
+        <v>1.4231</v>
       </c>
       <c r="C19" t="n">
-        <v>0.23156</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1710311640940182</v>
+        <v>0.1535</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3201</v>
+        <v>1.4231</v>
       </c>
       <c r="F19" t="n">
-        <v>5.320094760587402</v>
+        <v>0.8719</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5512</v>
       </c>
       <c r="H19" t="n">
-        <v>5.320094760587402</v>
+        <v>0.8719</v>
       </c>
       <c r="I19" t="n">
-        <v>5.337367795524374</v>
+        <v>0.876</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5512</v>
       </c>
       <c r="K19" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M19" t="n">
-        <v>5.3374</v>
+        <v>1.4272</v>
       </c>
       <c r="N19" t="n">
-        <v>103</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0252</v>
+        <v>1.4223</v>
       </c>
       <c r="C20" t="n">
-        <v>0.20504</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1443228962949594</v>
+        <v>0.1532</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4893</v>
+        <v>1.4223</v>
       </c>
       <c r="F20" t="n">
-        <v>4.489307480767282</v>
+        <v>0.9613</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="H20" t="n">
-        <v>4.489307480767282</v>
+        <v>0.9613</v>
       </c>
       <c r="I20" t="n">
-        <v>4.503883154406137</v>
+        <v>0.9613</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="K20" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5039</v>
+        <v>1.4223</v>
       </c>
       <c r="N20" t="n">
-        <v>103</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7852</v>
+        <v>1.2901</v>
       </c>
       <c r="C21" t="n">
-        <v>0.15704</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09755686664630378</v>
+        <v>0.0998</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0346</v>
+        <v>1.2901</v>
       </c>
       <c r="F21" t="n">
-        <v>10.47533078044967</v>
+        <v>1.8984</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.440727245745222</v>
+        <v>-0.6083</v>
       </c>
       <c r="H21" t="n">
-        <v>10.47533078044967</v>
+        <v>1.8984</v>
       </c>
       <c r="I21" t="n">
-        <v>10.30527670933848</v>
+        <v>1.9072</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.440727245745222</v>
+        <v>-0.6083</v>
       </c>
       <c r="K21" t="n">
         <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8645</v>
+        <v>1.2989</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7139</v>
+        <v>1.194</v>
       </c>
       <c r="C22" t="n">
-        <v>0.14278</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08403060562417164</v>
+        <v>0.061</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6139</v>
+        <v>1.194</v>
       </c>
       <c r="F22" t="n">
-        <v>2.613855709152466</v>
+        <v>1.823</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
       <c r="H22" t="n">
-        <v>2.613855709152466</v>
+        <v>1.823</v>
       </c>
       <c r="I22" t="n">
-        <v>2.724180787785524</v>
+        <v>1.4776</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
       <c r="K22" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7242</v>
+        <v>0.8486</v>
       </c>
       <c r="N22" t="n">
-        <v>107</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
@@ -1474,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6951000000000001</v>
+        <v>1.1936</v>
       </c>
       <c r="C23" t="n">
-        <v>0.13902</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08047529674856892</v>
+        <v>0.0608</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5033</v>
+        <v>1.1936</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6989394304431408</v>
+        <v>0.5864</v>
       </c>
       <c r="G23" t="n">
-        <v>1.80432485391515</v>
+        <v>0.6072</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6989394304431408</v>
+        <v>0.5864</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6875930111177651</v>
+        <v>0.5891</v>
       </c>
       <c r="J23" t="n">
-        <v>1.80432485391515</v>
+        <v>0.6072</v>
       </c>
       <c r="K23" t="n">
         <v>101</v>
@@ -1507,7 +1495,7 @@
         <v>68</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4919</v>
+        <v>1.1963</v>
       </c>
       <c r="N23" t="n">
         <v>169</v>
@@ -1516,127 +1504,127 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6877</v>
+        <v>1.1472</v>
       </c>
       <c r="C24" t="n">
-        <v>0.13754</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07910241126455618</v>
+        <v>0.0421</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4606</v>
+        <v>1.1472</v>
       </c>
       <c r="F24" t="n">
-        <v>5.242593705112965</v>
+        <v>1.1472</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.782034391565535</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.242593705112965</v>
+        <v>1.1472</v>
       </c>
       <c r="I24" t="n">
-        <v>5.361743562047351</v>
+        <v>1.1472</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.782034391565535</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5797</v>
+        <v>1.1472</v>
       </c>
       <c r="N24" t="n">
-        <v>255</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4311</v>
+        <v>1.0824</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08622</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03198859037716197</v>
+        <v>0.0159</v>
       </c>
       <c r="E25" t="n">
-        <v>0.995</v>
+        <v>1.0824</v>
       </c>
       <c r="F25" t="n">
-        <v>13.43888142231779</v>
+        <v>1.0824</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.44384444782486</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>13.43888142231779</v>
+        <v>1.0824</v>
       </c>
       <c r="I25" t="n">
-        <v>13.22071776286458</v>
+        <v>1.0824</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.44384444782486</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7769</v>
+        <v>1.0824</v>
       </c>
       <c r="N25" t="n">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0315</v>
+        <v>1.0306</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03872630864568503</v>
+        <v>-0.005</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2046</v>
+        <v>1.0306</v>
       </c>
       <c r="F26" t="n">
-        <v>5.370691616460732</v>
+        <v>1.5681</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.575312030606678</v>
+        <v>-0.5375</v>
       </c>
       <c r="H26" t="n">
-        <v>5.370691616460732</v>
+        <v>1.5681</v>
       </c>
       <c r="I26" t="n">
-        <v>5.28350506424546</v>
+        <v>1.5681</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.575312030606678</v>
+        <v>-0.5375</v>
       </c>
       <c r="K26" t="n">
         <v>101</v>
@@ -1645,7 +1633,7 @@
         <v>43</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2918</v>
+        <v>1.0306</v>
       </c>
       <c r="N26" t="n">
         <v>144</v>
@@ -1654,81 +1642,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.9981</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.01806</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.06095983412038157</v>
+        <v>-0.0182</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8962</v>
+        <v>0.9981</v>
       </c>
       <c r="F27" t="n">
-        <v>-13.60673580374753</v>
+        <v>1.5584</v>
       </c>
       <c r="G27" t="n">
-        <v>11.71051942804749</v>
+        <v>-0.5603</v>
       </c>
       <c r="H27" t="n">
-        <v>-13.60673580374753</v>
+        <v>1.5584</v>
       </c>
       <c r="I27" t="n">
-        <v>-13.38584723550488</v>
+        <v>1.5584</v>
       </c>
       <c r="J27" t="n">
-        <v>11.71051942804749</v>
+        <v>-0.5603</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.6753</v>
+        <v>0.9981</v>
       </c>
       <c r="N27" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6302</v>
+        <v>0.971</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.12604</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1654259840943374</v>
+        <v>-0.0291</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.1457</v>
+        <v>0.971</v>
       </c>
       <c r="F28" t="n">
-        <v>11.26561507355522</v>
+        <v>1.0232</v>
       </c>
       <c r="G28" t="n">
-        <v>-16.41135512571032</v>
+        <v>-0.0522</v>
       </c>
       <c r="H28" t="n">
-        <v>11.26561507355522</v>
+        <v>1.0232</v>
       </c>
       <c r="I28" t="n">
-        <v>11.08273171197153</v>
+        <v>1.0232</v>
       </c>
       <c r="J28" t="n">
-        <v>-16.41135512571032</v>
+        <v>-0.0522</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
@@ -1737,7 +1725,7 @@
         <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.3286</v>
+        <v>0.9710000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>144</v>
@@ -1746,277 +1734,277 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1056</v>
+        <v>0.9643</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.22112</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2658707872407823</v>
+        <v>-0.0318</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.270200000000001</v>
+        <v>0.9643</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.270175728999812</v>
+        <v>1.9643</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.270175728999812</v>
+        <v>1.9643</v>
       </c>
       <c r="I29" t="n">
-        <v>-7.894258650408911</v>
+        <v>1.5921</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K29" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>-7.8943</v>
+        <v>0.5921000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.1754</v>
+        <v>0.9095</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.23508</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2813365362042816</v>
+        <v>-0.0539</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.751300000000001</v>
+        <v>0.9095</v>
       </c>
       <c r="F30" t="n">
-        <v>7.937802116533109</v>
+        <v>0.9095</v>
       </c>
       <c r="G30" t="n">
-        <v>-16.68905537584806</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>7.937802116533109</v>
+        <v>0.9095</v>
       </c>
       <c r="I30" t="n">
-        <v>7.808941692563415</v>
+        <v>0.9095</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.68905537584806</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-8.880100000000001</v>
+        <v>0.9095</v>
       </c>
       <c r="N30" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.229</v>
+        <v>0.8371</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2458</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2933336797233666</v>
+        <v>-0.0832</v>
       </c>
       <c r="E31" t="n">
-        <v>-9.1244</v>
+        <v>0.8371</v>
       </c>
       <c r="F31" t="n">
-        <v>-9.124436361447218</v>
+        <v>0.7842</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="H31" t="n">
-        <v>-9.124436361447218</v>
+        <v>0.7842</v>
       </c>
       <c r="I31" t="n">
-        <v>-9.509558675404405</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="K31" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>-9.509600000000001</v>
+        <v>0.8407</v>
       </c>
       <c r="N31" t="n">
-        <v>107</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.5471</v>
+        <v>0.742</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.30942</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3668865762168061</v>
+        <v>-0.1216</v>
       </c>
       <c r="E32" t="n">
-        <v>-11.4124</v>
+        <v>0.742</v>
       </c>
       <c r="F32" t="n">
-        <v>-11.4123724889571</v>
+        <v>-0.9562</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.6982</v>
       </c>
       <c r="H32" t="n">
-        <v>-11.4123724889571</v>
+        <v>-0.9562</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.22667145114337</v>
+        <v>-0.9562</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.6982</v>
       </c>
       <c r="K32" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M32" t="n">
-        <v>-10.2267</v>
+        <v>0.7419999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>92</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.7574</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.35148</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.41781735470321</v>
+        <v>-0.1528</v>
       </c>
       <c r="E33" t="n">
-        <v>-12.9966</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.699800000058569</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>-9.296825096974132</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-3.699800000058569</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.63973831174593</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.296825096974132</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-12.9366</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.82</v>
+        <v>0.6161</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.364</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4333416032784936</v>
+        <v>-0.1725</v>
       </c>
       <c r="E34" t="n">
-        <v>-13.4795</v>
+        <v>0.6161</v>
       </c>
       <c r="F34" t="n">
-        <v>-13.47952231605661</v>
+        <v>0.6161</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-13.47952231605661</v>
+        <v>0.6161</v>
       </c>
       <c r="I34" t="n">
-        <v>-12.86681675623585</v>
+        <v>0.6161</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-12.8668</v>
+        <v>0.6161</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35">
@@ -2026,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.8494</v>
+        <v>0.4942</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.36988</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4406665691225637</v>
+        <v>-0.2217</v>
       </c>
       <c r="E35" t="n">
-        <v>-13.7074</v>
+        <v>0.4942</v>
       </c>
       <c r="F35" t="n">
-        <v>-13.7073726766324</v>
+        <v>0.4942</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-13.7073726766324</v>
+        <v>0.4942</v>
       </c>
       <c r="I35" t="n">
-        <v>-14.15241724405552</v>
+        <v>0.4942</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2059,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-14.1524</v>
+        <v>0.4942</v>
       </c>
       <c r="N35" t="n">
         <v>106</v>
@@ -2068,725 +2056,725 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.8554</v>
+        <v>0.4713</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.37108</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4421706486315031</v>
+        <v>-0.231</v>
       </c>
       <c r="E36" t="n">
-        <v>-13.7542</v>
+        <v>0.4713</v>
       </c>
       <c r="F36" t="n">
-        <v>-7.269018022132906</v>
+        <v>0.4713</v>
       </c>
       <c r="G36" t="n">
-        <v>-6.485140546166676</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-7.269018022132906</v>
+        <v>0.4713</v>
       </c>
       <c r="I36" t="n">
-        <v>-7.434222977181381</v>
+        <v>0.4713</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.485140546166676</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-13.9194</v>
+        <v>0.4713</v>
       </c>
       <c r="N36" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.9187</v>
+        <v>0.4681</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.38374</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.458150475109858</v>
+        <v>-0.2323</v>
       </c>
       <c r="E37" t="n">
-        <v>-14.2512</v>
+        <v>0.4681</v>
       </c>
       <c r="F37" t="n">
-        <v>-14.25122699189903</v>
+        <v>0.7149</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.2468</v>
       </c>
       <c r="H37" t="n">
-        <v>-14.25122699189903</v>
+        <v>0.7149</v>
       </c>
       <c r="I37" t="n">
-        <v>-14.29749720940519</v>
+        <v>0.7149</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.2468</v>
       </c>
       <c r="K37" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M37" t="n">
-        <v>-14.2975</v>
+        <v>0.4681</v>
       </c>
       <c r="N37" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.9496</v>
+        <v>0.4314</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.38992</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4660087333082668</v>
+        <v>-0.2471</v>
       </c>
       <c r="E38" t="n">
-        <v>-14.4957</v>
+        <v>0.4314</v>
       </c>
       <c r="F38" t="n">
-        <v>-14.49566594248534</v>
+        <v>-2.2475</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="H38" t="n">
-        <v>-14.49566594248534</v>
+        <v>-2.2475</v>
       </c>
       <c r="I38" t="n">
-        <v>-12.98962272768167</v>
+        <v>-1.8217</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="K38" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M38" t="n">
-        <v>-12.9896</v>
+        <v>0.8572</v>
       </c>
       <c r="N38" t="n">
-        <v>92</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0249</v>
+        <v>0.4081</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4049800000000001</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4853174900312465</v>
+        <v>-0.2565</v>
       </c>
       <c r="E39" t="n">
-        <v>-15.0963</v>
+        <v>0.4081</v>
       </c>
       <c r="F39" t="n">
-        <v>-15.09628405801727</v>
+        <v>0.4081</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-15.08848414965589</v>
+        <v>0.4081</v>
       </c>
       <c r="I39" t="n">
-        <v>-15.13747273455737</v>
+        <v>0.4081</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-15.1375</v>
+        <v>0.4081</v>
       </c>
       <c r="N39" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1662</v>
+        <v>0.201</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.43324</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5222866969473122</v>
+        <v>-0.3402</v>
       </c>
       <c r="E40" t="n">
-        <v>-16.2462</v>
+        <v>0.201</v>
       </c>
       <c r="F40" t="n">
-        <v>-16.24624807223116</v>
+        <v>0.201</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-16.18651635095035</v>
+        <v>0.201</v>
       </c>
       <c r="I40" t="n">
-        <v>-16.71205259611107</v>
+        <v>0.201</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-16.7121</v>
+        <v>0.201</v>
       </c>
       <c r="N40" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1971</v>
+        <v>-0.1123</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.43942</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5304934786409404</v>
+        <v>-0.4667</v>
       </c>
       <c r="E41" t="n">
-        <v>-16.5015</v>
+        <v>-0.1123</v>
       </c>
       <c r="F41" t="n">
-        <v>-16.50152819337654</v>
+        <v>-0.1123</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-16.44090810420881</v>
+        <v>-0.1123</v>
       </c>
       <c r="I41" t="n">
-        <v>-15.69359409947205</v>
+        <v>-0.1123</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-15.6936</v>
+        <v>-0.1123</v>
       </c>
       <c r="N41" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.4298</v>
+        <v>-0.1433</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4859600000000001</v>
+        <v>-0</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.593691235756001</v>
+        <v>-0.4793</v>
       </c>
       <c r="E42" t="n">
-        <v>-18.4674</v>
+        <v>-0.1433</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.46735739350925</v>
+        <v>-0.1433</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-18.53864299364332</v>
+        <v>-0.1433</v>
       </c>
       <c r="I42" t="n">
-        <v>-19.86283177890355</v>
+        <v>-0.1433</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-19.8628</v>
+        <v>-0.1433</v>
       </c>
       <c r="N42" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.6429</v>
+        <v>-0.1754</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.52858</v>
+        <v>-0</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.65385285222173</v>
+        <v>-0.4922</v>
       </c>
       <c r="E43" t="n">
-        <v>-20.3387</v>
+        <v>-0.1754</v>
       </c>
       <c r="F43" t="n">
-        <v>4.905583453709193</v>
+        <v>-0.1754</v>
       </c>
       <c r="G43" t="n">
-        <v>-25.24432786749183</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>4.905583453709193</v>
+        <v>-0.1754</v>
       </c>
       <c r="I43" t="n">
-        <v>5.351545585864574</v>
+        <v>-0.1754</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.24432786749183</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L43" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-19.8928</v>
+        <v>-0.1754</v>
       </c>
       <c r="N43" t="n">
-        <v>259</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-2.6526</v>
+        <v>-0.2227</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.53052</v>
+        <v>-0</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6566520664051864</v>
+        <v>-0.5113</v>
       </c>
       <c r="E44" t="n">
-        <v>-20.4258</v>
+        <v>-0.2227</v>
       </c>
       <c r="F44" t="n">
-        <v>-20.42581675986678</v>
+        <v>-0.2227</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-20.89462415519232</v>
+        <v>-0.2227</v>
       </c>
       <c r="I44" t="n">
-        <v>-21.77654010979459</v>
+        <v>-0.2227</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-21.7765</v>
+        <v>-0.2227</v>
       </c>
       <c r="N44" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-2.725</v>
+        <v>-0.4178</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.545</v>
+        <v>-0</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6776346399313031</v>
+        <v>-0.5901</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.0785</v>
+        <v>-0.4178</v>
       </c>
       <c r="F45" t="n">
-        <v>-21.07850061471425</v>
+        <v>-0.4178</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-21.74452031456755</v>
+        <v>-0.4178</v>
       </c>
       <c r="I45" t="n">
-        <v>-22.45051123387169</v>
+        <v>-0.4178</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-22.4505</v>
+        <v>-0.4178</v>
       </c>
       <c r="N45" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-2.7662</v>
+        <v>-0.4308</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.5532400000000001</v>
+        <v>-0</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6897101594368092</v>
+        <v>-0.5954</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.4541</v>
+        <v>-0.4308</v>
       </c>
       <c r="F46" t="n">
-        <v>5.13467932692812</v>
+        <v>-0.4308</v>
       </c>
       <c r="G46" t="n">
-        <v>-26.58880100691968</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>5.13467932692812</v>
+        <v>-0.4308</v>
       </c>
       <c r="I46" t="n">
-        <v>5.051324143049417</v>
+        <v>-0.4308</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.58880100691968</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L46" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-21.5375</v>
+        <v>-0.4308</v>
       </c>
       <c r="N46" t="n">
-        <v>249</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-2.8611</v>
+        <v>-0.6264</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.5722200000000001</v>
+        <v>-0</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.7178182269896497</v>
+        <v>-0.6744</v>
       </c>
       <c r="E47" t="n">
-        <v>-22.3285</v>
+        <v>-0.6264</v>
       </c>
       <c r="F47" t="n">
-        <v>-22.32845112579887</v>
+        <v>-0.6264</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-23.46984308660009</v>
+        <v>-0.6264</v>
       </c>
       <c r="I47" t="n">
-        <v>-25.14626044992867</v>
+        <v>-0.6264</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-25.1463</v>
+        <v>-0.6264</v>
       </c>
       <c r="N47" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.8788</v>
+        <v>-0.7042</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.57576</v>
+        <v>-0</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7231329155275057</v>
+        <v>-0.7058</v>
       </c>
       <c r="E48" t="n">
-        <v>-22.4938</v>
+        <v>-0.7042</v>
       </c>
       <c r="F48" t="n">
-        <v>-22.49376980788923</v>
+        <v>-0.7042</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-23.70805797311137</v>
+        <v>-0.7042</v>
       </c>
       <c r="I48" t="n">
-        <v>-25.40149068547647</v>
+        <v>-0.7042</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-25.4015</v>
+        <v>-0.7042</v>
       </c>
       <c r="N48" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-2.8879</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.5775800000000001</v>
+        <v>-0</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7258509756559409</v>
+        <v>-0.7327</v>
       </c>
       <c r="E49" t="n">
-        <v>-22.5783</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-22.57831777623668</v>
+        <v>-0.3886</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="H49" t="n">
-        <v>-23.83081975249444</v>
+        <v>-0.3886</v>
       </c>
       <c r="I49" t="n">
-        <v>-21.35489042755995</v>
+        <v>-0.3904</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="K49" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M49" t="n">
-        <v>-21.3549</v>
+        <v>-0.7725</v>
       </c>
       <c r="N49" t="n">
-        <v>92</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-3.0759</v>
+        <v>-0.854</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.6151800000000001</v>
+        <v>-0</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7832135631667113</v>
+        <v>-0.7664</v>
       </c>
       <c r="E50" t="n">
-        <v>-24.3626</v>
+        <v>-0.854</v>
       </c>
       <c r="F50" t="n">
-        <v>-24.3626382121429</v>
+        <v>-0.854</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-26.57515550458183</v>
+        <v>-0.854</v>
       </c>
       <c r="I50" t="n">
-        <v>-27.43798522875656</v>
+        <v>-0.854</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-27.438</v>
+        <v>-0.854</v>
       </c>
       <c r="N50" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-3.1019</v>
+        <v>-1.1524</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.62038</v>
+        <v>-0</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7912995663086845</v>
+        <v>-0.8869</v>
       </c>
       <c r="E51" t="n">
-        <v>-24.6142</v>
+        <v>-1.1524</v>
       </c>
       <c r="F51" t="n">
-        <v>8.478858981925493</v>
+        <v>-1.3582</v>
       </c>
       <c r="G51" t="n">
-        <v>-33.09302037803068</v>
+        <v>0.2058</v>
       </c>
       <c r="H51" t="n">
-        <v>8.478858981925493</v>
+        <v>-1.3582</v>
       </c>
       <c r="I51" t="n">
-        <v>7.928283723358902</v>
+        <v>-1.1008</v>
       </c>
       <c r="J51" t="n">
-        <v>-33.09302037803068</v>
+        <v>0.2058</v>
       </c>
       <c r="K51" t="n">
         <v>96</v>
@@ -2795,7 +2783,7 @@
         <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>-25.1647</v>
+        <v>-0.895</v>
       </c>
       <c r="N51" t="n">
         <v>136</v>
@@ -2804,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-3.195</v>
+        <v>-1.1832</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.639</v>
+        <v>-0</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8205197660213494</v>
+        <v>-0.8993</v>
       </c>
       <c r="E52" t="n">
-        <v>-25.5231</v>
+        <v>-1.1832</v>
       </c>
       <c r="F52" t="n">
-        <v>-25.52308482078124</v>
+        <v>-1.1832</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-28.5273670500644</v>
+        <v>-1.1832</v>
       </c>
       <c r="I52" t="n">
-        <v>-25.56348475914862</v>
+        <v>-1.1832</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-25.5635</v>
+        <v>-1.1832</v>
       </c>
       <c r="N52" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-3.2258</v>
+        <v>-1.1941</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.6451600000000001</v>
+        <v>-0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8302972903237921</v>
+        <v>-0.9038</v>
       </c>
       <c r="E53" t="n">
-        <v>-25.8272</v>
+        <v>-1.1941</v>
       </c>
       <c r="F53" t="n">
-        <v>-25.82722445573307</v>
+        <v>-1.1941</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-29.06232211291296</v>
+        <v>-1.1941</v>
       </c>
       <c r="I53" t="n">
-        <v>-29.15668030159124</v>
+        <v>-1.1941</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-29.1567</v>
+        <v>-1.1941</v>
       </c>
       <c r="N53" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
@@ -2900,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-3.2708</v>
+        <v>-1.2537</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.6541600000000001</v>
+        <v>-0</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8446786526430721</v>
+        <v>-0.9278</v>
       </c>
       <c r="E54" t="n">
-        <v>-26.2746</v>
+        <v>-1.2537</v>
       </c>
       <c r="F54" t="n">
-        <v>-26.27457105908573</v>
+        <v>-1.2537</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-29.86744821615441</v>
+        <v>-1.2537</v>
       </c>
       <c r="I54" t="n">
-        <v>-32.00083737445115</v>
+        <v>-1.2537</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2933,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-32.0008</v>
+        <v>-1.2537</v>
       </c>
       <c r="N54" t="n">
         <v>110</v>
@@ -2942,139 +2930,139 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-3.3285</v>
+        <v>-1.2791</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.6657000000000001</v>
+        <v>-0</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8632959399553828</v>
+        <v>-0.9381</v>
       </c>
       <c r="E55" t="n">
-        <v>-26.8537</v>
+        <v>-1.2791</v>
       </c>
       <c r="F55" t="n">
-        <v>-22.76187602808711</v>
+        <v>-1.2791</v>
       </c>
       <c r="G55" t="n">
-        <v>-4.09180430158821</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-24.09953483524866</v>
+        <v>-1.2791</v>
       </c>
       <c r="I55" t="n">
-        <v>-22.53462997581693</v>
+        <v>-1.2791</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.09180430158821</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L55" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-26.6264</v>
+        <v>-1.2791</v>
       </c>
       <c r="N55" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IceBerg</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-3.5387</v>
+        <v>-1.3221</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.70774</v>
+        <v>-0</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9326693846113483</v>
+        <v>-0.9555</v>
       </c>
       <c r="E56" t="n">
-        <v>-29.0116</v>
+        <v>-1.3221</v>
       </c>
       <c r="F56" t="n">
-        <v>-29.01161044371709</v>
+        <v>-1.3221</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-35.30286493635686</v>
+        <v>-1.3221</v>
       </c>
       <c r="I56" t="n">
-        <v>-36.79292092393036</v>
+        <v>-1.3221</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-36.7929</v>
+        <v>-1.3221</v>
       </c>
       <c r="N56" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>IceBerg</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-3.7127</v>
+        <v>-1.8367</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.74254</v>
+        <v>-0</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.9920520439666498</v>
+        <v>-1.1633</v>
       </c>
       <c r="E57" t="n">
-        <v>-30.8588</v>
+        <v>-1.8367</v>
       </c>
       <c r="F57" t="n">
-        <v>-30.85876722698157</v>
+        <v>-1.8367</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-39.51971375075001</v>
+        <v>-1.8367</v>
       </c>
       <c r="I57" t="n">
-        <v>-35.4137694649578</v>
+        <v>-1.8367</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-35.4138</v>
+        <v>-1.8367</v>
       </c>
       <c r="N57" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
@@ -3084,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-4.0347</v>
+        <v>-2.0056</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.80694</v>
+        <v>-0</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.106775433053716</v>
+        <v>-1.2316</v>
       </c>
       <c r="E58" t="n">
-        <v>-34.4274</v>
+        <v>-2.0056</v>
       </c>
       <c r="F58" t="n">
-        <v>-34.4273525455228</v>
+        <v>-2.0056</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-49.14575165745164</v>
+        <v>-2.0056</v>
       </c>
       <c r="I58" t="n">
-        <v>-51.22008533130511</v>
+        <v>-2.0056</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3117,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-51.2201</v>
+        <v>-2.0056</v>
       </c>
       <c r="N58" t="n">
         <v>107</v>
@@ -3130,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-4.0889</v>
+        <v>-2.0475</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.81778</v>
+        <v>-0</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.126736569837956</v>
+        <v>-1.2485</v>
       </c>
       <c r="E59" t="n">
-        <v>-35.0483</v>
+        <v>-2.0475</v>
       </c>
       <c r="F59" t="n">
-        <v>-35.04826359283828</v>
+        <v>-2.0475</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-51.04560297264501</v>
+        <v>-2.0475</v>
       </c>
       <c r="I59" t="n">
-        <v>-48.72534829207024</v>
+        <v>-2.0475</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3163,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-48.7253</v>
+        <v>-2.0475</v>
       </c>
       <c r="N59" t="n">
         <v>98</v>
@@ -3172,93 +3160,93 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-4.8812</v>
+        <v>-3.3092</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.97624</v>
+        <v>-0</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.440940674894086</v>
+        <v>-1.7582</v>
       </c>
       <c r="E60" t="n">
-        <v>-44.8219</v>
+        <v>-3.3092</v>
       </c>
       <c r="F60" t="n">
-        <v>-21.93338825073196</v>
+        <v>-2.3092</v>
       </c>
       <c r="G60" t="n">
-        <v>-22.88850707711148</v>
+        <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-22.91022904644038</v>
+        <v>-2.3092</v>
       </c>
       <c r="I60" t="n">
-        <v>-21.42255183563256</v>
+        <v>-2.3199</v>
       </c>
       <c r="J60" t="n">
-        <v>-22.88850707711148</v>
+        <v>-1</v>
       </c>
       <c r="K60" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L60" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="M60" t="n">
-        <v>-44.3111</v>
+        <v>-3.3199</v>
       </c>
       <c r="N60" t="n">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-5.4916</v>
+        <v>-3.5693</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.09832</v>
+        <v>-0</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.714293634784229</v>
+        <v>-1.8633</v>
       </c>
       <c r="E61" t="n">
-        <v>-53.3248</v>
+        <v>-3.5693</v>
       </c>
       <c r="F61" t="n">
-        <v>-23.98071342765271</v>
+        <v>-2.7409</v>
       </c>
       <c r="G61" t="n">
-        <v>-29.34409806407288</v>
+        <v>-0.8284</v>
       </c>
       <c r="H61" t="n">
-        <v>-25.96232632508733</v>
+        <v>-2.7409</v>
       </c>
       <c r="I61" t="n">
-        <v>-25.54085998864111</v>
+        <v>-2.2216</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.34409806407288</v>
+        <v>-0.8284</v>
       </c>
       <c r="K61" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L61" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="M61" t="n">
-        <v>-54.885</v>
+        <v>-3.05</v>
       </c>
       <c r="N61" t="n">
-        <v>169</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3276,52 +3264,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -3361,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3715371125271293</v>
+        <v>0.6193</v>
       </c>
       <c r="J2" t="n">
-        <v>10.40303915075962</v>
+        <v>17.3404</v>
       </c>
     </row>
     <row r="3">
@@ -3401,10 +3389,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.289966871404582</v>
+        <v>-0.1213</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.119072399328298</v>
+        <v>-3.3964</v>
       </c>
     </row>
     <row r="4">
@@ -3441,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4563002186766105</v>
+        <v>-0.2846</v>
       </c>
       <c r="J4" t="n">
-        <v>-12.77640612294509</v>
+        <v>-7.9688</v>
       </c>
     </row>
     <row r="5">
@@ -3481,10 +3469,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4753431086289191</v>
+        <v>-0.3005</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.30960704160973</v>
+        <v>-8.414</v>
       </c>
     </row>
     <row r="6">
@@ -3521,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5325452364695273</v>
+        <v>-0.3467</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.91126662114677</v>
+        <v>-9.707599999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3561,10 +3549,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1.041019827681487</v>
+        <v>0.9125</v>
       </c>
       <c r="J7" t="n">
-        <v>29.14855517508164</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="8">
@@ -3601,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2389400820226847</v>
+        <v>0.2772</v>
       </c>
       <c r="J8" t="n">
-        <v>6.690322296635173</v>
+        <v>7.7616</v>
       </c>
     </row>
     <row r="9">
@@ -3641,10 +3629,10 @@
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1368896626985865</v>
+        <v>0.149</v>
       </c>
       <c r="J9" t="n">
-        <v>3.832910555560423</v>
+        <v>4.172</v>
       </c>
     </row>
     <row r="10">
@@ -3681,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0277725810717015</v>
+        <v>-0.0614</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7776322700076421</v>
+        <v>-1.7192</v>
       </c>
     </row>
     <row r="11">
@@ -3721,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2975964322309793</v>
+        <v>-0.3571</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.33270010246742</v>
+        <v>-9.998799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -3761,10 +3749,10 @@
         <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7246725518939566</v>
+        <v>1.2153</v>
       </c>
       <c r="J12" t="n">
-        <v>14.49345103787913</v>
+        <v>24.306</v>
       </c>
     </row>
     <row r="13">
@@ -3801,10 +3789,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4080243693000831</v>
+        <v>0.7355</v>
       </c>
       <c r="J13" t="n">
-        <v>8.160487386001661</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="14">
@@ -3841,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3659468245630498</v>
+        <v>0.6599</v>
       </c>
       <c r="J14" t="n">
-        <v>7.318936491260997</v>
+        <v>13.198</v>
       </c>
     </row>
     <row r="15">
@@ -3881,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2493042846787203</v>
+        <v>0.397</v>
       </c>
       <c r="J15" t="n">
-        <v>4.986085693574406</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="16">
@@ -3921,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2044909111745735</v>
+        <v>-0.5342</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.089818223491469</v>
+        <v>-10.684</v>
       </c>
     </row>
     <row r="17">
@@ -3961,10 +3949,10 @@
         <v>1.23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1857930272221706</v>
+        <v>0.4655</v>
       </c>
       <c r="J17" t="n">
-        <v>3.715860544443411</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="18">
@@ -4001,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04550580246414825</v>
+        <v>0.3341</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9101160492829651</v>
+        <v>6.682</v>
       </c>
     </row>
     <row r="19">
@@ -4041,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1794492112200898</v>
+        <v>0.0919</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.588984224401796</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="20">
@@ -4081,10 +4069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9240863547741074</v>
+        <v>-0.6773</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.48172709548215</v>
+        <v>-13.546</v>
       </c>
     </row>
     <row r="21">
@@ -4121,10 +4109,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.004684709511314</v>
+        <v>-0.7377</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.09369419022628</v>
+        <v>-14.754</v>
       </c>
     </row>
     <row r="22">
@@ -4161,10 +4149,10 @@
         <v>1.65</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9308573060371922</v>
+        <v>1.4866</v>
       </c>
       <c r="J22" t="n">
-        <v>17.68628881470665</v>
+        <v>28.2454</v>
       </c>
     </row>
     <row r="23">
@@ -4201,10 +4189,10 @@
         <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5809946348364895</v>
+        <v>0.9885</v>
       </c>
       <c r="J23" t="n">
-        <v>11.0388980618933</v>
+        <v>18.7815</v>
       </c>
     </row>
     <row r="24">
@@ -4241,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3495841743380239</v>
+        <v>0.5615</v>
       </c>
       <c r="J24" t="n">
-        <v>6.642099312422454</v>
+        <v>10.6685</v>
       </c>
     </row>
     <row r="25">
@@ -4281,10 +4269,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05743794733420192</v>
+        <v>-0.0043</v>
       </c>
       <c r="J25" t="n">
-        <v>1.091320999349837</v>
+        <v>-0.08169999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -4321,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0780854130597648</v>
+        <v>-0.3446</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.483622848135531</v>
+        <v>-6.5474</v>
       </c>
     </row>
     <row r="27">
@@ -4361,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2367880314945467</v>
+        <v>0.5415</v>
       </c>
       <c r="J27" t="n">
-        <v>4.498972598396388</v>
+        <v>10.2885</v>
       </c>
     </row>
     <row r="28">
@@ -4401,10 +4389,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1551661828106313</v>
+        <v>0.1694</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.948157473401994</v>
+        <v>3.2186</v>
       </c>
     </row>
     <row r="29">
@@ -4441,10 +4429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5311911509265023</v>
+        <v>-0.3279</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.09263186760354</v>
+        <v>-6.2301</v>
       </c>
     </row>
     <row r="30">
@@ -4481,10 +4469,10 @@
         <v>0.76</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6151135194209054</v>
+        <v>-0.4052</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.6871568689972</v>
+        <v>-7.6988</v>
       </c>
     </row>
     <row r="31">
@@ -4521,10 +4509,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.125639344619911</v>
+        <v>-0.8052</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.38714754777831</v>
+        <v>-15.2988</v>
       </c>
     </row>
     <row r="32">
@@ -4561,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04088764329599157</v>
+        <v>0.2898</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8177528659198313</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="33">
@@ -4601,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02911870715363191</v>
+        <v>0.2726</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5823741430726381</v>
+        <v>5.452</v>
       </c>
     </row>
     <row r="34">
@@ -4641,10 +4629,10 @@
         <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.547394597233097</v>
+        <v>-0.469</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.94789194466194</v>
+        <v>-9.380000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -4681,10 +4669,10 @@
         <v>0.68</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5786606160964355</v>
+        <v>-0.4978</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.57321232192871</v>
+        <v>-9.956</v>
       </c>
     </row>
     <row r="36">
@@ -4721,10 +4709,10 @@
         <v>0.44</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9467470731807384</v>
+        <v>-0.8067</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.93494146361477</v>
+        <v>-16.134</v>
       </c>
     </row>
     <row r="37">
@@ -4761,10 +4749,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6545055678689575</v>
+        <v>1.2236</v>
       </c>
       <c r="J37" t="n">
-        <v>13.09011135737915</v>
+        <v>24.472</v>
       </c>
     </row>
     <row r="38">
@@ -4801,10 +4789,10 @@
         <v>1.48</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6177576520687822</v>
+        <v>1.1631</v>
       </c>
       <c r="J38" t="n">
-        <v>12.35515304137564</v>
+        <v>23.262</v>
       </c>
     </row>
     <row r="39">
@@ -4841,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2190812188107827</v>
+        <v>0.3566</v>
       </c>
       <c r="J39" t="n">
-        <v>4.381624376215655</v>
+        <v>7.132</v>
       </c>
     </row>
     <row r="40">
@@ -4881,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1806900770571088</v>
+        <v>0.2749</v>
       </c>
       <c r="J40" t="n">
-        <v>3.613801541142175</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="41">
@@ -4921,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.07589644927161086</v>
+        <v>-0.4017</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.517928985432217</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4961,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2475873611697617</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>4.951747223395235</v>
+        <v>11.522</v>
       </c>
     </row>
     <row r="43">
@@ -5001,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.197678280674836</v>
+        <v>-0.0217</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.953565613496719</v>
+        <v>-0.434</v>
       </c>
     </row>
     <row r="44">
@@ -5041,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2454778583754021</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.909557167508042</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="45">
@@ -5081,10 +5069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4351677644171128</v>
+        <v>-0.3329</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.703355288342255</v>
+        <v>-6.658</v>
       </c>
     </row>
     <row r="46">
@@ -5121,10 +5109,10 @@
         <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.107256421668437</v>
+        <v>-0.8979</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.14512843336874</v>
+        <v>-17.958</v>
       </c>
     </row>
     <row r="47">
@@ -5161,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>0.713800683044359</v>
+        <v>1.2977</v>
       </c>
       <c r="J47" t="n">
-        <v>14.27601366088718</v>
+        <v>25.954</v>
       </c>
     </row>
     <row r="48">
@@ -5201,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3634201364298469</v>
+        <v>0.6904</v>
       </c>
       <c r="J48" t="n">
-        <v>7.268402728596939</v>
+        <v>13.808</v>
       </c>
     </row>
     <row r="49">
@@ -5241,10 +5229,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2585544706468503</v>
+        <v>0.4323</v>
       </c>
       <c r="J49" t="n">
-        <v>5.171089412937007</v>
+        <v>8.646000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -5281,10 +5269,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1607967143322103</v>
+        <v>0.1929</v>
       </c>
       <c r="J50" t="n">
-        <v>3.215934286644206</v>
+        <v>3.858</v>
       </c>
     </row>
     <row r="51">
@@ -5321,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1959037150375924</v>
+        <v>-0.6736</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.918074300751847</v>
+        <v>-13.472</v>
       </c>
     </row>
     <row r="52">
@@ -5361,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>0.763357271366925</v>
+        <v>1.2061</v>
       </c>
       <c r="J52" t="n">
-        <v>15.2671454273385</v>
+        <v>24.122</v>
       </c>
     </row>
     <row r="53">
@@ -5401,10 +5389,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6621512757205366</v>
+        <v>1.0616</v>
       </c>
       <c r="J53" t="n">
-        <v>13.24302551441073</v>
+        <v>21.232</v>
       </c>
     </row>
     <row r="54">
@@ -5441,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4989316810410565</v>
+        <v>0.8193</v>
       </c>
       <c r="J54" t="n">
-        <v>9.978633620821128</v>
+        <v>16.386</v>
       </c>
     </row>
     <row r="55">
@@ -5481,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>0.05097315551078756</v>
+        <v>-0.1632</v>
       </c>
       <c r="J55" t="n">
-        <v>1.019463110215751</v>
+        <v>-3.264</v>
       </c>
     </row>
     <row r="56">
@@ -5521,10 +5509,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4622756696342666</v>
+        <v>-1.1964</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.245513392685332</v>
+        <v>-23.928</v>
       </c>
     </row>
     <row r="57">
@@ -5561,10 +5549,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1501565816421577</v>
+        <v>0.4551</v>
       </c>
       <c r="J57" t="n">
-        <v>3.003131632843154</v>
+        <v>9.102</v>
       </c>
     </row>
     <row r="58">
@@ -5601,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.09722724807532329</v>
+        <v>0.3984</v>
       </c>
       <c r="J58" t="n">
-        <v>1.944544961506466</v>
+        <v>7.968</v>
       </c>
     </row>
     <row r="59">
@@ -5641,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3084625995193609</v>
+        <v>-0.2131</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.169251990387218</v>
+        <v>-4.262</v>
       </c>
     </row>
     <row r="60">
@@ -5681,10 +5669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5917752258088809</v>
+        <v>-0.5169</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.83550451617762</v>
+        <v>-10.338</v>
       </c>
     </row>
     <row r="61">
@@ -5721,10 +5709,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7308926517800558</v>
+        <v>-0.6452</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.61785303560112</v>
+        <v>-12.904</v>
       </c>
     </row>
     <row r="62">
@@ -5761,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.05941280000077627</v>
+        <v>0.3716</v>
       </c>
       <c r="J62" t="n">
-        <v>1.128843200014749</v>
+        <v>7.0604</v>
       </c>
     </row>
     <row r="63">
@@ -5801,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1669669900930535</v>
+        <v>0.0145</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.172372811768017</v>
+        <v>0.2755</v>
       </c>
     </row>
     <row r="64">
@@ -5841,10 +5829,10 @@
         <v>0.72</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4661640632843797</v>
+        <v>-0.4385</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.857117202403215</v>
+        <v>-8.3315</v>
       </c>
     </row>
     <row r="65">
@@ -5881,10 +5869,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5651026110050438</v>
+        <v>-0.553</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.73694960909583</v>
+        <v>-10.507</v>
       </c>
     </row>
     <row r="66">
@@ -5921,10 +5909,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7241294346172165</v>
+        <v>-0.7215</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.75845925772711</v>
+        <v>-13.7085</v>
       </c>
     </row>
     <row r="67">
@@ -5961,10 +5949,10 @@
         <v>2.13</v>
       </c>
       <c r="I67" t="n">
-        <v>1.354738801034304</v>
+        <v>1.3095</v>
       </c>
       <c r="J67" t="n">
-        <v>25.74003721965179</v>
+        <v>24.8805</v>
       </c>
     </row>
     <row r="68">
@@ -6001,10 +5989,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.530690158698491</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>10.08311301527133</v>
+        <v>11.0998</v>
       </c>
     </row>
     <row r="69">
@@ -6041,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I69" t="n">
-        <v>0.324441896154262</v>
+        <v>0.3412</v>
       </c>
       <c r="J69" t="n">
-        <v>6.164396026930978</v>
+        <v>6.4828</v>
       </c>
     </row>
     <row r="70">
@@ -6081,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.12440762641564</v>
+        <v>-0.2436</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.363744901897159</v>
+        <v>-4.6284</v>
       </c>
     </row>
     <row r="71">
@@ -6121,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2208215672616889</v>
+        <v>-0.3516</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.19560977797209</v>
+        <v>-6.6804</v>
       </c>
     </row>
     <row r="72">
@@ -6161,10 +6149,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.352336706605318</v>
+        <v>0.6955</v>
       </c>
       <c r="J72" t="n">
-        <v>14.44580497081804</v>
+        <v>28.5155</v>
       </c>
     </row>
     <row r="73">
@@ -6201,10 +6189,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1292045990706633</v>
+        <v>0.2756</v>
       </c>
       <c r="J73" t="n">
-        <v>5.297388561897194</v>
+        <v>11.2996</v>
       </c>
     </row>
     <row r="74">
@@ -6241,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1160017955881302</v>
+        <v>0.2408</v>
       </c>
       <c r="J74" t="n">
-        <v>4.756073619113337</v>
+        <v>9.8728</v>
       </c>
     </row>
     <row r="75">
@@ -6281,10 +6269,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.07079960108449196</v>
+        <v>0.0693</v>
       </c>
       <c r="J75" t="n">
-        <v>2.90278364446417</v>
+        <v>2.8413</v>
       </c>
     </row>
     <row r="76">
@@ -6321,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2063486105049808</v>
+        <v>-0.6564</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.460293030704214</v>
+        <v>-26.9124</v>
       </c>
     </row>
     <row r="77">
@@ -6361,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1456210150588686</v>
+        <v>0.3963</v>
       </c>
       <c r="J77" t="n">
-        <v>5.970461617413612</v>
+        <v>16.2483</v>
       </c>
     </row>
     <row r="78">
@@ -6401,10 +6389,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.104524627356847</v>
+        <v>0.353</v>
       </c>
       <c r="J78" t="n">
-        <v>4.285509721630725</v>
+        <v>14.473</v>
       </c>
     </row>
     <row r="79">
@@ -6441,10 +6429,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.07019972454200911</v>
+        <v>0.1328</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.878188706222374</v>
+        <v>5.4448</v>
       </c>
     </row>
     <row r="80">
@@ -6481,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1531236256228926</v>
+        <v>-0.0624</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.278068650538595</v>
+        <v>-2.5584</v>
       </c>
     </row>
     <row r="81">
@@ -6521,10 +6509,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4704521051608153</v>
+        <v>-0.4354</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.28853631159343</v>
+        <v>-17.8514</v>
       </c>
     </row>
     <row r="82">
@@ -6561,10 +6549,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7382701508423487</v>
+        <v>1.6133</v>
       </c>
       <c r="J82" t="n">
-        <v>14.02713286600463</v>
+        <v>30.6527</v>
       </c>
     </row>
     <row r="83">
@@ -6601,10 +6589,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5719756437295944</v>
+        <v>1.294</v>
       </c>
       <c r="J83" t="n">
-        <v>10.86753723086229</v>
+        <v>24.586</v>
       </c>
     </row>
     <row r="84">
@@ -6641,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3440933951594177</v>
+        <v>0.8292</v>
       </c>
       <c r="J84" t="n">
-        <v>6.537774508028937</v>
+        <v>15.7548</v>
       </c>
     </row>
     <row r="85">
@@ -6681,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.03595386798631684</v>
+        <v>-0.279</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.68312349174002</v>
+        <v>-5.301</v>
       </c>
     </row>
     <row r="86">
@@ -6721,10 +6709,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3851950156454147</v>
+        <v>-0.9445</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.318705297262879</v>
+        <v>-17.9455</v>
       </c>
     </row>
     <row r="87">
@@ -6761,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.2254446775500721</v>
+        <v>0.0046</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.283448873451371</v>
+        <v>0.08740000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -6801,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2400604801889005</v>
+        <v>-0.0182</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.561149123589109</v>
+        <v>-0.3458</v>
       </c>
     </row>
     <row r="89">
@@ -6841,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.426354328682353</v>
+        <v>-0.2966</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.100732244964707</v>
+        <v>-5.6354</v>
       </c>
     </row>
     <row r="90">
@@ -6881,10 +6869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4540531931538651</v>
+        <v>-0.3296</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.627010669923436</v>
+        <v>-6.2624</v>
       </c>
     </row>
     <row r="91">
@@ -6921,10 +6909,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5107390433957406</v>
+        <v>-0.3917</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.704041824519072</v>
+        <v>-7.4423</v>
       </c>
     </row>
     <row r="92">
@@ -6961,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5650833432387856</v>
+        <v>1.421</v>
       </c>
       <c r="J92" t="n">
-        <v>13.56200023773085</v>
+        <v>34.104</v>
       </c>
     </row>
     <row r="93">
@@ -7001,10 +6989,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1423578183892386</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>3.416587641341727</v>
+        <v>12.3744</v>
       </c>
     </row>
     <row r="94">
@@ -7041,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1327489601461972</v>
+        <v>0.4863</v>
       </c>
       <c r="J94" t="n">
-        <v>3.185975043508734</v>
+        <v>11.6712</v>
       </c>
     </row>
     <row r="95">
@@ -7081,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.05337013176632196</v>
+        <v>-0.1051</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.280883162391727</v>
+        <v>-2.5224</v>
       </c>
     </row>
     <row r="96">
@@ -7121,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2887489010900812</v>
+        <v>-0.6451</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.929973626161949</v>
+        <v>-15.4824</v>
       </c>
     </row>
     <row r="97">
@@ -7161,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.09430477411557707</v>
+        <v>0.2942</v>
       </c>
       <c r="J97" t="n">
-        <v>2.26331457877385</v>
+        <v>7.0608</v>
       </c>
     </row>
     <row r="98">
@@ -7201,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.06355917559825119</v>
+        <v>0.2444</v>
       </c>
       <c r="J98" t="n">
-        <v>1.525420214358029</v>
+        <v>5.8656</v>
       </c>
     </row>
     <row r="99">
@@ -7241,10 +7229,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.02790893446044565</v>
+        <v>0.0828</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.6698144270506955</v>
+        <v>1.9872</v>
       </c>
     </row>
     <row r="100">
@@ -7281,10 +7269,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5053294271774561</v>
+        <v>-0.5421</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.12790625225895</v>
+        <v>-13.0104</v>
       </c>
     </row>
     <row r="101">
@@ -7321,10 +7309,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5053294271774561</v>
+        <v>-0.5421</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.12790625225895</v>
+        <v>-13.0104</v>
       </c>
     </row>
     <row r="102">
@@ -7361,10 +7349,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0459040419569223</v>
+        <v>0.2735</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.8262727552246015</v>
+        <v>4.923</v>
       </c>
     </row>
     <row r="103">
@@ -7401,10 +7389,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1939962505637861</v>
+        <v>-0.0267</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.491932510148149</v>
+        <v>-0.4806</v>
       </c>
     </row>
     <row r="104">
@@ -7441,10 +7429,10 @@
         <v>0.77</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3834824170503712</v>
+        <v>-0.3587</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.902683506906682</v>
+        <v>-6.4566</v>
       </c>
     </row>
     <row r="105">
@@ -7481,10 +7469,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5568066574134798</v>
+        <v>-0.5934</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.02251983344264</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="106">
@@ -7521,10 +7509,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6003619715752531</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.80651548835456</v>
+        <v>-11.6226</v>
       </c>
     </row>
     <row r="107">
@@ -7561,10 +7549,10 @@
         <v>2.08</v>
       </c>
       <c r="I107" t="n">
-        <v>1.142161351482079</v>
+        <v>1.9838</v>
       </c>
       <c r="J107" t="n">
-        <v>20.55890432667743</v>
+        <v>35.7084</v>
       </c>
     </row>
     <row r="108">
@@ -7601,10 +7589,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4025021597167096</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>7.245038874900773</v>
+        <v>15.4512</v>
       </c>
     </row>
     <row r="109">
@@ -7641,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1996045502070685</v>
+        <v>0.3712</v>
       </c>
       <c r="J109" t="n">
-        <v>3.592881903727233</v>
+        <v>6.6816</v>
       </c>
     </row>
     <row r="110">
@@ -7681,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.01446888874387909</v>
+        <v>-0.1043</v>
       </c>
       <c r="J110" t="n">
-        <v>0.2604399973898237</v>
+        <v>-1.8774</v>
       </c>
     </row>
     <row r="111">
@@ -7721,10 +7709,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.009734986148824265</v>
+        <v>-0.2197</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.1752297506788368</v>
+        <v>-3.9546</v>
       </c>
     </row>
     <row r="112">
@@ -7761,10 +7749,10 @@
         <v>1.99</v>
       </c>
       <c r="I112" t="n">
-        <v>1.218790226374934</v>
+        <v>1.2041</v>
       </c>
       <c r="J112" t="n">
-        <v>24.37580452749867</v>
+        <v>24.082</v>
       </c>
     </row>
     <row r="113">
@@ -7801,10 +7789,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2834162452951889</v>
+        <v>0.3409</v>
       </c>
       <c r="J113" t="n">
-        <v>5.668324905903779</v>
+        <v>6.818</v>
       </c>
     </row>
     <row r="114">
@@ -7841,10 +7829,10 @@
         <v>1.18</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2243794219455385</v>
+        <v>0.2553</v>
       </c>
       <c r="J114" t="n">
-        <v>4.48758843891077</v>
+        <v>5.106</v>
       </c>
     </row>
     <row r="115">
@@ -7881,10 +7869,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.08909482768625487</v>
+        <v>0.0953</v>
       </c>
       <c r="J115" t="n">
-        <v>1.781896553725097</v>
+        <v>1.906</v>
       </c>
     </row>
     <row r="116">
@@ -7921,10 +7909,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3962469495507611</v>
+        <v>-0.6127</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.924938991015223</v>
+        <v>-12.254</v>
       </c>
     </row>
     <row r="117">
@@ -7961,10 +7949,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1317767164520149</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>2.635534329040298</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="118">
@@ -8001,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1633476069832953</v>
+        <v>0.1192</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.266952139665906</v>
+        <v>2.384</v>
       </c>
     </row>
     <row r="119">
@@ -8041,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1899178065102634</v>
+        <v>0.0708</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.798356130205268</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="120">
@@ -8081,10 +8069,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3999709804574276</v>
+        <v>-0.3069</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.999419609148552</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="121">
@@ -8121,10 +8109,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7745886864193305</v>
+        <v>-0.6974</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.49177372838661</v>
+        <v>-13.948</v>
       </c>
     </row>
     <row r="122">
@@ -8161,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.09835953754714795</v>
+        <v>0.3163</v>
       </c>
       <c r="J122" t="n">
-        <v>2.950786126414438</v>
+        <v>9.489000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -8201,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.09835953754714795</v>
+        <v>0.3163</v>
       </c>
       <c r="J123" t="n">
-        <v>2.950786126414438</v>
+        <v>9.489000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -8241,10 +8229,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.06189969432570062</v>
+        <v>0.0784</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.856990829771018</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="125">
@@ -8281,10 +8269,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2435217955124694</v>
+        <v>-0.3035</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.305653865374083</v>
+        <v>-9.105</v>
       </c>
     </row>
     <row r="126">
@@ -8321,10 +8309,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3798879746538341</v>
+        <v>-0.4766</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.39663923961502</v>
+        <v>-14.298</v>
       </c>
     </row>
     <row r="127">
@@ -8361,10 +8349,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2592957594318542</v>
+        <v>0.7971</v>
       </c>
       <c r="J127" t="n">
-        <v>7.778872782955627</v>
+        <v>23.913</v>
       </c>
     </row>
     <row r="128">
@@ -8401,10 +8389,10 @@
         <v>1.28</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2476568312251942</v>
+        <v>0.7736</v>
       </c>
       <c r="J128" t="n">
-        <v>7.429704936755828</v>
+        <v>23.208</v>
       </c>
     </row>
     <row r="129">
@@ -8441,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1556104472916453</v>
+        <v>0.5738</v>
       </c>
       <c r="J129" t="n">
-        <v>4.668313418749359</v>
+        <v>17.214</v>
       </c>
     </row>
     <row r="130">
@@ -8481,10 +8469,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.08451622587579428</v>
+        <v>0.3555</v>
       </c>
       <c r="J130" t="n">
-        <v>2.535486776273828</v>
+        <v>10.665</v>
       </c>
     </row>
     <row r="131">
@@ -8521,10 +8509,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2676566199216236</v>
+        <v>-0.5936</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.029698597648707</v>
+        <v>-17.808</v>
       </c>
     </row>
     <row r="132">
@@ -8561,10 +8549,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4765895459240171</v>
+        <v>1.4659</v>
       </c>
       <c r="J132" t="n">
-        <v>10.96155955625239</v>
+        <v>33.7157</v>
       </c>
     </row>
     <row r="133">
@@ -8601,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1403989220223318</v>
+        <v>0.6333</v>
       </c>
       <c r="J133" t="n">
-        <v>3.229175206513631</v>
+        <v>14.5659</v>
       </c>
     </row>
     <row r="134">
@@ -8641,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1403989220223318</v>
+        <v>0.6333</v>
       </c>
       <c r="J134" t="n">
-        <v>3.229175206513631</v>
+        <v>14.5659</v>
       </c>
     </row>
     <row r="135">
@@ -8681,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.03934721603056128</v>
+        <v>0.024</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.9049859687029095</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="136">
@@ -8721,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3608737123802189</v>
+        <v>-0.7715</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.300095384745035</v>
+        <v>-17.7445</v>
       </c>
     </row>
     <row r="137">
@@ -8761,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2200394888469454</v>
+        <v>0.6573</v>
       </c>
       <c r="J137" t="n">
-        <v>5.060908243479743</v>
+        <v>15.1179</v>
       </c>
     </row>
     <row r="138">
@@ -8801,10 +8789,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1055711230071065</v>
+        <v>0.4665</v>
       </c>
       <c r="J138" t="n">
-        <v>2.428135829163449</v>
+        <v>10.7295</v>
       </c>
     </row>
     <row r="139">
@@ -8841,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1730225319564908</v>
+        <v>-0.0417</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.979518234999289</v>
+        <v>-0.9591</v>
       </c>
     </row>
     <row r="140">
@@ -8881,10 +8869,10 @@
         <v>0.7</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5794969367616805</v>
+        <v>-0.5206</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.32842954551865</v>
+        <v>-11.9738</v>
       </c>
     </row>
     <row r="141">
@@ -8921,10 +8909,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6477915192031914</v>
+        <v>-0.5845</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.8992049416734</v>
+        <v>-13.4435</v>
       </c>
     </row>
     <row r="142">
@@ -8961,10 +8949,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2976398859691643</v>
+        <v>1.0827</v>
       </c>
       <c r="J142" t="n">
-        <v>5.952797719383286</v>
+        <v>21.654</v>
       </c>
     </row>
     <row r="143">
@@ -9001,10 +8989,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2503767759522347</v>
+        <v>0.9545</v>
       </c>
       <c r="J143" t="n">
-        <v>5.007535519044694</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="144">
@@ -9041,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1015008519872383</v>
+        <v>0.4392</v>
       </c>
       <c r="J144" t="n">
-        <v>2.030017039744766</v>
+        <v>8.784000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -9081,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.03877348384099901</v>
+        <v>0.2205</v>
       </c>
       <c r="J145" t="n">
-        <v>0.7754696768199802</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="146">
@@ -9121,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I146" t="n">
-        <v>0.01539496980740199</v>
+        <v>0.1325</v>
       </c>
       <c r="J146" t="n">
-        <v>0.3078993961480398</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="147">
@@ -9161,10 +9149,10 @@
         <v>1.7</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3304676296359289</v>
+        <v>0.9687</v>
       </c>
       <c r="J147" t="n">
-        <v>6.609352592718578</v>
+        <v>19.374</v>
       </c>
     </row>
     <row r="148">
@@ -9201,10 +9189,10 @@
         <v>1.21</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.02568674110839977</v>
+        <v>0.3828</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.5137348221679954</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="149">
@@ -9241,10 +9229,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3734461587346557</v>
+        <v>-0.1311</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.468923174693114</v>
+        <v>-2.622</v>
       </c>
     </row>
     <row r="150">
@@ -9281,10 +9269,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.7479637258617848</v>
+        <v>-0.5278</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.9592745172357</v>
+        <v>-10.556</v>
       </c>
     </row>
     <row r="151">
@@ -9321,10 +9309,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8167191594535436</v>
+        <v>-0.5909</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.33438318907087</v>
+        <v>-11.818</v>
       </c>
     </row>
     <row r="152">
@@ -9361,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.09493415304555097</v>
+        <v>0.4074</v>
       </c>
       <c r="J152" t="n">
-        <v>2.088551367002121</v>
+        <v>8.9628</v>
       </c>
     </row>
     <row r="153">
@@ -9401,10 +9389,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1994544391907714</v>
+        <v>-0.1108</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.387997662196971</v>
+        <v>-2.4376</v>
       </c>
     </row>
     <row r="154">
@@ -9441,10 +9429,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2119935056502411</v>
+        <v>-0.1307</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.663857124305304</v>
+        <v>-2.8754</v>
       </c>
     </row>
     <row r="155">
@@ -9481,10 +9469,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3324920163768889</v>
+        <v>-0.3223</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.314824360291555</v>
+        <v>-7.0906</v>
       </c>
     </row>
     <row r="156">
@@ -9521,10 +9509,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6102357772020993</v>
+        <v>-0.6157</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.42518709844619</v>
+        <v>-13.5454</v>
       </c>
     </row>
     <row r="157">
@@ -9561,10 +9549,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6216247589276184</v>
+        <v>1.592</v>
       </c>
       <c r="J157" t="n">
-        <v>13.6757446964076</v>
+        <v>35.024</v>
       </c>
     </row>
     <row r="158">
@@ -9601,10 +9589,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>0.550257744132609</v>
+        <v>1.4436</v>
       </c>
       <c r="J158" t="n">
-        <v>12.1056703709174</v>
+        <v>31.7592</v>
       </c>
     </row>
     <row r="159">
@@ -9641,10 +9629,10 @@
         <v>1.32</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2645690267379722</v>
+        <v>0.8248</v>
       </c>
       <c r="J159" t="n">
-        <v>5.820518588235389</v>
+        <v>18.1456</v>
       </c>
     </row>
     <row r="160">
@@ -9681,10 +9669,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.327561567923811</v>
+        <v>-0.8279</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.206354494323842</v>
+        <v>-18.2138</v>
       </c>
     </row>
     <row r="161">
@@ -9721,10 +9709,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3734408629176665</v>
+        <v>-0.9167</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.215698984188665</v>
+        <v>-20.1674</v>
       </c>
     </row>
     <row r="162">
@@ -9761,10 +9749,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7087097428595729</v>
+        <v>1.903</v>
       </c>
       <c r="J162" t="n">
-        <v>14.88290460005103</v>
+        <v>39.963</v>
       </c>
     </row>
     <row r="163">
@@ -9801,10 +9789,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>0.389132280821073</v>
+        <v>1.1966</v>
       </c>
       <c r="J163" t="n">
-        <v>8.171777897242533</v>
+        <v>25.1286</v>
       </c>
     </row>
     <row r="164">
@@ -9841,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1594902817202423</v>
+        <v>0.5596</v>
       </c>
       <c r="J164" t="n">
-        <v>3.349295916125089</v>
+        <v>11.7516</v>
       </c>
     </row>
     <row r="165">
@@ -9881,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.08393503717271319</v>
+        <v>-0.1541</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.762635780626977</v>
+        <v>-3.2361</v>
       </c>
     </row>
     <row r="166">
@@ -9921,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3027924946488363</v>
+        <v>-0.7036</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.358642387625562</v>
+        <v>-14.7756</v>
       </c>
     </row>
     <row r="167">
@@ -9961,10 +9949,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2153951868609604</v>
+        <v>0.589</v>
       </c>
       <c r="J167" t="n">
-        <v>4.523298924080168</v>
+        <v>12.369</v>
       </c>
     </row>
     <row r="168">
@@ -10001,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2356925817178433</v>
+        <v>-0.1619</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.94954421607471</v>
+        <v>-3.3999</v>
       </c>
     </row>
     <row r="169">
@@ -10041,10 +10029,10 @@
         <v>0.88</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2541355323267453</v>
+        <v>-0.2054</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.336846178861651</v>
+        <v>-4.3134</v>
       </c>
     </row>
     <row r="170">
@@ -10081,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4586485883630811</v>
+        <v>-0.5079</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.631620355624703</v>
+        <v>-10.6659</v>
       </c>
     </row>
     <row r="171">
@@ -10121,10 +10109,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5462904344404702</v>
+        <v>-0.613</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.47209912324987</v>
+        <v>-12.873</v>
       </c>
     </row>
     <row r="172">
@@ -10161,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.03404808087395393</v>
+        <v>0.2666</v>
       </c>
       <c r="J172" t="n">
-        <v>0.8171539409748944</v>
+        <v>6.3984</v>
       </c>
     </row>
     <row r="173">
@@ -10201,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.02553494643130829</v>
+        <v>0.2501</v>
       </c>
       <c r="J173" t="n">
-        <v>0.6128387143513989</v>
+        <v>6.0024</v>
       </c>
     </row>
     <row r="174">
@@ -10241,10 +10229,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0399104344839054</v>
+        <v>0.1415</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.9578504276137295</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="175">
@@ -10281,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2517530566563836</v>
+        <v>-0.2571</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.042073359753206</v>
+        <v>-6.1704</v>
       </c>
     </row>
     <row r="176">
@@ -10321,10 +10309,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3989478779681531</v>
+        <v>-0.423</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.574749071235676</v>
+        <v>-10.152</v>
       </c>
     </row>
     <row r="177">
@@ -10361,10 +10349,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4876512917727694</v>
+        <v>1.422</v>
       </c>
       <c r="J177" t="n">
-        <v>11.70363100254647</v>
+        <v>34.128</v>
       </c>
     </row>
     <row r="178">
@@ -10401,10 +10389,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3337842471356118</v>
+        <v>1.0827</v>
       </c>
       <c r="J178" t="n">
-        <v>8.010821931254684</v>
+        <v>25.9848</v>
       </c>
     </row>
     <row r="179">
@@ -10441,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.06668101846437507</v>
+        <v>0.3538</v>
       </c>
       <c r="J179" t="n">
-        <v>1.600344443145002</v>
+        <v>8.491199999999999</v>
       </c>
     </row>
     <row r="180">
@@ -10481,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2290738726089812</v>
+        <v>-0.5424</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.497772942615549</v>
+        <v>-13.0176</v>
       </c>
     </row>
     <row r="181">
@@ -10521,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3763262194398799</v>
+        <v>-0.8341</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.031829266557118</v>
+        <v>-20.0184</v>
       </c>
     </row>
     <row r="182">
@@ -10561,10 +10549,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4329913366930395</v>
+        <v>1.409</v>
       </c>
       <c r="J182" t="n">
-        <v>8.65982673386079</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="183">
@@ -10601,10 +10589,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4180981166351269</v>
+        <v>1.371</v>
       </c>
       <c r="J183" t="n">
-        <v>8.361962332702538</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="184">
@@ -10641,10 +10629,10 @@
         <v>1.28</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1786673085099683</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>3.573346170199367</v>
+        <v>13.196</v>
       </c>
     </row>
     <row r="185">
@@ -10681,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.01805474420102424</v>
+        <v>0.0151</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.3610948840204848</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="186">
@@ -10721,10 +10709,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1431811911350035</v>
+        <v>-0.3573</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.86362382270007</v>
+        <v>-7.146</v>
       </c>
     </row>
     <row r="187">
@@ -10761,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.08926818358324222</v>
+        <v>0.4625</v>
       </c>
       <c r="J187" t="n">
-        <v>1.785363671664844</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="188">
@@ -10801,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.003792969021481156</v>
+        <v>0.331</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.07585938042962312</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="189">
@@ -10841,10 +10829,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0980738839642845</v>
+        <v>0.1963</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.96147767928569</v>
+        <v>3.926</v>
       </c>
     </row>
     <row r="190">
@@ -10881,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5541289754184633</v>
+        <v>-0.5652</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.08257950836927</v>
+        <v>-11.304</v>
       </c>
     </row>
     <row r="191">
@@ -10921,10 +10909,10 @@
         <v>0.41</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8109139960960987</v>
+        <v>-0.8549</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.21827992192198</v>
+        <v>-17.098</v>
       </c>
     </row>
     <row r="192">
@@ -10961,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.08275820661057735</v>
+        <v>0.3452</v>
       </c>
       <c r="J192" t="n">
-        <v>1.986196958653856</v>
+        <v>8.284800000000001</v>
       </c>
     </row>
     <row r="193">
@@ -11001,10 +10989,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.05704610499254642</v>
+        <v>0.2996</v>
       </c>
       <c r="J193" t="n">
-        <v>1.369106519821114</v>
+        <v>7.1904</v>
       </c>
     </row>
     <row r="194">
@@ -11041,10 +11029,10 @@
         <v>1.07</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.01456949918003372</v>
+        <v>0.163</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.3496679803208093</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="195">
@@ -11081,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1698071992711913</v>
+        <v>-0.1645</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.075372782508591</v>
+        <v>-3.948</v>
       </c>
     </row>
     <row r="196">
@@ -11121,10 +11109,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3748888497655069</v>
+        <v>-0.4036</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.997332394372165</v>
+        <v>-9.686400000000001</v>
       </c>
     </row>
     <row r="197">
@@ -11161,10 +11149,10 @@
         <v>1.36</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2713993813088896</v>
+        <v>1.0096</v>
       </c>
       <c r="J197" t="n">
-        <v>6.51358515141335</v>
+        <v>24.2304</v>
       </c>
     </row>
     <row r="198">
@@ -11201,10 +11189,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2020595557050897</v>
+        <v>0.8072</v>
       </c>
       <c r="J198" t="n">
-        <v>4.849429336922154</v>
+        <v>19.3728</v>
       </c>
     </row>
     <row r="199">
@@ -11241,10 +11229,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.06981640560573177</v>
+        <v>0.3612</v>
       </c>
       <c r="J199" t="n">
-        <v>1.675593734537562</v>
+        <v>8.668799999999999</v>
       </c>
     </row>
     <row r="200">
@@ -11281,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.04754823751896187</v>
+        <v>-0.2315</v>
       </c>
       <c r="J200" t="n">
-        <v>-1.141157700455085</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="201">
@@ -11321,10 +11309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6076386736222279</v>
+        <v>-1.2179</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.58332816693347</v>
+        <v>-29.2296</v>
       </c>
     </row>
     <row r="202">
@@ -11361,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1755586688950059</v>
+        <v>0.044</v>
       </c>
       <c r="J202" t="n">
-        <v>-3.335614709005112</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="203">
@@ -11401,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2393441622702741</v>
+        <v>-0.0578</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.547539083135207</v>
+        <v>-1.0982</v>
       </c>
     </row>
     <row r="204">
@@ -11441,10 +11429,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2520571198315772</v>
+        <v>-0.0762</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.789085276799968</v>
+        <v>-1.4478</v>
       </c>
     </row>
     <row r="205">
@@ -11481,10 +11469,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6081001285529684</v>
+        <v>-0.5755</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.5539024425064</v>
+        <v>-10.9345</v>
       </c>
     </row>
     <row r="206">
@@ -11521,10 +11509,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8130195492458643</v>
+        <v>-0.7917</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.44737143567142</v>
+        <v>-15.0423</v>
       </c>
     </row>
     <row r="207">
@@ -11561,10 +11549,10 @@
         <v>1.66</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4054025729124684</v>
+        <v>1.4309</v>
       </c>
       <c r="J207" t="n">
-        <v>7.7026488853369</v>
+        <v>27.1871</v>
       </c>
     </row>
     <row r="208">
@@ -11601,10 +11589,10 @@
         <v>1.65</v>
       </c>
       <c r="I208" t="n">
-        <v>0.398475227858707</v>
+        <v>1.4121</v>
       </c>
       <c r="J208" t="n">
-        <v>7.571029329315434</v>
+        <v>26.8299</v>
       </c>
     </row>
     <row r="209">
@@ -11641,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3354445668995987</v>
+        <v>1.2377</v>
       </c>
       <c r="J209" t="n">
-        <v>6.373446771092376</v>
+        <v>23.5163</v>
       </c>
     </row>
     <row r="210">
@@ -11681,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.05811991452229329</v>
+        <v>0.3133</v>
       </c>
       <c r="J210" t="n">
-        <v>1.104278375923573</v>
+        <v>5.9527</v>
       </c>
     </row>
     <row r="211">
@@ -11721,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.02851025438528722</v>
+        <v>0.0448</v>
       </c>
       <c r="J211" t="n">
-        <v>-0.5416948333204573</v>
+        <v>0.8512</v>
       </c>
     </row>
     <row r="212">
@@ -11761,10 +11749,10 @@
         <v>1.68</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4238490736062672</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>8.900830545731612</v>
+        <v>20.4183</v>
       </c>
     </row>
     <row r="213">
@@ -11801,10 +11789,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1984215104880026</v>
+        <v>0.056</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.166851720248054</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="214">
@@ -11841,10 +11829,10 @@
         <v>0.87</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3699261900480273</v>
+        <v>-0.2691</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.768449991008574</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="215">
@@ -11881,10 +11869,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.528563624945756</v>
+        <v>-0.4477</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.09983612386088</v>
+        <v>-9.4017</v>
       </c>
     </row>
     <row r="216">
@@ -11921,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7817475584839528</v>
+        <v>-0.7019</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.41669872816301</v>
+        <v>-14.7399</v>
       </c>
     </row>
     <row r="217">
@@ -11961,10 +11949,10 @@
         <v>1.85</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7396359195944662</v>
+        <v>1.8477</v>
       </c>
       <c r="J217" t="n">
-        <v>15.53235431148379</v>
+        <v>38.8017</v>
       </c>
     </row>
     <row r="218">
@@ -12001,10 +11989,10 @@
         <v>1.56</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4818551564322491</v>
+        <v>1.3192</v>
       </c>
       <c r="J218" t="n">
-        <v>10.11895828507723</v>
+        <v>27.7032</v>
       </c>
     </row>
     <row r="219">
@@ -12041,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I219" t="n">
-        <v>0.04266403204039224</v>
+        <v>0.2162</v>
       </c>
       <c r="J219" t="n">
-        <v>0.8959446728482371</v>
+        <v>4.5402</v>
       </c>
     </row>
     <row r="220">
@@ -12081,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1837524749699863</v>
+        <v>-0.4886</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.858801974369713</v>
+        <v>-10.2606</v>
       </c>
     </row>
     <row r="221">
@@ -12121,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2894273152992333</v>
+        <v>-0.7165</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.077973621283899</v>
+        <v>-15.0465</v>
       </c>
     </row>
     <row r="222">
@@ -12161,10 +12149,10 @@
         <v>2.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8574543581188938</v>
+        <v>2.0593</v>
       </c>
       <c r="J222" t="n">
-        <v>13.7192697299023</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="223">
@@ -12201,10 +12189,10 @@
         <v>1.69</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5116724011029227</v>
+        <v>1.485</v>
       </c>
       <c r="J223" t="n">
-        <v>8.186758417646763</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="224">
@@ -12241,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1106097704943701</v>
+        <v>0.2872</v>
       </c>
       <c r="J224" t="n">
-        <v>1.769756327909922</v>
+        <v>4.5952</v>
       </c>
     </row>
     <row r="225">
@@ -12281,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I225" t="n">
-        <v>0.06406136382734495</v>
+        <v>0.13</v>
       </c>
       <c r="J225" t="n">
-        <v>1.024981821237519</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="226">
@@ -12321,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0492479954121785</v>
+        <v>-0.3208</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.787967926594856</v>
+        <v>-5.1328</v>
       </c>
     </row>
     <row r="227">
@@ -12361,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1475791344845911</v>
+        <v>0.1814</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.361266151753458</v>
+        <v>2.9024</v>
       </c>
     </row>
     <row r="228">
@@ -12401,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.33760530321419</v>
+        <v>-0.1771</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.40168485142704</v>
+        <v>-2.8336</v>
       </c>
     </row>
     <row r="229">
@@ -12441,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.33760530321419</v>
+        <v>-0.1771</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.40168485142704</v>
+        <v>-2.8336</v>
       </c>
     </row>
     <row r="230">
@@ -12481,10 +12469,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5844062393345362</v>
+        <v>-0.5759</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.350499829352579</v>
+        <v>-9.214399999999999</v>
       </c>
     </row>
     <row r="231">
@@ -12521,10 +12509,10 @@
         <v>0.36</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8479990910064404</v>
+        <v>-0.8919</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.56798545610305</v>
+        <v>-14.2704</v>
       </c>
     </row>
     <row r="232">
@@ -12561,10 +12549,10 @@
         <v>1.17</v>
       </c>
       <c r="I232" t="n">
-        <v>0.01537223577186845</v>
+        <v>0.3706</v>
       </c>
       <c r="J232" t="n">
-        <v>0.2920724796655005</v>
+        <v>7.0414</v>
       </c>
     </row>
     <row r="233">
@@ -12601,10 +12589,10 @@
         <v>1.1</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.06752007403048114</v>
+        <v>0.2606</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.282881406579142</v>
+        <v>4.9514</v>
       </c>
     </row>
     <row r="234">
@@ -12641,10 +12629,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2876197485655894</v>
+        <v>-0.144</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.464775222746198</v>
+        <v>-2.736</v>
       </c>
     </row>
     <row r="235">
@@ -12681,10 +12669,10 @@
         <v>0.83</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3893171652676364</v>
+        <v>-0.3138</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.397026140085091</v>
+        <v>-5.9622</v>
       </c>
     </row>
     <row r="236">
@@ -12721,10 +12709,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7275976251542468</v>
+        <v>-0.6934</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.82435487793069</v>
+        <v>-13.1746</v>
       </c>
     </row>
     <row r="237">
@@ -12761,10 +12749,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7977457429286265</v>
+        <v>1.9918</v>
       </c>
       <c r="J237" t="n">
-        <v>15.1571691156439</v>
+        <v>37.8442</v>
       </c>
     </row>
     <row r="238">
@@ -12801,10 +12789,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3621438225266574</v>
+        <v>1.0225</v>
       </c>
       <c r="J238" t="n">
-        <v>6.88073262800649</v>
+        <v>19.4275</v>
       </c>
     </row>
     <row r="239">
@@ -12841,10 +12829,10 @@
         <v>0.96</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.03673189946343678</v>
+        <v>-0.3048</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.6979060898052988</v>
+        <v>-5.7912</v>
       </c>
     </row>
     <row r="240">
@@ -12881,10 +12869,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.09836508660909275</v>
+        <v>-0.4565</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.868936645572762</v>
+        <v>-8.673500000000001</v>
       </c>
     </row>
     <row r="241">
@@ -12921,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1103755399404091</v>
+        <v>-0.4842</v>
       </c>
       <c r="J241" t="n">
-        <v>-2.097135258867772</v>
+        <v>-9.1998</v>
       </c>
     </row>
     <row r="242">
@@ -12961,10 +12949,10 @@
         <v>1.34</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2110326943721619</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>4.009621193071077</v>
+        <v>12.0384</v>
       </c>
     </row>
     <row r="243">
@@ -13001,10 +12989,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1109477924939309</v>
+        <v>0.1632</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.108008057384688</v>
+        <v>3.1008</v>
       </c>
     </row>
     <row r="244">
@@ -13041,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4181409876738773</v>
+        <v>-0.4073</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.944678765803669</v>
+        <v>-7.7387</v>
       </c>
     </row>
     <row r="245">
@@ -13081,10 +13069,10 @@
         <v>0.54</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6527607606058694</v>
+        <v>-0.6913</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.40245445151152</v>
+        <v>-13.1347</v>
       </c>
     </row>
     <row r="246">
@@ -13121,10 +13109,10 @@
         <v>0.5</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6960677434629541</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.22528712579613</v>
+        <v>-14.0676</v>
       </c>
     </row>
     <row r="247">
@@ -13161,10 +13149,10 @@
         <v>1.89</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6347708856658028</v>
+        <v>1.878</v>
       </c>
       <c r="J247" t="n">
-        <v>12.06064682765025</v>
+        <v>35.682</v>
       </c>
     </row>
     <row r="248">
@@ -13201,10 +13189,10 @@
         <v>1.41</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2874440978106846</v>
+        <v>0.9728</v>
       </c>
       <c r="J248" t="n">
-        <v>5.461437858403008</v>
+        <v>18.4832</v>
       </c>
     </row>
     <row r="249">
@@ -13241,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1663156036671979</v>
+        <v>0.5446</v>
       </c>
       <c r="J249" t="n">
-        <v>3.159996469676761</v>
+        <v>10.3474</v>
       </c>
     </row>
     <row r="250">
@@ -13281,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1429954974155833</v>
+        <v>0.471</v>
       </c>
       <c r="J250" t="n">
-        <v>2.716914450896082</v>
+        <v>8.949</v>
       </c>
     </row>
     <row r="251">
@@ -13321,10 +13309,10 @@
         <v>0.86</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2311795294462326</v>
+        <v>-0.6118</v>
       </c>
       <c r="J251" t="n">
-        <v>-4.392411059478419</v>
+        <v>-11.6242</v>
       </c>
     </row>
     <row r="252">
@@ -13361,10 +13349,10 @@
         <v>1.48</v>
       </c>
       <c r="I252" t="n">
-        <v>0.48825227061724</v>
+        <v>1.246</v>
       </c>
       <c r="J252" t="n">
-        <v>11.71805449481376</v>
+        <v>29.904</v>
       </c>
     </row>
     <row r="253">
@@ -13401,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1529862450645209</v>
+        <v>0.5161</v>
       </c>
       <c r="J253" t="n">
-        <v>3.6716698815485</v>
+        <v>12.3864</v>
       </c>
     </row>
     <row r="254">
@@ -13441,10 +13429,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.05647065519885067</v>
+        <v>-0.2794</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.355295724772416</v>
+        <v>-6.7056</v>
       </c>
     </row>
     <row r="255">
@@ -13481,10 +13469,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1018445790027527</v>
+        <v>-0.4038</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.444269896066066</v>
+        <v>-9.6912</v>
       </c>
     </row>
     <row r="256">
@@ -13521,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1363011852063327</v>
+        <v>-0.4888</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.271228444951985</v>
+        <v>-11.7312</v>
       </c>
     </row>
     <row r="257">
@@ -13561,10 +13549,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.06607669298077383</v>
+        <v>0.3148</v>
       </c>
       <c r="J257" t="n">
-        <v>1.585840631538572</v>
+        <v>7.5552</v>
       </c>
     </row>
     <row r="258">
@@ -13601,10 +13589,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.04392544368006615</v>
+        <v>0.2673</v>
       </c>
       <c r="J258" t="n">
-        <v>1.054210648321588</v>
+        <v>6.4152</v>
       </c>
     </row>
     <row r="259">
@@ -13641,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.009622240329629612</v>
+        <v>0.1424</v>
       </c>
       <c r="J259" t="n">
-        <v>-0.2309337679111107</v>
+        <v>3.4176</v>
       </c>
     </row>
     <row r="260">
@@ -13681,10 +13669,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2694432894386005</v>
+        <v>-0.2889</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.466638946526411</v>
+        <v>-6.9336</v>
       </c>
     </row>
     <row r="261">
@@ -13721,10 +13709,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4459249485929447</v>
+        <v>-0.4639</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.70219876623067</v>
+        <v>-11.1336</v>
       </c>
     </row>
     <row r="262">
@@ -13761,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6257726357837621</v>
+        <v>1.5173</v>
       </c>
       <c r="J262" t="n">
-        <v>10.01236217254019</v>
+        <v>24.2768</v>
       </c>
     </row>
     <row r="263">
@@ -13801,10 +13789,10 @@
         <v>1.66</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5702497693728861</v>
+        <v>1.4055</v>
       </c>
       <c r="J263" t="n">
-        <v>9.123996309966177</v>
+        <v>22.488</v>
       </c>
     </row>
     <row r="264">
@@ -13841,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4316568051120107</v>
+        <v>1.1029</v>
       </c>
       <c r="J264" t="n">
-        <v>6.90650888179217</v>
+        <v>17.6464</v>
       </c>
     </row>
     <row r="265">
@@ -13881,10 +13869,10 @@
         <v>1.46</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3923462496057695</v>
+        <v>0.9749</v>
       </c>
       <c r="J265" t="n">
-        <v>6.277539993692312</v>
+        <v>15.5984</v>
       </c>
     </row>
     <row r="266">
@@ -13921,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.02020358052138115</v>
+        <v>-0.0646</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.3232572883420984</v>
+        <v>-1.0336</v>
       </c>
     </row>
     <row r="267">
@@ -13961,10 +13949,10 @@
         <v>1.37</v>
       </c>
       <c r="I267" t="n">
-        <v>0.138628407230527</v>
+        <v>0.7076</v>
       </c>
       <c r="J267" t="n">
-        <v>2.218054515688432</v>
+        <v>11.3216</v>
       </c>
     </row>
     <row r="268">
@@ -14001,10 +13989,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.4411836335833429</v>
+        <v>-0.1663</v>
       </c>
       <c r="J268" t="n">
-        <v>-7.058938137333487</v>
+        <v>-2.6608</v>
       </c>
     </row>
     <row r="269">
@@ -14041,10 +14029,10 @@
         <v>0.72</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.616633765327016</v>
+        <v>-0.4164</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.866140245232256</v>
+        <v>-6.6624</v>
       </c>
     </row>
     <row r="270">
@@ -14081,10 +14069,10 @@
         <v>0.4</v>
       </c>
       <c r="I270" t="n">
-        <v>-1.039012473143152</v>
+        <v>-0.8465</v>
       </c>
       <c r="J270" t="n">
-        <v>-16.62419957029043</v>
+        <v>-13.544</v>
       </c>
     </row>
     <row r="271">
@@ -14121,10 +14109,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.039012473143152</v>
+        <v>-0.8465</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.62419957029043</v>
+        <v>-13.544</v>
       </c>
     </row>
     <row r="272">
@@ -14161,10 +14149,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6111640010997413</v>
+        <v>1.5643</v>
       </c>
       <c r="J272" t="n">
-        <v>12.22328002199483</v>
+        <v>31.286</v>
       </c>
     </row>
     <row r="273">
@@ -14201,10 +14189,10 @@
         <v>1.63</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5591751963404414</v>
+        <v>1.4529</v>
       </c>
       <c r="J273" t="n">
-        <v>11.18350392680883</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="274">
@@ -14241,10 +14229,10 @@
         <v>1.11</v>
       </c>
       <c r="I274" t="n">
-        <v>0.08592114034435865</v>
+        <v>0.2444</v>
       </c>
       <c r="J274" t="n">
-        <v>1.718422806887173</v>
+        <v>4.888</v>
       </c>
     </row>
     <row r="275">
@@ -14281,10 +14269,10 @@
         <v>0.97</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.06342323617849394</v>
+        <v>-0.2753</v>
       </c>
       <c r="J275" t="n">
-        <v>-1.268464723569879</v>
+        <v>-5.506</v>
       </c>
     </row>
     <row r="276">
@@ -14321,10 +14309,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2402911899191939</v>
+        <v>-0.6926</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.805823798383878</v>
+        <v>-13.852</v>
       </c>
     </row>
     <row r="277">
@@ -14361,10 +14349,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1128968052225584</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>2.257936104451168</v>
+        <v>10.454</v>
       </c>
     </row>
     <row r="278">
@@ -14401,10 +14389,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.07405905980135841</v>
+        <v>0.4551</v>
       </c>
       <c r="J278" t="n">
-        <v>1.481181196027168</v>
+        <v>9.102</v>
       </c>
     </row>
     <row r="279">
@@ -14441,10 +14429,10 @@
         <v>0.98</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2194145879548797</v>
+        <v>-0.0156</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.388291759097594</v>
+        <v>-0.312</v>
       </c>
     </row>
     <row r="280">
@@ -14481,10 +14469,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5248718630028394</v>
+        <v>-0.4486</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.49743726005679</v>
+        <v>-8.972</v>
       </c>
     </row>
     <row r="281">
@@ -14521,10 +14509,10 @@
         <v>0.36</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.000401077738349</v>
+        <v>-0.9127</v>
       </c>
       <c r="J281" t="n">
-        <v>-20.00802155476698</v>
+        <v>-18.254</v>
       </c>
     </row>
     <row r="282">
@@ -14561,10 +14549,10 @@
         <v>1.46</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4522631145039087</v>
+        <v>1.1542</v>
       </c>
       <c r="J282" t="n">
-        <v>9.94978851908599</v>
+        <v>25.3924</v>
       </c>
     </row>
     <row r="283">
@@ -14601,10 +14589,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3716525411068343</v>
+        <v>0.9861</v>
       </c>
       <c r="J283" t="n">
-        <v>8.176355904350354</v>
+        <v>21.6942</v>
       </c>
     </row>
     <row r="284">
@@ -14641,10 +14629,10 @@
         <v>1.28</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2690471793092168</v>
+        <v>0.7597</v>
       </c>
       <c r="J284" t="n">
-        <v>5.91903794480277</v>
+        <v>16.7134</v>
       </c>
     </row>
     <row r="285">
@@ -14681,10 +14669,10 @@
         <v>0.95</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.06807390002911745</v>
+        <v>-0.3196</v>
       </c>
       <c r="J285" t="n">
-        <v>-1.497625800640584</v>
+        <v>-7.0312</v>
       </c>
     </row>
     <row r="286">
@@ -14721,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2355459544677321</v>
+        <v>-0.7234</v>
       </c>
       <c r="J286" t="n">
-        <v>-5.182010998290107</v>
+        <v>-15.9148</v>
       </c>
     </row>
     <row r="287">
@@ -14761,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.03685447384902898</v>
+        <v>0.281</v>
       </c>
       <c r="J287" t="n">
-        <v>0.8107984246786375</v>
+        <v>6.182</v>
       </c>
     </row>
     <row r="288">
@@ -14801,10 +14789,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0650362451012278</v>
+        <v>0.1113</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.430797392227011</v>
+        <v>2.4486</v>
       </c>
     </row>
     <row r="289">
@@ -14841,10 +14829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.167069325571236</v>
+        <v>-0.096</v>
       </c>
       <c r="J289" t="n">
-        <v>-3.675525162567192</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="290">
@@ -14881,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2948217875498795</v>
+        <v>-0.3101</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.486079326097348</v>
+        <v>-6.8222</v>
       </c>
     </row>
     <row r="291">
@@ -14921,10 +14909,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5615997336409602</v>
+        <v>-0.605</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.35519414010112</v>
+        <v>-13.31</v>
       </c>
     </row>
     <row r="292">
@@ -14961,10 +14949,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2483096863979048</v>
+        <v>0.6866</v>
       </c>
       <c r="J292" t="n">
-        <v>5.462813100753904</v>
+        <v>15.1052</v>
       </c>
     </row>
     <row r="293">
@@ -15001,10 +14989,10 @@
         <v>1.32</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1292595180105549</v>
+        <v>0.5149</v>
       </c>
       <c r="J293" t="n">
-        <v>2.843709396232207</v>
+        <v>11.3278</v>
       </c>
     </row>
     <row r="294">
@@ -15041,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.04177894608264934</v>
+        <v>0.3792</v>
       </c>
       <c r="J294" t="n">
-        <v>0.9191368138182854</v>
+        <v>8.3424</v>
       </c>
     </row>
     <row r="295">
@@ -15081,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4756463430122385</v>
+        <v>-0.4031</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.46421954626925</v>
+        <v>-8.8682</v>
       </c>
     </row>
     <row r="296">
@@ -15121,10 +15109,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.631420259602249</v>
+        <v>-0.5609</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.89124571124948</v>
+        <v>-12.3398</v>
       </c>
     </row>
     <row r="297">
@@ -15161,10 +15149,10 @@
         <v>1.46</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4153627549223534</v>
+        <v>1.2208</v>
       </c>
       <c r="J297" t="n">
-        <v>9.137980608291775</v>
+        <v>26.8576</v>
       </c>
     </row>
     <row r="298">
@@ -15201,10 +15189,10 @@
         <v>1.37</v>
       </c>
       <c r="I298" t="n">
-        <v>0.338183344882365</v>
+        <v>1.0324</v>
       </c>
       <c r="J298" t="n">
-        <v>7.440033587412029</v>
+        <v>22.7128</v>
       </c>
     </row>
     <row r="299">
@@ -15241,10 +15229,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0821533981022603</v>
+        <v>-0.3913</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.807374758249727</v>
+        <v>-8.608599999999999</v>
       </c>
     </row>
     <row r="300">
@@ -15281,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.09548572797674312</v>
+        <v>-0.4206</v>
       </c>
       <c r="J300" t="n">
-        <v>-2.100686015488349</v>
+        <v>-9.2532</v>
       </c>
     </row>
     <row r="301">
@@ -15321,10 +15309,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4816223526480302</v>
+        <v>-1.135</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.59569175825666</v>
+        <v>-24.97</v>
       </c>
     </row>
     <row r="302">
@@ -15361,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.3441068504254378</v>
+        <v>-0.1645</v>
       </c>
       <c r="J302" t="n">
-        <v>-5.849816457232443</v>
+        <v>-2.7965</v>
       </c>
     </row>
     <row r="303">
@@ -15401,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3577188320376093</v>
+        <v>-0.1804</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.081220144639359</v>
+        <v>-3.0668</v>
       </c>
     </row>
     <row r="304">
@@ -15441,10 +15429,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.6605833497750406</v>
+        <v>-0.583</v>
       </c>
       <c r="J304" t="n">
-        <v>-11.22991694617569</v>
+        <v>-9.911</v>
       </c>
     </row>
     <row r="305">
@@ -15481,10 +15469,10 @@
         <v>0.53</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.7258102882611785</v>
+        <v>-0.6552</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.33877490044004</v>
+        <v>-11.1384</v>
       </c>
     </row>
     <row r="306">
@@ -15521,10 +15509,10 @@
         <v>0.48</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7915794836262953</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.45685122164702</v>
+        <v>-12.2961</v>
       </c>
     </row>
     <row r="307">
@@ -15561,10 +15549,10 @@
         <v>1.9</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6285222312328502</v>
+        <v>1.8358</v>
       </c>
       <c r="J307" t="n">
-        <v>10.68487793095845</v>
+        <v>31.2086</v>
       </c>
     </row>
     <row r="308">
@@ -15601,10 +15589,10 @@
         <v>1.64</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4436760675271714</v>
+        <v>1.3692</v>
       </c>
       <c r="J308" t="n">
-        <v>7.542493147961914</v>
+        <v>23.2764</v>
       </c>
     </row>
     <row r="309">
@@ -15641,10 +15629,10 @@
         <v>1.52</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3559541693444411</v>
+        <v>1.1272</v>
       </c>
       <c r="J309" t="n">
-        <v>6.051220878855499</v>
+        <v>19.1624</v>
       </c>
     </row>
     <row r="310">
@@ -15681,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I310" t="n">
-        <v>0.08629423699554087</v>
+        <v>0.2734</v>
       </c>
       <c r="J310" t="n">
-        <v>1.467002028924195</v>
+        <v>4.6478</v>
       </c>
     </row>
     <row r="311">
@@ -15721,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I311" t="n">
-        <v>0.08629423699554087</v>
+        <v>0.2734</v>
       </c>
       <c r="J311" t="n">
-        <v>1.467002028924195</v>
+        <v>4.6478</v>
       </c>
     </row>
     <row r="312">
@@ -15761,10 +15749,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6123264932685433</v>
+        <v>1.5557</v>
       </c>
       <c r="J312" t="n">
-        <v>11.02187687883378</v>
+        <v>28.0026</v>
       </c>
     </row>
     <row r="313">
@@ -15801,10 +15789,10 @@
         <v>1.58</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4791328582925063</v>
+        <v>1.2727</v>
       </c>
       <c r="J313" t="n">
-        <v>8.624391449265113</v>
+        <v>22.9086</v>
       </c>
     </row>
     <row r="314">
@@ -15841,10 +15829,10 @@
         <v>1.58</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4791328582925063</v>
+        <v>1.2727</v>
       </c>
       <c r="J314" t="n">
-        <v>8.624391449265113</v>
+        <v>22.9086</v>
       </c>
     </row>
     <row r="315">
@@ -15881,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1062254288728382</v>
+        <v>0.3104</v>
       </c>
       <c r="J315" t="n">
-        <v>1.912057719711088</v>
+        <v>5.5872</v>
       </c>
     </row>
     <row r="316">
@@ -15921,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I316" t="n">
-        <v>0.0412309743651835</v>
+        <v>0.1285</v>
       </c>
       <c r="J316" t="n">
-        <v>0.742157538573303</v>
+        <v>2.313</v>
       </c>
     </row>
     <row r="317">
@@ -15961,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.06310353142870277</v>
+        <v>0.4697</v>
       </c>
       <c r="J317" t="n">
-        <v>1.13586356571665</v>
+        <v>8.454599999999999</v>
       </c>
     </row>
     <row r="318">
@@ -16001,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.5959638541585371</v>
+        <v>-0.5077</v>
       </c>
       <c r="J318" t="n">
-        <v>-10.72734937485367</v>
+        <v>-9.1386</v>
       </c>
     </row>
     <row r="319">
@@ -16041,10 +16029,10 @@
         <v>0.58</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.6895916730002021</v>
+        <v>-0.6087</v>
       </c>
       <c r="J319" t="n">
-        <v>-12.41265011400364</v>
+        <v>-10.9566</v>
       </c>
     </row>
     <row r="320">
@@ -16081,10 +16069,10 @@
         <v>0.58</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.6895916730002021</v>
+        <v>-0.6087</v>
       </c>
       <c r="J320" t="n">
-        <v>-12.41265011400364</v>
+        <v>-10.9566</v>
       </c>
     </row>
     <row r="321">
@@ -16121,10 +16109,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7030751356688252</v>
+        <v>-0.6224</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.65535244203885</v>
+        <v>-11.2032</v>
       </c>
     </row>
     <row r="322">
@@ -16161,10 +16149,10 @@
         <v>1.55</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5558170882230564</v>
+        <v>1.3613</v>
       </c>
       <c r="J322" t="n">
-        <v>12.7837930291303</v>
+        <v>31.3099</v>
       </c>
     </row>
     <row r="323">
@@ -16201,10 +16189,10 @@
         <v>1.34</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3485998792246271</v>
+        <v>0.9273</v>
       </c>
       <c r="J323" t="n">
-        <v>8.017797222166424</v>
+        <v>21.3279</v>
       </c>
     </row>
     <row r="324">
@@ -16241,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.01965774149134613</v>
+        <v>-0.0302</v>
       </c>
       <c r="J324" t="n">
-        <v>0.452128054300961</v>
+        <v>-0.6946</v>
       </c>
     </row>
     <row r="325">
@@ -16281,10 +16269,10 @@
         <v>0.92</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.08210275767650367</v>
+        <v>-0.3922</v>
       </c>
       <c r="J325" t="n">
-        <v>-1.888363426559584</v>
+        <v>-9.0206</v>
       </c>
     </row>
     <row r="326">
@@ -16321,10 +16309,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2403112719919873</v>
+        <v>-0.7563</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.527159255815709</v>
+        <v>-17.3949</v>
       </c>
     </row>
     <row r="327">
@@ -16361,10 +16349,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.2411426664839912</v>
+        <v>0.6422</v>
       </c>
       <c r="J327" t="n">
-        <v>5.546281329131797</v>
+        <v>14.7706</v>
       </c>
     </row>
     <row r="328">
@@ -16401,10 +16389,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1868176302988244</v>
+        <v>-0.1858</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.296805496872961</v>
+        <v>-4.2734</v>
       </c>
     </row>
     <row r="329">
@@ -16441,10 +16429,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1992557131706508</v>
+        <v>-0.2063</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.582881402924968</v>
+        <v>-4.7449</v>
       </c>
     </row>
     <row r="330">
@@ -16481,10 +16469,10 @@
         <v>0.78</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3553760578062652</v>
+        <v>-0.3878</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.173649329544102</v>
+        <v>-8.9194</v>
       </c>
     </row>
     <row r="331">
@@ -16521,10 +16509,10 @@
         <v>0.59</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6287502681254025</v>
+        <v>-0.6431</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.46125616688426</v>
+        <v>-14.7913</v>
       </c>
     </row>
     <row r="332">
@@ -16561,10 +16549,10 @@
         <v>2.18</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8153488880125805</v>
+        <v>2.0593</v>
       </c>
       <c r="J332" t="n">
-        <v>11.41488443217613</v>
+        <v>28.8302</v>
       </c>
     </row>
     <row r="333">
@@ -16601,10 +16589,10 @@
         <v>2.02</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6968693409365447</v>
+        <v>1.9307</v>
       </c>
       <c r="J333" t="n">
-        <v>9.756170773111627</v>
+        <v>27.0298</v>
       </c>
     </row>
     <row r="334">
@@ -16641,10 +16629,10 @@
         <v>1.96</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6506801870628967</v>
+        <v>1.8458</v>
       </c>
       <c r="J334" t="n">
-        <v>9.109522618880554</v>
+        <v>25.8412</v>
       </c>
     </row>
     <row r="335">
@@ -16681,10 +16669,10 @@
         <v>1.48</v>
       </c>
       <c r="I335" t="n">
-        <v>0.2792905179360713</v>
+        <v>0.9186</v>
       </c>
       <c r="J335" t="n">
-        <v>3.910067251104999</v>
+        <v>12.8604</v>
       </c>
     </row>
     <row r="336">
@@ -16721,10 +16709,10 @@
         <v>0.92</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.243109373450249</v>
+        <v>-0.5196</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.403531228303486</v>
+        <v>-7.2744</v>
       </c>
     </row>
     <row r="337">
@@ -16761,10 +16749,10 @@
         <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.2577629646470692</v>
+        <v>0.1776</v>
       </c>
       <c r="J337" t="n">
-        <v>-3.608681505058968</v>
+        <v>2.4864</v>
       </c>
     </row>
     <row r="338">
@@ -16801,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.7944165659471565</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>-11.12183192326019</v>
+        <v>-8.4322</v>
       </c>
     </row>
     <row r="339">
@@ -16841,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.806531160885071</v>
+        <v>-0.6172</v>
       </c>
       <c r="J339" t="n">
-        <v>-11.29143625239099</v>
+        <v>-8.6408</v>
       </c>
     </row>
     <row r="340">
@@ -16881,10 +16869,10 @@
         <v>0.52</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.8432834800988859</v>
+        <v>-0.6607</v>
       </c>
       <c r="J340" t="n">
-        <v>-11.8059687213844</v>
+        <v>-9.2498</v>
       </c>
     </row>
     <row r="341">
@@ -16921,10 +16909,10 @@
         <v>0.5</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.8679704037560207</v>
+        <v>-0.6887</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.15158565258429</v>
+        <v>-9.6418</v>
       </c>
     </row>
     <row r="342">
@@ -16961,10 +16949,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3367549663095804</v>
+        <v>1.0417</v>
       </c>
       <c r="J342" t="n">
-        <v>6.735099326191608</v>
+        <v>20.834</v>
       </c>
     </row>
     <row r="343">
@@ -17001,10 +16989,10 @@
         <v>1.41</v>
       </c>
       <c r="I343" t="n">
-        <v>0.329044896162925</v>
+        <v>1.0204</v>
       </c>
       <c r="J343" t="n">
-        <v>6.580897923258499</v>
+        <v>20.408</v>
       </c>
     </row>
     <row r="344">
@@ -17041,10 +17029,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.282610928510056</v>
+        <v>0.8889</v>
       </c>
       <c r="J344" t="n">
-        <v>5.652218570201121</v>
+        <v>17.778</v>
       </c>
     </row>
     <row r="345">
@@ -17081,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I345" t="n">
-        <v>0.1443305919496208</v>
+        <v>0.3867</v>
       </c>
       <c r="J345" t="n">
-        <v>2.886611838992415</v>
+        <v>7.734</v>
       </c>
     </row>
     <row r="346">
@@ -17121,10 +17109,10 @@
         <v>0.82</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2180269269524763</v>
+        <v>-0.6898</v>
       </c>
       <c r="J346" t="n">
-        <v>-4.360538539049526</v>
+        <v>-13.796</v>
       </c>
     </row>
     <row r="347">
@@ -17161,10 +17149,10 @@
         <v>1.05</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0118220761563418</v>
+        <v>0.2145</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.2364415231268361</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="348">
@@ -17201,10 +17189,10 @@
         <v>0.84</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2815842772653266</v>
+        <v>-0.2292</v>
       </c>
       <c r="J348" t="n">
-        <v>-5.631685545306532</v>
+        <v>-4.584</v>
       </c>
     </row>
     <row r="349">
@@ -17241,10 +17229,10 @@
         <v>0.79</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3351231643188685</v>
+        <v>-0.3296</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.702463286377371</v>
+        <v>-6.592</v>
       </c>
     </row>
     <row r="350">
@@ -17281,10 +17269,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3582257033872747</v>
+        <v>-0.3642</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.164514067745493</v>
+        <v>-7.284</v>
       </c>
     </row>
     <row r="351">
@@ -17321,10 +17309,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5951554460391603</v>
+        <v>-0.6352</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.90310892078321</v>
+        <v>-12.704</v>
       </c>
     </row>
     <row r="352">
@@ -17361,10 +17349,10 @@
         <v>1.58</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5046417739575553</v>
+        <v>1.3409</v>
       </c>
       <c r="J352" t="n">
-        <v>9.083551931235995</v>
+        <v>24.1362</v>
       </c>
     </row>
     <row r="353">
@@ -17401,10 +17389,10 @@
         <v>1.54</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4710914363158694</v>
+        <v>1.263</v>
       </c>
       <c r="J353" t="n">
-        <v>8.479645853685648</v>
+        <v>22.734</v>
       </c>
     </row>
     <row r="354">
@@ -17441,10 +17429,10 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4371149866892547</v>
+        <v>1.1832</v>
       </c>
       <c r="J354" t="n">
-        <v>7.868069760406586</v>
+        <v>21.2976</v>
       </c>
     </row>
     <row r="355">
@@ -17481,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I355" t="n">
-        <v>0.06306973675826642</v>
+        <v>0.0849</v>
       </c>
       <c r="J355" t="n">
-        <v>1.135255261648796</v>
+        <v>1.5282</v>
       </c>
     </row>
     <row r="356">
@@ -17521,10 +17509,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3325671437730234</v>
+        <v>-0.9273</v>
       </c>
       <c r="J356" t="n">
-        <v>-5.986208587914422</v>
+        <v>-16.6914</v>
       </c>
     </row>
     <row r="357">
@@ -17561,10 +17549,10 @@
         <v>1.47</v>
       </c>
       <c r="I357" t="n">
-        <v>0.292424367599546</v>
+        <v>0.7789</v>
       </c>
       <c r="J357" t="n">
-        <v>5.263638616791829</v>
+        <v>14.0202</v>
       </c>
     </row>
     <row r="358">
@@ -17601,10 +17589,10 @@
         <v>1.12</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.04229396936275857</v>
+        <v>0.3126</v>
       </c>
       <c r="J358" t="n">
-        <v>-0.7612914485296542</v>
+        <v>5.6268</v>
       </c>
     </row>
     <row r="359">
@@ -17641,10 +17629,10 @@
         <v>0.8</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.4138502186062219</v>
+        <v>-0.3424</v>
       </c>
       <c r="J359" t="n">
-        <v>-7.449303934911994</v>
+        <v>-6.1632</v>
       </c>
     </row>
     <row r="360">
@@ -17681,10 +17669,10 @@
         <v>0.53</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.7280934883020869</v>
+        <v>-0.7095</v>
       </c>
       <c r="J360" t="n">
-        <v>-13.10568278943756</v>
+        <v>-12.771</v>
       </c>
     </row>
     <row r="361">
@@ -17721,10 +17709,10 @@
         <v>0.4</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.8705978964496086</v>
+        <v>-0.8623</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.67076213609296</v>
+        <v>-15.5214</v>
       </c>
     </row>
     <row r="362">
@@ -17761,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.09558990441565386</v>
+        <v>0.4382</v>
       </c>
       <c r="J362" t="n">
-        <v>2.007387992728731</v>
+        <v>9.202199999999999</v>
       </c>
     </row>
     <row r="363">
@@ -17801,10 +17789,10 @@
         <v>0.95</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.1915576117670576</v>
+        <v>-0.0677</v>
       </c>
       <c r="J363" t="n">
-        <v>-4.022709847108209</v>
+        <v>-1.4217</v>
       </c>
     </row>
     <row r="364">
@@ -17841,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.344146268301159</v>
+        <v>-0.3037</v>
       </c>
       <c r="J364" t="n">
-        <v>-7.227071634324339</v>
+        <v>-6.3777</v>
       </c>
     </row>
     <row r="365">
@@ -17881,10 +17869,10 @@
         <v>0.77</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4271837657919644</v>
+        <v>-0.397</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.970859081631252</v>
+        <v>-8.337</v>
       </c>
     </row>
     <row r="366">
@@ -17921,10 +17909,10 @@
         <v>0.68</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5525967634488299</v>
+        <v>-0.5233</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.60453203242543</v>
+        <v>-10.9893</v>
       </c>
     </row>
     <row r="367">
@@ -17961,10 +17949,10 @@
         <v>1.58</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5953881268957527</v>
+        <v>1.382</v>
       </c>
       <c r="J367" t="n">
-        <v>12.50315066481081</v>
+        <v>29.022</v>
       </c>
     </row>
     <row r="368">
@@ -18001,10 +17989,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.2566585654855997</v>
+        <v>0.6738</v>
       </c>
       <c r="J368" t="n">
-        <v>5.389829875197593</v>
+        <v>14.1498</v>
       </c>
     </row>
     <row r="369">
@@ -18041,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.1419174415576598</v>
+        <v>0.3252</v>
       </c>
       <c r="J369" t="n">
-        <v>2.980266272710855</v>
+        <v>6.8292</v>
       </c>
     </row>
     <row r="370">
@@ -18081,10 +18069,10 @@
         <v>1.13</v>
       </c>
       <c r="I370" t="n">
-        <v>0.1419174415576598</v>
+        <v>0.3252</v>
       </c>
       <c r="J370" t="n">
-        <v>2.980266272710855</v>
+        <v>6.8292</v>
       </c>
     </row>
     <row r="371">
@@ -18121,10 +18109,10 @@
         <v>0.88</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1296588334481949</v>
+        <v>-0.5286</v>
       </c>
       <c r="J371" t="n">
-        <v>-2.722835502412094</v>
+        <v>-11.1006</v>
       </c>
     </row>
     <row r="372">
@@ -18161,10 +18149,10 @@
         <v>1.03</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.0964896494047312</v>
+        <v>0.1477</v>
       </c>
       <c r="J372" t="n">
-        <v>-1.929792988094624</v>
+        <v>2.954</v>
       </c>
     </row>
     <row r="373">
@@ -18201,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.1370799943641184</v>
+        <v>0.0655</v>
       </c>
       <c r="J373" t="n">
-        <v>-2.741599887282367</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="374">
@@ -18241,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1907559664959993</v>
+        <v>-0.0388</v>
       </c>
       <c r="J374" t="n">
-        <v>-3.815119329919986</v>
+        <v>-0.776</v>
       </c>
     </row>
     <row r="375">
@@ -18281,10 +18269,10 @@
         <v>0.72</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.4913410234724832</v>
+        <v>-0.4637</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.826820469449665</v>
+        <v>-9.273999999999999</v>
       </c>
     </row>
     <row r="376">
@@ -18321,10 +18309,10 @@
         <v>0.64</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5957867250641333</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.91573450128267</v>
+        <v>-11.442</v>
       </c>
     </row>
     <row r="377">
@@ -18361,10 +18349,10 @@
         <v>1.35</v>
       </c>
       <c r="I377" t="n">
-        <v>0.2666347076321071</v>
+        <v>0.8933</v>
       </c>
       <c r="J377" t="n">
-        <v>5.332694152642141</v>
+        <v>17.866</v>
       </c>
     </row>
     <row r="378">
@@ -18401,10 +18389,10 @@
         <v>1.32</v>
       </c>
       <c r="I378" t="n">
-        <v>0.2438123595567106</v>
+        <v>0.8248</v>
       </c>
       <c r="J378" t="n">
-        <v>4.876247191134212</v>
+        <v>16.496</v>
       </c>
     </row>
     <row r="379">
@@ -18441,10 +18429,10 @@
         <v>1.28</v>
       </c>
       <c r="I379" t="n">
-        <v>0.2137668238151353</v>
+        <v>0.729</v>
       </c>
       <c r="J379" t="n">
-        <v>4.275336476302706</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="380">
@@ -18481,10 +18469,10 @@
         <v>1.13</v>
       </c>
       <c r="I380" t="n">
-        <v>0.107529027488552</v>
+        <v>0.3091</v>
       </c>
       <c r="J380" t="n">
-        <v>2.15058054977104</v>
+        <v>6.182</v>
       </c>
     </row>
     <row r="381">
@@ -18521,10 +18509,10 @@
         <v>1.04</v>
       </c>
       <c r="I381" t="n">
-        <v>0.03709467600825313</v>
+        <v>0.0406</v>
       </c>
       <c r="J381" t="n">
-        <v>0.7418935201650625</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="382">
@@ -18561,10 +18549,10 @@
         <v>1.52</v>
       </c>
       <c r="I382" t="n">
-        <v>0.3916679089892649</v>
+        <v>1.2262</v>
       </c>
       <c r="J382" t="n">
-        <v>7.441690270796033</v>
+        <v>23.2978</v>
       </c>
     </row>
     <row r="383">
@@ -18601,10 +18589,10 @@
         <v>1.46</v>
       </c>
       <c r="I383" t="n">
-        <v>0.3456064733982575</v>
+        <v>1.1043</v>
       </c>
       <c r="J383" t="n">
-        <v>6.566522994566892</v>
+        <v>20.9817</v>
       </c>
     </row>
     <row r="384">
@@ -18641,10 +18629,10 @@
         <v>1.16</v>
       </c>
       <c r="I384" t="n">
-        <v>0.1209689594876049</v>
+        <v>0.3658</v>
       </c>
       <c r="J384" t="n">
-        <v>2.298410230264493</v>
+        <v>6.9502</v>
       </c>
     </row>
     <row r="385">
@@ -18681,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I385" t="n">
-        <v>0.09698967599793368</v>
+        <v>0.2865</v>
       </c>
       <c r="J385" t="n">
-        <v>1.84280384396074</v>
+        <v>5.4435</v>
       </c>
     </row>
     <row r="386">
@@ -18721,10 +18709,10 @@
         <v>1.1</v>
       </c>
       <c r="I386" t="n">
-        <v>0.07289829334708259</v>
+        <v>0.2043</v>
       </c>
       <c r="J386" t="n">
-        <v>1.385067573594569</v>
+        <v>3.8817</v>
       </c>
     </row>
     <row r="387">
@@ -18761,10 +18749,10 @@
         <v>1.28</v>
       </c>
       <c r="I387" t="n">
-        <v>0.09855016308819745</v>
+        <v>0.5384</v>
       </c>
       <c r="J387" t="n">
-        <v>1.872453098675751</v>
+        <v>10.2296</v>
       </c>
     </row>
     <row r="388">
@@ -18801,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.2080661543280768</v>
+        <v>0.063</v>
       </c>
       <c r="J388" t="n">
-        <v>-3.95325693223346</v>
+        <v>1.197</v>
       </c>
     </row>
     <row r="389">
@@ -18841,10 +18829,10 @@
         <v>0.77</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.522065803207203</v>
+        <v>-0.393</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.919250260936856</v>
+        <v>-7.467</v>
       </c>
     </row>
     <row r="390">
@@ -18881,10 +18869,10 @@
         <v>0.75</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.5506551711826657</v>
+        <v>-0.4225</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.46244825247065</v>
+        <v>-8.0275</v>
       </c>
     </row>
     <row r="391">
@@ -18921,10 +18909,10 @@
         <v>0.58</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.7907560630213759</v>
+        <v>-0.65</v>
       </c>
       <c r="J391" t="n">
-        <v>-15.02436519740614</v>
+        <v>-12.35</v>
       </c>
     </row>
     <row r="392">
@@ -18961,10 +18949,10 @@
         <v>1.36</v>
       </c>
       <c r="I392" t="n">
-        <v>0.1440685583498091</v>
+        <v>0.6672</v>
       </c>
       <c r="J392" t="n">
-        <v>2.305096933596946</v>
+        <v>10.6752</v>
       </c>
     </row>
     <row r="393">
@@ -19001,10 +18989,10 @@
         <v>0.77</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.5251902305612669</v>
+        <v>-0.3673</v>
       </c>
       <c r="J393" t="n">
-        <v>-8.40304368898027</v>
+        <v>-5.8768</v>
       </c>
     </row>
     <row r="394">
@@ -19041,10 +19029,10 @@
         <v>0.7</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.6122009532308105</v>
+        <v>-0.4739</v>
       </c>
       <c r="J394" t="n">
-        <v>-9.795215251692968</v>
+        <v>-7.5824</v>
       </c>
     </row>
     <row r="395">
@@ -19081,10 +19069,10 @@
         <v>0.63</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.7006372752933497</v>
+        <v>-0.571</v>
       </c>
       <c r="J395" t="n">
-        <v>-11.2101964046936</v>
+        <v>-9.135999999999999</v>
       </c>
     </row>
     <row r="396">
@@ -19121,10 +19109,10 @@
         <v>0.6</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.738307353094271</v>
+        <v>-0.6107</v>
       </c>
       <c r="J396" t="n">
-        <v>-11.81291764950834</v>
+        <v>-9.7712</v>
       </c>
     </row>
     <row r="397">
@@ -19161,10 +19149,10 @@
         <v>1.74</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6030133697931264</v>
+        <v>1.6003</v>
       </c>
       <c r="J397" t="n">
-        <v>9.648213916690022</v>
+        <v>25.6048</v>
       </c>
     </row>
     <row r="398">
@@ -19201,10 +19189,10 @@
         <v>1.64</v>
       </c>
       <c r="I398" t="n">
-        <v>0.5252022823782858</v>
+        <v>1.4162</v>
       </c>
       <c r="J398" t="n">
-        <v>8.403236518052573</v>
+        <v>22.6592</v>
       </c>
     </row>
     <row r="399">
@@ -19241,10 +19229,10 @@
         <v>1.22</v>
       </c>
       <c r="I399" t="n">
-        <v>0.1924587396853223</v>
+        <v>0.4769</v>
       </c>
       <c r="J399" t="n">
-        <v>3.079339834965158</v>
+        <v>7.6304</v>
       </c>
     </row>
     <row r="400">
@@ -19281,10 +19269,10 @@
         <v>1.14</v>
       </c>
       <c r="I400" t="n">
-        <v>0.1248336541928697</v>
+        <v>0.2791</v>
       </c>
       <c r="J400" t="n">
-        <v>1.997338467085915</v>
+        <v>4.4656</v>
       </c>
     </row>
     <row r="401">
@@ -19321,10 +19309,10 @@
         <v>1.09</v>
       </c>
       <c r="I401" t="n">
-        <v>0.08262914453116306</v>
+        <v>0.1455</v>
       </c>
       <c r="J401" t="n">
-        <v>1.322066312498609</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="402">
@@ -19361,10 +19349,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>0.4133533464438343</v>
+        <v>0.8111</v>
       </c>
       <c r="J402" t="n">
-        <v>12.40060039331503</v>
+        <v>24.333</v>
       </c>
     </row>
     <row r="403">
@@ -19401,10 +19389,10 @@
         <v>1.18</v>
       </c>
       <c r="I403" t="n">
-        <v>0.1064637371507238</v>
+        <v>0.3679</v>
       </c>
       <c r="J403" t="n">
-        <v>3.193912114521713</v>
+        <v>11.037</v>
       </c>
     </row>
     <row r="404">
@@ -19441,10 +19429,10 @@
         <v>0.82</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2938373749132905</v>
+        <v>-0.3444</v>
       </c>
       <c r="J404" t="n">
-        <v>-8.815121247398716</v>
+        <v>-10.332</v>
       </c>
     </row>
     <row r="405">
@@ -19481,10 +19469,10 @@
         <v>0.76</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3713784342072236</v>
+        <v>-0.4315</v>
       </c>
       <c r="J405" t="n">
-        <v>-11.14135302621671</v>
+        <v>-12.945</v>
       </c>
     </row>
     <row r="406">
@@ -19521,10 +19509,10 @@
         <v>0.52</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6683096693959903</v>
+        <v>-0.736</v>
       </c>
       <c r="J406" t="n">
-        <v>-20.04929008187971</v>
+        <v>-22.08</v>
       </c>
     </row>
     <row r="407">
@@ -19561,10 +19549,10 @@
         <v>1.64</v>
       </c>
       <c r="I407" t="n">
-        <v>0.4509558812706277</v>
+        <v>1.5236</v>
       </c>
       <c r="J407" t="n">
-        <v>13.52867643811883</v>
+        <v>45.708</v>
       </c>
     </row>
     <row r="408">
@@ -19601,10 +19589,10 @@
         <v>1.3</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1953016094757447</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J408" t="n">
-        <v>5.859048284272341</v>
+        <v>24.813</v>
       </c>
     </row>
     <row r="409">
@@ -19641,10 +19629,10 @@
         <v>1.07</v>
       </c>
       <c r="I409" t="n">
-        <v>0.02284034985793875</v>
+        <v>0.1783</v>
       </c>
       <c r="J409" t="n">
-        <v>0.6852104957381625</v>
+        <v>5.349</v>
       </c>
     </row>
     <row r="410">
@@ -19681,10 +19669,10 @@
         <v>0.97</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.09827438334601579</v>
+        <v>-0.2376</v>
       </c>
       <c r="J410" t="n">
-        <v>-2.948231500380474</v>
+        <v>-7.128</v>
       </c>
     </row>
     <row r="411">
@@ -19721,10 +19709,10 @@
         <v>0.71</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.4572274332063507</v>
+        <v>-0.9202</v>
       </c>
       <c r="J411" t="n">
-        <v>-13.71682299619052</v>
+        <v>-27.606</v>
       </c>
     </row>
     <row r="412">
@@ -19761,10 +19749,10 @@
         <v>1.23</v>
       </c>
       <c r="I412" t="n">
-        <v>0.1899114100710561</v>
+        <v>0.6702</v>
       </c>
       <c r="J412" t="n">
-        <v>5.507430892060626</v>
+        <v>19.4358</v>
       </c>
     </row>
     <row r="413">
@@ -19801,10 +19789,10 @@
         <v>1.2</v>
       </c>
       <c r="I413" t="n">
-        <v>0.1612552206679025</v>
+        <v>0.5939</v>
       </c>
       <c r="J413" t="n">
-        <v>4.676401399369172</v>
+        <v>17.2231</v>
       </c>
     </row>
     <row r="414">
@@ -19841,10 +19829,10 @@
         <v>1.07</v>
       </c>
       <c r="I414" t="n">
-        <v>0.04789285956249265</v>
+        <v>0.1894</v>
       </c>
       <c r="J414" t="n">
-        <v>1.388892927312287</v>
+        <v>5.4926</v>
       </c>
     </row>
     <row r="415">
@@ -19881,10 +19869,10 @@
         <v>1.05</v>
       </c>
       <c r="I415" t="n">
-        <v>0.02948938157849989</v>
+        <v>0.1228</v>
       </c>
       <c r="J415" t="n">
-        <v>0.8551920657764969</v>
+        <v>3.5612</v>
       </c>
     </row>
     <row r="416">
@@ -19921,10 +19909,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.02948938157849989</v>
+        <v>0.1228</v>
       </c>
       <c r="J416" t="n">
-        <v>0.8551920657764969</v>
+        <v>3.5612</v>
       </c>
     </row>
     <row r="417">
@@ -19961,10 +19949,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.2031209529393156</v>
+        <v>0.5332</v>
       </c>
       <c r="J417" t="n">
-        <v>5.890507635240153</v>
+        <v>15.4628</v>
       </c>
     </row>
     <row r="418">
@@ -20001,10 +19989,10 @@
         <v>1.21</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1038973382587164</v>
+        <v>0.3979</v>
       </c>
       <c r="J418" t="n">
-        <v>3.013022809502775</v>
+        <v>11.5391</v>
       </c>
     </row>
     <row r="419">
@@ -20041,10 +20029,10 @@
         <v>1</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.1147165357694166</v>
+        <v>0</v>
       </c>
       <c r="J419" t="n">
-        <v>-3.326779537313083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -20081,10 +20069,10 @@
         <v>0.76</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3990851104778521</v>
+        <v>-0.4399</v>
       </c>
       <c r="J420" t="n">
-        <v>-11.57346820385771</v>
+        <v>-12.7571</v>
       </c>
     </row>
     <row r="421">
@@ -20121,10 +20109,10 @@
         <v>0.72</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4468515034734771</v>
+        <v>-0.494</v>
       </c>
       <c r="J421" t="n">
-        <v>-12.95869360073084</v>
+        <v>-14.326</v>
       </c>
     </row>
     <row r="422">
@@ -20161,10 +20149,10 @@
         <v>1.77</v>
       </c>
       <c r="I422" t="n">
-        <v>0.7231060194351797</v>
+        <v>1.6506</v>
       </c>
       <c r="J422" t="n">
-        <v>13.73901436926841</v>
+        <v>31.3614</v>
       </c>
     </row>
     <row r="423">
@@ -20201,10 +20189,10 @@
         <v>1.37</v>
       </c>
       <c r="I423" t="n">
-        <v>0.3449528472981684</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J423" t="n">
-        <v>6.5541040986652</v>
+        <v>15.8498</v>
       </c>
     </row>
     <row r="424">
@@ -20241,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.3368093509942058</v>
+        <v>0.8071</v>
       </c>
       <c r="J424" t="n">
-        <v>6.399377668889911</v>
+        <v>15.3349</v>
       </c>
     </row>
     <row r="425">
@@ -20281,10 +20269,10 @@
         <v>1.26</v>
       </c>
       <c r="I425" t="n">
-        <v>0.2407111602576602</v>
+        <v>0.5685</v>
       </c>
       <c r="J425" t="n">
-        <v>4.573512044895542</v>
+        <v>10.8015</v>
       </c>
     </row>
     <row r="426">
@@ -20321,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.08828481642237913</v>
+        <v>0.1979</v>
       </c>
       <c r="J426" t="n">
-        <v>1.677411512025204</v>
+        <v>3.7601</v>
       </c>
     </row>
     <row r="427">
@@ -20361,10 +20349,10 @@
         <v>1.06</v>
       </c>
       <c r="I427" t="n">
-        <v>0.01718196857663944</v>
+        <v>0.2846</v>
       </c>
       <c r="J427" t="n">
-        <v>0.3264574029561493</v>
+        <v>5.4074</v>
       </c>
     </row>
     <row r="428">
@@ -20401,10 +20389,10 @@
         <v>0.82</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.2493742909550666</v>
+        <v>-0.2031</v>
       </c>
       <c r="J428" t="n">
-        <v>-4.738111528146266</v>
+        <v>-3.8589</v>
       </c>
     </row>
     <row r="429">
@@ -20441,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.4023211984867978</v>
+        <v>-0.4646</v>
       </c>
       <c r="J429" t="n">
-        <v>-7.644102771249159</v>
+        <v>-8.827400000000001</v>
       </c>
     </row>
     <row r="430">
@@ -20481,10 +20469,10 @@
         <v>0.51</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.5722731368597794</v>
+        <v>-0.6967</v>
       </c>
       <c r="J430" t="n">
-        <v>-10.87318960033581</v>
+        <v>-13.2373</v>
       </c>
     </row>
     <row r="431">
@@ -20521,10 +20509,10 @@
         <v>0.4</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.6891234322436582</v>
+        <v>-0.8361</v>
       </c>
       <c r="J431" t="n">
-        <v>-13.09334521262951</v>
+        <v>-15.8859</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>5.1445</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.9801</v>
       </c>
       <c r="D2" t="n">
         <v>1.6569</v>
@@ -545,7 +545,7 @@
         <v>5.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.9564</v>
       </c>
       <c r="D3" t="n">
         <v>1.6066</v>
@@ -591,7 +591,7 @@
         <v>4.9177</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.9369</v>
       </c>
       <c r="D4" t="n">
         <v>1.5653</v>
@@ -637,7 +637,7 @@
         <v>4.5864</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.8738</v>
       </c>
       <c r="D5" t="n">
         <v>1.4314</v>
@@ -683,7 +683,7 @@
         <v>4.4351</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.845</v>
       </c>
       <c r="D6" t="n">
         <v>1.3703</v>
@@ -729,7 +729,7 @@
         <v>4.1209</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.7851</v>
       </c>
       <c r="D7" t="n">
         <v>1.2434</v>
@@ -775,7 +775,7 @@
         <v>3.7879</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.7217</v>
       </c>
       <c r="D8" t="n">
         <v>1.1089</v>
@@ -821,7 +821,7 @@
         <v>3.7249</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.7097</v>
       </c>
       <c r="D9" t="n">
         <v>1.0834</v>
@@ -867,7 +867,7 @@
         <v>2.8066</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.5347</v>
       </c>
       <c r="D10" t="n">
         <v>0.7124</v>
@@ -913,7 +913,7 @@
         <v>2.6674</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.5082</v>
       </c>
       <c r="D11" t="n">
         <v>0.6562</v>
@@ -959,7 +959,7 @@
         <v>2.566</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.4889</v>
       </c>
       <c r="D12" t="n">
         <v>0.6152</v>
@@ -1005,7 +1005,7 @@
         <v>2.0219</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.3852</v>
       </c>
       <c r="D13" t="n">
         <v>0.3954</v>
@@ -1051,7 +1051,7 @@
         <v>1.9313</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="D14" t="n">
         <v>0.3588</v>
@@ -1097,7 +1097,7 @@
         <v>1.9054</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="D15" t="n">
         <v>0.3484</v>
@@ -1143,7 +1143,7 @@
         <v>1.7076</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.3253</v>
       </c>
       <c r="D16" t="n">
         <v>0.2685</v>
@@ -1189,7 +1189,7 @@
         <v>1.6762</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3194</v>
       </c>
       <c r="D17" t="n">
         <v>0.2558</v>
@@ -1235,7 +1235,7 @@
         <v>1.6414</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3127</v>
       </c>
       <c r="D18" t="n">
         <v>0.2417</v>
@@ -1281,7 +1281,7 @@
         <v>1.4231</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.2711</v>
       </c>
       <c r="D19" t="n">
         <v>0.1535</v>
@@ -1327,7 +1327,7 @@
         <v>1.4223</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="D20" t="n">
         <v>0.1532</v>
@@ -1373,7 +1373,7 @@
         <v>1.2901</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.2458</v>
       </c>
       <c r="D21" t="n">
         <v>0.0998</v>
@@ -1419,7 +1419,7 @@
         <v>1.194</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="D22" t="n">
         <v>0.061</v>
@@ -1465,7 +1465,7 @@
         <v>1.1936</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.2274</v>
       </c>
       <c r="D23" t="n">
         <v>0.0608</v>
@@ -1511,7 +1511,7 @@
         <v>1.1472</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2186</v>
       </c>
       <c r="D24" t="n">
         <v>0.0421</v>
@@ -1557,7 +1557,7 @@
         <v>1.0824</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2062</v>
       </c>
       <c r="D25" t="n">
         <v>0.0159</v>
@@ -1603,7 +1603,7 @@
         <v>1.0306</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.1964</v>
       </c>
       <c r="D26" t="n">
         <v>-0.005</v>
@@ -1649,7 +1649,7 @@
         <v>0.9981</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.1902</v>
       </c>
       <c r="D27" t="n">
         <v>-0.0182</v>
@@ -1695,7 +1695,7 @@
         <v>0.971</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="D28" t="n">
         <v>-0.0291</v>
@@ -1741,7 +1741,7 @@
         <v>0.9643</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1837</v>
       </c>
       <c r="D29" t="n">
         <v>-0.0318</v>
@@ -1787,7 +1787,7 @@
         <v>0.9095</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1733</v>
       </c>
       <c r="D30" t="n">
         <v>-0.0539</v>
@@ -1833,7 +1833,7 @@
         <v>0.8371</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1595</v>
       </c>
       <c r="D31" t="n">
         <v>-0.0832</v>
@@ -1879,7 +1879,7 @@
         <v>0.742</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.1414</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1216</v>
@@ -1925,7 +1925,7 @@
         <v>0.6647999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.1267</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1528</v>
@@ -1971,7 +1971,7 @@
         <v>0.6161</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1174</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1725</v>
@@ -2017,7 +2017,7 @@
         <v>0.4942</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>-0.2217</v>
@@ -2063,7 +2063,7 @@
         <v>0.4713</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.0898</v>
       </c>
       <c r="D36" t="n">
         <v>-0.231</v>
@@ -2109,7 +2109,7 @@
         <v>0.4681</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.0892</v>
       </c>
       <c r="D37" t="n">
         <v>-0.2323</v>
@@ -2155,7 +2155,7 @@
         <v>0.4314</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.0822</v>
       </c>
       <c r="D38" t="n">
         <v>-0.2471</v>
@@ -2201,7 +2201,7 @@
         <v>0.4081</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>-0.2565</v>
@@ -2247,7 +2247,7 @@
         <v>0.201</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.0383</v>
       </c>
       <c r="D40" t="n">
         <v>-0.3402</v>
@@ -2293,7 +2293,7 @@
         <v>-0.1123</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.0214</v>
       </c>
       <c r="D41" t="n">
         <v>-0.4667</v>
@@ -2339,7 +2339,7 @@
         <v>-0.1433</v>
       </c>
       <c r="C42" t="n">
-        <v>-0</v>
+        <v>-0.0273</v>
       </c>
       <c r="D42" t="n">
         <v>-0.4793</v>
@@ -2385,7 +2385,7 @@
         <v>-0.1754</v>
       </c>
       <c r="C43" t="n">
-        <v>-0</v>
+        <v>-0.0334</v>
       </c>
       <c r="D43" t="n">
         <v>-0.4922</v>
@@ -2431,7 +2431,7 @@
         <v>-0.2227</v>
       </c>
       <c r="C44" t="n">
-        <v>-0</v>
+        <v>-0.0424</v>
       </c>
       <c r="D44" t="n">
         <v>-0.5113</v>
@@ -2477,7 +2477,7 @@
         <v>-0.4178</v>
       </c>
       <c r="C45" t="n">
-        <v>-0</v>
+        <v>-0.0796</v>
       </c>
       <c r="D45" t="n">
         <v>-0.5901</v>
@@ -2523,7 +2523,7 @@
         <v>-0.4308</v>
       </c>
       <c r="C46" t="n">
-        <v>-0</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="D46" t="n">
         <v>-0.5954</v>
@@ -2569,7 +2569,7 @@
         <v>-0.6264</v>
       </c>
       <c r="C47" t="n">
-        <v>-0</v>
+        <v>-0.1193</v>
       </c>
       <c r="D47" t="n">
         <v>-0.6744</v>
@@ -2615,7 +2615,7 @@
         <v>-0.7042</v>
       </c>
       <c r="C48" t="n">
-        <v>-0</v>
+        <v>-0.1342</v>
       </c>
       <c r="D48" t="n">
         <v>-0.7058</v>
@@ -2661,7 +2661,7 @@
         <v>-0.7707000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.1468</v>
       </c>
       <c r="D49" t="n">
         <v>-0.7327</v>
@@ -2707,7 +2707,7 @@
         <v>-0.854</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.1627</v>
       </c>
       <c r="D50" t="n">
         <v>-0.7664</v>
@@ -2753,7 +2753,7 @@
         <v>-1.1524</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.2196</v>
       </c>
       <c r="D51" t="n">
         <v>-0.8869</v>
@@ -2799,7 +2799,7 @@
         <v>-1.1832</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.2254</v>
       </c>
       <c r="D52" t="n">
         <v>-0.8993</v>
@@ -2845,7 +2845,7 @@
         <v>-1.1941</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.2275</v>
       </c>
       <c r="D53" t="n">
         <v>-0.9038</v>
@@ -2891,7 +2891,7 @@
         <v>-1.2537</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.2389</v>
       </c>
       <c r="D54" t="n">
         <v>-0.9278</v>
@@ -2937,7 +2937,7 @@
         <v>-1.2791</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.2437</v>
       </c>
       <c r="D55" t="n">
         <v>-0.9381</v>
@@ -2983,7 +2983,7 @@
         <v>-1.3221</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2519</v>
       </c>
       <c r="D56" t="n">
         <v>-0.9555</v>
@@ -3029,7 +3029,7 @@
         <v>-1.8367</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.3499</v>
       </c>
       <c r="D57" t="n">
         <v>-1.1633</v>
@@ -3075,7 +3075,7 @@
         <v>-2.0056</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.3821</v>
       </c>
       <c r="D58" t="n">
         <v>-1.2316</v>
@@ -3121,7 +3121,7 @@
         <v>-2.0475</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.3901</v>
       </c>
       <c r="D59" t="n">
         <v>-1.2485</v>
@@ -3167,7 +3167,7 @@
         <v>-3.3092</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="D60" t="n">
         <v>-1.7582</v>
@@ -3213,7 +3213,7 @@
         <v>-3.5693</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.68</v>
       </c>
       <c r="D61" t="n">
         <v>-1.8633</v>

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1445</v>
+        <v>5.5163</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9801</v>
+        <v>1.051</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6569</v>
+        <v>1.7538</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1445</v>
+        <v>5.5163</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0291</v>
+        <v>2.4361</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1154</v>
+        <v>3.0802</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0291</v>
+        <v>2.4361</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6447</v>
+        <v>2.4566</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1154</v>
+        <v>3.0802</v>
       </c>
       <c r="K2" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>4.7601</v>
+        <v>5.536799999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.02</v>
+        <v>5.3871</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9564</v>
+        <v>1.0264</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6066</v>
+        <v>1.7023</v>
       </c>
       <c r="E3" t="n">
-        <v>5.02</v>
+        <v>5.3871</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1713</v>
+        <v>2.2717</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8487</v>
+        <v>3.1154</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2216</v>
+        <v>2.2717</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4218</v>
+        <v>1.8413</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8487</v>
+        <v>3.1154</v>
       </c>
       <c r="K3" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2705</v>
+        <v>4.9567</v>
       </c>
       <c r="N3" t="n">
-        <v>136</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9177</v>
+        <v>5.3686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9369</v>
+        <v>1.0228</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5653</v>
+        <v>1.6949</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9177</v>
+        <v>5.3686</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7926</v>
+        <v>4.2435</v>
       </c>
       <c r="G4" t="n">
         <v>1.1251</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7926</v>
+        <v>4.5122</v>
       </c>
       <c r="I4" t="n">
-        <v>3.074</v>
+        <v>3.6573</v>
       </c>
       <c r="J4" t="n">
         <v>1.1251</v>
@@ -621,7 +621,7 @@
         <v>147</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1991</v>
+        <v>4.7824</v>
       </c>
       <c r="N4" t="n">
         <v>259</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5864</v>
+        <v>5.3086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8738</v>
+        <v>1.0114</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4314</v>
+        <v>1.671</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5864</v>
+        <v>5.3086</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5062</v>
+        <v>4.4599</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0802</v>
+        <v>0.8487</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5062</v>
+        <v>5.3828</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5132</v>
+        <v>4.3629</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0802</v>
+        <v>0.8487</v>
       </c>
       <c r="K5" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5934</v>
+        <v>5.2116</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4351</v>
+        <v>4.7274</v>
       </c>
       <c r="C6" t="n">
-        <v>0.845</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3703</v>
+        <v>1.4395</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4351</v>
+        <v>4.7274</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3587</v>
+        <v>1.651</v>
       </c>
       <c r="G6" t="n">
         <v>3.0764</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3587</v>
+        <v>1.651</v>
       </c>
       <c r="I6" t="n">
-        <v>1.365</v>
+        <v>1.6649</v>
       </c>
       <c r="J6" t="n">
         <v>3.0764</v>
@@ -713,7 +713,7 @@
         <v>150</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4414</v>
+        <v>4.7413</v>
       </c>
       <c r="N6" t="n">
         <v>255</v>
@@ -722,415 +722,415 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1209</v>
+        <v>4.5504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7851</v>
+        <v>0.8669</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2434</v>
+        <v>1.369</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1209</v>
+        <v>4.5504</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3328</v>
+        <v>4.2533</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7881</v>
+        <v>0.2971</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3328</v>
+        <v>4.5516</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3328</v>
+        <v>3.6892</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7881</v>
+        <v>0.2971</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L7" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1209</v>
+        <v>3.9863</v>
       </c>
       <c r="N7" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7879</v>
+        <v>4.4302</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7217</v>
+        <v>0.844</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1089</v>
+        <v>1.3211</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7879</v>
+        <v>4.4302</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4908</v>
+        <v>3.2365</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2971</v>
+        <v>1.1937</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4908</v>
+        <v>3.2365</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8294</v>
+        <v>3.2365</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2971</v>
+        <v>1.1937</v>
       </c>
       <c r="K8" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1265</v>
+        <v>4.4302</v>
       </c>
       <c r="N8" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7249</v>
+        <v>4.1209</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7097</v>
+        <v>0.7851</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0834</v>
+        <v>1.1979</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7249</v>
+        <v>4.1209</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5556</v>
+        <v>1.3328</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8307</v>
+        <v>2.7881</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7676</v>
+        <v>1.3328</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6748</v>
+        <v>1.3328</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8307</v>
+        <v>2.7881</v>
       </c>
       <c r="K9" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8441</v>
+        <v>4.1209</v>
       </c>
       <c r="N9" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8066</v>
+        <v>4.0356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5347</v>
+        <v>0.7689</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7124</v>
+        <v>1.1639</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8066</v>
+        <v>4.0356</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6129</v>
+        <v>4.8663</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1937</v>
+        <v>-0.8307</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6129</v>
+        <v>7.3489</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6129</v>
+        <v>5.9565</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1937</v>
+        <v>-0.8307</v>
       </c>
       <c r="K10" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L10" t="n">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8066</v>
+        <v>5.1258</v>
       </c>
       <c r="N10" t="n">
-        <v>249</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6674</v>
+        <v>3.98</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5082</v>
+        <v>0.7583</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6562</v>
+        <v>1.1417</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6674</v>
+        <v>3.98</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6102</v>
+        <v>3.8344</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0572</v>
+        <v>0.1456</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6102</v>
+        <v>3.8344</v>
       </c>
       <c r="I11" t="n">
-        <v>0.613</v>
+        <v>3.8344</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0572</v>
+        <v>0.1456</v>
       </c>
       <c r="K11" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6702</v>
+        <v>3.98</v>
       </c>
       <c r="N11" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.566</v>
+        <v>3.0257</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4889</v>
+        <v>0.5765</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6152</v>
+        <v>0.7615</v>
       </c>
       <c r="E12" t="n">
-        <v>2.566</v>
+        <v>3.0257</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4204</v>
+        <v>3.5632</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1456</v>
+        <v>-0.5375</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4204</v>
+        <v>3.5632</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4204</v>
+        <v>3.5632</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1456</v>
+        <v>-0.5375</v>
       </c>
       <c r="K12" t="n">
         <v>101</v>
       </c>
       <c r="L12" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
-        <v>2.566</v>
+        <v>3.0257</v>
       </c>
       <c r="N12" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0219</v>
+        <v>3.0162</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3852</v>
+        <v>0.5746</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3954</v>
+        <v>0.7577</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0219</v>
+        <v>3.0162</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0219</v>
+        <v>0.959</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.0572</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0219</v>
+        <v>0.959</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0219</v>
+        <v>0.9671</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2.0572</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0219</v>
+        <v>3.0243</v>
       </c>
       <c r="N13" t="n">
-        <v>98</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9313</v>
+        <v>2.7809</v>
       </c>
       <c r="C14" t="n">
-        <v>0.368</v>
+        <v>0.5298</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3588</v>
+        <v>0.664</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9313</v>
+        <v>2.7809</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0288</v>
+        <v>2.7809</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0975</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0288</v>
+        <v>2.7809</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0288</v>
+        <v>2.7809</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0975</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9313</v>
+        <v>2.7809</v>
       </c>
       <c r="N14" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="C15" t="n">
-        <v>0.363</v>
+        <v>0.4534</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3484</v>
+        <v>0.5042</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9054</v>
+        <v>2.3799</v>
       </c>
       <c r="N15" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3253</v>
+        <v>0.4335</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2685</v>
+        <v>0.4626</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7076</v>
+        <v>2.2754</v>
       </c>
       <c r="N16" t="n">
         <v>103</v>
@@ -1182,219 +1182,219 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6762</v>
+        <v>2.2429</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3194</v>
+        <v>0.4273</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2558</v>
+        <v>0.4497</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6762</v>
+        <v>2.2429</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6762</v>
+        <v>2.8512</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6762</v>
+        <v>2.8512</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6762</v>
+        <v>2.8752</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6762</v>
+        <v>2.2669</v>
       </c>
       <c r="N17" t="n">
-        <v>106</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6414</v>
+        <v>2.2122</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3127</v>
+        <v>0.4215</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2417</v>
+        <v>0.4374</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6414</v>
+        <v>2.2122</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1477</v>
+        <v>1.7512</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4937</v>
+        <v>0.461</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1477</v>
+        <v>1.7512</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1484</v>
+        <v>1.7512</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4937</v>
+        <v>0.461</v>
       </c>
       <c r="K18" t="n">
         <v>101</v>
       </c>
       <c r="L18" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6421</v>
+        <v>2.2122</v>
       </c>
       <c r="N18" t="n">
-        <v>169</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4231</v>
+        <v>2.1411</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2711</v>
+        <v>0.4079</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1535</v>
+        <v>0.4091</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4231</v>
+        <v>2.1411</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8719</v>
+        <v>2.1411</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8719</v>
+        <v>2.1411</v>
       </c>
       <c r="I19" t="n">
-        <v>0.876</v>
+        <v>2.1411</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4272</v>
+        <v>2.1411</v>
       </c>
       <c r="N19" t="n">
-        <v>255</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4223</v>
+        <v>2.1321</v>
       </c>
       <c r="C20" t="n">
-        <v>0.271</v>
+        <v>0.4062</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1532</v>
+        <v>0.4055</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4223</v>
+        <v>2.1321</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9613</v>
+        <v>2.2296</v>
       </c>
       <c r="G20" t="n">
-        <v>0.461</v>
+        <v>-0.0975</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9613</v>
+        <v>2.2296</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9613</v>
+        <v>2.2296</v>
       </c>
       <c r="J20" t="n">
-        <v>0.461</v>
+        <v>-0.0975</v>
       </c>
       <c r="K20" t="n">
         <v>101</v>
       </c>
       <c r="L20" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4223</v>
+        <v>2.1321</v>
       </c>
       <c r="N20" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2901</v>
+        <v>2.1016</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2458</v>
+        <v>0.4004</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0998</v>
+        <v>0.3934</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2901</v>
+        <v>2.1016</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8984</v>
+        <v>2.0487</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6083</v>
+        <v>0.0529</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8984</v>
+        <v>2.0487</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9072</v>
+        <v>2.0659</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6083</v>
+        <v>0.0529</v>
       </c>
       <c r="K21" t="n">
         <v>101</v>
@@ -1403,7 +1403,7 @@
         <v>68</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2989</v>
+        <v>2.1188</v>
       </c>
       <c r="N21" t="n">
         <v>169</v>
@@ -1412,231 +1412,231 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.194</v>
+        <v>2.0993</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2275</v>
+        <v>0.4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.061</v>
+        <v>0.3925</v>
       </c>
       <c r="E22" t="n">
-        <v>1.194</v>
+        <v>2.0993</v>
       </c>
       <c r="F22" t="n">
-        <v>1.823</v>
+        <v>1.5481</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.629</v>
+        <v>0.5512</v>
       </c>
       <c r="H22" t="n">
-        <v>1.823</v>
+        <v>1.5481</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4776</v>
+        <v>1.5611</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.629</v>
+        <v>0.5512</v>
       </c>
       <c r="K22" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L22" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8486</v>
+        <v>2.1123</v>
       </c>
       <c r="N22" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1936</v>
+        <v>2.0395</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2274</v>
+        <v>0.3886</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0608</v>
+        <v>0.3686</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1936</v>
+        <v>2.0395</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5864</v>
+        <v>2.0395</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6072</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5864</v>
+        <v>2.0395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5891</v>
+        <v>2.0395</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6072</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L23" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1963</v>
+        <v>2.0395</v>
       </c>
       <c r="N23" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1472</v>
+        <v>1.9892</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2186</v>
+        <v>0.379</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0421</v>
+        <v>0.3486</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1472</v>
+        <v>1.9892</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1472</v>
+        <v>1.382</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.6072</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1472</v>
+        <v>1.382</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1472</v>
+        <v>1.3936</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.6072</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1472</v>
+        <v>2.0008</v>
       </c>
       <c r="N24" t="n">
-        <v>103</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0824</v>
+        <v>1.9787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2062</v>
+        <v>0.377</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0159</v>
+        <v>0.3444</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0824</v>
+        <v>1.9787</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0824</v>
+        <v>2.0309</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0824</v>
+        <v>2.0309</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0824</v>
+        <v>2.0309</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.0522</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0824</v>
+        <v>1.9787</v>
       </c>
       <c r="N25" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0306</v>
+        <v>1.8997</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1964</v>
+        <v>0.3619</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.005</v>
+        <v>0.3129</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0306</v>
+        <v>1.8997</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5681</v>
+        <v>2.5287</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5375</v>
+        <v>-0.629</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5681</v>
+        <v>2.5287</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5681</v>
+        <v>2.0496</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5375</v>
+        <v>-0.629</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0306</v>
+        <v>1.4206</v>
       </c>
       <c r="N26" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9981</v>
+        <v>1.7403</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1902</v>
+        <v>0.3316</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0182</v>
+        <v>0.2494</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9981</v>
+        <v>1.7403</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5584</v>
+        <v>2.3006</v>
       </c>
       <c r="G27" t="n">
         <v>-0.5603</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5584</v>
+        <v>2.3006</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5584</v>
+        <v>2.3006</v>
       </c>
       <c r="J27" t="n">
         <v>-0.5603</v>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9981</v>
+        <v>1.7403</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.971</v>
+        <v>1.74</v>
       </c>
       <c r="C28" t="n">
-        <v>0.185</v>
+        <v>0.3315</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0291</v>
+        <v>0.2493</v>
       </c>
       <c r="E28" t="n">
-        <v>0.971</v>
+        <v>1.74</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0232</v>
+        <v>0.2463</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0522</v>
+        <v>1.4937</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0232</v>
+        <v>0.2463</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0232</v>
+        <v>0.2484</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0522</v>
+        <v>1.4937</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9710000000000001</v>
+        <v>1.7421</v>
       </c>
       <c r="N28" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9643</v>
+        <v>1.7208</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1837</v>
+        <v>0.3278</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0318</v>
+        <v>0.2417</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9643</v>
+        <v>1.7208</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9643</v>
+        <v>2.7208</v>
       </c>
       <c r="G29" t="n">
         <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9643</v>
+        <v>2.7208</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5921</v>
+        <v>2.2053</v>
       </c>
       <c r="J29" t="n">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5921000000000001</v>
+        <v>1.2053</v>
       </c>
       <c r="N29" t="n">
         <v>136</v>
@@ -1780,1013 +1780,1013 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1733</v>
+        <v>0.3269</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0539</v>
+        <v>0.2397</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9095</v>
+        <v>1.7159</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8371</v>
+        <v>1.0773</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1595</v>
+        <v>0.2052</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0832</v>
+        <v>-0.0147</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8371</v>
+        <v>1.0773</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7842</v>
+        <v>1.0773</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0529</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7842</v>
+        <v>1.0773</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.0773</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0529</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="L31" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8407</v>
+        <v>1.0773</v>
       </c>
       <c r="N31" t="n">
-        <v>169</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.742</v>
+        <v>0.9822</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1414</v>
+        <v>0.1871</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1216</v>
+        <v>-0.0526</v>
       </c>
       <c r="E32" t="n">
-        <v>0.742</v>
+        <v>0.9822</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9562</v>
+        <v>0.9822</v>
       </c>
       <c r="G32" t="n">
-        <v>1.6982</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9562</v>
+        <v>0.9822</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9562</v>
+        <v>0.9822</v>
       </c>
       <c r="J32" t="n">
-        <v>1.6982</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L32" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7419999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="N32" t="n">
-        <v>249</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1267</v>
+        <v>0.178</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1528</v>
+        <v>-0.0717</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="N33" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1174</v>
+        <v>0.1737</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1725</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6161</v>
+        <v>0.9117</v>
       </c>
       <c r="N34" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="C35" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1641</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2217</v>
+        <v>-0.1008</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4942</v>
+        <v>0.8611</v>
       </c>
       <c r="N35" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4713</v>
+        <v>0.742</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0898</v>
+        <v>0.1414</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.231</v>
+        <v>-0.1483</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4713</v>
+        <v>0.742</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4713</v>
+        <v>-0.9562</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.6982</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4713</v>
+        <v>-0.9562</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4713</v>
+        <v>-0.9562</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1.6982</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4713</v>
+        <v>0.7419999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4681</v>
+        <v>0.6161</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0892</v>
+        <v>0.1174</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2323</v>
+        <v>-0.1985</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4681</v>
+        <v>0.6161</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7149</v>
+        <v>0.6161</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7149</v>
+        <v>0.6161</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7149</v>
+        <v>0.6161</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4681</v>
+        <v>0.6161</v>
       </c>
       <c r="N37" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4314</v>
+        <v>0.541</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0822</v>
+        <v>0.1031</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2471</v>
+        <v>-0.2284</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4314</v>
+        <v>0.541</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2475</v>
+        <v>0.541</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.2475</v>
+        <v>0.541</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8217</v>
+        <v>0.541</v>
       </c>
       <c r="J38" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L38" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8572</v>
+        <v>0.541</v>
       </c>
       <c r="N38" t="n">
-        <v>259</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0953</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2565</v>
+        <v>-0.2446</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4081</v>
+        <v>0.5002</v>
       </c>
       <c r="N39" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.201</v>
+        <v>0.4682</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0383</v>
+        <v>0.0892</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3402</v>
+        <v>-0.2574</v>
       </c>
       <c r="E40" t="n">
-        <v>0.201</v>
+        <v>0.4682</v>
       </c>
       <c r="F40" t="n">
-        <v>0.201</v>
+        <v>0.715</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.2468</v>
       </c>
       <c r="H40" t="n">
-        <v>0.201</v>
+        <v>0.715</v>
       </c>
       <c r="I40" t="n">
-        <v>0.201</v>
+        <v>0.715</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.2468</v>
       </c>
       <c r="K40" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M40" t="n">
-        <v>0.201</v>
+        <v>0.4681999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.1123</v>
+        <v>0.4314</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0214</v>
+        <v>0.0822</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4667</v>
+        <v>-0.272</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1123</v>
+        <v>0.4314</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1123</v>
+        <v>-2.2475</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1123</v>
+        <v>-2.2475</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1123</v>
+        <v>-1.8217</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="K41" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1123</v>
+        <v>0.8572</v>
       </c>
       <c r="N41" t="n">
-        <v>103</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0273</v>
+        <v>0.0183</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4793</v>
+        <v>-0.4057</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1433</v>
+        <v>0.0959</v>
       </c>
       <c r="N42" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0334</v>
+        <v>0.0166</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4922</v>
+        <v>-0.4093</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1754</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0424</v>
+        <v>-0.0124</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5113</v>
+        <v>-0.4699</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.2227</v>
+        <v>-0.0653</v>
       </c>
       <c r="N44" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0796</v>
+        <v>-0.0182</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5901</v>
+        <v>-0.482</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.4178</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0261</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5954</v>
+        <v>-0.4985</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.4308</v>
+        <v>-0.1369</v>
       </c>
       <c r="N46" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1193</v>
+        <v>-0.0328</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6744</v>
+        <v>-0.5124</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.6264</v>
+        <v>-0.1719</v>
       </c>
       <c r="N47" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1342</v>
+        <v>-0.0334</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7058</v>
+        <v>-0.5138</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.7042</v>
+        <v>-0.1754</v>
       </c>
       <c r="N48" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1468</v>
+        <v>-0.1119</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7327</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3886</v>
+        <v>-0.793</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3821</v>
+        <v>0.2058</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.3886</v>
+        <v>-0.793</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3904</v>
+        <v>-0.6428</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3821</v>
+        <v>0.2058</v>
       </c>
       <c r="K49" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="L49" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.7725</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>255</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.854</v>
+        <v>-0.7692</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1627</v>
+        <v>-0.1465</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7664</v>
+        <v>-0.7504</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.854</v>
+        <v>-0.7692</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.854</v>
+        <v>-0.3871</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.854</v>
+        <v>-0.3871</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.854</v>
+        <v>-0.3904</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.3821</v>
       </c>
       <c r="K50" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.854</v>
+        <v>-0.7725</v>
       </c>
       <c r="N50" t="n">
-        <v>110</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.1524</v>
+        <v>-0.854</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2196</v>
+        <v>-0.1627</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8869</v>
+        <v>-0.7841</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.1524</v>
+        <v>-0.854</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.3582</v>
+        <v>-0.854</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2058</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.3582</v>
+        <v>-0.854</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1008</v>
+        <v>-0.854</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2058</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.895</v>
+        <v>-0.854</v>
       </c>
       <c r="N51" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2254</v>
+        <v>-0.2211</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8993</v>
+        <v>-0.9062</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.1832</v>
+        <v>-1.1603</v>
       </c>
       <c r="N52" t="n">
         <v>106</v>
@@ -2848,7 +2848,7 @@
         <v>-0.2275</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9038</v>
+        <v>-0.9196</v>
       </c>
       <c r="E53" t="n">
         <v>-1.1941</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2389</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9278</v>
+        <v>-0.9434</v>
       </c>
       <c r="E54" t="n">
         <v>-1.2537</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2437</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9381</v>
+        <v>-0.9535</v>
       </c>
       <c r="E55" t="n">
         <v>-1.2791</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2519</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9555</v>
+        <v>-0.9706</v>
       </c>
       <c r="E56" t="n">
         <v>-1.3221</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3499</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1633</v>
+        <v>-1.1757</v>
       </c>
       <c r="E57" t="n">
         <v>-1.8367</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3821</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2316</v>
+        <v>-1.2429</v>
       </c>
       <c r="E58" t="n">
         <v>-2.0056</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3901</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2485</v>
+        <v>-1.2596</v>
       </c>
       <c r="E59" t="n">
         <v>-2.0475</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.3092</v>
+        <v>-3.3005</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6288</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.7582</v>
+        <v>-1.7588</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.3092</v>
+        <v>-3.3005</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.3092</v>
+        <v>-2.3005</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.3092</v>
+        <v>-2.3005</v>
       </c>
       <c r="I60" t="n">
         <v>-2.3199</v>
@@ -3216,7 +3216,7 @@
         <v>-0.68</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.8633</v>
+        <v>-1.8659</v>
       </c>
       <c r="E61" t="n">
         <v>-3.5693</v>

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -492,231 +492,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5163</v>
+        <v>5.5089</v>
       </c>
       <c r="C2" t="n">
-        <v>1.051</v>
+        <v>1.0496</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7538</v>
+        <v>1.849</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5163</v>
+        <v>5.5089</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4361</v>
+        <v>2.6538</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0802</v>
+        <v>2.8551</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4361</v>
+        <v>3.864</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4566</v>
+        <v>2.0091</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0802</v>
+        <v>2.8551</v>
       </c>
       <c r="K2" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L2" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>5.536799999999999</v>
+        <v>4.8642</v>
       </c>
       <c r="N2" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3871</v>
+        <v>5.1024</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0264</v>
+        <v>0.9721</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7023</v>
+        <v>1.6655</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3871</v>
+        <v>5.1024</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2717</v>
+        <v>2.4741</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1154</v>
+        <v>2.6283</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2717</v>
+        <v>2.4741</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8413</v>
+        <v>2.5758</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1154</v>
+        <v>2.6283</v>
       </c>
       <c r="K3" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L3" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9567</v>
+        <v>5.2041</v>
       </c>
       <c r="N3" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3686</v>
+        <v>4.6647</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0228</v>
+        <v>0.8887</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6949</v>
+        <v>1.4679</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3686</v>
+        <v>4.6647</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2435</v>
+        <v>3.8421</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1251</v>
+        <v>0.8226</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5122</v>
+        <v>8.0509</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6573</v>
+        <v>4.1861</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1251</v>
+        <v>0.8226</v>
       </c>
       <c r="K4" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7824</v>
+        <v>5.008699999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>259</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3086</v>
+        <v>4.3814</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0114</v>
+        <v>0.8347</v>
       </c>
       <c r="D5" t="n">
-        <v>1.671</v>
+        <v>1.34</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3086</v>
+        <v>4.3814</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4599</v>
+        <v>3.5822</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8487</v>
+        <v>0.7992</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3828</v>
+        <v>7.1351</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3629</v>
+        <v>3.7099</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8487</v>
+        <v>0.7992</v>
       </c>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2116</v>
+        <v>4.5091</v>
       </c>
       <c r="N5" t="n">
-        <v>136</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7274</v>
+        <v>4.3052</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8202</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4395</v>
+        <v>1.3056</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7274</v>
+        <v>4.3052</v>
       </c>
       <c r="F6" t="n">
-        <v>1.651</v>
+        <v>3.0222</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0764</v>
+        <v>1.283</v>
       </c>
       <c r="H6" t="n">
-        <v>1.651</v>
+        <v>3.2765</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6649</v>
+        <v>3.2765</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0764</v>
+        <v>1.283</v>
       </c>
       <c r="K6" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L6" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7413</v>
+        <v>4.5595</v>
       </c>
       <c r="N6" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5504</v>
+        <v>4.289</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8669</v>
+        <v>0.8171</v>
       </c>
       <c r="D7" t="n">
-        <v>1.369</v>
+        <v>1.2983</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5504</v>
+        <v>4.289</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2533</v>
+        <v>3.5535</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2971</v>
+        <v>0.7355</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5516</v>
+        <v>7.0341</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6892</v>
+        <v>3.6574</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2971</v>
+        <v>0.7355</v>
       </c>
       <c r="K7" t="n">
         <v>112</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9863</v>
+        <v>4.3929</v>
       </c>
       <c r="N7" t="n">
         <v>259</v>
@@ -768,173 +768,173 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4302</v>
+        <v>4.2504</v>
       </c>
       <c r="C8" t="n">
-        <v>0.844</v>
+        <v>0.8098</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3211</v>
+        <v>1.2808</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4302</v>
+        <v>4.2504</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2365</v>
+        <v>1.6568</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1937</v>
+        <v>2.5936</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2365</v>
+        <v>1.6568</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2365</v>
+        <v>1.7249</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1937</v>
+        <v>2.5936</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L8" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4302</v>
+        <v>4.3185</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1209</v>
+        <v>3.9082</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7851</v>
+        <v>0.7446</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1979</v>
+        <v>1.1263</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1209</v>
+        <v>3.9082</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3328</v>
+        <v>4.4518</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7881</v>
+        <v>-0.5436</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3328</v>
+        <v>10.5175</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3328</v>
+        <v>5.4686</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7881</v>
+        <v>-0.5436</v>
       </c>
       <c r="K9" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L9" t="n">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1209</v>
+        <v>4.925000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>249</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0356</v>
+        <v>3.8503</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7689</v>
+        <v>0.7336</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1639</v>
+        <v>1.1002</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0356</v>
+        <v>3.8503</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8663</v>
+        <v>3.312</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8307</v>
+        <v>0.5383</v>
       </c>
       <c r="H10" t="n">
-        <v>7.3489</v>
+        <v>3.9129</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9565</v>
+        <v>3.9129</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8307</v>
+        <v>0.5383</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1258</v>
+        <v>4.4512</v>
       </c>
       <c r="N10" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.98</v>
+        <v>3.832</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7583</v>
+        <v>0.7301</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1417</v>
+        <v>1.0919</v>
       </c>
       <c r="E11" t="n">
-        <v>3.98</v>
+        <v>3.832</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8344</v>
+        <v>1.6089</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1456</v>
+        <v>2.2231</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8344</v>
+        <v>1.6089</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8344</v>
+        <v>1.6089</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1456</v>
+        <v>2.2231</v>
       </c>
       <c r="K11" t="n">
         <v>101</v>
@@ -943,7 +943,7 @@
         <v>148</v>
       </c>
       <c r="M11" t="n">
-        <v>3.98</v>
+        <v>3.832</v>
       </c>
       <c r="N11" t="n">
         <v>249</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0257</v>
+        <v>2.8875</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5765</v>
+        <v>0.5501</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7615</v>
+        <v>0.6655</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0257</v>
+        <v>2.8875</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5632</v>
+        <v>2.8875</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5375</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5632</v>
+        <v>2.9806</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5632</v>
+        <v>2.9806</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5375</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0257</v>
+        <v>2.9806</v>
       </c>
       <c r="N12" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0162</v>
+        <v>2.8445</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5746</v>
+        <v>0.5419</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7577</v>
+        <v>0.6461</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0162</v>
+        <v>2.8445</v>
       </c>
       <c r="F13" t="n">
-        <v>0.959</v>
+        <v>1.2977</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0572</v>
+        <v>1.5468</v>
       </c>
       <c r="H13" t="n">
-        <v>0.959</v>
+        <v>1.2977</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9671</v>
+        <v>1.3511</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0572</v>
+        <v>1.5468</v>
       </c>
       <c r="K13" t="n">
         <v>105</v>
@@ -1035,7 +1035,7 @@
         <v>150</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0243</v>
+        <v>2.8979</v>
       </c>
       <c r="N13" t="n">
         <v>255</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7809</v>
+        <v>2.7002</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5298</v>
+        <v>0.5144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.664</v>
+        <v>0.581</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7809</v>
+        <v>2.7002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7809</v>
+        <v>3.076</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.3758</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7809</v>
+        <v>3.3946</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7809</v>
+        <v>3.3946</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3758</v>
       </c>
       <c r="K14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7809</v>
+        <v>3.0188</v>
       </c>
       <c r="N14" t="n">
-        <v>98</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4534</v>
+        <v>0.4919</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5042</v>
+        <v>0.5275</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3799</v>
+        <v>2.5817</v>
       </c>
       <c r="N15" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4335</v>
+        <v>0.4912</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4626</v>
+        <v>0.5259</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2754</v>
+        <v>2.5782</v>
       </c>
       <c r="N16" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2429</v>
+        <v>2.5367</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4273</v>
+        <v>0.4833</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4497</v>
+        <v>0.5072</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2429</v>
+        <v>2.5367</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8512</v>
+        <v>2.8401</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6083</v>
+        <v>-0.3034</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8512</v>
+        <v>2.8767</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8752</v>
+        <v>2.995</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6083</v>
+        <v>-0.3034</v>
       </c>
       <c r="K17" t="n">
         <v>101</v>
@@ -1219,7 +1219,7 @@
         <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2669</v>
+        <v>2.6916</v>
       </c>
       <c r="N17" t="n">
         <v>169</v>
@@ -1228,449 +1228,449 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2122</v>
+        <v>2.4874</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4215</v>
+        <v>0.4739</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4374</v>
+        <v>0.4849</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2122</v>
+        <v>2.4874</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7512</v>
+        <v>2.4266</v>
       </c>
       <c r="G18" t="n">
-        <v>0.461</v>
+        <v>0.0608</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7512</v>
+        <v>2.4266</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7512</v>
+        <v>2.4266</v>
       </c>
       <c r="J18" t="n">
-        <v>0.461</v>
+        <v>0.0608</v>
       </c>
       <c r="K18" t="n">
         <v>101</v>
       </c>
       <c r="L18" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2122</v>
+        <v>2.4874</v>
       </c>
       <c r="N18" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1411</v>
+        <v>2.391</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4079</v>
+        <v>0.4555</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4091</v>
+        <v>0.4414</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1411</v>
+        <v>2.391</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1411</v>
+        <v>1.5193</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.8717</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1411</v>
+        <v>1.5193</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1411</v>
+        <v>1.5818</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8717</v>
       </c>
       <c r="K19" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1411</v>
+        <v>2.4535</v>
       </c>
       <c r="N19" t="n">
-        <v>110</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1321</v>
+        <v>2.2878</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4062</v>
+        <v>0.4359</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4055</v>
+        <v>0.3948</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1321</v>
+        <v>2.2878</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2296</v>
+        <v>2.7156</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0975</v>
+        <v>-0.4278</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2296</v>
+        <v>4.0817</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2296</v>
+        <v>2.1223</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0975</v>
+        <v>-0.4278</v>
       </c>
       <c r="K20" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1321</v>
+        <v>1.6945</v>
       </c>
       <c r="N20" t="n">
-        <v>144</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1016</v>
+        <v>2.287</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4004</v>
+        <v>0.4357</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3934</v>
+        <v>0.3945</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1016</v>
+        <v>2.287</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0487</v>
+        <v>2.287</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0529</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0487</v>
+        <v>2.287</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0659</v>
+        <v>2.287</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0529</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L21" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1188</v>
+        <v>2.287</v>
       </c>
       <c r="N21" t="n">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0993</v>
+        <v>2.2858</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>0.4355</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3925</v>
+        <v>0.3939</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0993</v>
+        <v>2.2858</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5481</v>
+        <v>2.2858</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5481</v>
+        <v>2.2858</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5611</v>
+        <v>2.2858</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5512</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L22" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.1123</v>
+        <v>2.2858</v>
       </c>
       <c r="N22" t="n">
-        <v>255</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0395</v>
+        <v>2.2644</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3886</v>
+        <v>0.4314</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3686</v>
+        <v>0.3842</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0395</v>
+        <v>2.2644</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0395</v>
+        <v>2.0446</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.2198</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0395</v>
+        <v>2.0446</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0395</v>
+        <v>2.1287</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.2198</v>
       </c>
       <c r="K23" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0395</v>
+        <v>2.3485</v>
       </c>
       <c r="N23" t="n">
-        <v>103</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9892</v>
+        <v>2.1677</v>
       </c>
       <c r="C24" t="n">
-        <v>0.379</v>
+        <v>0.413</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3486</v>
+        <v>0.3406</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9892</v>
+        <v>2.1677</v>
       </c>
       <c r="F24" t="n">
-        <v>1.382</v>
+        <v>1.9509</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6072</v>
+        <v>0.2168</v>
       </c>
       <c r="H24" t="n">
-        <v>1.382</v>
+        <v>1.9509</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3936</v>
+        <v>1.9509</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6072</v>
+        <v>0.2168</v>
       </c>
       <c r="K24" t="n">
         <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0008</v>
+        <v>2.1677</v>
       </c>
       <c r="N24" t="n">
-        <v>169</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9787</v>
+        <v>2.1391</v>
       </c>
       <c r="C25" t="n">
-        <v>0.377</v>
+        <v>0.4075</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3444</v>
+        <v>0.3277</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9787</v>
+        <v>2.1391</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0309</v>
+        <v>2.1391</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0522</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0309</v>
+        <v>2.1391</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0309</v>
+        <v>2.1391</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0522</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9787</v>
+        <v>2.1391</v>
       </c>
       <c r="N25" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8997</v>
+        <v>2.0019</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3619</v>
+        <v>0.3814</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3129</v>
+        <v>0.2657</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8997</v>
+        <v>2.0019</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5287</v>
+        <v>1.3976</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.629</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5287</v>
+        <v>1.3976</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0496</v>
+        <v>1.4551</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.629</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L26" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4206</v>
+        <v>2.0594</v>
       </c>
       <c r="N26" t="n">
-        <v>259</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7403</v>
+        <v>1.944</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3316</v>
+        <v>0.3704</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2494</v>
+        <v>0.2396</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7403</v>
+        <v>1.944</v>
       </c>
       <c r="F27" t="n">
-        <v>2.3006</v>
+        <v>1.8859</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5603</v>
+        <v>0.0581</v>
       </c>
       <c r="H27" t="n">
-        <v>2.3006</v>
+        <v>1.8859</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3006</v>
+        <v>1.8859</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5603</v>
+        <v>0.0581</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7403</v>
+        <v>1.944</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.74</v>
+        <v>1.9421</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3315</v>
+        <v>0.37</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2493</v>
+        <v>0.2387</v>
       </c>
       <c r="E28" t="n">
-        <v>1.74</v>
+        <v>1.9421</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2463</v>
+        <v>2.3325</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4937</v>
+        <v>-0.3904</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2463</v>
+        <v>2.3325</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2484</v>
+        <v>2.3325</v>
       </c>
       <c r="J28" t="n">
-        <v>1.4937</v>
+        <v>-0.3904</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
       </c>
       <c r="L28" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7421</v>
+        <v>1.9421</v>
       </c>
       <c r="N28" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7208</v>
+        <v>1.9188</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3278</v>
+        <v>0.3656</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2417</v>
+        <v>0.2282</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7208</v>
+        <v>1.9188</v>
       </c>
       <c r="F29" t="n">
-        <v>2.7208</v>
+        <v>2.853</v>
       </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>-0.9342</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7208</v>
+        <v>4.566</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2053</v>
+        <v>2.3741</v>
       </c>
       <c r="J29" t="n">
-        <v>-1</v>
+        <v>-0.9342</v>
       </c>
       <c r="K29" t="n">
         <v>96</v>
@@ -1771,7 +1771,7 @@
         <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2053</v>
+        <v>1.4399</v>
       </c>
       <c r="N29" t="n">
         <v>136</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3269</v>
+        <v>0.2866</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2397</v>
+        <v>0.0411</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7159</v>
+        <v>1.5044</v>
       </c>
       <c r="N30" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2052</v>
+        <v>0.2853</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0147</v>
+        <v>0.0379</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0773</v>
+        <v>1.4973</v>
       </c>
       <c r="N31" t="n">
         <v>92</v>
@@ -1872,691 +1872,691 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9822</v>
+        <v>1.4822</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1871</v>
+        <v>0.2824</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0526</v>
+        <v>0.0311</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9822</v>
+        <v>1.4822</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9822</v>
+        <v>0.3861</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.0961</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9822</v>
+        <v>0.3861</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9822</v>
+        <v>0.402</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.0961</v>
       </c>
       <c r="K32" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9822</v>
+        <v>1.4981</v>
       </c>
       <c r="N32" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="C33" t="n">
-        <v>0.178</v>
+        <v>0.238</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0717</v>
+        <v>-0.074</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9343</v>
+        <v>1.2494</v>
       </c>
       <c r="N33" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1737</v>
+        <v>0.2373</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0757</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9117</v>
+        <v>1.2455</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1641</v>
+        <v>0.2138</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1008</v>
+        <v>-0.1313</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8611</v>
+        <v>1.1224</v>
       </c>
       <c r="N35" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.742</v>
+        <v>1.1046</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1414</v>
+        <v>0.2104</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1483</v>
+        <v>-0.1393</v>
       </c>
       <c r="E36" t="n">
-        <v>0.742</v>
+        <v>1.1046</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9562</v>
+        <v>1.1046</v>
       </c>
       <c r="G36" t="n">
-        <v>1.6982</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9562</v>
+        <v>1.1046</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9562</v>
+        <v>1.1046</v>
       </c>
       <c r="J36" t="n">
-        <v>1.6982</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L36" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7419999999999999</v>
+        <v>1.1046</v>
       </c>
       <c r="N36" t="n">
-        <v>249</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6161</v>
+        <v>0.9506</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1174</v>
+        <v>0.1811</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1985</v>
+        <v>-0.2089</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6161</v>
+        <v>0.9506</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6161</v>
+        <v>1.1075</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.1569</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6161</v>
+        <v>1.1075</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6161</v>
+        <v>1.1075</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.1569</v>
       </c>
       <c r="K37" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6161</v>
+        <v>0.9505999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.541</v>
+        <v>0.8942</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1031</v>
+        <v>0.1704</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2284</v>
+        <v>-0.2343</v>
       </c>
       <c r="E38" t="n">
-        <v>0.541</v>
+        <v>0.8942</v>
       </c>
       <c r="F38" t="n">
-        <v>0.541</v>
+        <v>-0.5505</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.4447</v>
       </c>
       <c r="H38" t="n">
-        <v>0.541</v>
+        <v>-0.5505</v>
       </c>
       <c r="I38" t="n">
-        <v>0.541</v>
+        <v>-0.5505</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.4447</v>
       </c>
       <c r="K38" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M38" t="n">
-        <v>0.541</v>
+        <v>0.8942000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0953</v>
+        <v>0.163</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2446</v>
+        <v>-0.2519</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5002</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4682</v>
+        <v>0.7973</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0892</v>
+        <v>0.1519</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2574</v>
+        <v>-0.2781</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4682</v>
+        <v>0.7973</v>
       </c>
       <c r="F40" t="n">
-        <v>0.715</v>
+        <v>0.7973</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.715</v>
+        <v>0.7973</v>
       </c>
       <c r="I40" t="n">
-        <v>0.715</v>
+        <v>0.7973</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L40" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4681999999999999</v>
+        <v>0.7973</v>
       </c>
       <c r="N40" t="n">
-        <v>144</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4314</v>
+        <v>0.4734</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0822</v>
+        <v>0.0902</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.272</v>
+        <v>-0.4243</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4314</v>
+        <v>0.4734</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2475</v>
+        <v>0.4734</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2475</v>
+        <v>0.4734</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8217</v>
+        <v>0.4734</v>
       </c>
       <c r="J41" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="L41" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8572</v>
+        <v>0.4734</v>
       </c>
       <c r="N41" t="n">
-        <v>259</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0183</v>
+        <v>0.0893</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4057</v>
+        <v>-0.4265</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0959</v>
+        <v>0.4686</v>
       </c>
       <c r="N42" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0166</v>
+        <v>0.0772</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4093</v>
+        <v>-0.4551</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.4051</v>
       </c>
       <c r="N43" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0124</v>
+        <v>0.0521</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4699</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0653</v>
+        <v>0.2733</v>
       </c>
       <c r="N44" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0182</v>
+        <v>0.0489</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.482</v>
+        <v>-0.5222</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.2565</v>
       </c>
       <c r="N45" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0261</v>
+        <v>0.0486</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4985</v>
+        <v>-0.5229</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1369</v>
+        <v>0.255</v>
       </c>
       <c r="N46" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0328</v>
+        <v>0.0149</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5124</v>
+        <v>-0.6028</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1719</v>
+        <v>0.0781</v>
       </c>
       <c r="N47" t="n">
         <v>103</v>
@@ -2608,170 +2608,170 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1754</v>
+        <v>-0.2191</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0334</v>
+        <v>-0.0417</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5138</v>
+        <v>-0.7369</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1754</v>
+        <v>-0.2191</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1754</v>
+        <v>-2.8637</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2.6446</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1754</v>
+        <v>-2.8637</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1754</v>
+        <v>-1.489</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>2.6446</v>
       </c>
       <c r="K48" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1754</v>
+        <v>1.1556</v>
       </c>
       <c r="N48" t="n">
-        <v>106</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3127</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1119</v>
+        <v>-0.0596</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.7792</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3127</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.793</v>
+        <v>-0.3127</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2058</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.793</v>
+        <v>-0.3127</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6428</v>
+        <v>-0.3127</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2058</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.4370000000000001</v>
+        <v>-0.3127</v>
       </c>
       <c r="N49" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7692</v>
+        <v>-0.5185</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1465</v>
+        <v>-0.0988</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7504</v>
+        <v>-0.8721</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.7692</v>
+        <v>-0.5185</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3871</v>
+        <v>-0.5185</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.3821</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3871</v>
+        <v>-0.5185</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3904</v>
+        <v>-0.5185</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3821</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L50" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.7725</v>
+        <v>-0.5185</v>
       </c>
       <c r="N50" t="n">
-        <v>255</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1627</v>
+        <v>-0.1072</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.7841</v>
+        <v>-0.8921</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.854</v>
+        <v>-0.5628</v>
       </c>
       <c r="N51" t="n">
         <v>110</v>
@@ -2792,47 +2792,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.1603</v>
+        <v>-0.5875</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2211</v>
+        <v>-0.1119</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9062</v>
+        <v>-0.9032</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1603</v>
+        <v>-0.5875</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.1603</v>
+        <v>-0.1697</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.4178</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.1603</v>
+        <v>-0.1697</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.1603</v>
+        <v>-0.1767</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.4178</v>
       </c>
       <c r="K52" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.1603</v>
+        <v>-0.5945</v>
       </c>
       <c r="N52" t="n">
-        <v>106</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2275</v>
+        <v>-0.1138</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9196</v>
+        <v>-0.9076</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-1.1941</v>
+        <v>-0.5971</v>
       </c>
       <c r="N53" t="n">
         <v>92</v>
@@ -2884,32 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2389</v>
+        <v>-0.1215</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9434</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-1.2537</v>
+        <v>-0.6377</v>
       </c>
       <c r="N54" t="n">
         <v>110</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2437</v>
+        <v>-0.1319</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9535</v>
+        <v>-0.9506</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-1.2791</v>
+        <v>-0.6925</v>
       </c>
       <c r="N55" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.3221</v>
+        <v>-0.8563</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2519</v>
+        <v>-0.1631</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9706</v>
+        <v>-1.0246</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3221</v>
+        <v>-0.8563</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.3221</v>
+        <v>-1.0805</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.2242</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.3221</v>
+        <v>-1.0805</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.3221</v>
+        <v>-0.5618</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.2242</v>
       </c>
       <c r="K56" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.3221</v>
+        <v>-0.3376</v>
       </c>
       <c r="N56" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3499</v>
+        <v>-0.2172</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1757</v>
+        <v>-1.1528</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.8367</v>
+        <v>-1.1402</v>
       </c>
       <c r="N57" t="n">
         <v>107</v>
@@ -3068,93 +3068,93 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kwezz</t>
+          <t>prosus</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3821</v>
+        <v>-0.2202</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2429</v>
+        <v>-1.1598</v>
       </c>
       <c r="E58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-2.0056</v>
+        <v>-1.1559</v>
       </c>
       <c r="N58" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>prosus</t>
+          <t>kwezz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3901</v>
+        <v>-0.2236</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.2596</v>
+        <v>-1.1679</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="I59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-2.0475</v>
+        <v>-1.1737</v>
       </c>
       <c r="N59" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.3005</v>
+        <v>-2.8028</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.6288</v>
+        <v>-0.534</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.7588</v>
+        <v>-1.9033</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.3005</v>
+        <v>-2.8028</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.3005</v>
+        <v>-1.8028</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.3005</v>
+        <v>-1.8028</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.3199</v>
+        <v>-1.8769</v>
       </c>
       <c r="J60" t="n">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>68</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.3199</v>
+        <v>-2.8769</v>
       </c>
       <c r="N60" t="n">
         <v>169</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.5693</v>
+        <v>-4.1305</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.68</v>
+        <v>-0.7869</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.8659</v>
+        <v>-2.5027</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.5693</v>
+        <v>-4.1305</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.7409</v>
+        <v>-3.5407</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.8284</v>
+        <v>-0.5898</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.7409</v>
+        <v>-3.5407</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.2216</v>
+        <v>-1.841</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.8284</v>
+        <v>-0.5898</v>
       </c>
       <c r="K61" t="n">
         <v>96</v>
@@ -3243,7 +3243,7 @@
         <v>40</v>
       </c>
       <c r="M61" t="n">
-        <v>-3.05</v>
+        <v>-2.4308</v>
       </c>
       <c r="N61" t="n">
         <v>136</v>
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6193</v>
+        <v>0.5743</v>
       </c>
       <c r="J2" t="n">
-        <v>17.3404</v>
+        <v>16.0804</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1213</v>
+        <v>-0.0731</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.3964</v>
+        <v>-2.0468</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2846</v>
+        <v>-0.174</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.9688</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3005</v>
+        <v>-0.1845</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.414</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3467</v>
+        <v>-0.2153</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.707599999999999</v>
+        <v>-6.0284</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9125</v>
+        <v>0.8285</v>
       </c>
       <c r="J7" t="n">
-        <v>25.55</v>
+        <v>23.198</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2772</v>
+        <v>0.2484</v>
       </c>
       <c r="J8" t="n">
-        <v>7.7616</v>
+        <v>6.9552</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="J9" t="n">
-        <v>4.172</v>
+        <v>4.396</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0614</v>
+        <v>-0.0146</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7192</v>
+        <v>-0.4088</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3571</v>
+        <v>-0.2153</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.998799999999999</v>
+        <v>-6.0284</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2153</v>
+        <v>1.138</v>
       </c>
       <c r="J12" t="n">
-        <v>24.306</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7355</v>
+        <v>0.7439</v>
       </c>
       <c r="J13" t="n">
-        <v>14.71</v>
+        <v>14.878</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6599</v>
+        <v>0.6745</v>
       </c>
       <c r="J14" t="n">
-        <v>13.198</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.397</v>
+        <v>0.4598</v>
       </c>
       <c r="J15" t="n">
-        <v>7.94</v>
+        <v>9.196</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5342</v>
+        <v>-0.464</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.684</v>
+        <v>-9.279999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4655</v>
+        <v>0.5382</v>
       </c>
       <c r="J17" t="n">
-        <v>9.31</v>
+        <v>10.764</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3341</v>
+        <v>0.3637</v>
       </c>
       <c r="J18" t="n">
-        <v>6.682</v>
+        <v>7.274</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0919</v>
+        <v>0.0631</v>
       </c>
       <c r="J19" t="n">
-        <v>1.838</v>
+        <v>1.262</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6773</v>
+        <v>-0.4536</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.546</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7377</v>
+        <v>-0.4993</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.754</v>
+        <v>-9.986000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.65</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4866</v>
+        <v>1.316</v>
       </c>
       <c r="J22" t="n">
-        <v>28.2454</v>
+        <v>25.004</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9885</v>
+        <v>0.9922</v>
       </c>
       <c r="J23" t="n">
-        <v>18.7815</v>
+        <v>18.8518</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5615</v>
+        <v>0.623</v>
       </c>
       <c r="J24" t="n">
-        <v>10.6685</v>
+        <v>11.837</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0043</v>
+        <v>0.0717</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.08169999999999999</v>
+        <v>1.3623</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3446</v>
+        <v>-0.2632</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.5474</v>
+        <v>-5.0008</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5415</v>
+        <v>0.6427</v>
       </c>
       <c r="J27" t="n">
-        <v>10.2885</v>
+        <v>12.2113</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1694</v>
+        <v>0.1528</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2186</v>
+        <v>2.9032</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3279</v>
+        <v>-0.213</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.2301</v>
+        <v>-4.047</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.76</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4052</v>
+        <v>-0.2622</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.6988</v>
+        <v>-4.9818</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8052</v>
+        <v>-0.5511</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.2988</v>
+        <v>-10.4709</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2898</v>
+        <v>0.3009</v>
       </c>
       <c r="J32" t="n">
-        <v>5.796</v>
+        <v>6.018</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2726</v>
+        <v>0.2784</v>
       </c>
       <c r="J33" t="n">
-        <v>5.452</v>
+        <v>5.568</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.469</v>
+        <v>-0.3102</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.380000000000001</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.68</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4978</v>
+        <v>-0.3292</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.956</v>
+        <v>-6.584</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.44</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8067</v>
+        <v>-0.5522</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.134</v>
+        <v>-11.044</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2236</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>24.472</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.48</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1631</v>
+        <v>0.8335</v>
       </c>
       <c r="J38" t="n">
-        <v>23.262</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3566</v>
+        <v>0.39</v>
       </c>
       <c r="J39" t="n">
-        <v>7.132</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2749</v>
+        <v>0.3419</v>
       </c>
       <c r="J40" t="n">
-        <v>5.498</v>
+        <v>6.838</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4017</v>
+        <v>-0.3233</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.034000000000001</v>
+        <v>-6.466</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5442</v>
       </c>
       <c r="J42" t="n">
-        <v>11.522</v>
+        <v>10.884</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0217</v>
+        <v>-0.0376</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.434</v>
+        <v>-0.752</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.68</v>
+        <v>-1.534</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3329</v>
+        <v>-0.2144</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.658</v>
+        <v>-4.288</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8979</v>
+        <v>-0.624</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.958</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2977</v>
+        <v>0.9145</v>
       </c>
       <c r="J47" t="n">
-        <v>25.954</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6904</v>
+        <v>0.541</v>
       </c>
       <c r="J48" t="n">
-        <v>13.808</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4323</v>
+        <v>0.4132</v>
       </c>
       <c r="J49" t="n">
-        <v>8.646000000000001</v>
+        <v>8.263999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1929</v>
+        <v>0.2525</v>
       </c>
       <c r="J50" t="n">
-        <v>3.858</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6736</v>
+        <v>-0.6152</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.472</v>
+        <v>-12.304</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2061</v>
+        <v>0.8542</v>
       </c>
       <c r="J52" t="n">
-        <v>24.122</v>
+        <v>17.084</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0616</v>
+        <v>0.7621</v>
       </c>
       <c r="J53" t="n">
-        <v>21.232</v>
+        <v>15.242</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8193</v>
+        <v>0.6133</v>
       </c>
       <c r="J54" t="n">
-        <v>16.386</v>
+        <v>12.266</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1632</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.264</v>
+        <v>-1.826</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.1964</v>
+        <v>-1.1982</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.928</v>
+        <v>-23.964</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4551</v>
+        <v>0.4467</v>
       </c>
       <c r="J57" t="n">
-        <v>9.102</v>
+        <v>8.933999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3984</v>
+        <v>0.4024</v>
       </c>
       <c r="J58" t="n">
-        <v>7.968</v>
+        <v>8.048</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2131</v>
+        <v>-0.1364</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.262</v>
+        <v>-2.728</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5169</v>
+        <v>-0.336</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.338</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6452</v>
+        <v>-0.4294</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.904</v>
+        <v>-8.587999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3716</v>
+        <v>0.3132</v>
       </c>
       <c r="J62" t="n">
-        <v>7.0604</v>
+        <v>5.9508</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0145</v>
+        <v>-0.0216</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2755</v>
+        <v>-0.4104</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.72</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4385</v>
+        <v>-0.291</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.3315</v>
+        <v>-5.529</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.553</v>
+        <v>-0.3666</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.507</v>
+        <v>-6.9654</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7215</v>
+        <v>-0.4877</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.7085</v>
+        <v>-9.266299999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>2.13</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3095</v>
+        <v>0.8659</v>
       </c>
       <c r="J67" t="n">
-        <v>24.8805</v>
+        <v>16.4521</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.448</v>
       </c>
       <c r="J68" t="n">
-        <v>11.0998</v>
+        <v>8.512</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3412</v>
+        <v>0.3367</v>
       </c>
       <c r="J69" t="n">
-        <v>6.4828</v>
+        <v>6.3973</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2436</v>
+        <v>-0.1319</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.6284</v>
+        <v>-2.5061</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3516</v>
+        <v>-0.2093</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.6804</v>
+        <v>-3.9767</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6955</v>
+        <v>0.5242</v>
       </c>
       <c r="J72" t="n">
-        <v>28.5155</v>
+        <v>21.4922</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2756</v>
+        <v>0.2499</v>
       </c>
       <c r="J73" t="n">
-        <v>11.2996</v>
+        <v>10.2459</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2408</v>
+        <v>0.2195</v>
       </c>
       <c r="J74" t="n">
-        <v>9.8728</v>
+        <v>8.999499999999999</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0693</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.8413</v>
+        <v>3.5875</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6564</v>
+        <v>-0.6057</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.9124</v>
+        <v>-24.8337</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3963</v>
+        <v>0.4089</v>
       </c>
       <c r="J77" t="n">
-        <v>16.2483</v>
+        <v>16.7649</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.353</v>
+        <v>0.377</v>
       </c>
       <c r="J78" t="n">
-        <v>14.473</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1328</v>
+        <v>0.1536</v>
       </c>
       <c r="J79" t="n">
-        <v>5.4448</v>
+        <v>6.2976</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0624</v>
+        <v>-0.0245</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.5584</v>
+        <v>-1.0045</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4354</v>
+        <v>-0.274</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.8514</v>
+        <v>-11.234</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6133</v>
+        <v>1.1266</v>
       </c>
       <c r="J82" t="n">
-        <v>30.6527</v>
+        <v>21.4054</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>1.294</v>
+        <v>0.9177</v>
       </c>
       <c r="J83" t="n">
-        <v>24.586</v>
+        <v>17.4363</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8292</v>
+        <v>0.6363</v>
       </c>
       <c r="J84" t="n">
-        <v>15.7548</v>
+        <v>12.0897</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.279</v>
+        <v>-0.1958</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.301</v>
+        <v>-3.7202</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.9445</v>
+        <v>-0.9122</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.9455</v>
+        <v>-17.3318</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J87" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.4123</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0182</v>
+        <v>-0.0363</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.3458</v>
+        <v>-0.6897</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2966</v>
+        <v>-0.1935</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.6354</v>
+        <v>-3.6765</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3296</v>
+        <v>-0.2135</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.2624</v>
+        <v>-4.0565</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3917</v>
+        <v>-0.2529</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.4423</v>
+        <v>-4.8051</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I92" t="n">
-        <v>1.421</v>
+        <v>0.9954</v>
       </c>
       <c r="J92" t="n">
-        <v>34.104</v>
+        <v>23.8896</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4432</v>
       </c>
       <c r="J93" t="n">
-        <v>12.3744</v>
+        <v>10.6368</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4863</v>
+        <v>0.4286</v>
       </c>
       <c r="J94" t="n">
-        <v>11.6712</v>
+        <v>10.2864</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1051</v>
+        <v>-0.0369</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.5224</v>
+        <v>-0.8856000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6451</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.4824</v>
+        <v>-14.0448</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2942</v>
+        <v>0.3137</v>
       </c>
       <c r="J97" t="n">
-        <v>7.0608</v>
+        <v>7.5288</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2444</v>
+        <v>0.2516</v>
       </c>
       <c r="J98" t="n">
-        <v>5.8656</v>
+        <v>6.0384</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0828</v>
+        <v>0.0566</v>
       </c>
       <c r="J99" t="n">
-        <v>1.9872</v>
+        <v>1.3584</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5421</v>
+        <v>-0.3541</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.0104</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5421</v>
+        <v>-0.3541</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.0104</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2735</v>
+        <v>0.2794</v>
       </c>
       <c r="J102" t="n">
-        <v>4.923</v>
+        <v>5.0292</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0267</v>
+        <v>-0.0492</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.4806</v>
+        <v>-0.8856000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.77</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3587</v>
+        <v>-0.2433</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.4566</v>
+        <v>-4.3794</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5934</v>
+        <v>-0.3948</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.6812</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4321</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.6226</v>
+        <v>-7.7778</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>2.08</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9838</v>
+        <v>1.529</v>
       </c>
       <c r="J107" t="n">
-        <v>35.7084</v>
+        <v>27.522</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>15.4512</v>
+        <v>12.0024</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3712</v>
+        <v>0.4093</v>
       </c>
       <c r="J109" t="n">
-        <v>6.6816</v>
+        <v>7.3674</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1043</v>
+        <v>-0.023</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.8774</v>
+        <v>-0.414</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2197</v>
+        <v>-0.1328</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.9546</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.99</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2041</v>
+        <v>0.8022</v>
       </c>
       <c r="J112" t="n">
-        <v>24.082</v>
+        <v>16.044</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3409</v>
+        <v>0.3143</v>
       </c>
       <c r="J113" t="n">
-        <v>6.818</v>
+        <v>6.286</v>
       </c>
     </row>
     <row r="114">
@@ -7869,10 +7869,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0953</v>
+        <v>0.12</v>
       </c>
       <c r="J115" t="n">
-        <v>1.906</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6127</v>
+        <v>-0.4039</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.254</v>
+        <v>-8.077999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4026</v>
       </c>
       <c r="J117" t="n">
-        <v>10.03</v>
+        <v>8.052</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1192</v>
+        <v>0.0803</v>
       </c>
       <c r="J118" t="n">
-        <v>2.384</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0708</v>
+        <v>0.0377</v>
       </c>
       <c r="J119" t="n">
-        <v>1.416</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3069</v>
+        <v>-0.1913</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.138</v>
+        <v>-3.826</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6974</v>
+        <v>-0.4684</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.948</v>
+        <v>-9.368</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3163</v>
+        <v>0.3431</v>
       </c>
       <c r="J122" t="n">
-        <v>9.489000000000001</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3163</v>
+        <v>0.3431</v>
       </c>
       <c r="J123" t="n">
-        <v>9.489000000000001</v>
+        <v>10.293</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0784</v>
+        <v>0.0696</v>
       </c>
       <c r="J124" t="n">
-        <v>2.352</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3035</v>
+        <v>-0.1856</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.105</v>
+        <v>-5.568</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4766</v>
+        <v>-0.3053</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.298</v>
+        <v>-9.159000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7971</v>
+        <v>0.5999</v>
       </c>
       <c r="J127" t="n">
-        <v>23.913</v>
+        <v>17.997</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.28</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7736</v>
+        <v>0.586</v>
       </c>
       <c r="J128" t="n">
-        <v>23.208</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5738</v>
+        <v>0.4727</v>
       </c>
       <c r="J129" t="n">
-        <v>17.214</v>
+        <v>14.181</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3555</v>
+        <v>0.37</v>
       </c>
       <c r="J130" t="n">
-        <v>10.665</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5936</v>
+        <v>-0.5306</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.808</v>
+        <v>-15.918</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4659</v>
+        <v>1.2997</v>
       </c>
       <c r="J132" t="n">
-        <v>33.7157</v>
+        <v>29.8931</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6333</v>
+        <v>0.6353</v>
       </c>
       <c r="J133" t="n">
-        <v>14.5659</v>
+        <v>14.6119</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6333</v>
+        <v>0.6353</v>
       </c>
       <c r="J134" t="n">
-        <v>14.5659</v>
+        <v>14.6119</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.024</v>
+        <v>0.09</v>
       </c>
       <c r="J135" t="n">
-        <v>0.552</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7715</v>
+        <v>-0.7211</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.7445</v>
+        <v>-16.5853</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6573</v>
+        <v>0.8037</v>
       </c>
       <c r="J137" t="n">
-        <v>15.1179</v>
+        <v>18.4851</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4665</v>
+        <v>0.5462</v>
       </c>
       <c r="J138" t="n">
-        <v>10.7295</v>
+        <v>12.5626</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0417</v>
+        <v>-0.0207</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.9591</v>
+        <v>-0.4761</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.7</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5206</v>
+        <v>-0.3365</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.9738</v>
+        <v>-7.7395</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5845</v>
+        <v>-0.3834</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.4435</v>
+        <v>-8.818199999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0827</v>
+        <v>1.0566</v>
       </c>
       <c r="J142" t="n">
-        <v>21.654</v>
+        <v>21.132</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9545</v>
+        <v>0.96</v>
       </c>
       <c r="J143" t="n">
-        <v>19.09</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4392</v>
+        <v>0.506</v>
       </c>
       <c r="J144" t="n">
-        <v>8.784000000000001</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2205</v>
+        <v>0.2945</v>
       </c>
       <c r="J145" t="n">
-        <v>4.41</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1325</v>
+        <v>0.2067</v>
       </c>
       <c r="J146" t="n">
-        <v>2.65</v>
+        <v>4.134</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.7</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9687</v>
+        <v>1.1462</v>
       </c>
       <c r="J147" t="n">
-        <v>19.374</v>
+        <v>22.924</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.21</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3828</v>
+        <v>0.4437</v>
       </c>
       <c r="J148" t="n">
-        <v>7.656</v>
+        <v>8.874000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1311</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.622</v>
+        <v>-1.352</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5278</v>
+        <v>-0.341</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.556</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5909</v>
+        <v>-0.3878</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.818</v>
+        <v>-7.756</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4074</v>
+        <v>0.4604</v>
       </c>
       <c r="J152" t="n">
-        <v>8.9628</v>
+        <v>10.1288</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1108</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.4376</v>
+        <v>-1.9888</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1307</v>
+        <v>-0.102</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.8754</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3223</v>
+        <v>-0.2061</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.0906</v>
+        <v>-4.5342</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6157</v>
+        <v>-0.408</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.5454</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.592</v>
+        <v>1.3852</v>
       </c>
       <c r="J157" t="n">
-        <v>35.024</v>
+        <v>30.4744</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4436</v>
+        <v>1.2865</v>
       </c>
       <c r="J158" t="n">
-        <v>31.7592</v>
+        <v>28.303</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.32</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8248</v>
+        <v>0.8327</v>
       </c>
       <c r="J159" t="n">
-        <v>18.1456</v>
+        <v>18.3194</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.8279</v>
+        <v>-0.7823</v>
       </c>
       <c r="J160" t="n">
-        <v>-18.2138</v>
+        <v>-17.2106</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9167</v>
+        <v>-0.8811</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.1674</v>
+        <v>-19.3842</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.903</v>
+        <v>1.6036</v>
       </c>
       <c r="J162" t="n">
-        <v>39.963</v>
+        <v>33.6756</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1966</v>
+        <v>1.1336</v>
       </c>
       <c r="J163" t="n">
-        <v>25.1286</v>
+        <v>23.8056</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5596</v>
+        <v>0.6387</v>
       </c>
       <c r="J164" t="n">
-        <v>11.7516</v>
+        <v>13.4127</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1541</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.2361</v>
+        <v>-1.4994</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7036</v>
+        <v>-0.6444</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.7756</v>
+        <v>-13.5324</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.589</v>
+        <v>0.7089</v>
       </c>
       <c r="J167" t="n">
-        <v>12.369</v>
+        <v>14.8869</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1619</v>
+        <v>-0.1227</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.3999</v>
+        <v>-2.5767</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.88</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2054</v>
+        <v>-0.1437</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.3134</v>
+        <v>-3.0177</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5079</v>
+        <v>-0.3311</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.6659</v>
+        <v>-6.9531</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.613</v>
+        <v>-0.4062</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.873</v>
+        <v>-8.530200000000001</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2666</v>
+        <v>0.2904</v>
       </c>
       <c r="J172" t="n">
-        <v>6.3984</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2501</v>
+        <v>0.2703</v>
       </c>
       <c r="J173" t="n">
-        <v>6.0024</v>
+        <v>6.4872</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1415</v>
+        <v>0.1422</v>
       </c>
       <c r="J174" t="n">
-        <v>3.396</v>
+        <v>3.4128</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2571</v>
+        <v>-0.1545</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.1704</v>
+        <v>-3.708</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.423</v>
+        <v>-0.2671</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.152</v>
+        <v>-6.4104</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.422</v>
+        <v>1.2697</v>
       </c>
       <c r="J177" t="n">
-        <v>34.128</v>
+        <v>30.4728</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0827</v>
+        <v>1.0485</v>
       </c>
       <c r="J178" t="n">
-        <v>25.9848</v>
+        <v>25.164</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3538</v>
+        <v>0.3946</v>
       </c>
       <c r="J179" t="n">
-        <v>8.491199999999999</v>
+        <v>9.4704</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5424</v>
+        <v>-0.4762</v>
       </c>
       <c r="J180" t="n">
-        <v>-13.0176</v>
+        <v>-11.4288</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8341</v>
+        <v>-0.7904</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.0184</v>
+        <v>-18.9696</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.409</v>
+        <v>1.2682</v>
       </c>
       <c r="J182" t="n">
-        <v>28.18</v>
+        <v>25.364</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.371</v>
+        <v>1.2438</v>
       </c>
       <c r="J183" t="n">
-        <v>27.42</v>
+        <v>24.876</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.28</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="J184" t="n">
-        <v>13.196</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0151</v>
+        <v>0.0956</v>
       </c>
       <c r="J185" t="n">
-        <v>0.302</v>
+        <v>1.912</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3573</v>
+        <v>-0.274</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.146</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4625</v>
+        <v>0.5344</v>
       </c>
       <c r="J187" t="n">
-        <v>9.25</v>
+        <v>10.688</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.331</v>
+        <v>0.3604</v>
       </c>
       <c r="J188" t="n">
-        <v>6.62</v>
+        <v>7.208</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1963</v>
+        <v>0.19</v>
       </c>
       <c r="J189" t="n">
-        <v>3.926</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5652</v>
+        <v>-0.3712</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.304</v>
+        <v>-7.424</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.41</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8549</v>
+        <v>-0.59</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.098</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3452</v>
+        <v>0.394</v>
       </c>
       <c r="J192" t="n">
-        <v>8.284800000000001</v>
+        <v>9.456</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2996</v>
+        <v>0.3379</v>
       </c>
       <c r="J193" t="n">
-        <v>7.1904</v>
+        <v>8.1096</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.07</v>
       </c>
       <c r="I194" t="n">
-        <v>0.163</v>
+        <v>0.1783</v>
       </c>
       <c r="J194" t="n">
-        <v>3.912</v>
+        <v>4.2792</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1645</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.948</v>
+        <v>-2.1792</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4036</v>
+        <v>-0.252</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.686400000000001</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.36</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0096</v>
+        <v>0.9836</v>
       </c>
       <c r="J197" t="n">
-        <v>24.2304</v>
+        <v>23.6064</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8072</v>
+        <v>0.7755</v>
       </c>
       <c r="J198" t="n">
-        <v>19.3728</v>
+        <v>18.612</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3612</v>
+        <v>0.3333</v>
       </c>
       <c r="J199" t="n">
-        <v>8.668799999999999</v>
+        <v>7.9992</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2315</v>
+        <v>-0.1774</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.556</v>
+        <v>-4.2576</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.2179</v>
+        <v>-1.2222</v>
       </c>
       <c r="J201" t="n">
-        <v>-29.2296</v>
+        <v>-29.3328</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>0.044</v>
+        <v>-0.0027</v>
       </c>
       <c r="J202" t="n">
-        <v>0.836</v>
+        <v>-0.0513</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0578</v>
+        <v>-0.0713</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.0982</v>
+        <v>-1.3547</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0762</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.4478</v>
+        <v>-1.5884</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5755</v>
+        <v>-0.3831</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.9345</v>
+        <v>-7.2789</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7917</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.0423</v>
+        <v>-10.2752</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.66</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4309</v>
+        <v>1.292</v>
       </c>
       <c r="J207" t="n">
-        <v>27.1871</v>
+        <v>24.548</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.65</v>
       </c>
       <c r="I208" t="n">
-        <v>1.4121</v>
+        <v>1.2803</v>
       </c>
       <c r="J208" t="n">
-        <v>26.8299</v>
+        <v>24.3257</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I209" t="n">
-        <v>1.2377</v>
+        <v>1.1736</v>
       </c>
       <c r="J209" t="n">
-        <v>23.5163</v>
+        <v>22.2984</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3133</v>
+        <v>0.415</v>
       </c>
       <c r="J210" t="n">
-        <v>5.9527</v>
+        <v>7.885</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0448</v>
+        <v>0.1339</v>
       </c>
       <c r="J211" t="n">
-        <v>0.8512</v>
+        <v>2.5441</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.68</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9723000000000001</v>
+        <v>1.153</v>
       </c>
       <c r="J212" t="n">
-        <v>20.4183</v>
+        <v>24.213</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J213" t="n">
-        <v>1.176</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.87</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2691</v>
+        <v>-0.1636</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.6511</v>
+        <v>-3.4356</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4477</v>
+        <v>-0.285</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.4017</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7019</v>
+        <v>-0.4718</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.7399</v>
+        <v>-9.9078</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.85</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8477</v>
+        <v>1.5604</v>
       </c>
       <c r="J217" t="n">
-        <v>38.8017</v>
+        <v>32.7684</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.56</v>
       </c>
       <c r="I218" t="n">
-        <v>1.3192</v>
+        <v>1.2067</v>
       </c>
       <c r="J218" t="n">
-        <v>27.7032</v>
+        <v>25.3407</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2162</v>
+        <v>0.2922</v>
       </c>
       <c r="J219" t="n">
-        <v>4.5402</v>
+        <v>6.1362</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4886</v>
+        <v>-0.4142</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.2606</v>
+        <v>-8.6982</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7165</v>
+        <v>-0.6594</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.0465</v>
+        <v>-13.8474</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>2.21</v>
       </c>
       <c r="I222" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J222" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.69</v>
       </c>
       <c r="I223" t="n">
-        <v>1.485</v>
+        <v>1.3265</v>
       </c>
       <c r="J223" t="n">
-        <v>23.76</v>
+        <v>21.224</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2872</v>
+        <v>0.3881</v>
       </c>
       <c r="J224" t="n">
-        <v>4.5952</v>
+        <v>6.2096</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I225" t="n">
-        <v>0.13</v>
+        <v>0.2233</v>
       </c>
       <c r="J225" t="n">
-        <v>2.08</v>
+        <v>3.5728</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3208</v>
+        <v>-0.2325</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.1328</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1814</v>
+        <v>0.1597</v>
       </c>
       <c r="J227" t="n">
-        <v>2.9024</v>
+        <v>2.5552</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1771</v>
+        <v>-0.1549</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.8336</v>
+        <v>-2.4784</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1771</v>
+        <v>-0.1549</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.8336</v>
+        <v>-2.4784</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5759</v>
+        <v>-0.386</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.214399999999999</v>
+        <v>-6.176</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.36</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8919</v>
+        <v>-0.6182</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.2704</v>
+        <v>-9.8912</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.17</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3706</v>
+        <v>0.4131</v>
       </c>
       <c r="J232" t="n">
-        <v>7.0414</v>
+        <v>7.8489</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2606</v>
+        <v>0.2722</v>
       </c>
       <c r="J233" t="n">
-        <v>4.9514</v>
+        <v>5.1718</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.144</v>
+        <v>-0.1038</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.736</v>
+        <v>-1.9722</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.83</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3138</v>
+        <v>-0.1984</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.9622</v>
+        <v>-3.7696</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6934</v>
+        <v>-0.4656</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.1746</v>
+        <v>-8.846399999999999</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.9918</v>
+        <v>1.6969</v>
       </c>
       <c r="J237" t="n">
-        <v>37.8442</v>
+        <v>32.2411</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0225</v>
+        <v>1.0145</v>
       </c>
       <c r="J238" t="n">
-        <v>19.4275</v>
+        <v>19.2755</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.96</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3048</v>
+        <v>-0.224</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.7912</v>
+        <v>-4.256</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4565</v>
+        <v>-0.3811</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.673500000000001</v>
+        <v>-7.2409</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4842</v>
+        <v>-0.4104</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.1998</v>
+        <v>-7.7976</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.34</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="J242" t="n">
-        <v>12.0384</v>
+        <v>14.725</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1632</v>
+        <v>0.1411</v>
       </c>
       <c r="J243" t="n">
-        <v>3.1008</v>
+        <v>2.6809</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4073</v>
+        <v>-0.2671</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.7387</v>
+        <v>-5.0749</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.54</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6913</v>
+        <v>-0.4648</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.1347</v>
+        <v>-8.831200000000001</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.5</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.0676</v>
+        <v>-9.528499999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.89</v>
       </c>
       <c r="I247" t="n">
-        <v>1.878</v>
+        <v>1.5835</v>
       </c>
       <c r="J247" t="n">
-        <v>35.682</v>
+        <v>30.0865</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.41</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9728</v>
+        <v>0.9947</v>
       </c>
       <c r="J248" t="n">
-        <v>18.4832</v>
+        <v>18.8993</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5446</v>
+        <v>0.6332</v>
       </c>
       <c r="J249" t="n">
-        <v>10.3474</v>
+        <v>12.0308</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I250" t="n">
-        <v>0.471</v>
+        <v>0.5613</v>
       </c>
       <c r="J250" t="n">
-        <v>8.949</v>
+        <v>10.6647</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.86</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6118</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.6242</v>
+        <v>-10.3341</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.48</v>
       </c>
       <c r="I252" t="n">
-        <v>1.246</v>
+        <v>1.1508</v>
       </c>
       <c r="J252" t="n">
-        <v>29.904</v>
+        <v>27.6192</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5161</v>
+        <v>0.4882</v>
       </c>
       <c r="J253" t="n">
-        <v>12.3864</v>
+        <v>11.7168</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2794</v>
+        <v>-0.2177</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.7056</v>
+        <v>-5.2248</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4038</v>
+        <v>-0.3413</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.6912</v>
+        <v>-8.1912</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4888</v>
+        <v>-0.4277</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.7312</v>
+        <v>-10.2648</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3148</v>
+        <v>0.3497</v>
       </c>
       <c r="J257" t="n">
-        <v>7.5552</v>
+        <v>8.392799999999999</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2673</v>
+        <v>0.2909</v>
       </c>
       <c r="J258" t="n">
-        <v>6.4152</v>
+        <v>6.9816</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1424</v>
+        <v>0.1427</v>
       </c>
       <c r="J259" t="n">
-        <v>3.4176</v>
+        <v>3.4248</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2889</v>
+        <v>-0.1756</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.9336</v>
+        <v>-4.2144</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4639</v>
+        <v>-0.2961</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.1336</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5173</v>
+        <v>1.3518</v>
       </c>
       <c r="J262" t="n">
-        <v>24.2768</v>
+        <v>21.6288</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.66</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4055</v>
+        <v>1.2825</v>
       </c>
       <c r="J263" t="n">
-        <v>22.488</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>1.1029</v>
+        <v>1.1074</v>
       </c>
       <c r="J264" t="n">
-        <v>17.6464</v>
+        <v>17.7184</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.46</v>
       </c>
       <c r="I265" t="n">
-        <v>0.9749</v>
+        <v>1.0488</v>
       </c>
       <c r="J265" t="n">
-        <v>15.5984</v>
+        <v>16.7808</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0646</v>
+        <v>0.0225</v>
       </c>
       <c r="J266" t="n">
-        <v>-1.0336</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.37</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7076</v>
+        <v>0.8954</v>
       </c>
       <c r="J267" t="n">
-        <v>11.3216</v>
+        <v>14.3264</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1663</v>
+        <v>-0.1464</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.6608</v>
+        <v>-2.3424</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.72</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4164</v>
+        <v>-0.2848</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.6624</v>
+        <v>-4.5568</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.4</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.8465</v>
+        <v>-0.5829</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.544</v>
+        <v>-9.3264</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8465</v>
+        <v>-0.5829</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.544</v>
+        <v>-9.3264</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5643</v>
+        <v>1.3672</v>
       </c>
       <c r="J272" t="n">
-        <v>31.286</v>
+        <v>27.344</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.63</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4529</v>
+        <v>1.2936</v>
       </c>
       <c r="J273" t="n">
-        <v>29.058</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.11</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2444</v>
+        <v>0.3202</v>
       </c>
       <c r="J274" t="n">
-        <v>4.888</v>
+        <v>6.404</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.97</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2753</v>
+        <v>-0.1929</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.506</v>
+        <v>-3.858</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6926</v>
+        <v>-0.6334</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.852</v>
+        <v>-12.668</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6168</v>
       </c>
       <c r="J277" t="n">
-        <v>10.454</v>
+        <v>12.336</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4551</v>
+        <v>0.5252</v>
       </c>
       <c r="J278" t="n">
-        <v>9.102</v>
+        <v>10.504</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.98</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0156</v>
+        <v>-0.0285</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.312</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4486</v>
+        <v>-0.2881</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.972</v>
+        <v>-5.762</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.36</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.9127</v>
+        <v>-0.6361</v>
       </c>
       <c r="J281" t="n">
-        <v>-18.254</v>
+        <v>-12.722</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.46</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1542</v>
+        <v>1.0962</v>
       </c>
       <c r="J282" t="n">
-        <v>25.3924</v>
+        <v>24.1164</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9861</v>
+        <v>0.9771</v>
       </c>
       <c r="J283" t="n">
-        <v>21.6942</v>
+        <v>21.4962</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.28</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7597</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>16.7134</v>
+        <v>16.599</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.95</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3196</v>
+        <v>-0.2438</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.0312</v>
+        <v>-5.3636</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7234</v>
+        <v>-0.6688</v>
       </c>
       <c r="J286" t="n">
-        <v>-15.9148</v>
+        <v>-14.7136</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.281</v>
+        <v>0.2967</v>
       </c>
       <c r="J287" t="n">
-        <v>6.182</v>
+        <v>6.5274</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1113</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>2.4486</v>
+        <v>1.9448</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.096</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.112</v>
+        <v>-1.7534</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3101</v>
+        <v>-0.1972</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.8222</v>
+        <v>-4.3384</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.605</v>
+        <v>-0.3999</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.31</v>
+        <v>-8.797800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>0.6866</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J292" t="n">
-        <v>15.1052</v>
+        <v>18.6406</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.32</v>
       </c>
       <c r="I293" t="n">
-        <v>0.5149</v>
+        <v>0.6189</v>
       </c>
       <c r="J293" t="n">
-        <v>11.3278</v>
+        <v>13.6158</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3792</v>
+        <v>0.448</v>
       </c>
       <c r="J294" t="n">
-        <v>8.3424</v>
+        <v>9.856</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4031</v>
+        <v>-0.2496</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.8682</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5609</v>
+        <v>-0.365</v>
       </c>
       <c r="J296" t="n">
-        <v>-12.3398</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.46</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2208</v>
+        <v>1.1334</v>
       </c>
       <c r="J297" t="n">
-        <v>26.8576</v>
+        <v>24.9348</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.37</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0324</v>
+        <v>1.0029</v>
       </c>
       <c r="J298" t="n">
-        <v>22.7128</v>
+        <v>22.0638</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3913</v>
+        <v>-0.3334</v>
       </c>
       <c r="J299" t="n">
-        <v>-8.608599999999999</v>
+        <v>-7.3348</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4206</v>
+        <v>-0.3626</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.2532</v>
+        <v>-7.9772</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.135</v>
+        <v>-1.1278</v>
       </c>
       <c r="J301" t="n">
-        <v>-24.97</v>
+        <v>-24.8116</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.1645</v>
+        <v>-0.1537</v>
       </c>
       <c r="J302" t="n">
-        <v>-2.7965</v>
+        <v>-2.6129</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1804</v>
+        <v>-0.1649</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.0668</v>
+        <v>-2.8033</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.583</v>
+        <v>-0.3991</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.911</v>
+        <v>-6.7847</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.53</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.6552</v>
+        <v>-0.4457</v>
       </c>
       <c r="J305" t="n">
-        <v>-11.1384</v>
+        <v>-7.5769</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.48</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4927</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.2961</v>
+        <v>-8.3759</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.9</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8358</v>
+        <v>1.5575</v>
       </c>
       <c r="J307" t="n">
-        <v>31.2086</v>
+        <v>26.4775</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.64</v>
       </c>
       <c r="I308" t="n">
-        <v>1.3692</v>
+        <v>1.2599</v>
       </c>
       <c r="J308" t="n">
-        <v>23.2764</v>
+        <v>21.4183</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.52</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1272</v>
+        <v>1.1195</v>
       </c>
       <c r="J309" t="n">
-        <v>19.1624</v>
+        <v>19.0315</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2734</v>
+        <v>0.3777</v>
       </c>
       <c r="J310" t="n">
-        <v>4.6478</v>
+        <v>6.4209</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2734</v>
+        <v>0.3777</v>
       </c>
       <c r="J311" t="n">
-        <v>4.6478</v>
+        <v>6.4209</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5557</v>
+        <v>1.372</v>
       </c>
       <c r="J312" t="n">
-        <v>28.0026</v>
+        <v>24.696</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.58</v>
       </c>
       <c r="I313" t="n">
-        <v>1.2727</v>
+        <v>1.1959</v>
       </c>
       <c r="J313" t="n">
-        <v>22.9086</v>
+        <v>21.5262</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.58</v>
       </c>
       <c r="I314" t="n">
-        <v>1.2727</v>
+        <v>1.1959</v>
       </c>
       <c r="J314" t="n">
-        <v>22.9086</v>
+        <v>21.5262</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3104</v>
+        <v>0.4129</v>
       </c>
       <c r="J315" t="n">
-        <v>5.5872</v>
+        <v>7.4322</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1285</v>
+        <v>0.222</v>
       </c>
       <c r="J316" t="n">
-        <v>2.313</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4697</v>
+        <v>0.5524</v>
       </c>
       <c r="J317" t="n">
-        <v>8.454599999999999</v>
+        <v>9.943199999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.5077</v>
+        <v>-0.3445</v>
       </c>
       <c r="J318" t="n">
-        <v>-9.1386</v>
+        <v>-6.201</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.58</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.6087</v>
+        <v>-0.4099</v>
       </c>
       <c r="J319" t="n">
-        <v>-10.9566</v>
+        <v>-7.3782</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.58</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.6087</v>
+        <v>-0.4099</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.9566</v>
+        <v>-7.3782</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6224</v>
+        <v>-0.4192</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.2032</v>
+        <v>-7.5456</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.55</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3613</v>
+        <v>1.2285</v>
       </c>
       <c r="J322" t="n">
-        <v>31.3099</v>
+        <v>28.2555</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.34</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9273</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J323" t="n">
-        <v>21.3279</v>
+        <v>20.9944</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0302</v>
+        <v>0.0267</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.6946</v>
+        <v>0.6141</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.92</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3922</v>
+        <v>-0.3236</v>
       </c>
       <c r="J325" t="n">
-        <v>-9.0206</v>
+        <v>-7.4428</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7563</v>
+        <v>-0.7066</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.3949</v>
+        <v>-16.2518</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6422</v>
+        <v>0.7832</v>
       </c>
       <c r="J327" t="n">
-        <v>14.7706</v>
+        <v>18.0136</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1858</v>
+        <v>-0.1247</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.2734</v>
+        <v>-2.8681</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2063</v>
+        <v>-0.1352</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.7449</v>
+        <v>-3.1096</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.78</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3878</v>
+        <v>-0.2475</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.9194</v>
+        <v>-5.6925</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.59</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6431</v>
+        <v>-0.428</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.7913</v>
+        <v>-9.843999999999999</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>2.18</v>
       </c>
       <c r="I332" t="n">
-        <v>2.0593</v>
+        <v>1.8146</v>
       </c>
       <c r="J332" t="n">
-        <v>28.8302</v>
+        <v>25.4044</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>2.02</v>
       </c>
       <c r="I333" t="n">
-        <v>1.9307</v>
+        <v>1.6456</v>
       </c>
       <c r="J333" t="n">
-        <v>27.0298</v>
+        <v>23.0384</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.96</v>
       </c>
       <c r="I334" t="n">
-        <v>1.8458</v>
+        <v>1.5817</v>
       </c>
       <c r="J334" t="n">
-        <v>25.8412</v>
+        <v>22.1438</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>1.48</v>
       </c>
       <c r="I335" t="n">
-        <v>0.9186</v>
+        <v>1.0496</v>
       </c>
       <c r="J335" t="n">
-        <v>12.8604</v>
+        <v>14.6944</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.92</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5196</v>
+        <v>-0.4432</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.2744</v>
+        <v>-6.2048</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.1776</v>
+        <v>0.1675</v>
       </c>
       <c r="J337" t="n">
-        <v>2.4864</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.4138</v>
       </c>
       <c r="J338" t="n">
-        <v>-8.4322</v>
+        <v>-5.7932</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.6172</v>
+        <v>-0.423</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.6408</v>
+        <v>-5.922</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.52</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.6607</v>
+        <v>-0.4511</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.2498</v>
+        <v>-6.3154</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.5</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6887</v>
+        <v>-0.4699</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.6418</v>
+        <v>-6.5786</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>1.0417</v>
+        <v>1.029</v>
       </c>
       <c r="J342" t="n">
-        <v>20.834</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.41</v>
       </c>
       <c r="I343" t="n">
-        <v>1.0204</v>
+        <v>1.0136</v>
       </c>
       <c r="J343" t="n">
-        <v>20.408</v>
+        <v>20.272</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8889</v>
+        <v>0.8979</v>
       </c>
       <c r="J344" t="n">
-        <v>17.778</v>
+        <v>17.958</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I345" t="n">
-        <v>0.3867</v>
+        <v>0.456</v>
       </c>
       <c r="J345" t="n">
-        <v>7.734</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.82</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6898</v>
+        <v>-0.6306</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.796</v>
+        <v>-12.612</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.05</v>
       </c>
       <c r="I347" t="n">
-        <v>0.2145</v>
+        <v>0.2036</v>
       </c>
       <c r="J347" t="n">
-        <v>4.29</v>
+        <v>4.072</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.84</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2292</v>
+        <v>-0.1772</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.584</v>
+        <v>-3.544</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.79</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3296</v>
+        <v>-0.2254</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.592</v>
+        <v>-4.508</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3642</v>
+        <v>-0.2445</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.284</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6352</v>
+        <v>-0.4242</v>
       </c>
       <c r="J351" t="n">
-        <v>-12.704</v>
+        <v>-8.484</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.58</v>
       </c>
       <c r="I352" t="n">
-        <v>1.3409</v>
+        <v>1.2232</v>
       </c>
       <c r="J352" t="n">
-        <v>24.1362</v>
+        <v>22.0176</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.54</v>
       </c>
       <c r="I353" t="n">
-        <v>1.263</v>
+        <v>1.1737</v>
       </c>
       <c r="J353" t="n">
-        <v>22.734</v>
+        <v>21.1266</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>1.1832</v>
+        <v>1.1238</v>
       </c>
       <c r="J354" t="n">
-        <v>21.2976</v>
+        <v>20.2284</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I355" t="n">
-        <v>0.0849</v>
+        <v>0.1648</v>
       </c>
       <c r="J355" t="n">
-        <v>1.5282</v>
+        <v>2.9664</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.9273</v>
+        <v>-0.8928</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.6914</v>
+        <v>-16.0704</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.47</v>
       </c>
       <c r="I357" t="n">
-        <v>0.7789</v>
+        <v>0.9769</v>
       </c>
       <c r="J357" t="n">
-        <v>14.0202</v>
+        <v>17.5842</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.12</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3126</v>
+        <v>0.3339</v>
       </c>
       <c r="J358" t="n">
-        <v>5.6268</v>
+        <v>6.0102</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.8</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3424</v>
+        <v>-0.2224</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.1632</v>
+        <v>-4.0032</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.53</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.7095</v>
+        <v>-0.478</v>
       </c>
       <c r="J360" t="n">
-        <v>-12.771</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.4</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.8623</v>
+        <v>-0.5957</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.5214</v>
+        <v>-10.7226</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.4382</v>
+        <v>0.5014</v>
       </c>
       <c r="J362" t="n">
-        <v>9.202199999999999</v>
+        <v>10.5294</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.95</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.0677</v>
+        <v>-0.0653</v>
       </c>
       <c r="J363" t="n">
-        <v>-1.4217</v>
+        <v>-1.3713</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3037</v>
+        <v>-0.1953</v>
       </c>
       <c r="J364" t="n">
-        <v>-6.3777</v>
+        <v>-4.1013</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.77</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.397</v>
+        <v>-0.255</v>
       </c>
       <c r="J365" t="n">
-        <v>-8.337</v>
+        <v>-5.355</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.68</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5233</v>
+        <v>-0.3416</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.9893</v>
+        <v>-7.1736</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.58</v>
       </c>
       <c r="I367" t="n">
-        <v>1.382</v>
+        <v>1.2447</v>
       </c>
       <c r="J367" t="n">
-        <v>29.022</v>
+        <v>26.1387</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6738</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J368" t="n">
-        <v>14.1498</v>
+        <v>14.2569</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.3252</v>
+        <v>0.386</v>
       </c>
       <c r="J369" t="n">
-        <v>6.8292</v>
+        <v>8.106</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.13</v>
       </c>
       <c r="I370" t="n">
-        <v>0.3252</v>
+        <v>0.386</v>
       </c>
       <c r="J370" t="n">
-        <v>6.8292</v>
+        <v>8.106</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.88</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5286</v>
+        <v>-0.459</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.1006</v>
+        <v>-9.638999999999999</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.03</v>
       </c>
       <c r="I372" t="n">
-        <v>0.1477</v>
+        <v>0.1265</v>
       </c>
       <c r="J372" t="n">
-        <v>2.954</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>0.0655</v>
+        <v>0.03</v>
       </c>
       <c r="J373" t="n">
-        <v>1.31</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0388</v>
+        <v>-0.0497</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.776</v>
+        <v>-0.994</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.72</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.4637</v>
+        <v>-0.3011</v>
       </c>
       <c r="J375" t="n">
-        <v>-9.273999999999999</v>
+        <v>-6.022</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.64</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.3769</v>
       </c>
       <c r="J376" t="n">
-        <v>-11.442</v>
+        <v>-7.538</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.35</v>
       </c>
       <c r="I377" t="n">
-        <v>0.8933</v>
+        <v>0.9001</v>
       </c>
       <c r="J377" t="n">
-        <v>17.866</v>
+        <v>18.002</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.32</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8248</v>
+        <v>0.8327</v>
       </c>
       <c r="J378" t="n">
-        <v>16.496</v>
+        <v>16.654</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.28</v>
       </c>
       <c r="I379" t="n">
-        <v>0.729</v>
+        <v>0.7415</v>
       </c>
       <c r="J379" t="n">
-        <v>14.58</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.13</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3091</v>
+        <v>0.3793</v>
       </c>
       <c r="J380" t="n">
-        <v>6.182</v>
+        <v>7.586</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.04</v>
       </c>
       <c r="I381" t="n">
-        <v>0.0406</v>
+        <v>0.1133</v>
       </c>
       <c r="J381" t="n">
-        <v>0.8120000000000001</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.52</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2262</v>
+        <v>1.1501</v>
       </c>
       <c r="J382" t="n">
-        <v>23.2978</v>
+        <v>21.8519</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.46</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1043</v>
+        <v>1.0746</v>
       </c>
       <c r="J383" t="n">
-        <v>20.9817</v>
+        <v>20.4174</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.16</v>
       </c>
       <c r="I384" t="n">
-        <v>0.3658</v>
+        <v>0.4468</v>
       </c>
       <c r="J384" t="n">
-        <v>6.9502</v>
+        <v>8.4892</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2865</v>
+        <v>0.3679</v>
       </c>
       <c r="J385" t="n">
-        <v>5.4435</v>
+        <v>6.9901</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.1</v>
       </c>
       <c r="I386" t="n">
-        <v>0.2043</v>
+        <v>0.2851</v>
       </c>
       <c r="J386" t="n">
-        <v>3.8817</v>
+        <v>5.4169</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.28</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5384</v>
+        <v>0.6383</v>
       </c>
       <c r="J387" t="n">
-        <v>10.2296</v>
+        <v>12.1277</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.063</v>
+        <v>0.028</v>
       </c>
       <c r="J388" t="n">
-        <v>1.197</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.77</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.393</v>
+        <v>-0.2534</v>
       </c>
       <c r="J389" t="n">
-        <v>-7.467</v>
+        <v>-4.8146</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.75</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4225</v>
+        <v>-0.2729</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.0275</v>
+        <v>-5.1851</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.58</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.65</v>
+        <v>-0.4335</v>
       </c>
       <c r="J391" t="n">
-        <v>-12.35</v>
+        <v>-8.236499999999999</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.36</v>
       </c>
       <c r="I392" t="n">
-        <v>0.6672</v>
+        <v>0.8258</v>
       </c>
       <c r="J392" t="n">
-        <v>10.6752</v>
+        <v>13.2128</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.77</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.3673</v>
+        <v>-0.2452</v>
       </c>
       <c r="J393" t="n">
-        <v>-5.8768</v>
+        <v>-3.9232</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.7</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.4739</v>
+        <v>-0.3122</v>
       </c>
       <c r="J394" t="n">
-        <v>-7.5824</v>
+        <v>-4.9952</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.63</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.571</v>
+        <v>-0.3784</v>
       </c>
       <c r="J395" t="n">
-        <v>-9.135999999999999</v>
+        <v>-6.0544</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.6</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.6107</v>
+        <v>-0.4064</v>
       </c>
       <c r="J396" t="n">
-        <v>-9.7712</v>
+        <v>-6.5024</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.74</v>
       </c>
       <c r="I397" t="n">
-        <v>1.6003</v>
+        <v>1.3966</v>
       </c>
       <c r="J397" t="n">
-        <v>25.6048</v>
+        <v>22.3456</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.64</v>
       </c>
       <c r="I398" t="n">
-        <v>1.4162</v>
+        <v>1.278</v>
       </c>
       <c r="J398" t="n">
-        <v>22.6592</v>
+        <v>20.448</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.22</v>
       </c>
       <c r="I399" t="n">
-        <v>0.4769</v>
+        <v>0.5762</v>
       </c>
       <c r="J399" t="n">
-        <v>7.6304</v>
+        <v>9.219200000000001</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.14</v>
       </c>
       <c r="I400" t="n">
-        <v>0.2791</v>
+        <v>0.3738</v>
       </c>
       <c r="J400" t="n">
-        <v>4.4656</v>
+        <v>5.9808</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.09</v>
       </c>
       <c r="I401" t="n">
-        <v>0.1455</v>
+        <v>0.2354</v>
       </c>
       <c r="J401" t="n">
-        <v>2.328</v>
+        <v>3.7664</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>0.8111</v>
+        <v>1.0074</v>
       </c>
       <c r="J402" t="n">
-        <v>24.333</v>
+        <v>30.222</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.18</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3679</v>
+        <v>0.4142</v>
       </c>
       <c r="J403" t="n">
-        <v>11.037</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.82</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.3444</v>
+        <v>-0.2144</v>
       </c>
       <c r="J404" t="n">
-        <v>-10.332</v>
+        <v>-6.432</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.76</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.4315</v>
+        <v>-0.2741</v>
       </c>
       <c r="J405" t="n">
-        <v>-12.945</v>
+        <v>-8.223000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.52</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.736</v>
+        <v>-0.4979</v>
       </c>
       <c r="J406" t="n">
-        <v>-22.08</v>
+        <v>-14.937</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.64</v>
       </c>
       <c r="I407" t="n">
-        <v>1.5236</v>
+        <v>1.3378</v>
       </c>
       <c r="J407" t="n">
-        <v>45.708</v>
+        <v>40.134</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.3</v>
       </c>
       <c r="I408" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8129</v>
       </c>
       <c r="J408" t="n">
-        <v>24.813</v>
+        <v>24.387</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.07</v>
       </c>
       <c r="I409" t="n">
-        <v>0.1783</v>
+        <v>0.2298</v>
       </c>
       <c r="J409" t="n">
-        <v>5.349</v>
+        <v>6.894</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.97</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2376</v>
+        <v>-0.166</v>
       </c>
       <c r="J410" t="n">
-        <v>-7.128</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.71</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.9202</v>
+        <v>-0.8859</v>
       </c>
       <c r="J411" t="n">
-        <v>-27.606</v>
+        <v>-26.577</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.23</v>
       </c>
       <c r="I412" t="n">
-        <v>0.6702</v>
+        <v>0.6511</v>
       </c>
       <c r="J412" t="n">
-        <v>19.4358</v>
+        <v>18.8819</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.2</v>
       </c>
       <c r="I413" t="n">
-        <v>0.5939</v>
+        <v>0.5772</v>
       </c>
       <c r="J413" t="n">
-        <v>17.2231</v>
+        <v>16.7388</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.07</v>
       </c>
       <c r="I414" t="n">
-        <v>0.1894</v>
+        <v>0.2339</v>
       </c>
       <c r="J414" t="n">
-        <v>5.4926</v>
+        <v>6.7831</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.05</v>
       </c>
       <c r="I415" t="n">
-        <v>0.1228</v>
+        <v>0.1719</v>
       </c>
       <c r="J415" t="n">
-        <v>3.5612</v>
+        <v>4.9851</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.1228</v>
+        <v>0.1719</v>
       </c>
       <c r="J416" t="n">
-        <v>3.5612</v>
+        <v>4.9851</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.5332</v>
+        <v>0.6345</v>
       </c>
       <c r="J417" t="n">
-        <v>15.4628</v>
+        <v>18.4005</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.21</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3979</v>
+        <v>0.457</v>
       </c>
       <c r="J418" t="n">
-        <v>11.5391</v>
+        <v>13.253</v>
       </c>
     </row>
     <row r="419">
@@ -20069,10 +20069,10 @@
         <v>0.76</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4399</v>
+        <v>-0.2786</v>
       </c>
       <c r="J420" t="n">
-        <v>-12.7571</v>
+        <v>-8.0794</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.72</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.494</v>
+        <v>-0.3172</v>
       </c>
       <c r="J421" t="n">
-        <v>-14.326</v>
+        <v>-9.1988</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.77</v>
       </c>
       <c r="I422" t="n">
-        <v>1.6506</v>
+        <v>1.4299</v>
       </c>
       <c r="J422" t="n">
-        <v>31.3614</v>
+        <v>27.1681</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.37</v>
       </c>
       <c r="I423" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.9122</v>
       </c>
       <c r="J423" t="n">
-        <v>15.8498</v>
+        <v>17.3318</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8071</v>
+        <v>0.8918</v>
       </c>
       <c r="J424" t="n">
-        <v>15.3349</v>
+        <v>16.9442</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.26</v>
       </c>
       <c r="I425" t="n">
-        <v>0.5685</v>
+        <v>0.6695</v>
       </c>
       <c r="J425" t="n">
-        <v>10.8015</v>
+        <v>12.7205</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.1979</v>
+        <v>0.2905</v>
       </c>
       <c r="J426" t="n">
-        <v>3.7601</v>
+        <v>5.5195</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.06</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2846</v>
+        <v>0.297</v>
       </c>
       <c r="J427" t="n">
-        <v>5.4074</v>
+        <v>5.643</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.82</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.2031</v>
+        <v>-0.177</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.8589</v>
+        <v>-3.363</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.4646</v>
+        <v>-0.3232</v>
       </c>
       <c r="J429" t="n">
-        <v>-8.827400000000001</v>
+        <v>-6.1408</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.51</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.6967</v>
+        <v>-0.4721</v>
       </c>
       <c r="J430" t="n">
-        <v>-13.2373</v>
+        <v>-8.969900000000001</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.4</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.8361</v>
+        <v>-0.575</v>
       </c>
       <c r="J431" t="n">
-        <v>-15.8859</v>
+        <v>-10.925</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5089</v>
+        <v>5.57</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0496</v>
+        <v>1.0612</v>
       </c>
       <c r="D2" t="n">
-        <v>1.849</v>
+        <v>1.9114</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5089</v>
+        <v>5.57</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6538</v>
+        <v>2.5735</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8551</v>
+        <v>2.9965</v>
       </c>
       <c r="H2" t="n">
-        <v>3.864</v>
+        <v>3.5967</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0091</v>
+        <v>1.9422</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8551</v>
+        <v>2.9965</v>
       </c>
       <c r="K2" t="n">
         <v>112</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8642</v>
+        <v>4.9387</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1024</v>
+        <v>5.2198</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9721</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6655</v>
+        <v>1.752</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1024</v>
+        <v>5.2198</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4741</v>
+        <v>2.3611</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6283</v>
+        <v>2.8587</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4741</v>
+        <v>2.4428</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5758</v>
+        <v>2.5057</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6283</v>
+        <v>2.8587</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -575,7 +575,7 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2041</v>
+        <v>5.3644</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6647</v>
+        <v>4.7046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8887</v>
+        <v>0.8963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4679</v>
+        <v>1.5174</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6647</v>
+        <v>4.7046</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8421</v>
+        <v>3.84</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8226</v>
+        <v>0.8646</v>
       </c>
       <c r="H4" t="n">
-        <v>8.0509</v>
+        <v>7.7755</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1861</v>
+        <v>4.1987</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8226</v>
+        <v>0.8646</v>
       </c>
       <c r="K4" t="n">
         <v>96</v>
@@ -621,7 +621,7 @@
         <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>5.008699999999999</v>
+        <v>5.0633</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3814</v>
+        <v>4.4583</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8347</v>
+        <v>0.8494</v>
       </c>
       <c r="D5" t="n">
-        <v>1.34</v>
+        <v>1.4053</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3814</v>
+        <v>4.4583</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5822</v>
+        <v>1.6391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7992</v>
+        <v>2.8192</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1351</v>
+        <v>1.6391</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7099</v>
+        <v>1.6813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7992</v>
+        <v>2.8192</v>
       </c>
       <c r="K5" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5091</v>
+        <v>4.5005</v>
       </c>
       <c r="N5" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3052</v>
+        <v>4.4307</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8202</v>
+        <v>0.8441</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3056</v>
+        <v>1.3927</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3052</v>
+        <v>4.4307</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0222</v>
+        <v>3.4751</v>
       </c>
       <c r="G6" t="n">
-        <v>1.283</v>
+        <v>0.9556</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2765</v>
+        <v>6.5714</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2765</v>
+        <v>3.5485</v>
       </c>
       <c r="J6" t="n">
-        <v>1.283</v>
+        <v>0.9556</v>
       </c>
       <c r="K6" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5595</v>
+        <v>4.5041</v>
       </c>
       <c r="N6" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.289</v>
+        <v>4.1633</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8171</v>
+        <v>0.7932</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2983</v>
+        <v>1.271</v>
       </c>
       <c r="E7" t="n">
-        <v>4.289</v>
+        <v>4.1633</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5535</v>
+        <v>3.4733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7355</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>7.0341</v>
+        <v>6.5657</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6574</v>
+        <v>3.5454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7355</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>112</v>
@@ -759,7 +759,7 @@
         <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3929</v>
+        <v>4.2354</v>
       </c>
       <c r="N7" t="n">
         <v>259</v>
@@ -768,173 +768,173 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2504</v>
+        <v>4.1397</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8098</v>
+        <v>0.7887</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2808</v>
+        <v>1.2603</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2504</v>
+        <v>4.1397</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6568</v>
+        <v>2.7114</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5936</v>
+        <v>1.4283</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6568</v>
+        <v>3.2095</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7249</v>
+        <v>3.2095</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5936</v>
+        <v>1.4283</v>
       </c>
       <c r="K8" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3185</v>
+        <v>4.637799999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9082</v>
+        <v>4.1001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7446</v>
+        <v>0.7812</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1263</v>
+        <v>1.2422</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9082</v>
+        <v>4.1001</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4518</v>
+        <v>1.5897</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5436</v>
+        <v>2.5104</v>
       </c>
       <c r="H9" t="n">
-        <v>10.5175</v>
+        <v>1.5897</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4686</v>
+        <v>1.5897</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5436</v>
+        <v>2.5104</v>
       </c>
       <c r="K9" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M9" t="n">
-        <v>4.925000000000001</v>
+        <v>4.1001</v>
       </c>
       <c r="N9" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8503</v>
+        <v>3.9378</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7336</v>
+        <v>0.7502</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1002</v>
+        <v>1.1684</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8503</v>
+        <v>3.9378</v>
       </c>
       <c r="F10" t="n">
-        <v>3.312</v>
+        <v>4.5147</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5383</v>
+        <v>-0.5769</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9129</v>
+        <v>10.0016</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9129</v>
+        <v>5.4008</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5383</v>
+        <v>-0.5769</v>
       </c>
       <c r="K10" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L10" t="n">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4512</v>
+        <v>4.8239</v>
       </c>
       <c r="N10" t="n">
-        <v>249</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.832</v>
+        <v>3.7328</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7301</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0919</v>
+        <v>1.075</v>
       </c>
       <c r="E11" t="n">
-        <v>3.832</v>
+        <v>3.7328</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6089</v>
+        <v>3.0863</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2231</v>
+        <v>0.6465</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6089</v>
+        <v>4.03</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6089</v>
+        <v>4.03</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2231</v>
+        <v>0.6465</v>
       </c>
       <c r="K11" t="n">
         <v>101</v>
@@ -943,7 +943,7 @@
         <v>148</v>
       </c>
       <c r="M11" t="n">
-        <v>3.832</v>
+        <v>4.6765</v>
       </c>
       <c r="N11" t="n">
         <v>249</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8875</v>
+        <v>2.9985</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5501</v>
+        <v>0.5713</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6655</v>
+        <v>0.7408</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8875</v>
+        <v>2.9985</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8875</v>
+        <v>1.2154</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.7831</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9806</v>
+        <v>1.2154</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9806</v>
+        <v>1.2467</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.7831</v>
       </c>
       <c r="K12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9806</v>
+        <v>3.0298</v>
       </c>
       <c r="N12" t="n">
-        <v>98</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8445</v>
+        <v>2.5658</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5419</v>
+        <v>0.4888</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6461</v>
+        <v>0.5438</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8445</v>
+        <v>2.5658</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2977</v>
+        <v>2.5658</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5468</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2977</v>
+        <v>2.8907</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3511</v>
+        <v>2.8907</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5468</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8979</v>
+        <v>2.8907</v>
       </c>
       <c r="N13" t="n">
-        <v>255</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7002</v>
+        <v>2.4174</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5144</v>
+        <v>0.4606</v>
       </c>
       <c r="D14" t="n">
-        <v>0.581</v>
+        <v>0.4762</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7002</v>
+        <v>2.4174</v>
       </c>
       <c r="F14" t="n">
-        <v>3.076</v>
+        <v>1.4615</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3758</v>
+        <v>0.9559</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3946</v>
+        <v>1.4615</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3946</v>
+        <v>1.4992</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3758</v>
+        <v>0.9559</v>
       </c>
       <c r="K14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L14" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0188</v>
+        <v>2.4551</v>
       </c>
       <c r="N14" t="n">
-        <v>144</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5817</v>
+        <v>2.3774</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4919</v>
+        <v>0.4529</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5275</v>
+        <v>0.458</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5817</v>
+        <v>2.3774</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5817</v>
+        <v>2.3356</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5817</v>
+        <v>2.3869</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5817</v>
+        <v>2.3869</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0418</v>
       </c>
       <c r="K15" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5817</v>
+        <v>2.4287</v>
       </c>
       <c r="N15" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5782</v>
+        <v>2.3723</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4912</v>
+        <v>0.452</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5259</v>
+        <v>0.4557</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5782</v>
+        <v>2.3723</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5782</v>
+        <v>2.3723</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5782</v>
+        <v>2.4674</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5782</v>
+        <v>2.4674</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5782</v>
+        <v>2.4674</v>
       </c>
       <c r="N16" t="n">
         <v>106</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5367</v>
+        <v>2.3681</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4833</v>
+        <v>0.4512</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5072</v>
+        <v>0.4538</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5367</v>
+        <v>2.3681</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8401</v>
+        <v>2.3681</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3034</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8767</v>
+        <v>2.458</v>
       </c>
       <c r="I17" t="n">
-        <v>2.995</v>
+        <v>2.458</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3034</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L17" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6916</v>
+        <v>2.458</v>
       </c>
       <c r="N17" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4874</v>
+        <v>2.3615</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4739</v>
+        <v>0.4499</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4849</v>
+        <v>0.4508</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4874</v>
+        <v>2.3615</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4266</v>
+        <v>2.7602</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0608</v>
+        <v>-0.3987</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4266</v>
+        <v>3.3163</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4266</v>
+        <v>3.3163</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0608</v>
+        <v>-0.3987</v>
       </c>
       <c r="K18" t="n">
         <v>101</v>
@@ -1265,7 +1265,7 @@
         <v>43</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4874</v>
+        <v>2.9176</v>
       </c>
       <c r="N18" t="n">
         <v>144</v>
@@ -1274,277 +1274,277 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.391</v>
+        <v>2.2929</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4555</v>
+        <v>0.4368</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4414</v>
+        <v>0.4196</v>
       </c>
       <c r="E19" t="n">
-        <v>2.391</v>
+        <v>2.2929</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5193</v>
+        <v>1.943</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8717</v>
+        <v>0.3499</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5193</v>
+        <v>1.943</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5818</v>
+        <v>1.943</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8717</v>
+        <v>0.3499</v>
       </c>
       <c r="K19" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L19" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4535</v>
+        <v>2.2929</v>
       </c>
       <c r="N19" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2878</v>
+        <v>2.2779</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4359</v>
+        <v>0.434</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3948</v>
+        <v>0.4127</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2878</v>
+        <v>2.2779</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7156</v>
+        <v>2.051</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4278</v>
+        <v>0.2269</v>
       </c>
       <c r="H20" t="n">
-        <v>4.0817</v>
+        <v>2.051</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1223</v>
+        <v>2.1039</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4278</v>
+        <v>0.2269</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L20" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6945</v>
+        <v>2.3308</v>
       </c>
       <c r="N20" t="n">
-        <v>259</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.287</v>
+        <v>2.1993</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4357</v>
+        <v>0.419</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3945</v>
+        <v>0.377</v>
       </c>
       <c r="E21" t="n">
-        <v>2.287</v>
+        <v>2.1993</v>
       </c>
       <c r="F21" t="n">
-        <v>2.287</v>
+        <v>2.5107</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3114</v>
       </c>
       <c r="H21" t="n">
-        <v>2.287</v>
+        <v>2.7703</v>
       </c>
       <c r="I21" t="n">
-        <v>2.287</v>
+        <v>2.8417</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3114</v>
       </c>
       <c r="K21" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M21" t="n">
-        <v>2.287</v>
+        <v>2.5303</v>
       </c>
       <c r="N21" t="n">
-        <v>107</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2858</v>
+        <v>2.1831</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4355</v>
+        <v>0.4159</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3939</v>
+        <v>0.3696</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2858</v>
+        <v>2.1831</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2858</v>
+        <v>2.6277</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4446</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2858</v>
+        <v>3.7754</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2858</v>
+        <v>2.0387</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4446</v>
       </c>
       <c r="K22" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2858</v>
+        <v>1.5941</v>
       </c>
       <c r="N22" t="n">
-        <v>110</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2644</v>
+        <v>2.1787</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4314</v>
+        <v>0.4151</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3842</v>
+        <v>0.3676</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2644</v>
+        <v>2.1787</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0446</v>
+        <v>2.1787</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2198</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0446</v>
+        <v>2.1787</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1287</v>
+        <v>2.1787</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2198</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L23" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.3485</v>
+        <v>2.1787</v>
       </c>
       <c r="N23" t="n">
-        <v>169</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1677</v>
+        <v>2.1271</v>
       </c>
       <c r="C24" t="n">
-        <v>0.413</v>
+        <v>0.4053</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3406</v>
+        <v>0.3441</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1677</v>
+        <v>2.1271</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9509</v>
+        <v>2.1271</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2168</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9509</v>
+        <v>2.1271</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9509</v>
+        <v>2.1271</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2168</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.1677</v>
+        <v>2.1271</v>
       </c>
       <c r="N24" t="n">
-        <v>249</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4075</v>
+        <v>0.3981</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3277</v>
+        <v>0.327</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1391</v>
+        <v>2.0895</v>
       </c>
       <c r="N25" t="n">
         <v>103</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.0019</v>
+        <v>2.0036</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3814</v>
+        <v>0.3817</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2657</v>
+        <v>0.2879</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0019</v>
+        <v>2.0036</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3976</v>
+        <v>1.3871</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6165</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3976</v>
+        <v>1.3871</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4551</v>
+        <v>1.4228</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6165</v>
       </c>
       <c r="K26" t="n">
         <v>101</v>
@@ -1633,7 +1633,7 @@
         <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>2.0594</v>
+        <v>2.0393</v>
       </c>
       <c r="N26" t="n">
         <v>169</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.944</v>
+        <v>1.9365</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3704</v>
+        <v>0.3689</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2396</v>
+        <v>0.2573</v>
       </c>
       <c r="E27" t="n">
-        <v>1.944</v>
+        <v>1.9365</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8859</v>
+        <v>1.8955</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0581</v>
+        <v>0.041</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8859</v>
+        <v>1.8955</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8859</v>
+        <v>1.8955</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0581</v>
+        <v>0.041</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.944</v>
+        <v>1.9365</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9421</v>
+        <v>1.8622</v>
       </c>
       <c r="C28" t="n">
-        <v>0.37</v>
+        <v>0.3548</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2387</v>
+        <v>0.2235</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9421</v>
+        <v>1.8622</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3325</v>
+        <v>2.2768</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3904</v>
+        <v>-0.4146</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3325</v>
+        <v>2.2768</v>
       </c>
       <c r="I28" t="n">
-        <v>2.3325</v>
+        <v>2.2768</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3904</v>
+        <v>-0.4146</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
@@ -1725,7 +1725,7 @@
         <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9421</v>
+        <v>1.8622</v>
       </c>
       <c r="N28" t="n">
         <v>144</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9188</v>
+        <v>1.8112</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3656</v>
+        <v>0.3451</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2282</v>
+        <v>0.2003</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9188</v>
+        <v>1.8112</v>
       </c>
       <c r="F29" t="n">
-        <v>2.853</v>
+        <v>2.7612</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9342</v>
+        <v>-0.95</v>
       </c>
       <c r="H29" t="n">
-        <v>4.566</v>
+        <v>4.216</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3741</v>
+        <v>2.2766</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9342</v>
+        <v>-0.95</v>
       </c>
       <c r="K29" t="n">
         <v>96</v>
@@ -1771,7 +1771,7 @@
         <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4399</v>
+        <v>1.3266</v>
       </c>
       <c r="N29" t="n">
         <v>136</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5044</v>
+        <v>1.5651</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2866</v>
+        <v>0.2982</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0411</v>
+        <v>0.0883</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5044</v>
+        <v>1.5651</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5044</v>
+        <v>0.3609</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.2042</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5044</v>
+        <v>0.3609</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5044</v>
+        <v>0.3702</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.2042</v>
       </c>
       <c r="K30" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5044</v>
+        <v>1.5744</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2853</v>
+        <v>0.2784</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0379</v>
+        <v>0.0411</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4973</v>
+        <v>1.4614</v>
       </c>
       <c r="N31" t="n">
         <v>92</v>
@@ -1872,415 +1872,415 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4822</v>
+        <v>1.4544</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2824</v>
+        <v>0.2771</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0311</v>
+        <v>0.0379</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4822</v>
+        <v>1.4544</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3861</v>
+        <v>1.4544</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0961</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3861</v>
+        <v>1.4544</v>
       </c>
       <c r="I32" t="n">
-        <v>0.402</v>
+        <v>1.4544</v>
       </c>
       <c r="J32" t="n">
-        <v>1.0961</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L32" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4981</v>
+        <v>1.4544</v>
       </c>
       <c r="N32" t="n">
-        <v>169</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>MistR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="C33" t="n">
-        <v>0.238</v>
+        <v>0.2239</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.074</v>
+        <v>-0.0893</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2494</v>
+        <v>1.175</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MistR</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2373</v>
+        <v>0.2226</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0757</v>
+        <v>-0.0924</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2455</v>
+        <v>1.1682</v>
       </c>
       <c r="N34" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1224</v>
+        <v>1.1658</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2138</v>
+        <v>0.2221</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1313</v>
+        <v>-0.0935</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1224</v>
+        <v>1.1658</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1224</v>
+        <v>-0.4697</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.6355</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1224</v>
+        <v>-0.4697</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1224</v>
+        <v>-0.4697</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.6355</v>
       </c>
       <c r="K35" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1224</v>
+        <v>1.1658</v>
       </c>
       <c r="N35" t="n">
-        <v>98</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2104</v>
+        <v>0.2031</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1393</v>
+        <v>-0.1389</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1046</v>
+        <v>1.066</v>
       </c>
       <c r="N36" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9506</v>
+        <v>1.0035</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1811</v>
+        <v>0.1912</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2089</v>
+        <v>-0.1674</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9506</v>
+        <v>1.0035</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1075</v>
+        <v>1.0035</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1569</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1075</v>
+        <v>1.0035</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1075</v>
+        <v>1.0035</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1569</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9505999999999999</v>
+        <v>1.0035</v>
       </c>
       <c r="N37" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8942</v>
+        <v>0.9457</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1704</v>
+        <v>0.1802</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2343</v>
+        <v>-0.1937</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8942</v>
+        <v>0.9457</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5505</v>
+        <v>1.1192</v>
       </c>
       <c r="G38" t="n">
-        <v>1.4447</v>
+        <v>-0.1735</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5505</v>
+        <v>1.1192</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5505</v>
+        <v>1.1192</v>
       </c>
       <c r="J38" t="n">
-        <v>1.4447</v>
+        <v>-0.1735</v>
       </c>
       <c r="K38" t="n">
         <v>101</v>
       </c>
       <c r="L38" t="n">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8942000000000001</v>
+        <v>0.9457</v>
       </c>
       <c r="N38" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="C39" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2519</v>
+        <v>-0.2395</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="N39" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1519</v>
+        <v>0.1535</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2781</v>
+        <v>-0.2573</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7973</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0902</v>
+        <v>0.0751</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4243</v>
+        <v>-0.4447</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4734</v>
+        <v>0.3944</v>
       </c>
       <c r="N41" t="n">
         <v>92</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0893</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4265</v>
+        <v>-0.4475</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4686</v>
+        <v>0.3881</v>
       </c>
       <c r="N42" t="n">
         <v>103</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0772</v>
+        <v>0.0655</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4551</v>
+        <v>-0.4677</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4051</v>
+        <v>0.3439</v>
       </c>
       <c r="N43" t="n">
         <v>106</v>
@@ -2424,93 +2424,93 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0521</v>
+        <v>0.0525</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4988</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2733</v>
+        <v>0.2755</v>
       </c>
       <c r="N44" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0489</v>
+        <v>0.0358</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5222</v>
+        <v>-0.5386</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2565</v>
+        <v>0.1881</v>
       </c>
       <c r="N45" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0486</v>
+        <v>0.032</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5229</v>
+        <v>-0.5478</v>
       </c>
       <c r="E46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="F46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="I46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.255</v>
+        <v>0.1679</v>
       </c>
       <c r="N46" t="n">
         <v>92</v>
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0149</v>
+        <v>0.0142</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6028</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0781</v>
+        <v>0.0746</v>
       </c>
       <c r="N47" t="n">
         <v>103</v>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2191</v>
+        <v>0.0707</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0417</v>
+        <v>0.0135</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.7369</v>
+        <v>-0.592</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2191</v>
+        <v>0.0707</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.8637</v>
+        <v>-2.5306</v>
       </c>
       <c r="G48" t="n">
-        <v>2.6446</v>
+        <v>2.6013</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.8637</v>
+        <v>-2.5306</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.489</v>
+        <v>-1.3665</v>
       </c>
       <c r="J48" t="n">
-        <v>2.6446</v>
+        <v>2.6013</v>
       </c>
       <c r="K48" t="n">
         <v>112</v>
@@ -2645,7 +2645,7 @@
         <v>147</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1556</v>
+        <v>1.2348</v>
       </c>
       <c r="N48" t="n">
         <v>259</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0596</v>
+        <v>-0.0629</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7792</v>
+        <v>-0.7744</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.3127</v>
+        <v>-0.33</v>
       </c>
       <c r="N49" t="n">
         <v>110</v>
@@ -2700,323 +2700,323 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.5185</v>
+        <v>-0.334</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0988</v>
+        <v>-0.0636</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8721</v>
+        <v>-0.7762</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5185</v>
+        <v>-0.334</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.5185</v>
+        <v>-0.1288</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.2052</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.5185</v>
+        <v>-0.1288</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5185</v>
+        <v>-0.1321</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.2052</v>
       </c>
       <c r="K50" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.5185</v>
+        <v>-0.3373</v>
       </c>
       <c r="N50" t="n">
-        <v>106</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.5628</v>
+        <v>-0.3953</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1072</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8921</v>
+        <v>-0.8042</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5628</v>
+        <v>-0.3953</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5628</v>
+        <v>-0.5928</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.1975</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5628</v>
+        <v>-0.5928</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5628</v>
+        <v>-0.3201</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.1975</v>
       </c>
       <c r="K51" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.5628</v>
+        <v>-0.1226</v>
       </c>
       <c r="N51" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5875</v>
+        <v>-0.5251</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1119</v>
+        <v>-0.1</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9032</v>
+        <v>-0.8632</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5875</v>
+        <v>-0.5251</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1697</v>
+        <v>-0.5251</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4178</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1697</v>
+        <v>-0.5251</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1767</v>
+        <v>-0.5251</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4178</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5945</v>
+        <v>-0.5251</v>
       </c>
       <c r="N52" t="n">
-        <v>255</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1138</v>
+        <v>-0.1174</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9076</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.5971</v>
+        <v>-0.6161</v>
       </c>
       <c r="N53" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1215</v>
+        <v>-0.1188</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.9079</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6377</v>
+        <v>-0.6233</v>
       </c>
       <c r="N54" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1319</v>
+        <v>-0.1289</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9506</v>
+        <v>-0.9322</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.6925</v>
+        <v>-0.6766</v>
       </c>
       <c r="N55" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.8563</v>
+        <v>-0.7171</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1631</v>
+        <v>-0.1366</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.0246</v>
+        <v>-0.9506</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.8563</v>
+        <v>-0.7171</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.0805</v>
+        <v>-0.7171</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2242</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.0805</v>
+        <v>-0.7171</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5618</v>
+        <v>-0.7171</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2242</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L56" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3376</v>
+        <v>-0.7171</v>
       </c>
       <c r="N56" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2172</v>
+        <v>-0.2199</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1528</v>
+        <v>-1.1496</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.1402</v>
+        <v>-1.1542</v>
       </c>
       <c r="N57" t="n">
         <v>107</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2202</v>
+        <v>-0.2255</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1598</v>
+        <v>-1.1631</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.1559</v>
+        <v>-1.1838</v>
       </c>
       <c r="N58" t="n">
         <v>98</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2236</v>
+        <v>-0.2297</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1679</v>
+        <v>-1.1731</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.1737</v>
+        <v>-1.2058</v>
       </c>
       <c r="N59" t="n">
         <v>107</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.8028</v>
+        <v>-2.7303</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.534</v>
+        <v>-0.5202</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.9033</v>
+        <v>-1.8671</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.8028</v>
+        <v>-2.7303</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.8028</v>
+        <v>-1.7303</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.8028</v>
+        <v>-1.7303</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.8769</v>
+        <v>-1.7749</v>
       </c>
       <c r="J60" t="n">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>68</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.8769</v>
+        <v>-2.7749</v>
       </c>
       <c r="N60" t="n">
         <v>169</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-4.1305</v>
+        <v>-3.8184</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.7869</v>
+        <v>-0.7275</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.5027</v>
+        <v>-2.3624</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.1305</v>
+        <v>-3.8184</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.5407</v>
+        <v>-3.2128</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.5898</v>
+        <v>-0.6056</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.5407</v>
+        <v>-3.2128</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.841</v>
+        <v>-1.7349</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.5898</v>
+        <v>-0.6056</v>
       </c>
       <c r="K61" t="n">
         <v>96</v>
@@ -3243,7 +3243,7 @@
         <v>40</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.4308</v>
+        <v>-2.3405</v>
       </c>
       <c r="N61" t="n">
         <v>136</v>
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5743</v>
+        <v>0.5606</v>
       </c>
       <c r="J2" t="n">
-        <v>16.0804</v>
+        <v>15.6968</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0731</v>
+        <v>-0.0839</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.0468</v>
+        <v>-2.3492</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.174</v>
+        <v>-0.1882</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.872</v>
+        <v>-5.2696</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1845</v>
+        <v>-0.1988</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.166</v>
+        <v>-5.5664</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2153</v>
+        <v>-0.2296</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.0284</v>
+        <v>-6.4288</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8285</v>
+        <v>0.8128</v>
       </c>
       <c r="J7" t="n">
-        <v>23.198</v>
+        <v>22.7584</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2484</v>
+        <v>0.2654</v>
       </c>
       <c r="J8" t="n">
-        <v>6.9552</v>
+        <v>7.4312</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.157</v>
+        <v>0.1738</v>
       </c>
       <c r="J9" t="n">
-        <v>4.396</v>
+        <v>4.8664</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0146</v>
+        <v>-0.0112</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4088</v>
+        <v>-0.3136</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2153</v>
+        <v>-0.2252</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.0284</v>
+        <v>-6.3056</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.138</v>
+        <v>1.1355</v>
       </c>
       <c r="J12" t="n">
-        <v>22.76</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7439</v>
+        <v>0.7099</v>
       </c>
       <c r="J13" t="n">
-        <v>14.878</v>
+        <v>14.198</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6745</v>
+        <v>0.6484</v>
       </c>
       <c r="J14" t="n">
-        <v>13.49</v>
+        <v>12.968</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4598</v>
+        <v>0.4549</v>
       </c>
       <c r="J15" t="n">
-        <v>9.196</v>
+        <v>9.098000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.464</v>
+        <v>-0.4347</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.279999999999999</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5382</v>
+        <v>0.5172</v>
       </c>
       <c r="J17" t="n">
-        <v>10.764</v>
+        <v>10.344</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3637</v>
+        <v>0.3558</v>
       </c>
       <c r="J18" t="n">
-        <v>7.274</v>
+        <v>7.116</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0631</v>
+        <v>0.0616</v>
       </c>
       <c r="J19" t="n">
-        <v>1.262</v>
+        <v>1.232</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4536</v>
+        <v>-0.4625</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.071999999999999</v>
+        <v>-9.25</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4993</v>
+        <v>-0.5056</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.986000000000001</v>
+        <v>-10.112</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.65</v>
       </c>
       <c r="I22" t="n">
-        <v>1.316</v>
+        <v>1.3944</v>
       </c>
       <c r="J22" t="n">
-        <v>25.004</v>
+        <v>26.4936</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9922</v>
+        <v>0.9385</v>
       </c>
       <c r="J23" t="n">
-        <v>18.8518</v>
+        <v>17.8315</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I24" t="n">
-        <v>0.623</v>
+        <v>0.6035</v>
       </c>
       <c r="J24" t="n">
-        <v>11.837</v>
+        <v>11.4665</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0717</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3623</v>
+        <v>1.8088</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2632</v>
+        <v>-0.2463</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.0008</v>
+        <v>-4.6797</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6427</v>
+        <v>0.6103</v>
       </c>
       <c r="J27" t="n">
-        <v>12.2113</v>
+        <v>11.5957</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1528</v>
+        <v>0.1513</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9032</v>
+        <v>2.8747</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.213</v>
+        <v>-0.23</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.047</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.76</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2622</v>
+        <v>-0.2786</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.9818</v>
+        <v>-5.2934</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5511</v>
+        <v>-0.5548</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.4709</v>
+        <v>-10.5412</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3009</v>
+        <v>0.2878</v>
       </c>
       <c r="J32" t="n">
-        <v>6.018</v>
+        <v>5.756</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2784</v>
+        <v>0.2662</v>
       </c>
       <c r="J33" t="n">
-        <v>5.568</v>
+        <v>5.324</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3102</v>
+        <v>-0.3273</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.204</v>
+        <v>-6.546</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.68</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3292</v>
+        <v>-0.3457</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.584</v>
+        <v>-6.914</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.44</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5522</v>
+        <v>-0.5569</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.044</v>
+        <v>-11.138</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.9627</v>
       </c>
       <c r="J37" t="n">
-        <v>17.43</v>
+        <v>19.254</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.48</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8335</v>
+        <v>0.9218</v>
       </c>
       <c r="J38" t="n">
-        <v>16.67</v>
+        <v>18.436</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.39</v>
+        <v>0.4264</v>
       </c>
       <c r="J39" t="n">
-        <v>7.8</v>
+        <v>8.528</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3419</v>
+        <v>0.3551</v>
       </c>
       <c r="J40" t="n">
-        <v>6.838</v>
+        <v>7.102</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3233</v>
+        <v>-0.3037</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.466</v>
+        <v>-6.074</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5442</v>
+        <v>0.5984</v>
       </c>
       <c r="J42" t="n">
-        <v>10.884</v>
+        <v>11.968</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0376</v>
+        <v>-0.0487</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.752</v>
+        <v>-0.974</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0767</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.534</v>
+        <v>-1.806</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2144</v>
+        <v>-0.2312</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.288</v>
+        <v>-4.624</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.624</v>
+        <v>-0.6227</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.48</v>
+        <v>-12.454</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9145</v>
+        <v>1.0055</v>
       </c>
       <c r="J47" t="n">
-        <v>18.29</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I48" t="n">
-        <v>0.541</v>
+        <v>0.5992</v>
       </c>
       <c r="J48" t="n">
-        <v>10.82</v>
+        <v>11.984</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4132</v>
+        <v>0.4542</v>
       </c>
       <c r="J49" t="n">
-        <v>8.263999999999999</v>
+        <v>9.084</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2525</v>
+        <v>0.2619</v>
       </c>
       <c r="J50" t="n">
-        <v>5.05</v>
+        <v>5.238</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6152</v>
+        <v>-0.5734</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.304</v>
+        <v>-11.468</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8542</v>
+        <v>0.9401</v>
       </c>
       <c r="J52" t="n">
-        <v>17.084</v>
+        <v>18.802</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7621</v>
+        <v>0.8408</v>
       </c>
       <c r="J53" t="n">
-        <v>15.242</v>
+        <v>16.816</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6133</v>
+        <v>0.6786</v>
       </c>
       <c r="J54" t="n">
-        <v>12.266</v>
+        <v>13.572</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.826</v>
+        <v>-1.696</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.1982</v>
+        <v>-1.083</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.964</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4467</v>
+        <v>0.4896</v>
       </c>
       <c r="J57" t="n">
-        <v>8.933999999999999</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4024</v>
+        <v>0.4356</v>
       </c>
       <c r="J58" t="n">
-        <v>8.048</v>
+        <v>8.712</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1364</v>
+        <v>-0.1514</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.728</v>
+        <v>-3.028</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.336</v>
+        <v>-0.3492</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.72</v>
+        <v>-6.984</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4294</v>
+        <v>-0.4389</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.587999999999999</v>
+        <v>-8.778</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3132</v>
+        <v>0.3055</v>
       </c>
       <c r="J62" t="n">
-        <v>5.9508</v>
+        <v>5.8045</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0216</v>
+        <v>-0.0362</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.4104</v>
+        <v>-0.6878</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.72</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.291</v>
+        <v>-0.3087</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.529</v>
+        <v>-5.8653</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3666</v>
+        <v>-0.3817</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.9654</v>
+        <v>-7.2523</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4877</v>
+        <v>-0.4965</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.266299999999999</v>
+        <v>-9.4335</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>2.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8659</v>
+        <v>0.994</v>
       </c>
       <c r="J67" t="n">
-        <v>16.4521</v>
+        <v>18.886</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.448</v>
+        <v>0.5124</v>
       </c>
       <c r="J68" t="n">
-        <v>8.512</v>
+        <v>9.7356</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3367</v>
+        <v>0.3604</v>
       </c>
       <c r="J69" t="n">
-        <v>6.3973</v>
+        <v>6.8476</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1319</v>
+        <v>-0.1364</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.5061</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2093</v>
+        <v>-0.2159</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.9767</v>
+        <v>-4.1021</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5242</v>
+        <v>0.5742</v>
       </c>
       <c r="J72" t="n">
-        <v>21.4922</v>
+        <v>23.5422</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2499</v>
+        <v>0.2526</v>
       </c>
       <c r="J73" t="n">
-        <v>10.2459</v>
+        <v>10.3566</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2195</v>
+        <v>0.2239</v>
       </c>
       <c r="J74" t="n">
-        <v>8.999499999999999</v>
+        <v>9.1799</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="J75" t="n">
-        <v>3.5875</v>
+        <v>3.9114</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6057</v>
+        <v>-0.5717</v>
       </c>
       <c r="J76" t="n">
-        <v>-24.8337</v>
+        <v>-23.4397</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4089</v>
+        <v>0.4513</v>
       </c>
       <c r="J77" t="n">
-        <v>16.7649</v>
+        <v>18.5033</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.377</v>
+        <v>0.4066</v>
       </c>
       <c r="J78" t="n">
-        <v>15.457</v>
+        <v>16.6706</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1536</v>
+        <v>0.1643</v>
       </c>
       <c r="J79" t="n">
-        <v>6.2976</v>
+        <v>6.7363</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0245</v>
+        <v>-0.0283</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.0045</v>
+        <v>-1.1603</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.274</v>
+        <v>-0.2858</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.234</v>
+        <v>-11.7178</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1266</v>
+        <v>1.235</v>
       </c>
       <c r="J82" t="n">
-        <v>21.4054</v>
+        <v>23.465</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9177</v>
+        <v>1.013</v>
       </c>
       <c r="J83" t="n">
-        <v>17.4363</v>
+        <v>19.247</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6363</v>
+        <v>0.7079</v>
       </c>
       <c r="J84" t="n">
-        <v>12.0897</v>
+        <v>13.4501</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1958</v>
+        <v>-0.1812</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.7202</v>
+        <v>-3.4428</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.9122</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.3318</v>
+        <v>-15.8118</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.4123</v>
+        <v>-0.6042</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0363</v>
+        <v>-0.0477</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.6897</v>
+        <v>-0.9063</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1935</v>
+        <v>-0.2105</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.6765</v>
+        <v>-3.9995</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2135</v>
+        <v>-0.2304</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.0565</v>
+        <v>-4.3776</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2529</v>
+        <v>-0.2694</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.8051</v>
+        <v>-5.1186</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9954</v>
+        <v>1.0909</v>
       </c>
       <c r="J92" t="n">
-        <v>23.8896</v>
+        <v>26.1816</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4432</v>
+        <v>0.4888</v>
       </c>
       <c r="J93" t="n">
-        <v>10.6368</v>
+        <v>11.7312</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4286</v>
+        <v>0.4722</v>
       </c>
       <c r="J94" t="n">
-        <v>10.2864</v>
+        <v>11.3328</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0369</v>
+        <v>-0.0254</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.6096</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5473</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.0448</v>
+        <v>-13.1352</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3137</v>
+        <v>0.3112</v>
       </c>
       <c r="J97" t="n">
-        <v>7.5288</v>
+        <v>7.4688</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2516</v>
+        <v>0.2515</v>
       </c>
       <c r="J98" t="n">
-        <v>6.0384</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0566</v>
+        <v>0.0569</v>
       </c>
       <c r="J99" t="n">
-        <v>1.3584</v>
+        <v>1.3656</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3541</v>
+        <v>-0.3669</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.4984</v>
+        <v>-8.8056</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3541</v>
+        <v>-0.3669</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.4984</v>
+        <v>-8.8056</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2794</v>
+        <v>0.267</v>
       </c>
       <c r="J102" t="n">
-        <v>5.0292</v>
+        <v>4.806</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0492</v>
+        <v>-0.0655</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-1.179</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.77</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2433</v>
+        <v>-0.262</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.3794</v>
+        <v>-4.716</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3948</v>
+        <v>-0.4086</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.1064</v>
+        <v>-7.3548</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4321</v>
+        <v>-0.444</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.7778</v>
+        <v>-7.992</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>2.08</v>
       </c>
       <c r="I107" t="n">
-        <v>1.529</v>
+        <v>1.6588</v>
       </c>
       <c r="J107" t="n">
-        <v>27.522</v>
+        <v>29.8584</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>12.0024</v>
+        <v>13.3812</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4093</v>
+        <v>0.4549</v>
       </c>
       <c r="J109" t="n">
-        <v>7.3674</v>
+        <v>8.1882</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.023</v>
+        <v>0.0058</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.414</v>
+        <v>0.1044</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1328</v>
+        <v>-0.1139</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.3904</v>
+        <v>-2.0502</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.99</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8022</v>
+        <v>0.9192</v>
       </c>
       <c r="J112" t="n">
-        <v>16.044</v>
+        <v>18.384</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3143</v>
+        <v>0.3323</v>
       </c>
       <c r="J113" t="n">
-        <v>6.286</v>
+        <v>6.646</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.18</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2553</v>
+        <v>0.2736</v>
       </c>
       <c r="J114" t="n">
-        <v>5.106</v>
+        <v>5.472</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.12</v>
+        <v>0.1384</v>
       </c>
       <c r="J115" t="n">
-        <v>2.4</v>
+        <v>2.768</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4039</v>
+        <v>-0.4094</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.077999999999999</v>
+        <v>-8.188000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4026</v>
+        <v>0.4407</v>
       </c>
       <c r="J117" t="n">
-        <v>8.052</v>
+        <v>8.814</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0803</v>
+        <v>0.0857</v>
       </c>
       <c r="J118" t="n">
-        <v>1.606</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0377</v>
+        <v>0.0404</v>
       </c>
       <c r="J119" t="n">
-        <v>0.754</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1913</v>
+        <v>-0.2064</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.826</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4684</v>
+        <v>-0.4756</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.368</v>
+        <v>-9.512</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3431</v>
+        <v>0.3505</v>
       </c>
       <c r="J122" t="n">
-        <v>10.293</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3431</v>
+        <v>0.3505</v>
       </c>
       <c r="J123" t="n">
-        <v>10.293</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0696</v>
+        <v>0.0759</v>
       </c>
       <c r="J124" t="n">
-        <v>2.088</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1856</v>
+        <v>-0.1997</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.568</v>
+        <v>-5.991</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3053</v>
+        <v>-0.318</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.159000000000001</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5999</v>
+        <v>0.6637</v>
       </c>
       <c r="J127" t="n">
-        <v>17.997</v>
+        <v>19.911</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.28</v>
       </c>
       <c r="I128" t="n">
-        <v>0.586</v>
+        <v>0.6484</v>
       </c>
       <c r="J128" t="n">
-        <v>17.58</v>
+        <v>19.452</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4727</v>
+        <v>0.522</v>
       </c>
       <c r="J129" t="n">
-        <v>14.181</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.37</v>
+        <v>0.3928</v>
       </c>
       <c r="J130" t="n">
-        <v>11.1</v>
+        <v>11.784</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5306</v>
+        <v>-0.4984</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.918</v>
+        <v>-14.952</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2997</v>
+        <v>1.2719</v>
       </c>
       <c r="J132" t="n">
-        <v>29.8931</v>
+        <v>29.2537</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6353</v>
+        <v>0.6118</v>
       </c>
       <c r="J133" t="n">
-        <v>14.6119</v>
+        <v>14.0714</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6353</v>
+        <v>0.6118</v>
       </c>
       <c r="J134" t="n">
-        <v>14.6119</v>
+        <v>14.0714</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J135" t="n">
-        <v>2.07</v>
+        <v>2.484</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7211</v>
+        <v>-0.6671</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.5853</v>
+        <v>-15.3433</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8037</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>18.4851</v>
+        <v>17.6088</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5462</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>12.5626</v>
+        <v>12.2544</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0207</v>
+        <v>-0.0253</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.4761</v>
+        <v>-0.5819</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.7</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3365</v>
+        <v>-0.3479</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.7395</v>
+        <v>-8.0017</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3834</v>
+        <v>-0.3932</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.818199999999999</v>
+        <v>-9.0436</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0566</v>
+        <v>1.0099</v>
       </c>
       <c r="J142" t="n">
-        <v>21.132</v>
+        <v>20.198</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.96</v>
+        <v>0.9039</v>
       </c>
       <c r="J143" t="n">
-        <v>19.2</v>
+        <v>18.078</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.506</v>
+        <v>0.4976</v>
       </c>
       <c r="J144" t="n">
-        <v>10.12</v>
+        <v>9.952</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2945</v>
+        <v>0.3047</v>
       </c>
       <c r="J145" t="n">
-        <v>5.89</v>
+        <v>6.094</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2067</v>
+        <v>0.2229</v>
       </c>
       <c r="J146" t="n">
-        <v>4.134</v>
+        <v>4.458</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.7</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1462</v>
+        <v>1.12</v>
       </c>
       <c r="J147" t="n">
-        <v>22.924</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.21</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4437</v>
+        <v>0.4409</v>
       </c>
       <c r="J148" t="n">
-        <v>8.874000000000001</v>
+        <v>8.818</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.352</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.341</v>
+        <v>-0.3514</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.82</v>
+        <v>-7.028</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3878</v>
+        <v>-0.3966</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.756</v>
+        <v>-7.932</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4604</v>
+        <v>0.446</v>
       </c>
       <c r="J152" t="n">
-        <v>10.1288</v>
+        <v>9.811999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.9888</v>
+        <v>-2.2924</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.102</v>
+        <v>-0.1163</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.244</v>
+        <v>-2.5586</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2061</v>
+        <v>-0.2225</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.5342</v>
+        <v>-4.895</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.408</v>
+        <v>-0.4189</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.976000000000001</v>
+        <v>-9.2158</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3852</v>
+        <v>1.3648</v>
       </c>
       <c r="J157" t="n">
-        <v>30.4744</v>
+        <v>30.0256</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2865</v>
+        <v>1.2603</v>
       </c>
       <c r="J158" t="n">
-        <v>28.303</v>
+        <v>27.7266</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.32</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8327</v>
+        <v>0.7886</v>
       </c>
       <c r="J159" t="n">
-        <v>18.3194</v>
+        <v>17.3492</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.7823</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-17.2106</v>
+        <v>-15.8246</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8811</v>
+        <v>-0.8061</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.3842</v>
+        <v>-17.7342</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.6036</v>
+        <v>1.5975</v>
       </c>
       <c r="J162" t="n">
-        <v>33.6756</v>
+        <v>33.5475</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1336</v>
+        <v>1.0998</v>
       </c>
       <c r="J163" t="n">
-        <v>23.8056</v>
+        <v>23.0958</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6387</v>
+        <v>0.6192</v>
       </c>
       <c r="J164" t="n">
-        <v>13.4127</v>
+        <v>13.0032</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0495</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.4994</v>
+        <v>-1.0395</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6444</v>
+        <v>-0.594</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.5324</v>
+        <v>-12.474</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7089</v>
+        <v>0.671</v>
       </c>
       <c r="J167" t="n">
-        <v>14.8869</v>
+        <v>14.091</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1227</v>
+        <v>-0.1382</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.5767</v>
+        <v>-2.9022</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.88</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1437</v>
+        <v>-0.1598</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.0177</v>
+        <v>-3.3558</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3311</v>
+        <v>-0.3454</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.9531</v>
+        <v>-7.2534</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4062</v>
+        <v>-0.4175</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.530200000000001</v>
+        <v>-8.7675</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2904</v>
+        <v>0.2937</v>
       </c>
       <c r="J172" t="n">
-        <v>6.9696</v>
+        <v>7.0488</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2703</v>
+        <v>0.2746</v>
       </c>
       <c r="J173" t="n">
-        <v>6.4872</v>
+        <v>6.5904</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1422</v>
+        <v>0.15</v>
       </c>
       <c r="J174" t="n">
-        <v>3.4128</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1545</v>
+        <v>-0.1681</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.708</v>
+        <v>-4.0344</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2671</v>
+        <v>-0.2805</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.4104</v>
+        <v>-6.732</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2697</v>
+        <v>1.2387</v>
       </c>
       <c r="J177" t="n">
-        <v>30.4728</v>
+        <v>29.7288</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0485</v>
+        <v>0.9958</v>
       </c>
       <c r="J178" t="n">
-        <v>25.164</v>
+        <v>23.8992</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3946</v>
+        <v>0.3926</v>
       </c>
       <c r="J179" t="n">
-        <v>9.4704</v>
+        <v>9.4224</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4762</v>
+        <v>-0.4491</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.4288</v>
+        <v>-10.7784</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7904</v>
+        <v>-0.7294</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.9696</v>
+        <v>-17.5056</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2682</v>
+        <v>1.2441</v>
       </c>
       <c r="J182" t="n">
-        <v>25.364</v>
+        <v>24.882</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2438</v>
+        <v>1.218</v>
       </c>
       <c r="J183" t="n">
-        <v>24.876</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.28</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7295</v>
+        <v>0.7002</v>
       </c>
       <c r="J184" t="n">
-        <v>14.59</v>
+        <v>14.004</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0956</v>
+        <v>0.1213</v>
       </c>
       <c r="J185" t="n">
-        <v>1.912</v>
+        <v>2.426</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.274</v>
+        <v>-0.2538</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.48</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5344</v>
+        <v>0.5144</v>
       </c>
       <c r="J187" t="n">
-        <v>10.688</v>
+        <v>10.288</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3604</v>
+        <v>0.3534</v>
       </c>
       <c r="J188" t="n">
-        <v>7.208</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.19</v>
+        <v>0.1906</v>
       </c>
       <c r="J189" t="n">
-        <v>3.8</v>
+        <v>3.812</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3712</v>
+        <v>-0.3836</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.424</v>
+        <v>-7.672</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.41</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.59</v>
+        <v>-0.5908</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.8</v>
+        <v>-11.816</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.394</v>
+        <v>0.3937</v>
       </c>
       <c r="J192" t="n">
-        <v>9.456</v>
+        <v>9.4488</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3379</v>
+        <v>0.341</v>
       </c>
       <c r="J193" t="n">
-        <v>8.1096</v>
+        <v>8.183999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.07</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1783</v>
+        <v>0.1878</v>
       </c>
       <c r="J194" t="n">
-        <v>4.2792</v>
+        <v>4.5072</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.1792</v>
+        <v>-2.4264</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.252</v>
+        <v>-0.2646</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.048</v>
+        <v>-6.3504</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.36</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9836</v>
+        <v>0.9157</v>
       </c>
       <c r="J197" t="n">
-        <v>23.6064</v>
+        <v>21.9768</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7755</v>
+        <v>0.7275</v>
       </c>
       <c r="J198" t="n">
-        <v>18.612</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3333</v>
+        <v>0.3312</v>
       </c>
       <c r="J199" t="n">
-        <v>7.9992</v>
+        <v>7.9488</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1774</v>
+        <v>-0.1777</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.2576</v>
+        <v>-4.2648</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.2222</v>
+        <v>-1.1069</v>
       </c>
       <c r="J201" t="n">
-        <v>-29.3328</v>
+        <v>-26.5656</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0027</v>
+        <v>-0.0169</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.0513</v>
+        <v>-0.3211</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0713</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.3547</v>
+        <v>-1.6986</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.1021</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.5884</v>
+        <v>-1.9399</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3831</v>
+        <v>-0.3978</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.2789</v>
+        <v>-7.5582</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5466</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.2752</v>
+        <v>-10.3854</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.66</v>
       </c>
       <c r="I207" t="n">
-        <v>1.292</v>
+        <v>1.2739</v>
       </c>
       <c r="J207" t="n">
-        <v>24.548</v>
+        <v>24.2041</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.65</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2803</v>
+        <v>1.2614</v>
       </c>
       <c r="J208" t="n">
-        <v>24.3257</v>
+        <v>23.9666</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I209" t="n">
-        <v>1.1736</v>
+        <v>1.1471</v>
       </c>
       <c r="J209" t="n">
-        <v>22.2984</v>
+        <v>21.7949</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.415</v>
+        <v>0.4238</v>
       </c>
       <c r="J210" t="n">
-        <v>7.885</v>
+        <v>8.052199999999999</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1339</v>
+        <v>0.1646</v>
       </c>
       <c r="J211" t="n">
-        <v>2.5441</v>
+        <v>3.1274</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.68</v>
       </c>
       <c r="I212" t="n">
-        <v>1.153</v>
+        <v>1.1234</v>
       </c>
       <c r="J212" t="n">
-        <v>24.213</v>
+        <v>23.5914</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J213" t="n">
-        <v>0.8883</v>
+        <v>0.9786</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.87</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1636</v>
+        <v>-0.1777</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.4356</v>
+        <v>-3.7317</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.285</v>
+        <v>-0.2984</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.985</v>
+        <v>-6.2664</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4718</v>
+        <v>-0.4783</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.9078</v>
+        <v>-10.0443</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.85</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5604</v>
+        <v>1.5499</v>
       </c>
       <c r="J217" t="n">
-        <v>32.7684</v>
+        <v>32.5479</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.56</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2067</v>
+        <v>1.1761</v>
       </c>
       <c r="J218" t="n">
-        <v>25.3407</v>
+        <v>24.6981</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2922</v>
+        <v>0.303</v>
       </c>
       <c r="J219" t="n">
-        <v>6.1362</v>
+        <v>6.363</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4142</v>
+        <v>-0.3877</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.6982</v>
+        <v>-8.1417</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6594</v>
+        <v>-0.6095</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.8474</v>
+        <v>-12.7995</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>2.21</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8338</v>
+        <v>1.9282</v>
       </c>
       <c r="J222" t="n">
-        <v>29.3408</v>
+        <v>30.8512</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.69</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3265</v>
+        <v>1.3108</v>
       </c>
       <c r="J223" t="n">
-        <v>21.224</v>
+        <v>20.9728</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3881</v>
+        <v>0.3996</v>
       </c>
       <c r="J224" t="n">
-        <v>6.2096</v>
+        <v>6.3936</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2233</v>
+        <v>0.2484</v>
       </c>
       <c r="J225" t="n">
-        <v>3.5728</v>
+        <v>3.9744</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2325</v>
+        <v>-0.207</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.72</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1597</v>
+        <v>0.1419</v>
       </c>
       <c r="J227" t="n">
-        <v>2.5552</v>
+        <v>2.2704</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1549</v>
+        <v>-0.176</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.4784</v>
+        <v>-2.816</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1549</v>
+        <v>-0.176</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.4784</v>
+        <v>-2.816</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.386</v>
+        <v>-0.4017</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.176</v>
+        <v>-6.4272</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.36</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6182</v>
+        <v>-0.6193</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.8912</v>
+        <v>-9.908799999999999</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.17</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4131</v>
+        <v>0.4039</v>
       </c>
       <c r="J232" t="n">
-        <v>7.8489</v>
+        <v>7.6741</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2722</v>
+        <v>0.2713</v>
       </c>
       <c r="J233" t="n">
-        <v>5.1718</v>
+        <v>5.1547</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1038</v>
+        <v>-0.1176</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.9722</v>
+        <v>-2.2344</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.83</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1984</v>
+        <v>-0.2142</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.7696</v>
+        <v>-4.0698</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4656</v>
+        <v>-0.4733</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.846399999999999</v>
+        <v>-8.992699999999999</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6969</v>
+        <v>1.6913</v>
       </c>
       <c r="J237" t="n">
-        <v>32.2411</v>
+        <v>32.1347</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0145</v>
+        <v>0.9606</v>
       </c>
       <c r="J238" t="n">
-        <v>19.2755</v>
+        <v>18.2514</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.96</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.224</v>
+        <v>-0.2102</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.256</v>
+        <v>-3.9938</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3811</v>
+        <v>-0.358</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.2409</v>
+        <v>-6.802</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4104</v>
+        <v>-0.385</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.7976</v>
+        <v>-7.315</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.34</v>
       </c>
       <c r="I242" t="n">
-        <v>0.775</v>
+        <v>0.7257</v>
       </c>
       <c r="J242" t="n">
-        <v>14.725</v>
+        <v>13.7883</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1411</v>
+        <v>0.1359</v>
       </c>
       <c r="J243" t="n">
-        <v>2.6809</v>
+        <v>2.5821</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2671</v>
+        <v>-0.2844</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.0749</v>
+        <v>-5.4036</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.54</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4648</v>
+        <v>-0.4742</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.831200000000001</v>
+        <v>-9.0098</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.5</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5088</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.528499999999999</v>
+        <v>-9.667199999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.89</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5835</v>
+        <v>1.5778</v>
       </c>
       <c r="J247" t="n">
-        <v>30.0865</v>
+        <v>29.9782</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.41</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9947</v>
+        <v>0.9433</v>
       </c>
       <c r="J248" t="n">
-        <v>18.8993</v>
+        <v>17.9227</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6332</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J249" t="n">
-        <v>12.0308</v>
+        <v>11.6926</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I250" t="n">
-        <v>0.5613</v>
+        <v>0.5512</v>
       </c>
       <c r="J250" t="n">
-        <v>10.6647</v>
+        <v>10.4728</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.86</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5023</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.3341</v>
+        <v>-9.543699999999999</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.48</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1508</v>
+        <v>1.1076</v>
       </c>
       <c r="J252" t="n">
-        <v>27.6192</v>
+        <v>26.5824</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4882</v>
+        <v>0.4742</v>
       </c>
       <c r="J253" t="n">
-        <v>11.7168</v>
+        <v>11.3808</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2177</v>
+        <v>-0.2144</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.2248</v>
+        <v>-5.1456</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3413</v>
+        <v>-0.3301</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.1912</v>
+        <v>-7.9224</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4277</v>
+        <v>-0.4093</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.2648</v>
+        <v>-9.8232</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3497</v>
+        <v>0.3496</v>
       </c>
       <c r="J257" t="n">
-        <v>8.392799999999999</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2909</v>
+        <v>0.2941</v>
       </c>
       <c r="J258" t="n">
-        <v>6.9816</v>
+        <v>7.0584</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1427</v>
+        <v>0.1503</v>
       </c>
       <c r="J259" t="n">
-        <v>3.4248</v>
+        <v>3.6072</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1756</v>
+        <v>-0.1895</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.2144</v>
+        <v>-4.548</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2961</v>
+        <v>-0.309</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.1064</v>
+        <v>-7.416</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3518</v>
+        <v>1.3394</v>
       </c>
       <c r="J262" t="n">
-        <v>21.6288</v>
+        <v>21.4304</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.66</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2825</v>
+        <v>1.2656</v>
       </c>
       <c r="J263" t="n">
-        <v>20.52</v>
+        <v>20.2496</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>1.1074</v>
+        <v>1.0769</v>
       </c>
       <c r="J264" t="n">
-        <v>17.7184</v>
+        <v>17.2304</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.46</v>
       </c>
       <c r="I265" t="n">
-        <v>1.0488</v>
+        <v>1.0088</v>
       </c>
       <c r="J265" t="n">
-        <v>16.7808</v>
+        <v>16.1408</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0225</v>
+        <v>0.0607</v>
       </c>
       <c r="J266" t="n">
-        <v>0.36</v>
+        <v>0.9712</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.37</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8954</v>
+        <v>0.8235</v>
       </c>
       <c r="J267" t="n">
-        <v>14.3264</v>
+        <v>13.176</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1464</v>
+        <v>-0.167</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3424</v>
+        <v>-2.672</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.72</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2848</v>
+        <v>-0.3039</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.5568</v>
+        <v>-4.8624</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.4</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5829</v>
+        <v>-0.5864</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.3264</v>
+        <v>-9.382400000000001</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5829</v>
+        <v>-0.5864</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.3264</v>
+        <v>-9.382400000000001</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3672</v>
+        <v>1.3467</v>
       </c>
       <c r="J272" t="n">
-        <v>27.344</v>
+        <v>26.934</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.63</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2936</v>
+        <v>1.2687</v>
       </c>
       <c r="J273" t="n">
-        <v>25.872</v>
+        <v>25.374</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.11</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3202</v>
+        <v>0.3289</v>
       </c>
       <c r="J274" t="n">
-        <v>6.404</v>
+        <v>6.578</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.97</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1929</v>
+        <v>-0.1791</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.858</v>
+        <v>-3.582</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6334</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.668</v>
+        <v>-11.724</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6168</v>
+        <v>0.5911</v>
       </c>
       <c r="J277" t="n">
-        <v>12.336</v>
+        <v>11.822</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5252</v>
+        <v>0.5077</v>
       </c>
       <c r="J278" t="n">
-        <v>10.504</v>
+        <v>10.154</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.98</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0285</v>
+        <v>-0.0371</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.57</v>
+        <v>-0.742</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2881</v>
+        <v>-0.3027</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.762</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.36</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6361</v>
+        <v>-0.6335</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.722</v>
+        <v>-12.67</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.46</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0962</v>
+        <v>1.0535</v>
       </c>
       <c r="J282" t="n">
-        <v>24.1164</v>
+        <v>23.177</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9771</v>
+        <v>0.9177</v>
       </c>
       <c r="J283" t="n">
-        <v>21.4962</v>
+        <v>20.1894</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.28</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>16.599</v>
+        <v>15.7784</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.95</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2438</v>
+        <v>-0.2326</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.3636</v>
+        <v>-5.1172</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6688</v>
+        <v>-0.6209</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.7136</v>
+        <v>-13.6598</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2967</v>
+        <v>0.2939</v>
       </c>
       <c r="J287" t="n">
-        <v>6.5274</v>
+        <v>6.4658</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0895</v>
       </c>
       <c r="J288" t="n">
-        <v>1.9448</v>
+        <v>1.969</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="J289" t="n">
-        <v>-1.7534</v>
+        <v>-2.0372</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1972</v>
+        <v>-0.2133</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.3384</v>
+        <v>-4.6926</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3999</v>
+        <v>-0.411</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.797800000000001</v>
+        <v>-9.042</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="J292" t="n">
-        <v>18.6406</v>
+        <v>17.831</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.32</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6189</v>
+        <v>0.6046</v>
       </c>
       <c r="J293" t="n">
-        <v>13.6158</v>
+        <v>13.3012</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.448</v>
+        <v>0.4476</v>
       </c>
       <c r="J294" t="n">
-        <v>9.856</v>
+        <v>9.847200000000001</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2496</v>
+        <v>-0.2607</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.4912</v>
+        <v>-5.7354</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.365</v>
+        <v>-0.3738</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.223599999999999</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.46</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1334</v>
+        <v>1.0873</v>
       </c>
       <c r="J297" t="n">
-        <v>24.9348</v>
+        <v>23.9206</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.37</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0029</v>
+        <v>0.9362</v>
       </c>
       <c r="J298" t="n">
-        <v>22.0638</v>
+        <v>20.5964</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3334</v>
+        <v>-0.3246</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.3348</v>
+        <v>-7.1412</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3626</v>
+        <v>-0.3515</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.9772</v>
+        <v>-7.733</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.1278</v>
+        <v>-1.0262</v>
       </c>
       <c r="J301" t="n">
-        <v>-24.8116</v>
+        <v>-22.5764</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.1537</v>
+        <v>-0.1797</v>
       </c>
       <c r="J302" t="n">
-        <v>-2.6129</v>
+        <v>-3.0549</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1649</v>
+        <v>-0.1906</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.8033</v>
+        <v>-3.2402</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3991</v>
+        <v>-0.4167</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.7847</v>
+        <v>-7.0839</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.53</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4457</v>
+        <v>-0.4607</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.5769</v>
+        <v>-7.8319</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.48</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4927</v>
+        <v>-0.5047</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.3759</v>
+        <v>-8.5799</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.9</v>
       </c>
       <c r="I307" t="n">
-        <v>1.5575</v>
+        <v>1.5566</v>
       </c>
       <c r="J307" t="n">
-        <v>26.4775</v>
+        <v>26.4622</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.64</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2599</v>
+        <v>1.2413</v>
       </c>
       <c r="J308" t="n">
-        <v>21.4183</v>
+        <v>21.1021</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.52</v>
       </c>
       <c r="I309" t="n">
-        <v>1.1195</v>
+        <v>1.09</v>
       </c>
       <c r="J309" t="n">
-        <v>19.0315</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3777</v>
+        <v>0.3923</v>
       </c>
       <c r="J310" t="n">
-        <v>6.4209</v>
+        <v>6.6691</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3777</v>
+        <v>0.3923</v>
       </c>
       <c r="J311" t="n">
-        <v>6.4209</v>
+        <v>6.6691</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.372</v>
+        <v>1.3593</v>
       </c>
       <c r="J312" t="n">
-        <v>24.696</v>
+        <v>24.4674</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.58</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1959</v>
+        <v>1.1714</v>
       </c>
       <c r="J313" t="n">
-        <v>21.5262</v>
+        <v>21.0852</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.58</v>
       </c>
       <c r="I314" t="n">
-        <v>1.1959</v>
+        <v>1.1714</v>
       </c>
       <c r="J314" t="n">
-        <v>21.5262</v>
+        <v>21.0852</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4129</v>
+        <v>0.4223</v>
       </c>
       <c r="J315" t="n">
-        <v>7.4322</v>
+        <v>7.6014</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I316" t="n">
-        <v>0.222</v>
+        <v>0.2475</v>
       </c>
       <c r="J316" t="n">
-        <v>3.996</v>
+        <v>4.455</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5524</v>
+        <v>0.5108</v>
       </c>
       <c r="J317" t="n">
-        <v>9.943199999999999</v>
+        <v>9.1944</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3445</v>
+        <v>-0.3628</v>
       </c>
       <c r="J318" t="n">
-        <v>-6.201</v>
+        <v>-6.5304</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.58</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.4099</v>
+        <v>-0.4251</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.3782</v>
+        <v>-7.6518</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.58</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4099</v>
+        <v>-0.4251</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.3782</v>
+        <v>-7.6518</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4192</v>
+        <v>-0.4339</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.5456</v>
+        <v>-7.8102</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.55</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2285</v>
+        <v>1.1931</v>
       </c>
       <c r="J322" t="n">
-        <v>28.2555</v>
+        <v>27.4413</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.34</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8528</v>
       </c>
       <c r="J323" t="n">
-        <v>20.9944</v>
+        <v>19.6144</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0267</v>
+        <v>0.0404</v>
       </c>
       <c r="J324" t="n">
-        <v>0.6141</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.92</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3236</v>
+        <v>-0.3109</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.4428</v>
+        <v>-7.1507</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.7066</v>
+        <v>-0.6569</v>
       </c>
       <c r="J326" t="n">
-        <v>-16.2518</v>
+        <v>-15.1087</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7832</v>
+        <v>0.7399</v>
       </c>
       <c r="J327" t="n">
-        <v>18.0136</v>
+        <v>17.0177</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1247</v>
+        <v>-0.1396</v>
       </c>
       <c r="J328" t="n">
-        <v>-2.8681</v>
+        <v>-3.2108</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1352</v>
+        <v>-0.1505</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.1096</v>
+        <v>-3.4615</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.78</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2475</v>
+        <v>-0.2631</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.6925</v>
+        <v>-6.0513</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.59</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.428</v>
+        <v>-0.4377</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.843999999999999</v>
+        <v>-10.0671</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>2.18</v>
       </c>
       <c r="I332" t="n">
-        <v>1.8146</v>
+        <v>1.8332</v>
       </c>
       <c r="J332" t="n">
-        <v>25.4044</v>
+        <v>25.6648</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>2.02</v>
       </c>
       <c r="I333" t="n">
-        <v>1.6456</v>
+        <v>1.6565</v>
       </c>
       <c r="J333" t="n">
-        <v>23.0384</v>
+        <v>23.191</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.96</v>
       </c>
       <c r="I334" t="n">
-        <v>1.5817</v>
+        <v>1.5892</v>
       </c>
       <c r="J334" t="n">
-        <v>22.1438</v>
+        <v>22.2488</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>1.48</v>
       </c>
       <c r="I335" t="n">
-        <v>1.0496</v>
+        <v>1.0157</v>
       </c>
       <c r="J335" t="n">
-        <v>14.6944</v>
+        <v>14.2198</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.92</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4432</v>
+        <v>-0.3953</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.2048</v>
+        <v>-5.5342</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.1675</v>
+        <v>0.1231</v>
       </c>
       <c r="J337" t="n">
-        <v>2.345</v>
+        <v>1.7234</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.4138</v>
+        <v>-0.4312</v>
       </c>
       <c r="J338" t="n">
-        <v>-5.7932</v>
+        <v>-6.0368</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.423</v>
+        <v>-0.44</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.922</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.52</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4511</v>
+        <v>-0.4663</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.3154</v>
+        <v>-6.5282</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.5</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4699</v>
+        <v>-0.4839</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.5786</v>
+        <v>-6.7746</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>1.029</v>
+        <v>0.9772</v>
       </c>
       <c r="J342" t="n">
-        <v>20.58</v>
+        <v>19.544</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.41</v>
       </c>
       <c r="I343" t="n">
-        <v>1.0136</v>
+        <v>0.9597</v>
       </c>
       <c r="J343" t="n">
-        <v>20.272</v>
+        <v>19.194</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8979</v>
+        <v>0.8462</v>
       </c>
       <c r="J344" t="n">
-        <v>17.958</v>
+        <v>16.924</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I345" t="n">
-        <v>0.456</v>
+        <v>0.4522</v>
       </c>
       <c r="J345" t="n">
-        <v>9.119999999999999</v>
+        <v>9.044</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.82</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6306</v>
+        <v>-0.5843</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.612</v>
+        <v>-11.686</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.05</v>
       </c>
       <c r="I347" t="n">
-        <v>0.2036</v>
+        <v>0.1948</v>
       </c>
       <c r="J347" t="n">
-        <v>4.072</v>
+        <v>3.896</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.84</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1772</v>
+        <v>-0.1956</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.544</v>
+        <v>-3.912</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.79</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2254</v>
+        <v>-0.244</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.508</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2445</v>
+        <v>-0.2629</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.89</v>
+        <v>-5.258</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4242</v>
+        <v>-0.4363</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.484</v>
+        <v>-8.726000000000001</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.58</v>
       </c>
       <c r="I352" t="n">
-        <v>1.2232</v>
+        <v>1.1953</v>
       </c>
       <c r="J352" t="n">
-        <v>22.0176</v>
+        <v>21.5154</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.54</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1737</v>
+        <v>1.1424</v>
       </c>
       <c r="J353" t="n">
-        <v>21.1266</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>1.1238</v>
+        <v>1.0887</v>
       </c>
       <c r="J354" t="n">
-        <v>20.2284</v>
+        <v>19.5966</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1648</v>
+        <v>0.1862</v>
       </c>
       <c r="J355" t="n">
-        <v>2.9664</v>
+        <v>3.3516</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.8928</v>
+        <v>-0.8144</v>
       </c>
       <c r="J356" t="n">
-        <v>-16.0704</v>
+        <v>-14.6592</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.47</v>
       </c>
       <c r="I357" t="n">
-        <v>0.9769</v>
+        <v>0.9141</v>
       </c>
       <c r="J357" t="n">
-        <v>17.5842</v>
+        <v>16.4538</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.12</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3339</v>
+        <v>0.3255</v>
       </c>
       <c r="J358" t="n">
-        <v>6.0102</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.8</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2224</v>
+        <v>-0.2395</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.0032</v>
+        <v>-4.311</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.53</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.478</v>
+        <v>-0.486</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.747999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.4</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5957</v>
+        <v>-0.5965</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.7226</v>
+        <v>-10.737</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5014</v>
+        <v>0.4833</v>
       </c>
       <c r="J362" t="n">
-        <v>10.5294</v>
+        <v>10.1493</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.95</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.0653</v>
+        <v>-0.078</v>
       </c>
       <c r="J363" t="n">
-        <v>-1.3713</v>
+        <v>-1.638</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.1953</v>
+        <v>-0.2119</v>
       </c>
       <c r="J364" t="n">
-        <v>-4.1013</v>
+        <v>-4.4499</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.77</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.255</v>
+        <v>-0.271</v>
       </c>
       <c r="J365" t="n">
-        <v>-5.355</v>
+        <v>-5.691</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.68</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3416</v>
+        <v>-0.3554</v>
       </c>
       <c r="J366" t="n">
-        <v>-7.1736</v>
+        <v>-7.4634</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.58</v>
       </c>
       <c r="I367" t="n">
-        <v>1.2447</v>
+        <v>1.2143</v>
       </c>
       <c r="J367" t="n">
-        <v>26.1387</v>
+        <v>25.5003</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6513</v>
       </c>
       <c r="J368" t="n">
-        <v>14.2569</v>
+        <v>13.6773</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.386</v>
+        <v>0.3867</v>
       </c>
       <c r="J369" t="n">
-        <v>8.106</v>
+        <v>8.120699999999999</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.13</v>
       </c>
       <c r="I370" t="n">
-        <v>0.386</v>
+        <v>0.3867</v>
       </c>
       <c r="J370" t="n">
-        <v>8.106</v>
+        <v>8.120699999999999</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.88</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.459</v>
+        <v>-0.4313</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.638999999999999</v>
+        <v>-9.0573</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.03</v>
       </c>
       <c r="I372" t="n">
-        <v>0.1265</v>
+        <v>0.1251</v>
       </c>
       <c r="J372" t="n">
-        <v>2.53</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>0.03</v>
+        <v>0.0216</v>
       </c>
       <c r="J373" t="n">
-        <v>0.6</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0497</v>
+        <v>-0.0622</v>
       </c>
       <c r="J374" t="n">
-        <v>-0.994</v>
+        <v>-1.244</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.72</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3011</v>
+        <v>-0.3166</v>
       </c>
       <c r="J375" t="n">
-        <v>-6.022</v>
+        <v>-6.332</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.64</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3769</v>
+        <v>-0.3897</v>
       </c>
       <c r="J376" t="n">
-        <v>-7.538</v>
+        <v>-7.794</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.35</v>
       </c>
       <c r="I377" t="n">
-        <v>0.9001</v>
+        <v>0.8477</v>
       </c>
       <c r="J377" t="n">
-        <v>18.002</v>
+        <v>16.954</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.32</v>
       </c>
       <c r="I378" t="n">
-        <v>0.8327</v>
+        <v>0.7886</v>
       </c>
       <c r="J378" t="n">
-        <v>16.654</v>
+        <v>15.772</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.28</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7415</v>
+        <v>0.7083</v>
       </c>
       <c r="J379" t="n">
-        <v>14.83</v>
+        <v>14.166</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.13</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3793</v>
+        <v>0.3821</v>
       </c>
       <c r="J380" t="n">
-        <v>7.586</v>
+        <v>7.642</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.04</v>
       </c>
       <c r="I381" t="n">
-        <v>0.1133</v>
+        <v>0.1337</v>
       </c>
       <c r="J381" t="n">
-        <v>2.266</v>
+        <v>2.674</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.52</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1501</v>
+        <v>1.1167</v>
       </c>
       <c r="J382" t="n">
-        <v>21.8519</v>
+        <v>21.2173</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.46</v>
       </c>
       <c r="I383" t="n">
-        <v>1.0746</v>
+        <v>1.0332</v>
       </c>
       <c r="J383" t="n">
-        <v>20.4174</v>
+        <v>19.6308</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.16</v>
       </c>
       <c r="I384" t="n">
-        <v>0.4468</v>
+        <v>0.4459</v>
       </c>
       <c r="J384" t="n">
-        <v>8.4892</v>
+        <v>8.472099999999999</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3679</v>
+        <v>0.3742</v>
       </c>
       <c r="J385" t="n">
-        <v>6.9901</v>
+        <v>7.1098</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.1</v>
       </c>
       <c r="I386" t="n">
-        <v>0.2851</v>
+        <v>0.2981</v>
       </c>
       <c r="J386" t="n">
-        <v>5.4169</v>
+        <v>5.6639</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.28</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6383</v>
+        <v>0.607</v>
       </c>
       <c r="J387" t="n">
-        <v>12.1277</v>
+        <v>11.533</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.028</v>
+        <v>0.0202</v>
       </c>
       <c r="J388" t="n">
-        <v>0.532</v>
+        <v>0.3838</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.77</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2534</v>
+        <v>-0.2698</v>
       </c>
       <c r="J389" t="n">
-        <v>-4.8146</v>
+        <v>-5.1262</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.75</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2729</v>
+        <v>-0.2889</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.1851</v>
+        <v>-5.4891</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.58</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4335</v>
+        <v>-0.4436</v>
       </c>
       <c r="J391" t="n">
-        <v>-8.236499999999999</v>
+        <v>-8.4284</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.36</v>
       </c>
       <c r="I392" t="n">
-        <v>0.8258</v>
+        <v>0.7689</v>
       </c>
       <c r="J392" t="n">
-        <v>13.2128</v>
+        <v>12.3024</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.77</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.2452</v>
+        <v>-0.2635</v>
       </c>
       <c r="J393" t="n">
-        <v>-3.9232</v>
+        <v>-4.216</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.7</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.3122</v>
+        <v>-0.3289</v>
       </c>
       <c r="J394" t="n">
-        <v>-4.9952</v>
+        <v>-5.2624</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.63</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3784</v>
+        <v>-0.3925</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.0544</v>
+        <v>-6.28</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.6</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4064</v>
+        <v>-0.4193</v>
       </c>
       <c r="J396" t="n">
-        <v>-6.5024</v>
+        <v>-6.7088</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.74</v>
       </c>
       <c r="I397" t="n">
-        <v>1.3966</v>
+        <v>1.383</v>
       </c>
       <c r="J397" t="n">
-        <v>22.3456</v>
+        <v>22.128</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.64</v>
       </c>
       <c r="I398" t="n">
-        <v>1.278</v>
+        <v>1.2572</v>
       </c>
       <c r="J398" t="n">
-        <v>20.448</v>
+        <v>20.1152</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.22</v>
       </c>
       <c r="I399" t="n">
-        <v>0.5762</v>
+        <v>0.5664</v>
       </c>
       <c r="J399" t="n">
-        <v>9.219200000000001</v>
+        <v>9.0624</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.14</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3738</v>
+        <v>0.3841</v>
       </c>
       <c r="J400" t="n">
-        <v>5.9808</v>
+        <v>6.1456</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.09</v>
       </c>
       <c r="I401" t="n">
-        <v>0.2354</v>
+        <v>0.2569</v>
       </c>
       <c r="J401" t="n">
-        <v>3.7664</v>
+        <v>4.1104</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>1.0074</v>
+        <v>0.9552</v>
       </c>
       <c r="J402" t="n">
-        <v>30.222</v>
+        <v>28.656</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.18</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4142</v>
+        <v>0.4084</v>
       </c>
       <c r="J403" t="n">
-        <v>12.426</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.82</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2144</v>
+        <v>-0.2289</v>
       </c>
       <c r="J404" t="n">
-        <v>-6.432</v>
+        <v>-6.867</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.76</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2741</v>
+        <v>-0.2879</v>
       </c>
       <c r="J405" t="n">
-        <v>-8.223000000000001</v>
+        <v>-8.637</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.52</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4979</v>
+        <v>-0.5031</v>
       </c>
       <c r="J406" t="n">
-        <v>-14.937</v>
+        <v>-15.093</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.64</v>
       </c>
       <c r="I407" t="n">
-        <v>1.3378</v>
+        <v>1.3101</v>
       </c>
       <c r="J407" t="n">
-        <v>40.134</v>
+        <v>39.303</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.3</v>
       </c>
       <c r="I408" t="n">
-        <v>0.8129</v>
+        <v>0.7664</v>
       </c>
       <c r="J408" t="n">
-        <v>24.387</v>
+        <v>22.992</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.07</v>
       </c>
       <c r="I409" t="n">
-        <v>0.2298</v>
+        <v>0.2389</v>
       </c>
       <c r="J409" t="n">
-        <v>6.894</v>
+        <v>7.167</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.97</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.166</v>
+        <v>-0.1603</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.98</v>
+        <v>-4.809</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.71</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.8859</v>
+        <v>-0.8136</v>
       </c>
       <c r="J411" t="n">
-        <v>-26.577</v>
+        <v>-24.408</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.23</v>
       </c>
       <c r="I412" t="n">
-        <v>0.6511</v>
+        <v>0.6227</v>
       </c>
       <c r="J412" t="n">
-        <v>18.8819</v>
+        <v>18.0583</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.2</v>
       </c>
       <c r="I413" t="n">
-        <v>0.5772</v>
+        <v>0.5568</v>
       </c>
       <c r="J413" t="n">
-        <v>16.7388</v>
+        <v>16.1472</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.07</v>
       </c>
       <c r="I414" t="n">
-        <v>0.2339</v>
+        <v>0.2418</v>
       </c>
       <c r="J414" t="n">
-        <v>6.7831</v>
+        <v>7.0122</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.05</v>
       </c>
       <c r="I415" t="n">
-        <v>0.1719</v>
+        <v>0.1831</v>
       </c>
       <c r="J415" t="n">
-        <v>4.9851</v>
+        <v>5.3099</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.1719</v>
+        <v>0.1831</v>
       </c>
       <c r="J416" t="n">
-        <v>4.9851</v>
+        <v>5.3099</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6345</v>
+        <v>0.6131</v>
       </c>
       <c r="J417" t="n">
-        <v>18.4005</v>
+        <v>17.7799</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.21</v>
       </c>
       <c r="I418" t="n">
-        <v>0.457</v>
+        <v>0.4507</v>
       </c>
       <c r="J418" t="n">
-        <v>13.253</v>
+        <v>13.0703</v>
       </c>
     </row>
     <row r="419">
@@ -20069,10 +20069,10 @@
         <v>0.76</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2786</v>
+        <v>-0.2914</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.0794</v>
+        <v>-8.4506</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.72</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3172</v>
+        <v>-0.3292</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.1988</v>
+        <v>-9.546799999999999</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.77</v>
       </c>
       <c r="I422" t="n">
-        <v>1.4299</v>
+        <v>1.4186</v>
       </c>
       <c r="J422" t="n">
-        <v>27.1681</v>
+        <v>26.9534</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.37</v>
       </c>
       <c r="I423" t="n">
-        <v>0.9122</v>
+        <v>0.8645</v>
       </c>
       <c r="J423" t="n">
-        <v>17.3318</v>
+        <v>16.4255</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8918</v>
+        <v>0.8461</v>
       </c>
       <c r="J424" t="n">
-        <v>16.9442</v>
+        <v>16.0759</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.26</v>
       </c>
       <c r="I425" t="n">
-        <v>0.6695</v>
+        <v>0.6498</v>
       </c>
       <c r="J425" t="n">
-        <v>12.7205</v>
+        <v>12.3462</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.2905</v>
+        <v>0.3082</v>
       </c>
       <c r="J426" t="n">
-        <v>5.5195</v>
+        <v>5.8558</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.06</v>
       </c>
       <c r="I427" t="n">
-        <v>0.297</v>
+        <v>0.2696</v>
       </c>
       <c r="J427" t="n">
-        <v>5.643</v>
+        <v>5.1224</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.82</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.177</v>
+        <v>-0.2001</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.363</v>
+        <v>-3.8019</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.3232</v>
+        <v>-0.3428</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.1408</v>
+        <v>-6.5132</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.51</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4721</v>
+        <v>-0.4842</v>
       </c>
       <c r="J430" t="n">
-        <v>-8.969900000000001</v>
+        <v>-9.1998</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.4</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.575</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J431" t="n">
-        <v>-10.925</v>
+        <v>-11.0219</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.57</v>
+        <v>5.6536</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0612</v>
+        <v>1.0771</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9114</v>
+        <v>1.9115</v>
       </c>
       <c r="E2" t="n">
-        <v>5.57</v>
+        <v>5.6536</v>
       </c>
       <c r="F2" t="n">
         <v>2.5735</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2198</v>
+        <v>5.4816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.0444</v>
       </c>
       <c r="D3" t="n">
-        <v>1.752</v>
+        <v>1.8347</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2198</v>
+        <v>5.4816</v>
       </c>
       <c r="F3" t="n">
         <v>2.3611</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7046</v>
+        <v>4.8458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8963</v>
+        <v>0.9232</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5174</v>
+        <v>1.5507</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7046</v>
+        <v>4.8458</v>
       </c>
       <c r="F4" t="n">
         <v>3.84</v>
@@ -630,219 +630,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4583</v>
+        <v>4.5932</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8494</v>
+        <v>0.8751</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4053</v>
+        <v>1.4379</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4583</v>
+        <v>4.5932</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6391</v>
+        <v>3.4751</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8192</v>
+        <v>0.9556</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6391</v>
+        <v>6.5714</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6813</v>
+        <v>3.5485</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8192</v>
+        <v>0.9556</v>
       </c>
       <c r="K5" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L5" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5005</v>
+        <v>4.5041</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4307</v>
+        <v>4.5467</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8441</v>
+        <v>0.8662</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3927</v>
+        <v>1.4171</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4307</v>
+        <v>4.5467</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4751</v>
+        <v>1.6391</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9556</v>
+        <v>2.8192</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5714</v>
+        <v>1.6391</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5485</v>
+        <v>1.6813</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9556</v>
+        <v>2.8192</v>
       </c>
       <c r="K6" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L6" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5041</v>
+        <v>4.5005</v>
       </c>
       <c r="N6" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1633</v>
+        <v>4.3151</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7932</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.271</v>
+        <v>1.3136</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1633</v>
+        <v>4.3151</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4733</v>
+        <v>1.5897</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.5104</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5657</v>
+        <v>1.5897</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5454</v>
+        <v>1.5897</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.5104</v>
       </c>
       <c r="K7" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L7" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2354</v>
+        <v>4.1001</v>
       </c>
       <c r="N7" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1397</v>
+        <v>4.313</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7887</v>
+        <v>0.8217</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2603</v>
+        <v>1.3127</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1397</v>
+        <v>4.313</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7114</v>
+        <v>3.4733</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4283</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2095</v>
+        <v>6.5657</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2095</v>
+        <v>3.5454</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4283</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L8" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>4.637799999999999</v>
+        <v>4.2354</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1001</v>
+        <v>4.2368</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7812</v>
+        <v>0.8072</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2422</v>
+        <v>1.2787</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1001</v>
+        <v>4.2368</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5897</v>
+        <v>2.7114</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5104</v>
+        <v>1.4283</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5897</v>
+        <v>3.2095</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5897</v>
+        <v>3.2095</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5104</v>
+        <v>1.4283</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -851,7 +851,7 @@
         <v>148</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1001</v>
+        <v>4.637799999999999</v>
       </c>
       <c r="N9" t="n">
         <v>249</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9378</v>
+        <v>3.8946</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7502</v>
+        <v>0.742</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1684</v>
+        <v>1.1258</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9378</v>
+        <v>3.8946</v>
       </c>
       <c r="F10" t="n">
         <v>4.5147</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7328</v>
+        <v>3.8567</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7348</v>
       </c>
       <c r="D11" t="n">
-        <v>1.075</v>
+        <v>1.1089</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7328</v>
+        <v>3.8567</v>
       </c>
       <c r="F11" t="n">
         <v>3.0863</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9985</v>
+        <v>3.0238</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5713</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7408</v>
+        <v>0.7368</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9985</v>
+        <v>3.0238</v>
       </c>
       <c r="F12" t="n">
         <v>1.2154</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5658</v>
+        <v>2.8226</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4888</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5438</v>
+        <v>0.647</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5658</v>
+        <v>2.8226</v>
       </c>
       <c r="F13" t="n">
         <v>2.5658</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4174</v>
+        <v>2.6514</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4606</v>
+        <v>0.5051</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4762</v>
+        <v>0.5705</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4174</v>
+        <v>2.6514</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4615</v>
+        <v>2.3681</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9559</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4615</v>
+        <v>2.458</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4992</v>
+        <v>2.458</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9559</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4551</v>
+        <v>2.458</v>
       </c>
       <c r="N14" t="n">
-        <v>255</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3774</v>
+        <v>2.5722</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4529</v>
+        <v>0.4901</v>
       </c>
       <c r="D15" t="n">
-        <v>0.458</v>
+        <v>0.5351</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3774</v>
+        <v>2.5722</v>
       </c>
       <c r="F15" t="n">
         <v>2.3356</v>
@@ -1136,415 +1136,415 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3723</v>
+        <v>2.5561</v>
       </c>
       <c r="C16" t="n">
-        <v>0.452</v>
+        <v>0.487</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4557</v>
+        <v>0.5279</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3723</v>
+        <v>2.5561</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3723</v>
+        <v>1.4615</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.9559</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4674</v>
+        <v>1.4615</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4674</v>
+        <v>1.4992</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.9559</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4674</v>
+        <v>2.4551</v>
       </c>
       <c r="N16" t="n">
-        <v>106</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3681</v>
+        <v>2.4489</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4512</v>
+        <v>0.4666</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4538</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3681</v>
+        <v>2.4489</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3681</v>
+        <v>2.051</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2269</v>
       </c>
       <c r="H17" t="n">
-        <v>2.458</v>
+        <v>2.051</v>
       </c>
       <c r="I17" t="n">
-        <v>2.458</v>
+        <v>2.1039</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2269</v>
       </c>
       <c r="K17" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>2.458</v>
+        <v>2.3308</v>
       </c>
       <c r="N17" t="n">
-        <v>103</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3615</v>
+        <v>2.4488</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4499</v>
+        <v>0.4665</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4508</v>
+        <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3615</v>
+        <v>2.4488</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7602</v>
+        <v>2.1271</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3987</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3163</v>
+        <v>2.1271</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3163</v>
+        <v>2.1271</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3987</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9176</v>
+        <v>2.1271</v>
       </c>
       <c r="N18" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2929</v>
+        <v>2.3867</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4368</v>
+        <v>0.4547</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4196</v>
+        <v>0.4523</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2929</v>
+        <v>2.3867</v>
       </c>
       <c r="F19" t="n">
-        <v>1.943</v>
+        <v>2.3723</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.943</v>
+        <v>2.4674</v>
       </c>
       <c r="I19" t="n">
-        <v>1.943</v>
+        <v>2.4674</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L19" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2929</v>
+        <v>2.4674</v>
       </c>
       <c r="N19" t="n">
-        <v>249</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2779</v>
+        <v>2.3637</v>
       </c>
       <c r="C20" t="n">
-        <v>0.434</v>
+        <v>0.4503</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4127</v>
+        <v>0.442</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2779</v>
+        <v>2.3637</v>
       </c>
       <c r="F20" t="n">
-        <v>2.051</v>
+        <v>2.1787</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2269</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.051</v>
+        <v>2.1787</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1039</v>
+        <v>2.1787</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2269</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L20" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3308</v>
+        <v>2.1787</v>
       </c>
       <c r="N20" t="n">
-        <v>169</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1993</v>
+        <v>2.326</v>
       </c>
       <c r="C21" t="n">
-        <v>0.419</v>
+        <v>0.4432</v>
       </c>
       <c r="D21" t="n">
-        <v>0.377</v>
+        <v>0.4252</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1993</v>
+        <v>2.326</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5107</v>
+        <v>2.7602</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3114</v>
+        <v>-0.3987</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7703</v>
+        <v>3.3163</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8417</v>
+        <v>3.3163</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3114</v>
+        <v>-0.3987</v>
       </c>
       <c r="K21" t="n">
         <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5303</v>
+        <v>2.9176</v>
       </c>
       <c r="N21" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1831</v>
+        <v>2.2481</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4159</v>
+        <v>0.4283</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3696</v>
+        <v>0.3904</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1831</v>
+        <v>2.2481</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6277</v>
+        <v>1.943</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4446</v>
+        <v>0.3499</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7754</v>
+        <v>1.943</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0387</v>
+        <v>1.943</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4446</v>
+        <v>0.3499</v>
       </c>
       <c r="K22" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L22" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5941</v>
+        <v>2.2929</v>
       </c>
       <c r="N22" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1787</v>
+        <v>2.2229</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4151</v>
+        <v>0.4235</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3676</v>
+        <v>0.3791</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1787</v>
+        <v>2.2229</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1787</v>
+        <v>2.5107</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.3114</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1787</v>
+        <v>2.7703</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1787</v>
+        <v>2.8417</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.3114</v>
       </c>
       <c r="K23" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M23" t="n">
-        <v>2.1787</v>
+        <v>2.5303</v>
       </c>
       <c r="N23" t="n">
-        <v>110</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1271</v>
+        <v>2.082</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4053</v>
+        <v>0.3967</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3441</v>
+        <v>0.3162</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1271</v>
+        <v>2.082</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1271</v>
+        <v>1.3871</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.6165</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1271</v>
+        <v>1.3871</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1271</v>
+        <v>1.4228</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.6165</v>
       </c>
       <c r="K24" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M24" t="n">
-        <v>2.1271</v>
+        <v>2.0393</v>
       </c>
       <c r="N24" t="n">
-        <v>107</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0895</v>
+        <v>2.0511</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3981</v>
+        <v>0.3908</v>
       </c>
       <c r="D25" t="n">
-        <v>0.327</v>
+        <v>0.3024</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0895</v>
+        <v>2.0511</v>
       </c>
       <c r="F25" t="n">
         <v>2.0895</v>
@@ -1596,81 +1596,81 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.0036</v>
+        <v>2.033</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3817</v>
+        <v>0.3873</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2879</v>
+        <v>0.2943</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0036</v>
+        <v>2.033</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3871</v>
+        <v>2.6277</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6165</v>
+        <v>-0.4446</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3871</v>
+        <v>3.7754</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4228</v>
+        <v>2.0387</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6165</v>
+        <v>-0.4446</v>
       </c>
       <c r="K26" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L26" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="M26" t="n">
-        <v>2.0393</v>
+        <v>1.5941</v>
       </c>
       <c r="N26" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9365</v>
+        <v>1.9026</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3689</v>
+        <v>0.3625</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2573</v>
+        <v>0.236</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9365</v>
+        <v>1.9026</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8955</v>
+        <v>2.2768</v>
       </c>
       <c r="G27" t="n">
-        <v>0.041</v>
+        <v>-0.4146</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8955</v>
+        <v>2.2768</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8955</v>
+        <v>2.2768</v>
       </c>
       <c r="J27" t="n">
-        <v>0.041</v>
+        <v>-0.4146</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.9365</v>
+        <v>1.8622</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1688,35 +1688,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.8622</v>
+        <v>1.8557</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3548</v>
+        <v>0.3535</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2235</v>
+        <v>0.2151</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8622</v>
+        <v>1.8557</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2768</v>
+        <v>1.8955</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4146</v>
+        <v>0.041</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2768</v>
+        <v>1.8955</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2768</v>
+        <v>1.8955</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4146</v>
+        <v>0.041</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
@@ -1725,7 +1725,7 @@
         <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.8622</v>
+        <v>1.9365</v>
       </c>
       <c r="N28" t="n">
         <v>144</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8112</v>
+        <v>1.8376</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3451</v>
+        <v>0.3501</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2003</v>
+        <v>0.207</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8112</v>
+        <v>1.8376</v>
       </c>
       <c r="F29" t="n">
-        <v>2.7612</v>
+        <v>1.4614</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.216</v>
+        <v>1.4614</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2766</v>
+        <v>1.4614</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3266</v>
+        <v>1.4614</v>
       </c>
       <c r="N29" t="n">
-        <v>136</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5651</v>
+        <v>1.7063</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2982</v>
+        <v>0.3251</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0883</v>
+        <v>0.1483</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5651</v>
+        <v>1.7063</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3609</v>
+        <v>1.4544</v>
       </c>
       <c r="G30" t="n">
-        <v>1.2042</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3609</v>
+        <v>1.4544</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3702</v>
+        <v>1.4544</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2042</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L30" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5744</v>
+        <v>1.4544</v>
       </c>
       <c r="N30" t="n">
-        <v>169</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4614</v>
+        <v>1.6536</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2784</v>
+        <v>0.315</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0411</v>
+        <v>0.1248</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4614</v>
+        <v>1.6536</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4614</v>
+        <v>0.3609</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.2042</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4614</v>
+        <v>0.3609</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4614</v>
+        <v>0.3702</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.2042</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4614</v>
+        <v>1.5744</v>
       </c>
       <c r="N31" t="n">
-        <v>92</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.4544</v>
+        <v>1.5972</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2771</v>
+        <v>0.3043</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0379</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4544</v>
+        <v>1.5972</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4544</v>
+        <v>2.7612</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4544</v>
+        <v>4.216</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4544</v>
+        <v>2.2766</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="K32" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4544</v>
+        <v>1.3266</v>
       </c>
       <c r="N32" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.175</v>
+        <v>1.3597</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2239</v>
+        <v>0.2591</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0893</v>
+        <v>-0.0065</v>
       </c>
       <c r="E33" t="n">
-        <v>1.175</v>
+        <v>1.3597</v>
       </c>
       <c r="F33" t="n">
         <v>1.175</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1682</v>
+        <v>1.2204</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2226</v>
+        <v>0.2325</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0924</v>
+        <v>-0.0687</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1682</v>
+        <v>1.2204</v>
       </c>
       <c r="F34" t="n">
         <v>1.1682</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1658</v>
+        <v>1.1843</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2221</v>
+        <v>0.2256</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0935</v>
+        <v>-0.0848</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1658</v>
+        <v>1.1843</v>
       </c>
       <c r="F35" t="n">
         <v>-0.4697</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.066</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2031</v>
+        <v>0.1835</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1389</v>
+        <v>-0.1836</v>
       </c>
       <c r="E36" t="n">
-        <v>1.066</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>1.066</v>
+        <v>0.845</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.066</v>
+        <v>0.845</v>
       </c>
       <c r="I36" t="n">
-        <v>1.066</v>
+        <v>0.845</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.066</v>
+        <v>0.845</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.0035</v>
+        <v>0.9226</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1912</v>
+        <v>0.1758</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1674</v>
+        <v>-0.2017</v>
       </c>
       <c r="E37" t="n">
-        <v>1.0035</v>
+        <v>0.9226</v>
       </c>
       <c r="F37" t="n">
         <v>1.0035</v>
@@ -2148,308 +2148,308 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9457</v>
+        <v>0.9211</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1802</v>
+        <v>0.1755</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1937</v>
+        <v>-0.2024</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9457</v>
+        <v>0.9211</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1192</v>
+        <v>1.066</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1735</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1192</v>
+        <v>1.066</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1192</v>
+        <v>1.066</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1735</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L38" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9457</v>
+        <v>1.066</v>
       </c>
       <c r="N38" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>podi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.845</v>
+        <v>0.9177</v>
       </c>
       <c r="C39" t="n">
-        <v>0.161</v>
+        <v>0.1748</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2395</v>
+        <v>-0.2039</v>
       </c>
       <c r="E39" t="n">
-        <v>0.845</v>
+        <v>0.9177</v>
       </c>
       <c r="F39" t="n">
-        <v>0.845</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.845</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.845</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.845</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>podi</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1535</v>
+        <v>0.1516</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2573</v>
+        <v>-0.2583</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8058999999999999</v>
+        <v>1.1192</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.1735</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8058999999999999</v>
+        <v>1.1192</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8058999999999999</v>
+        <v>1.1192</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.1735</v>
       </c>
       <c r="K40" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.9457</v>
       </c>
       <c r="N40" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kylar</t>
+          <t>Cabbi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3944</v>
+        <v>0.4623</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0751</v>
+        <v>0.0881</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4447</v>
+        <v>-0.4073</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3944</v>
+        <v>0.4623</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3944</v>
+        <v>0.1881</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3944</v>
+        <v>0.1881</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3944</v>
+        <v>0.1881</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3944</v>
+        <v>0.1881</v>
       </c>
       <c r="N41" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Kylar</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3881</v>
+        <v>0.3717</v>
       </c>
       <c r="C42" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4475</v>
+        <v>-0.4478</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3881</v>
+        <v>0.3717</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3881</v>
+        <v>0.3944</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3881</v>
+        <v>0.3944</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3881</v>
+        <v>0.3944</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3881</v>
+        <v>0.3944</v>
       </c>
       <c r="N42" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3439</v>
+        <v>0.3405</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0655</v>
+        <v>0.0649</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4677</v>
+        <v>-0.4617</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3439</v>
+        <v>0.3405</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3439</v>
+        <v>0.3881</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3439</v>
+        <v>0.3881</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3439</v>
+        <v>0.3881</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3439</v>
+        <v>0.3881</v>
       </c>
       <c r="N43" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2755</v>
+        <v>0.2895</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0525</v>
+        <v>0.0552</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4988</v>
+        <v>-0.4845</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2755</v>
+        <v>0.2895</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2755</v>
+        <v>0.3439</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2755</v>
+        <v>0.3439</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2755</v>
+        <v>0.3439</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2755</v>
+        <v>0.3439</v>
       </c>
       <c r="N44" t="n">
         <v>106</v>
@@ -2470,139 +2470,139 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cabbi</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1881</v>
+        <v>0.2607</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0358</v>
+        <v>0.0497</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5386</v>
+        <v>-0.4974</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1881</v>
+        <v>0.2607</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1881</v>
+        <v>0.2755</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1881</v>
+        <v>0.2755</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1881</v>
+        <v>0.2755</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1881</v>
+        <v>0.2755</v>
       </c>
       <c r="N45" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1679</v>
+        <v>0.2145</v>
       </c>
       <c r="C46" t="n">
-        <v>0.032</v>
+        <v>0.0409</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5478</v>
+        <v>-0.518</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1679</v>
+        <v>0.2145</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1679</v>
+        <v>0.0746</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1679</v>
+        <v>0.0746</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1679</v>
+        <v>0.0746</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1679</v>
+        <v>0.0746</v>
       </c>
       <c r="N46" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0746</v>
+        <v>0.0618</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0142</v>
+        <v>0.0118</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0746</v>
+        <v>0.0618</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0746</v>
+        <v>0.1679</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0746</v>
+        <v>0.1679</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0746</v>
+        <v>0.1679</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0746</v>
+        <v>0.1679</v>
       </c>
       <c r="N47" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0707</v>
+        <v>-0.0298</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0135</v>
+        <v>-0.0057</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.592</v>
+        <v>-0.6271</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0707</v>
+        <v>-0.0298</v>
       </c>
       <c r="F48" t="n">
         <v>-2.5306</v>
@@ -2654,47 +2654,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.33</v>
+        <v>-0.441</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0629</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7744</v>
+        <v>-0.8108</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.33</v>
+        <v>-0.441</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.33</v>
+        <v>-0.5928</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.1975</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.33</v>
+        <v>-0.5928</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.33</v>
+        <v>-0.3201</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.1975</v>
       </c>
       <c r="K49" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.33</v>
+        <v>-0.1226</v>
       </c>
       <c r="N49" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.334</v>
+        <v>-0.5441</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0636</v>
+        <v>-0.1037</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7762</v>
+        <v>-0.8569</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.334</v>
+        <v>-0.5441</v>
       </c>
       <c r="F50" t="n">
         <v>-0.1288</v>
@@ -2746,47 +2746,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3953</v>
+        <v>-0.6297</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8042</v>
+        <v>-0.8951</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3953</v>
+        <v>-0.6297</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.5928</v>
+        <v>-0.33</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1975</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5928</v>
+        <v>-0.33</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3201</v>
+        <v>-0.33</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1975</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1226</v>
+        <v>-0.33</v>
       </c>
       <c r="N51" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52">
@@ -2796,16 +2796,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.5251</v>
+        <v>-0.6329</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1</v>
+        <v>-0.1206</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8632</v>
+        <v>-0.8965</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5251</v>
+        <v>-0.6329</v>
       </c>
       <c r="F52" t="n">
         <v>-0.5251</v>
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.6161</v>
+        <v>-0.6883</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1174</v>
+        <v>-0.1311</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9046999999999999</v>
+        <v>-0.9213</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6161</v>
+        <v>-0.6883</v>
       </c>
       <c r="F53" t="n">
         <v>-0.6161</v>
@@ -2884,93 +2884,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Goofy</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.6233</v>
+        <v>-0.841</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1188</v>
+        <v>-0.1602</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9079</v>
+        <v>-0.9895</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6233</v>
+        <v>-0.841</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6233</v>
+        <v>-0.6766</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6233</v>
+        <v>-0.6766</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6233</v>
+        <v>-0.6766</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6233</v>
+        <v>-0.6766</v>
       </c>
       <c r="N54" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Goofy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.6766</v>
+        <v>-1.1373</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1289</v>
+        <v>-0.2167</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.9322</v>
+        <v>-1.1218</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.6766</v>
+        <v>-1.1373</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.6766</v>
+        <v>-0.6233</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6766</v>
+        <v>-0.6233</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6766</v>
+        <v>-0.6233</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.6766</v>
+        <v>-0.6233</v>
       </c>
       <c r="N55" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56">
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.7171</v>
+        <v>-1.2543</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1366</v>
+        <v>-0.239</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.9506</v>
+        <v>-1.1741</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.7171</v>
+        <v>-1.2543</v>
       </c>
       <c r="F56" t="n">
         <v>-0.7171</v>
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.1542</v>
+        <v>-1.3084</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2199</v>
+        <v>-0.2493</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1496</v>
+        <v>-1.1983</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.1542</v>
+        <v>-1.3084</v>
       </c>
       <c r="F57" t="n">
         <v>-1.1542</v>
@@ -3072,16 +3072,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.1838</v>
+        <v>-1.385</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2255</v>
+        <v>-0.2639</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.1631</v>
+        <v>-1.2325</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.1838</v>
+        <v>-1.385</v>
       </c>
       <c r="F58" t="n">
         <v>-1.1838</v>
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2058</v>
+        <v>-1.6613</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2297</v>
+        <v>-0.3165</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.1731</v>
+        <v>-1.3559</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.2058</v>
+        <v>-1.6613</v>
       </c>
       <c r="F59" t="n">
         <v>-1.2058</v>
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2.7303</v>
+        <v>-3.1022</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5202</v>
+        <v>-0.591</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.8671</v>
+        <v>-1.9995</v>
       </c>
       <c r="E60" t="n">
-        <v>-2.7303</v>
+        <v>-3.1022</v>
       </c>
       <c r="F60" t="n">
         <v>-1.7303</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-3.8184</v>
+        <v>-4.0291</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.7275</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.3624</v>
+        <v>-2.4135</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.8184</v>
+        <v>-4.0291</v>
       </c>
       <c r="F61" t="n">
         <v>-3.2128</v>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">

--- a/database/event/7475/event_7475_evp_summary.xlsx
+++ b/database/event/7475/event_7475_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6536</v>
+        <v>5.6915</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0771</v>
+        <v>1.0843</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9115</v>
+        <v>1.987</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6536</v>
+        <v>5.6915</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5735</v>
+        <v>2.598</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9965</v>
+        <v>3.0099</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5967</v>
+        <v>3.3113</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9422</v>
+        <v>1.8592</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9965</v>
+        <v>3.0099</v>
       </c>
       <c r="K2" t="n">
         <v>112</v>
@@ -529,7 +529,7 @@
         <v>147</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9387</v>
+        <v>4.8691</v>
       </c>
       <c r="N2" t="n">
         <v>259</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4816</v>
+        <v>5.3363</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0444</v>
+        <v>1.0167</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8347</v>
+        <v>1.8252</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4816</v>
+        <v>5.3363</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3611</v>
+        <v>2.3429</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8587</v>
+        <v>2.7316</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4428</v>
+        <v>2.4191</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5057</v>
+        <v>2.4837</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8587</v>
+        <v>2.7316</v>
       </c>
       <c r="K3" t="n">
         <v>105</v>
@@ -575,7 +575,7 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3644</v>
+        <v>5.215299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>255</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8458</v>
+        <v>4.6638</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9232</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5507</v>
+        <v>1.5188</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8458</v>
+        <v>4.6638</v>
       </c>
       <c r="F4" t="n">
-        <v>3.84</v>
+        <v>3.723</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8646</v>
+        <v>0.7996</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7755</v>
+        <v>7.5352</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1987</v>
+        <v>4.2308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8646</v>
+        <v>0.7996</v>
       </c>
       <c r="K4" t="n">
         <v>96</v>
@@ -621,7 +621,7 @@
         <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0633</v>
+        <v>5.0304</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5932</v>
+        <v>4.5596</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8751</v>
+        <v>0.8687</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4379</v>
+        <v>1.4713</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5932</v>
+        <v>4.5596</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4751</v>
+        <v>3.3825</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9556</v>
+        <v>1.0146</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5714</v>
+        <v>6.2566</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5485</v>
+        <v>3.5129</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9556</v>
+        <v>1.0146</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -667,7 +667,7 @@
         <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5041</v>
+        <v>4.5275</v>
       </c>
       <c r="N5" t="n">
         <v>259</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5467</v>
+        <v>4.3707</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8662</v>
+        <v>0.8327</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4171</v>
+        <v>1.3853</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5467</v>
+        <v>4.3707</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6391</v>
+        <v>1.5761</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8192</v>
+        <v>2.7062</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6391</v>
+        <v>1.5761</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6813</v>
+        <v>1.6182</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8192</v>
+        <v>2.7062</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>150</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5005</v>
+        <v>4.3244</v>
       </c>
       <c r="N6" t="n">
         <v>255</v>
@@ -722,127 +722,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3151</v>
+        <v>4.2065</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8014</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3136</v>
+        <v>1.3105</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3151</v>
+        <v>4.2065</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5897</v>
+        <v>3.4078</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5104</v>
+        <v>0.649</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5897</v>
+        <v>6.3517</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5897</v>
+        <v>3.5663</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5104</v>
+        <v>0.649</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L7" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1001</v>
+        <v>4.2153</v>
       </c>
       <c r="N7" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.313</v>
+        <v>4.0994</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8217</v>
+        <v>0.781</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3127</v>
+        <v>1.2617</v>
       </c>
       <c r="E8" t="n">
-        <v>4.313</v>
+        <v>4.0994</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4733</v>
+        <v>2.7247</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.2776</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5657</v>
+        <v>3.294</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5454</v>
+        <v>3.294</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.2776</v>
       </c>
       <c r="K8" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2354</v>
+        <v>4.5716</v>
       </c>
       <c r="N8" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2368</v>
+        <v>4.0365</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8072</v>
+        <v>0.769</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2787</v>
+        <v>1.233</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2368</v>
+        <v>4.0365</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7114</v>
+        <v>1.4833</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4283</v>
+        <v>2.3382</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2095</v>
+        <v>1.4833</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2095</v>
+        <v>1.4833</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4283</v>
+        <v>2.3382</v>
       </c>
       <c r="K9" t="n">
         <v>101</v>
@@ -851,7 +851,7 @@
         <v>148</v>
       </c>
       <c r="M9" t="n">
-        <v>4.637799999999999</v>
+        <v>3.8215</v>
       </c>
       <c r="N9" t="n">
         <v>249</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8946</v>
+        <v>3.7805</v>
       </c>
       <c r="C10" t="n">
-        <v>0.742</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1258</v>
+        <v>1.1164</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8946</v>
+        <v>3.7805</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5147</v>
+        <v>3.0534</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5769</v>
+        <v>0.6032</v>
       </c>
       <c r="H10" t="n">
-        <v>10.0016</v>
+        <v>4.0473</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4008</v>
+        <v>4.0473</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5769</v>
+        <v>0.6032</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8239</v>
+        <v>4.6505</v>
       </c>
       <c r="N10" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8567</v>
+        <v>3.6985</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7348</v>
+        <v>0.7046</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1089</v>
+        <v>1.0791</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8567</v>
+        <v>3.6985</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0863</v>
+        <v>4.2839</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6465</v>
+        <v>-0.5422</v>
       </c>
       <c r="H11" t="n">
-        <v>4.03</v>
+        <v>9.6408</v>
       </c>
       <c r="I11" t="n">
-        <v>4.03</v>
+        <v>5.413</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6465</v>
+        <v>-0.5422</v>
       </c>
       <c r="K11" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L11" t="n">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6765</v>
+        <v>4.8708</v>
       </c>
       <c r="N11" t="n">
-        <v>249</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0238</v>
+        <v>2.9355</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5593</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7368</v>
+        <v>0.7315</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0238</v>
+        <v>2.9355</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2154</v>
+        <v>1.1825</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7831</v>
+        <v>1.7277</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2154</v>
+        <v>1.1825</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2467</v>
+        <v>1.2141</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7831</v>
+        <v>1.7277</v>
       </c>
       <c r="K12" t="n">
         <v>105</v>
@@ -989,7 +989,7 @@
         <v>150</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0298</v>
+        <v>2.9418</v>
       </c>
       <c r="N12" t="n">
         <v>255</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8226</v>
+        <v>2.7459</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5232</v>
       </c>
       <c r="D13" t="n">
-        <v>0.647</v>
+        <v>0.6451</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8226</v>
+        <v>2.7459</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5658</v>
+        <v>2.4891</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8907</v>
+        <v>2.7541</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8907</v>
+        <v>2.7541</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8907</v>
+        <v>2.7541</v>
       </c>
       <c r="N13" t="n">
         <v>98</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6514</v>
+        <v>2.6067</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5051</v>
+        <v>0.4966</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5705</v>
+        <v>0.5817</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6514</v>
+        <v>2.6067</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3681</v>
+        <v>2.3234</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.458</v>
+        <v>2.3745</v>
       </c>
       <c r="I14" t="n">
-        <v>2.458</v>
+        <v>2.3745</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.458</v>
+        <v>2.3745</v>
       </c>
       <c r="N14" t="n">
         <v>103</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5722</v>
+        <v>2.5616</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4901</v>
+        <v>0.488</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5351</v>
+        <v>0.5611</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5722</v>
+        <v>2.5616</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3356</v>
+        <v>1.5612</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0418</v>
+        <v>0.8617</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3869</v>
+        <v>1.5612</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3869</v>
+        <v>1.6029</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0418</v>
+        <v>0.8617</v>
       </c>
       <c r="K15" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L15" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4287</v>
+        <v>2.4646</v>
       </c>
       <c r="N15" t="n">
-        <v>144</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5561</v>
+        <v>2.4443</v>
       </c>
       <c r="C16" t="n">
-        <v>0.487</v>
+        <v>0.4657</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5279</v>
+        <v>0.5077</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5561</v>
+        <v>2.4443</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4615</v>
+        <v>2.2397</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9559</v>
+        <v>0.0098</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4615</v>
+        <v>2.2397</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4992</v>
+        <v>2.2397</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9559</v>
+        <v>0.0098</v>
       </c>
       <c r="K16" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L16" t="n">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4551</v>
+        <v>2.2495</v>
       </c>
       <c r="N16" t="n">
-        <v>255</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4489</v>
+        <v>2.4413</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4666</v>
+        <v>0.4651</v>
       </c>
       <c r="D17" t="n">
-        <v>0.48</v>
+        <v>0.5063</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4489</v>
+        <v>2.4413</v>
       </c>
       <c r="F17" t="n">
-        <v>2.051</v>
+        <v>2.1124</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2269</v>
+        <v>0.1579</v>
       </c>
       <c r="H17" t="n">
-        <v>2.051</v>
+        <v>2.1124</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1039</v>
+        <v>2.1688</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2269</v>
+        <v>0.1579</v>
       </c>
       <c r="K17" t="n">
         <v>101</v>
@@ -1219,7 +1219,7 @@
         <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3308</v>
+        <v>2.3267</v>
       </c>
       <c r="N17" t="n">
         <v>169</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4488</v>
+        <v>2.4004</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4665</v>
+        <v>0.4573</v>
       </c>
       <c r="D18" t="n">
-        <v>0.48</v>
+        <v>0.4877</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4488</v>
+        <v>2.4004</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1271</v>
+        <v>2.0787</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1271</v>
+        <v>2.0787</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1271</v>
+        <v>2.0787</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1271</v>
+        <v>2.0787</v>
       </c>
       <c r="N18" t="n">
         <v>107</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3867</v>
+        <v>2.3764</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4547</v>
+        <v>0.4528</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4523</v>
+        <v>0.4768</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3867</v>
+        <v>2.3764</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3723</v>
+        <v>2.362</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4674</v>
+        <v>2.4629</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4674</v>
+        <v>2.4629</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4674</v>
+        <v>2.4629</v>
       </c>
       <c r="N19" t="n">
         <v>106</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3637</v>
+        <v>2.3636</v>
       </c>
       <c r="C20" t="n">
         <v>0.4503</v>
       </c>
       <c r="D20" t="n">
-        <v>0.442</v>
+        <v>0.4709</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3637</v>
+        <v>2.3636</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1787</v>
+        <v>2.7765</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1787</v>
+        <v>3.4128</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1787</v>
+        <v>3.4128</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="K20" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1787</v>
+        <v>3.0354</v>
       </c>
       <c r="N20" t="n">
-        <v>110</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.326</v>
+        <v>2.3269</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4432</v>
+        <v>0.4433</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4252</v>
+        <v>0.4542</v>
       </c>
       <c r="E21" t="n">
-        <v>2.326</v>
+        <v>2.3269</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7602</v>
+        <v>1.9011</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3987</v>
+        <v>0.4706</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3163</v>
+        <v>1.9011</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3163</v>
+        <v>1.9011</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3987</v>
+        <v>0.4706</v>
       </c>
       <c r="K21" t="n">
         <v>101</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9176</v>
+        <v>2.3717</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2481</v>
+        <v>2.2127</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4283</v>
+        <v>0.4216</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3904</v>
+        <v>0.4022</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2481</v>
+        <v>2.2127</v>
       </c>
       <c r="F22" t="n">
-        <v>1.943</v>
+        <v>2.0277</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.943</v>
+        <v>2.0277</v>
       </c>
       <c r="I22" t="n">
-        <v>1.943</v>
+        <v>2.0277</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3499</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L22" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2929</v>
+        <v>2.0277</v>
       </c>
       <c r="N22" t="n">
-        <v>249</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2229</v>
+        <v>2.1616</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4235</v>
+        <v>0.4118</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3791</v>
+        <v>0.3789</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2229</v>
+        <v>2.1616</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5107</v>
+        <v>2.4766</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3114</v>
+        <v>-0.3386</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7703</v>
+        <v>2.7255</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8417</v>
+        <v>2.7983</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3114</v>
+        <v>-0.3386</v>
       </c>
       <c r="K23" t="n">
         <v>101</v>
@@ -1495,7 +1495,7 @@
         <v>68</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5303</v>
+        <v>2.4597</v>
       </c>
       <c r="N23" t="n">
         <v>169</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.082</v>
+        <v>2.0736</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3967</v>
+        <v>0.3951</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3162</v>
+        <v>0.3388</v>
       </c>
       <c r="E24" t="n">
-        <v>2.082</v>
+        <v>2.0736</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3871</v>
+        <v>2.6994</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6165</v>
+        <v>-0.4757</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3871</v>
+        <v>3.6919</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4228</v>
+        <v>2.0729</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6165</v>
+        <v>-0.4757</v>
       </c>
       <c r="K24" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L24" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0393</v>
+        <v>1.5972</v>
       </c>
       <c r="N24" t="n">
-        <v>169</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0511</v>
+        <v>2.0449</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3908</v>
+        <v>0.3896</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3024</v>
+        <v>0.3258</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0511</v>
+        <v>2.0449</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0895</v>
+        <v>2.0833</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0895</v>
+        <v>2.0833</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0895</v>
+        <v>2.0833</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0895</v>
+        <v>2.0833</v>
       </c>
       <c r="N25" t="n">
         <v>103</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.033</v>
+        <v>1.953</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3873</v>
+        <v>0.3721</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2943</v>
+        <v>0.2839</v>
       </c>
       <c r="E26" t="n">
-        <v>2.033</v>
+        <v>1.953</v>
       </c>
       <c r="F26" t="n">
-        <v>2.6277</v>
+        <v>1.3745</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4446</v>
+        <v>0.5001</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7754</v>
+        <v>1.3745</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0387</v>
+        <v>1.4112</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4446</v>
+        <v>0.5001</v>
       </c>
       <c r="K26" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L26" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5941</v>
+        <v>1.9113</v>
       </c>
       <c r="N26" t="n">
-        <v>259</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9026</v>
+        <v>1.94</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3625</v>
+        <v>0.3696</v>
       </c>
       <c r="D27" t="n">
-        <v>0.236</v>
+        <v>0.278</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9026</v>
+        <v>1.94</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2768</v>
+        <v>2.2909</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4146</v>
+        <v>-0.3913</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2768</v>
+        <v>2.2999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2768</v>
+        <v>2.2999</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4146</v>
+        <v>-0.3913</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.8622</v>
+        <v>1.9086</v>
       </c>
       <c r="N27" t="n">
         <v>144</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.8557</v>
+        <v>1.8677</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3535</v>
+        <v>0.3558</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2151</v>
+        <v>0.245</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8557</v>
+        <v>1.8677</v>
       </c>
       <c r="F28" t="n">
-        <v>1.8955</v>
+        <v>1.9348</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041</v>
+        <v>0.0137</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8955</v>
+        <v>1.9348</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8955</v>
+        <v>1.9348</v>
       </c>
       <c r="J28" t="n">
-        <v>0.041</v>
+        <v>0.0137</v>
       </c>
       <c r="K28" t="n">
         <v>101</v>
@@ -1725,7 +1725,7 @@
         <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9365</v>
+        <v>1.9485</v>
       </c>
       <c r="N28" t="n">
         <v>144</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8376</v>
+        <v>1.7536</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3501</v>
+        <v>0.3341</v>
       </c>
       <c r="D29" t="n">
-        <v>0.207</v>
+        <v>0.1931</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8376</v>
+        <v>1.7536</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4614</v>
+        <v>1.3774</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4614</v>
+        <v>1.3774</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4614</v>
+        <v>1.3774</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4614</v>
+        <v>1.3774</v>
       </c>
       <c r="N29" t="n">
         <v>92</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7063</v>
+        <v>1.6611</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3251</v>
+        <v>0.3165</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1483</v>
+        <v>0.1509</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7063</v>
+        <v>1.6611</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4544</v>
+        <v>2.8287</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.9536</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4544</v>
+        <v>4.1776</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4544</v>
+        <v>2.3456</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.9536</v>
       </c>
       <c r="K30" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4544</v>
+        <v>1.392</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6536</v>
+        <v>1.5748</v>
       </c>
       <c r="C31" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1248</v>
+        <v>0.1116</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6536</v>
+        <v>1.5748</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3609</v>
+        <v>0.3849</v>
       </c>
       <c r="G31" t="n">
-        <v>1.2042</v>
+        <v>1.1014</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3609</v>
+        <v>0.3849</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3702</v>
+        <v>0.3952</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2042</v>
+        <v>1.1014</v>
       </c>
       <c r="K31" t="n">
         <v>101</v>
@@ -1863,7 +1863,7 @@
         <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>1.5744</v>
+        <v>1.4966</v>
       </c>
       <c r="N31" t="n">
         <v>169</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5972</v>
+        <v>1.4962</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3043</v>
+        <v>0.2851</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5972</v>
+        <v>1.4962</v>
       </c>
       <c r="F32" t="n">
-        <v>2.7612</v>
+        <v>1.2443</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4.216</v>
+        <v>1.2443</v>
       </c>
       <c r="I32" t="n">
-        <v>2.2766</v>
+        <v>1.2443</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3266</v>
+        <v>1.2443</v>
       </c>
       <c r="N32" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3597</v>
+        <v>1.3119</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2591</v>
+        <v>0.2499</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0065</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3597</v>
+        <v>1.3119</v>
       </c>
       <c r="F33" t="n">
-        <v>1.175</v>
+        <v>1.1272</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.175</v>
+        <v>1.1272</v>
       </c>
       <c r="I33" t="n">
-        <v>1.175</v>
+        <v>1.1272</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.175</v>
+        <v>1.1272</v>
       </c>
       <c r="N33" t="n">
         <v>107</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2204</v>
+        <v>1.1214</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2325</v>
+        <v>0.2137</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0687</v>
+        <v>-0.0949</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2204</v>
+        <v>1.1214</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1682</v>
+        <v>1.0692</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1682</v>
+        <v>1.0692</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1682</v>
+        <v>1.0692</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1682</v>
+        <v>1.0692</v>
       </c>
       <c r="N34" t="n">
         <v>98</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1843</v>
+        <v>1.1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2256</v>
+        <v>0.2096</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0848</v>
+        <v>-0.1047</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1843</v>
+        <v>1.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4697</v>
+        <v>-0.4752</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6355</v>
+        <v>1.5567</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4697</v>
+        <v>-0.4752</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4697</v>
+        <v>-0.4752</v>
       </c>
       <c r="J35" t="n">
-        <v>1.6355</v>
+        <v>1.5567</v>
       </c>
       <c r="K35" t="n">
         <v>101</v>
@@ -2047,7 +2047,7 @@
         <v>148</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1658</v>
+        <v>1.0815</v>
       </c>
       <c r="N35" t="n">
         <v>249</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1835</v>
+        <v>0.1855</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1836</v>
+        <v>-0.1622</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="F36" t="n">
-        <v>0.845</v>
+        <v>0.8556</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.845</v>
+        <v>0.8556</v>
       </c>
       <c r="I36" t="n">
-        <v>0.845</v>
+        <v>0.8556</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.845</v>
+        <v>0.8556</v>
       </c>
       <c r="N36" t="n">
         <v>110</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9226</v>
+        <v>0.9326</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1758</v>
+        <v>0.1777</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2017</v>
+        <v>-0.1809</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9226</v>
+        <v>0.9326</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0035</v>
+        <v>1.0135</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.0035</v>
+        <v>1.0135</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0035</v>
+        <v>1.0135</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.0035</v>
+        <v>1.0135</v>
       </c>
       <c r="N37" t="n">
         <v>106</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9211</v>
+        <v>0.9221</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1755</v>
+        <v>0.1757</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2024</v>
+        <v>-0.1857</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9211</v>
+        <v>0.9221</v>
       </c>
       <c r="F38" t="n">
-        <v>1.066</v>
+        <v>1.067</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.066</v>
+        <v>1.067</v>
       </c>
       <c r="I38" t="n">
-        <v>1.066</v>
+        <v>1.067</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.066</v>
+        <v>1.067</v>
       </c>
       <c r="N38" t="n">
         <v>98</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9177</v>
+        <v>0.8159</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1748</v>
+        <v>0.1554</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2039</v>
+        <v>-0.2341</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9177</v>
+        <v>0.8159</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>92</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.6698</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1516</v>
+        <v>0.1276</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2583</v>
+        <v>-0.3007</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.6698</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1192</v>
+        <v>0.9917</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1735</v>
+        <v>-0.1721</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1192</v>
+        <v>0.9917</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1192</v>
+        <v>0.9917</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1735</v>
+        <v>-0.1721</v>
       </c>
       <c r="K40" t="n">
         <v>101</v>
@@ -2277,7 +2277,7 @@
         <v>43</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9457</v>
+        <v>0.8196</v>
       </c>
       <c r="N40" t="n">
         <v>144</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4623</v>
+        <v>0.4158</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0881</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4073</v>
+        <v>-0.4164</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4623</v>
+        <v>0.4158</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1881</v>
+        <v>0.1416</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1881</v>
+        <v>0.1416</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1881</v>
+        <v>0.1416</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1881</v>
+        <v>0.1416</v>
       </c>
       <c r="N41" t="n">
         <v>107</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3717</v>
+        <v>0.3934</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0708</v>
+        <v>0.075</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4478</v>
+        <v>-0.4266</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3717</v>
+        <v>0.3934</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3944</v>
+        <v>0.4161</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3944</v>
+        <v>0.4161</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3944</v>
+        <v>0.4161</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3944</v>
+        <v>0.4161</v>
       </c>
       <c r="N42" t="n">
         <v>92</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3405</v>
+        <v>0.3632</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0649</v>
+        <v>0.0692</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4617</v>
+        <v>-0.4403</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3405</v>
+        <v>0.3632</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3881</v>
+        <v>0.4108</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3881</v>
+        <v>0.4108</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3881</v>
+        <v>0.4108</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3881</v>
+        <v>0.4108</v>
       </c>
       <c r="N43" t="n">
         <v>103</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2895</v>
+        <v>0.2971</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0552</v>
+        <v>0.0566</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4845</v>
+        <v>-0.4704</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2895</v>
+        <v>0.2971</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3439</v>
+        <v>0.3515</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3439</v>
+        <v>0.3515</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3439</v>
+        <v>0.3515</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3439</v>
+        <v>0.3515</v>
       </c>
       <c r="N44" t="n">
         <v>106</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2607</v>
+        <v>0.2495</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0497</v>
+        <v>0.0475</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4974</v>
+        <v>-0.4921</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2607</v>
+        <v>0.2495</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2755</v>
+        <v>0.1096</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2755</v>
+        <v>0.1096</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2755</v>
+        <v>0.1096</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2755</v>
+        <v>0.1096</v>
       </c>
       <c r="N45" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2145</v>
+        <v>0.1665</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0409</v>
+        <v>0.0317</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.518</v>
+        <v>-0.5299</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2145</v>
+        <v>0.1665</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0746</v>
+        <v>-2.292</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2.559</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0746</v>
+        <v>-2.292</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0746</v>
+        <v>-1.2869</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2.559</v>
       </c>
       <c r="K46" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0746</v>
+        <v>1.2721</v>
       </c>
       <c r="N46" t="n">
-        <v>103</v>
+        <v>259</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0618</v>
+        <v>0.1457</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0118</v>
+        <v>0.0278</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5394</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0618</v>
+        <v>0.1457</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1679</v>
+        <v>0.2518</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1679</v>
+        <v>0.2518</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1679</v>
+        <v>0.2518</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1679</v>
+        <v>0.2518</v>
       </c>
       <c r="N47" t="n">
         <v>92</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0298</v>
+        <v>0.1203</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0057</v>
+        <v>0.0229</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6271</v>
+        <v>-0.551</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0298</v>
+        <v>0.1203</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.5306</v>
+        <v>0.1351</v>
       </c>
       <c r="G48" t="n">
-        <v>2.6013</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.5306</v>
+        <v>0.1351</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.3665</v>
+        <v>0.1351</v>
       </c>
       <c r="J48" t="n">
-        <v>2.6013</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L48" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.2348</v>
+        <v>0.1351</v>
       </c>
       <c r="N48" t="n">
-        <v>259</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49">
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.441</v>
+        <v>-0.3909</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0745</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8108</v>
+        <v>-0.7839</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.441</v>
+        <v>-0.3909</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5928</v>
+        <v>-0.5128</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1975</v>
+        <v>0.1676</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.5928</v>
+        <v>-0.5128</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3201</v>
+        <v>-0.2879</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1975</v>
+        <v>0.1676</v>
       </c>
       <c r="K49" t="n">
         <v>96</v>
@@ -2691,7 +2691,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1226</v>
+        <v>-0.1203</v>
       </c>
       <c r="N49" t="n">
         <v>136</v>
@@ -2704,31 +2704,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.5441</v>
+        <v>-0.5411</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1037</v>
+        <v>-0.1031</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8569</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5441</v>
+        <v>-0.5411</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1288</v>
+        <v>-0.1108</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.2052</v>
+        <v>-0.2202</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1288</v>
+        <v>-0.1108</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1321</v>
+        <v>-0.1138</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.2052</v>
+        <v>-0.2202</v>
       </c>
       <c r="K50" t="n">
         <v>105</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.3373</v>
+        <v>-0.334</v>
       </c>
       <c r="N50" t="n">
         <v>255</v>
@@ -2746,124 +2746,124 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.6297</v>
+        <v>-0.6408</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8951</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.6297</v>
+        <v>-0.6408</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.33</v>
+        <v>-0.533</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.33</v>
+        <v>-0.533</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.33</v>
+        <v>-0.533</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.33</v>
+        <v>-0.533</v>
       </c>
       <c r="N51" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6329</v>
+        <v>-0.6674</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1206</v>
+        <v>-0.1272</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.8965</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.6329</v>
+        <v>-0.6674</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5251</v>
+        <v>-0.5952</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5251</v>
+        <v>-0.5952</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.5251</v>
+        <v>-0.5952</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.5251</v>
+        <v>-0.5952</v>
       </c>
       <c r="N52" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.6883</v>
+        <v>-0.6744</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1311</v>
+        <v>-0.1285</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.9213</v>
+        <v>-0.913</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6883</v>
+        <v>-0.6744</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.6161</v>
+        <v>-0.3747</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.6161</v>
+        <v>-0.3747</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.6161</v>
+        <v>-0.3747</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.6161</v>
+        <v>-0.3747</v>
       </c>
       <c r="N53" t="n">
         <v>110</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.841</v>
+        <v>-0.8164</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1602</v>
+        <v>-0.1555</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9895</v>
+        <v>-0.9777</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.841</v>
+        <v>-0.8164</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.6766</v>
+        <v>-0.652</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6766</v>
+        <v>-0.652</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6766</v>
+        <v>-0.652</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.6766</v>
+        <v>-0.652</v>
       </c>
       <c r="N54" t="n">
         <v>110</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1373</v>
+        <v>-1.1988</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2167</v>
+        <v>-0.2284</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.1218</v>
+        <v>-1.1519</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.1373</v>
+        <v>-1.1988</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.6233</v>
+        <v>-0.6848</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6233</v>
+        <v>-0.6848</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6233</v>
+        <v>-0.6848</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.6233</v>
+        <v>-0.6848</v>
       </c>
       <c r="N55" t="n">
         <v>92</v>
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2543</v>
+        <v>-1.2235</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.239</v>
+        <v>-0.2331</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.1741</v>
+        <v>-1.1632</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.2543</v>
+        <v>-1.2235</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.7171</v>
+        <v>-0.6863</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.7171</v>
+        <v>-0.6863</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7171</v>
+        <v>-0.6863</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.7171</v>
+        <v>-0.6863</v>
       </c>
       <c r="N56" t="n">
         <v>103</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.3084</v>
+        <v>-1.2977</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2493</v>
+        <v>-0.2472</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.1983</v>
+        <v>-1.197</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3084</v>
+        <v>-1.2977</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.1542</v>
+        <v>-1.1435</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.1542</v>
+        <v>-1.1435</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.1542</v>
+        <v>-1.1435</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.1542</v>
+        <v>-1.1435</v>
       </c>
       <c r="N57" t="n">
         <v>107</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.385</v>
+        <v>-1.3781</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2639</v>
+        <v>-0.2626</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.2325</v>
+        <v>-1.2336</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.385</v>
+        <v>-1.3781</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.1838</v>
+        <v>-1.1769</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.1838</v>
+        <v>-1.1769</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.1838</v>
+        <v>-1.1769</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.1838</v>
+        <v>-1.1769</v>
       </c>
       <c r="N58" t="n">
         <v>98</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.6613</v>
+        <v>-1.6815</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3165</v>
+        <v>-0.3204</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.3559</v>
+        <v>-1.3718</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.6613</v>
+        <v>-1.6815</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.2058</v>
+        <v>-1.226</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.2058</v>
+        <v>-1.226</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.2058</v>
+        <v>-1.226</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.2058</v>
+        <v>-1.226</v>
       </c>
       <c r="N59" t="n">
         <v>107</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.1022</v>
+        <v>-3.0093</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.591</v>
+        <v>-0.5733</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.9995</v>
+        <v>-1.9767</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.1022</v>
+        <v>-3.0093</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.7303</v>
+        <v>-1.6374</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.7303</v>
+        <v>-1.6374</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.7749</v>
+        <v>-1.6812</v>
       </c>
       <c r="J60" t="n">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>68</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.7749</v>
+        <v>-2.6812</v>
       </c>
       <c r="N60" t="n">
         <v>169</v>
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-4.0291</v>
+        <v>-3.6667</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.6986</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.4135</v>
+        <v>-2.2761</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.0291</v>
+        <v>-3.6667</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.2128</v>
+        <v>-2.8527</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.6056</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.2128</v>
+        <v>-2.8527</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.7349</v>
+        <v>-1.6017</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.6056</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K61" t="n">
         <v>96</v>
@@ -3243,7 +3243,7 @@
         <v>40</v>
       </c>
       <c r="M61" t="n">
-        <v>-2.3405</v>
+        <v>-2.205</v>
       </c>
       <c r="N61" t="n">
         <v>136</v>
@@ -3349,10 +3349,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5606</v>
+        <v>0.5815</v>
       </c>
       <c r="J2" t="n">
-        <v>15.6968</v>
+        <v>16.282</v>
       </c>
     </row>
     <row r="3">
@@ -3389,10 +3389,10 @@
         <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0839</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.3492</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="4">
@@ -3429,10 +3429,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1882</v>
+        <v>-0.1678</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.2696</v>
+        <v>-4.6984</v>
       </c>
     </row>
     <row r="5">
@@ -3469,10 +3469,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1988</v>
+        <v>-0.1783</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.5664</v>
+        <v>-4.9924</v>
       </c>
     </row>
     <row r="6">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2296</v>
+        <v>-0.2093</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.4288</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="7">
@@ -3549,10 +3549,10 @@
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8128</v>
+        <v>0.7439</v>
       </c>
       <c r="J7" t="n">
-        <v>22.7584</v>
+        <v>20.8292</v>
       </c>
     </row>
     <row r="8">
@@ -3589,10 +3589,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2654</v>
+        <v>0.2157</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4312</v>
+        <v>6.0396</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3629,10 @@
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1738</v>
+        <v>0.1364</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8664</v>
+        <v>3.8192</v>
       </c>
     </row>
     <row r="10">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0112</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3136</v>
+        <v>-0.2464</v>
       </c>
     </row>
     <row r="11">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2252</v>
+        <v>-0.2055</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.3056</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="12">
@@ -3749,10 +3749,10 @@
         <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1355</v>
+        <v>1.1424</v>
       </c>
       <c r="J12" t="n">
-        <v>22.71</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="13">
@@ -3789,10 +3789,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7099</v>
+        <v>0.6812</v>
       </c>
       <c r="J13" t="n">
-        <v>14.198</v>
+        <v>13.624</v>
       </c>
     </row>
     <row r="14">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6484</v>
+        <v>0.6173</v>
       </c>
       <c r="J14" t="n">
-        <v>12.968</v>
+        <v>12.346</v>
       </c>
     </row>
     <row r="15">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4549</v>
+        <v>0.4208</v>
       </c>
       <c r="J15" t="n">
-        <v>9.098000000000001</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="16">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4347</v>
+        <v>-0.3943</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.694000000000001</v>
+        <v>-7.886</v>
       </c>
     </row>
     <row r="17">
@@ -3949,10 +3949,10 @@
         <v>1.23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5172</v>
+        <v>0.462</v>
       </c>
       <c r="J17" t="n">
-        <v>10.344</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="18">
@@ -3989,10 +3989,10 @@
         <v>1.14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3558</v>
+        <v>0.3033</v>
       </c>
       <c r="J18" t="n">
-        <v>7.116</v>
+        <v>6.066</v>
       </c>
     </row>
     <row r="19">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0616</v>
+        <v>0.043</v>
       </c>
       <c r="J19" t="n">
-        <v>1.232</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="20">
@@ -4069,10 +4069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4625</v>
+        <v>-0.4579</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.25</v>
+        <v>-9.157999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4109,10 +4109,10 @@
         <v>0.51</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5056</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.112</v>
+        <v>-10.132</v>
       </c>
     </row>
     <row r="22">
@@ -4149,10 +4149,10 @@
         <v>1.65</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3944</v>
+        <v>1.43</v>
       </c>
       <c r="J22" t="n">
-        <v>26.4936</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="23">
@@ -4189,10 +4189,10 @@
         <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9385</v>
+        <v>0.9262</v>
       </c>
       <c r="J23" t="n">
-        <v>17.8315</v>
+        <v>17.5978</v>
       </c>
     </row>
     <row r="24">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6035</v>
+        <v>0.5732</v>
       </c>
       <c r="J24" t="n">
-        <v>11.4665</v>
+        <v>10.8908</v>
       </c>
     </row>
     <row r="25">
@@ -4269,10 +4269,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8088</v>
+        <v>1.4212</v>
       </c>
     </row>
     <row r="26">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2463</v>
+        <v>-0.2105</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.6797</v>
+        <v>-3.9995</v>
       </c>
     </row>
     <row r="27">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6103</v>
+        <v>0.5586</v>
       </c>
       <c r="J27" t="n">
-        <v>11.5957</v>
+        <v>10.6134</v>
       </c>
     </row>
     <row r="28">
@@ -4389,10 +4389,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1513</v>
+        <v>0.117</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8747</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="29">
@@ -4429,10 +4429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.23</v>
+        <v>-0.2108</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.37</v>
+        <v>-4.0052</v>
       </c>
     </row>
     <row r="30">
@@ -4469,10 +4469,10 @@
         <v>0.76</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2786</v>
+        <v>-0.26</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.2934</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="31">
@@ -4509,10 +4509,10 @@
         <v>0.45</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5548</v>
+        <v>-0.5627</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.5412</v>
+        <v>-10.6913</v>
       </c>
     </row>
     <row r="32">
@@ -4549,10 +4549,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2878</v>
+        <v>0.2442</v>
       </c>
       <c r="J32" t="n">
-        <v>5.756</v>
+        <v>4.884</v>
       </c>
     </row>
     <row r="33">
@@ -4589,10 +4589,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2662</v>
+        <v>0.2241</v>
       </c>
       <c r="J33" t="n">
-        <v>5.324</v>
+        <v>4.482</v>
       </c>
     </row>
     <row r="34">
@@ -4629,10 +4629,10 @@
         <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3273</v>
+        <v>-0.3113</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.546</v>
+        <v>-6.226</v>
       </c>
     </row>
     <row r="35">
@@ -4669,10 +4669,10 @@
         <v>0.68</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3457</v>
+        <v>-0.3305</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.914</v>
+        <v>-6.61</v>
       </c>
     </row>
     <row r="36">
@@ -4709,10 +4709,10 @@
         <v>0.44</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5569</v>
+        <v>-0.5642</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.138</v>
+        <v>-11.284</v>
       </c>
     </row>
     <row r="37">
@@ -4749,10 +4749,10 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9627</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>19.254</v>
+        <v>18.982</v>
       </c>
     </row>
     <row r="38">
@@ -4789,10 +4789,10 @@
         <v>1.48</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9218</v>
+        <v>0.9074</v>
       </c>
       <c r="J38" t="n">
-        <v>18.436</v>
+        <v>18.148</v>
       </c>
     </row>
     <row r="39">
@@ -4829,10 +4829,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4264</v>
+        <v>0.3947</v>
       </c>
       <c r="J39" t="n">
-        <v>8.528</v>
+        <v>7.894</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3551</v>
+        <v>0.3223</v>
       </c>
       <c r="J40" t="n">
-        <v>7.102</v>
+        <v>6.446</v>
       </c>
     </row>
     <row r="41">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3037</v>
+        <v>-0.265</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.074</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="42">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5984</v>
+        <v>0.5755</v>
       </c>
       <c r="J42" t="n">
-        <v>11.968</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="43">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0487</v>
+        <v>-0.0391</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.974</v>
+        <v>-0.782</v>
       </c>
     </row>
     <row r="44">
@@ -5029,10 +5029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0766</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.806</v>
+        <v>-1.532</v>
       </c>
     </row>
     <row r="45">
@@ -5069,10 +5069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2312</v>
+        <v>-0.2117</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.624</v>
+        <v>-4.234</v>
       </c>
     </row>
     <row r="46">
@@ -5109,10 +5109,10 @@
         <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6227</v>
+        <v>-0.6423</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.454</v>
+        <v>-12.846</v>
       </c>
     </row>
     <row r="47">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0055</v>
+        <v>0.9935</v>
       </c>
       <c r="J47" t="n">
-        <v>20.11</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="48">
@@ -5189,10 +5189,10 @@
         <v>1.25</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5992</v>
+        <v>0.5884</v>
       </c>
       <c r="J48" t="n">
-        <v>11.984</v>
+        <v>11.768</v>
       </c>
     </row>
     <row r="49">
@@ -5229,10 +5229,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4542</v>
+        <v>0.4243</v>
       </c>
       <c r="J49" t="n">
-        <v>9.084</v>
+        <v>8.486000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -5269,10 +5269,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2619</v>
+        <v>0.2302</v>
       </c>
       <c r="J50" t="n">
-        <v>5.238</v>
+        <v>4.604</v>
       </c>
     </row>
     <row r="51">
@@ -5309,10 +5309,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5734</v>
+        <v>-0.536</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.468</v>
+        <v>-10.72</v>
       </c>
     </row>
     <row r="52">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9401</v>
+        <v>0.926</v>
       </c>
       <c r="J52" t="n">
-        <v>18.802</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="53">
@@ -5389,10 +5389,10 @@
         <v>1.41</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8408</v>
+        <v>0.8249</v>
       </c>
       <c r="J53" t="n">
-        <v>16.816</v>
+        <v>16.498</v>
       </c>
     </row>
     <row r="54">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6786</v>
+        <v>0.6642</v>
       </c>
       <c r="J54" t="n">
-        <v>13.572</v>
+        <v>13.284</v>
       </c>
     </row>
     <row r="55">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0848</v>
+        <v>-0.0639</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.696</v>
+        <v>-1.278</v>
       </c>
     </row>
     <row r="56">
@@ -5509,10 +5509,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.083</v>
+        <v>-1.0948</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.66</v>
+        <v>-21.896</v>
       </c>
     </row>
     <row r="57">
@@ -5549,10 +5549,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4896</v>
+        <v>0.4509</v>
       </c>
       <c r="J57" t="n">
-        <v>9.792</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4356</v>
+        <v>0.3823</v>
       </c>
       <c r="J58" t="n">
-        <v>8.712</v>
+        <v>7.646</v>
       </c>
     </row>
     <row r="59">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1514</v>
+        <v>-0.1328</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.028</v>
+        <v>-2.656</v>
       </c>
     </row>
     <row r="60">
@@ -5669,10 +5669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3492</v>
+        <v>-0.334</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.984</v>
+        <v>-6.68</v>
       </c>
     </row>
     <row r="61">
@@ -5709,10 +5709,10 @@
         <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4389</v>
+        <v>-0.4319</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.778</v>
+        <v>-8.638</v>
       </c>
     </row>
     <row r="62">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3055</v>
+        <v>0.3013</v>
       </c>
       <c r="J62" t="n">
-        <v>5.8045</v>
+        <v>5.7247</v>
       </c>
     </row>
     <row r="63">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0362</v>
+        <v>-0.0268</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.6878</v>
+        <v>-0.5092</v>
       </c>
     </row>
     <row r="64">
@@ -5829,10 +5829,10 @@
         <v>0.72</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3087</v>
+        <v>-0.292</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.8653</v>
+        <v>-5.548</v>
       </c>
     </row>
     <row r="65">
@@ -5869,10 +5869,10 @@
         <v>0.64</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3817</v>
+        <v>-0.3687</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.2523</v>
+        <v>-7.0053</v>
       </c>
     </row>
     <row r="66">
@@ -5909,10 +5909,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4965</v>
+        <v>-0.4951</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.4335</v>
+        <v>-9.4069</v>
       </c>
     </row>
     <row r="67">
@@ -5949,10 +5949,10 @@
         <v>2.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.994</v>
+        <v>0.9376</v>
       </c>
       <c r="J67" t="n">
-        <v>18.886</v>
+        <v>17.8144</v>
       </c>
     </row>
     <row r="68">
@@ -5989,10 +5989,10 @@
         <v>1.43</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5124</v>
+        <v>0.4705</v>
       </c>
       <c r="J68" t="n">
-        <v>9.7356</v>
+        <v>8.939500000000001</v>
       </c>
     </row>
     <row r="69">
@@ -6029,10 +6029,10 @@
         <v>1.26</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3604</v>
+        <v>0.3048</v>
       </c>
       <c r="J69" t="n">
-        <v>6.8476</v>
+        <v>5.7912</v>
       </c>
     </row>
     <row r="70">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1364</v>
+        <v>-0.1191</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.5916</v>
+        <v>-2.2629</v>
       </c>
     </row>
     <row r="71">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2159</v>
+        <v>-0.1979</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.1021</v>
+        <v>-3.7601</v>
       </c>
     </row>
     <row r="72">
@@ -6149,10 +6149,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5742</v>
+        <v>0.5622</v>
       </c>
       <c r="J72" t="n">
-        <v>23.5422</v>
+        <v>23.0502</v>
       </c>
     </row>
     <row r="73">
@@ -6189,10 +6189,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2526</v>
+        <v>0.2159</v>
       </c>
       <c r="J73" t="n">
-        <v>10.3566</v>
+        <v>8.851900000000001</v>
       </c>
     </row>
     <row r="74">
@@ -6229,10 +6229,10 @@
         <v>1.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2239</v>
+        <v>0.1892</v>
       </c>
       <c r="J74" t="n">
-        <v>9.1799</v>
+        <v>7.7572</v>
       </c>
     </row>
     <row r="75">
@@ -6269,10 +6269,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0954</v>
+        <v>0.0746</v>
       </c>
       <c r="J75" t="n">
-        <v>3.9114</v>
+        <v>3.0586</v>
       </c>
     </row>
     <row r="76">
@@ -6309,10 +6309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5717</v>
+        <v>-0.5319</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.4397</v>
+        <v>-21.8079</v>
       </c>
     </row>
     <row r="77">
@@ -6349,10 +6349,10 @@
         <v>1.22</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4513</v>
+        <v>0.3989</v>
       </c>
       <c r="J77" t="n">
-        <v>18.5033</v>
+        <v>16.3549</v>
       </c>
     </row>
     <row r="78">
@@ -6389,10 +6389,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4066</v>
+        <v>0.3505</v>
       </c>
       <c r="J78" t="n">
-        <v>16.6706</v>
+        <v>14.3705</v>
       </c>
     </row>
     <row r="79">
@@ -6429,10 +6429,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1643</v>
+        <v>0.1293</v>
       </c>
       <c r="J79" t="n">
-        <v>6.7363</v>
+        <v>5.3013</v>
       </c>
     </row>
     <row r="80">
@@ -6469,10 +6469,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0283</v>
+        <v>-0.0201</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.1603</v>
+        <v>-0.8241000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6509,10 +6509,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2858</v>
+        <v>-0.2675</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.7178</v>
+        <v>-10.9675</v>
       </c>
     </row>
     <row r="82">
@@ -6549,10 +6549,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.235</v>
+        <v>1.2341</v>
       </c>
       <c r="J82" t="n">
-        <v>23.465</v>
+        <v>23.4479</v>
       </c>
     </row>
     <row r="83">
@@ -6589,10 +6589,10 @@
         <v>1.55</v>
       </c>
       <c r="I83" t="n">
-        <v>1.013</v>
+        <v>1.0009</v>
       </c>
       <c r="J83" t="n">
-        <v>19.247</v>
+        <v>19.0171</v>
       </c>
     </row>
     <row r="84">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7079</v>
+        <v>0.6953</v>
       </c>
       <c r="J84" t="n">
-        <v>13.4501</v>
+        <v>13.2107</v>
       </c>
     </row>
     <row r="85">
@@ -6669,10 +6669,10 @@
         <v>0.97</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1812</v>
+        <v>-0.1506</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.4428</v>
+        <v>-2.8614</v>
       </c>
     </row>
     <row r="86">
@@ -6709,10 +6709,10 @@
         <v>0.71</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.8166</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.8118</v>
+        <v>-15.5154</v>
       </c>
     </row>
     <row r="87">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.6042</v>
+        <v>-0.4636</v>
       </c>
     </row>
     <row r="88">
@@ -6789,10 +6789,10 @@
         <v>0.97</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0477</v>
+        <v>-0.0383</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.9063</v>
+        <v>-0.7277</v>
       </c>
     </row>
     <row r="89">
@@ -6829,10 +6829,10 @@
         <v>0.83</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.9995</v>
+        <v>-3.6328</v>
       </c>
     </row>
     <row r="90">
@@ -6869,10 +6869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2304</v>
+        <v>-0.211</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.3776</v>
+        <v>-4.009</v>
       </c>
     </row>
     <row r="91">
@@ -6909,10 +6909,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2694</v>
+        <v>-0.2505</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.1186</v>
+        <v>-4.7595</v>
       </c>
     </row>
     <row r="92">
@@ -6949,10 +6949,10 @@
         <v>1.59</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0909</v>
+        <v>1.0832</v>
       </c>
       <c r="J92" t="n">
-        <v>26.1816</v>
+        <v>25.9968</v>
       </c>
     </row>
     <row r="93">
@@ -6989,10 +6989,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4888</v>
+        <v>0.4694</v>
       </c>
       <c r="J93" t="n">
-        <v>11.7312</v>
+        <v>11.2656</v>
       </c>
     </row>
     <row r="94">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4722</v>
+        <v>0.4471</v>
       </c>
       <c r="J94" t="n">
-        <v>11.3328</v>
+        <v>10.7304</v>
       </c>
     </row>
     <row r="95">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0254</v>
+        <v>-0.02</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.6096</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="96">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5473</v>
+        <v>-0.5084</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.1352</v>
+        <v>-12.2016</v>
       </c>
     </row>
     <row r="97">
@@ -7149,10 +7149,10 @@
         <v>1.12</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3112</v>
+        <v>0.2604</v>
       </c>
       <c r="J97" t="n">
-        <v>7.4688</v>
+        <v>6.2496</v>
       </c>
     </row>
     <row r="98">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2515</v>
+        <v>0.205</v>
       </c>
       <c r="J98" t="n">
-        <v>6.036</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="99">
@@ -7229,10 +7229,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0569</v>
+        <v>0.0389</v>
       </c>
       <c r="J99" t="n">
-        <v>1.3656</v>
+        <v>0.9336</v>
       </c>
     </row>
     <row r="100">
@@ -7269,10 +7269,10 @@
         <v>0.67</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3669</v>
+        <v>-0.353</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.8056</v>
+        <v>-8.472</v>
       </c>
     </row>
     <row r="101">
@@ -7309,10 +7309,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3669</v>
+        <v>-0.353</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.8056</v>
+        <v>-8.472</v>
       </c>
     </row>
     <row r="102">
@@ -7349,10 +7349,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.267</v>
+        <v>0.225</v>
       </c>
       <c r="J102" t="n">
-        <v>4.806</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="103">
@@ -7389,10 +7389,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0655</v>
+        <v>-0.0536</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.179</v>
+        <v>-0.9648</v>
       </c>
     </row>
     <row r="104">
@@ -7429,10 +7429,10 @@
         <v>0.77</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.262</v>
+        <v>-0.2446</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.716</v>
+        <v>-4.4028</v>
       </c>
     </row>
     <row r="105">
@@ -7469,10 +7469,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4086</v>
+        <v>-0.3977</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.3548</v>
+        <v>-7.1586</v>
       </c>
     </row>
     <row r="106">
@@ -7509,10 +7509,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.444</v>
+        <v>-0.4366</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.992</v>
+        <v>-7.8588</v>
       </c>
     </row>
     <row r="107">
@@ -7549,10 +7549,10 @@
         <v>2.08</v>
       </c>
       <c r="I107" t="n">
-        <v>1.6588</v>
+        <v>1.6972</v>
       </c>
       <c r="J107" t="n">
-        <v>29.8584</v>
+        <v>30.5496</v>
       </c>
     </row>
     <row r="108">
@@ -7589,10 +7589,10 @@
         <v>1.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7321</v>
       </c>
       <c r="J108" t="n">
-        <v>13.3812</v>
+        <v>13.1778</v>
       </c>
     </row>
     <row r="109">
@@ -7629,10 +7629,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4549</v>
+        <v>0.4306</v>
       </c>
       <c r="J109" t="n">
-        <v>8.1882</v>
+        <v>7.7508</v>
       </c>
     </row>
     <row r="110">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0058</v>
+        <v>-0.0052</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1044</v>
+        <v>-0.0936</v>
       </c>
     </row>
     <row r="111">
@@ -7709,10 +7709,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1139</v>
+        <v>-0.0946</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.0502</v>
+        <v>-1.7028</v>
       </c>
     </row>
     <row r="112">
@@ -7749,10 +7749,10 @@
         <v>1.99</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9192</v>
+        <v>0.8661</v>
       </c>
       <c r="J112" t="n">
-        <v>18.384</v>
+        <v>17.322</v>
       </c>
     </row>
     <row r="113">
@@ -7789,10 +7789,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3323</v>
+        <v>0.2771</v>
       </c>
       <c r="J113" t="n">
-        <v>6.646</v>
+        <v>5.542</v>
       </c>
     </row>
     <row r="114">
@@ -7829,10 +7829,10 @@
         <v>1.18</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2736</v>
+        <v>0.2246</v>
       </c>
       <c r="J114" t="n">
-        <v>5.472</v>
+        <v>4.492</v>
       </c>
     </row>
     <row r="115">
@@ -7869,10 +7869,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1384</v>
+        <v>0.107</v>
       </c>
       <c r="J115" t="n">
-        <v>2.768</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="116">
@@ -7909,10 +7909,10 @@
         <v>0.65</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4094</v>
+        <v>-0.4029</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.188000000000001</v>
+        <v>-8.058</v>
       </c>
     </row>
     <row r="117">
@@ -7949,10 +7949,10 @@
         <v>1.27</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4407</v>
+        <v>0.4484</v>
       </c>
       <c r="J117" t="n">
-        <v>8.814</v>
+        <v>8.968</v>
       </c>
     </row>
     <row r="118">
@@ -7989,10 +7989,10 @@
         <v>1.03</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0857</v>
+        <v>0.0709</v>
       </c>
       <c r="J118" t="n">
-        <v>1.714</v>
+        <v>1.418</v>
       </c>
     </row>
     <row r="119">
@@ -8029,10 +8029,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0404</v>
+        <v>0.0305</v>
       </c>
       <c r="J119" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="120">
@@ -8069,10 +8069,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2064</v>
+        <v>-0.1861</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.128</v>
+        <v>-3.722</v>
       </c>
     </row>
     <row r="121">
@@ -8109,10 +8109,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4756</v>
+        <v>-0.4732</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.512</v>
+        <v>-9.464</v>
       </c>
     </row>
     <row r="122">
@@ -8149,10 +8149,10 @@
         <v>1.15</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3505</v>
+        <v>0.2966</v>
       </c>
       <c r="J122" t="n">
-        <v>10.515</v>
+        <v>8.898</v>
       </c>
     </row>
     <row r="123">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3505</v>
+        <v>0.2966</v>
       </c>
       <c r="J123" t="n">
-        <v>10.515</v>
+        <v>8.898</v>
       </c>
     </row>
     <row r="124">
@@ -8229,10 +8229,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0759</v>
+        <v>0.054</v>
       </c>
       <c r="J124" t="n">
-        <v>2.277</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="125">
@@ -8269,10 +8269,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1997</v>
+        <v>-0.1791</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.991</v>
+        <v>-5.373</v>
       </c>
     </row>
     <row r="126">
@@ -8309,10 +8309,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.318</v>
+        <v>-0.301</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8349,10 +8349,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6637</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J127" t="n">
-        <v>19.911</v>
+        <v>19.491</v>
       </c>
     </row>
     <row r="128">
@@ -8389,10 +8389,10 @@
         <v>1.28</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6484</v>
+        <v>0.6349</v>
       </c>
       <c r="J128" t="n">
-        <v>19.452</v>
+        <v>19.047</v>
       </c>
     </row>
     <row r="129">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.522</v>
+        <v>0.5108</v>
       </c>
       <c r="J129" t="n">
-        <v>15.66</v>
+        <v>15.324</v>
       </c>
     </row>
     <row r="130">
@@ -8469,10 +8469,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3928</v>
+        <v>0.3563</v>
       </c>
       <c r="J130" t="n">
-        <v>11.784</v>
+        <v>10.689</v>
       </c>
     </row>
     <row r="131">
@@ -8509,10 +8509,10 @@
         <v>0.85</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4984</v>
+        <v>-0.4577</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.952</v>
+        <v>-13.731</v>
       </c>
     </row>
     <row r="132">
@@ -8549,10 +8549,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2719</v>
+        <v>1.2912</v>
       </c>
       <c r="J132" t="n">
-        <v>29.2537</v>
+        <v>29.6976</v>
       </c>
     </row>
     <row r="133">
@@ -8589,10 +8589,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6118</v>
+        <v>0.5778</v>
       </c>
       <c r="J133" t="n">
-        <v>14.0714</v>
+        <v>13.2894</v>
       </c>
     </row>
     <row r="134">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6118</v>
+        <v>0.5778</v>
       </c>
       <c r="J134" t="n">
-        <v>14.0714</v>
+        <v>13.2894</v>
       </c>
     </row>
     <row r="135">
@@ -8669,10 +8669,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.108</v>
+        <v>0.0873</v>
       </c>
       <c r="J135" t="n">
-        <v>2.484</v>
+        <v>2.0079</v>
       </c>
     </row>
     <row r="136">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6671</v>
+        <v>-0.6354</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.3433</v>
+        <v>-14.6142</v>
       </c>
     </row>
     <row r="137">
@@ -8749,10 +8749,10 @@
         <v>1.41</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7121</v>
       </c>
       <c r="J137" t="n">
-        <v>17.6088</v>
+        <v>16.3783</v>
       </c>
     </row>
     <row r="138">
@@ -8789,10 +8789,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.4736</v>
       </c>
       <c r="J138" t="n">
-        <v>12.2544</v>
+        <v>10.8928</v>
       </c>
     </row>
     <row r="139">
@@ -8829,10 +8829,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0253</v>
+        <v>-0.0182</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.5819</v>
+        <v>-0.4186</v>
       </c>
     </row>
     <row r="140">
@@ -8869,10 +8869,10 @@
         <v>0.7</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3479</v>
+        <v>-0.3331</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.0017</v>
+        <v>-7.6613</v>
       </c>
     </row>
     <row r="141">
@@ -8909,10 +8909,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3932</v>
+        <v>-0.3823</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.0436</v>
+        <v>-8.792899999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8949,10 +8949,10 @@
         <v>1.44</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0099</v>
+        <v>1.0092</v>
       </c>
       <c r="J142" t="n">
-        <v>20.198</v>
+        <v>20.184</v>
       </c>
     </row>
     <row r="143">
@@ -8989,10 +8989,10 @@
         <v>1.38</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9039</v>
+        <v>0.8882</v>
       </c>
       <c r="J143" t="n">
-        <v>18.078</v>
+        <v>17.764</v>
       </c>
     </row>
     <row r="144">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4976</v>
+        <v>0.4646</v>
       </c>
       <c r="J144" t="n">
-        <v>9.952</v>
+        <v>9.292</v>
       </c>
     </row>
     <row r="145">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3047</v>
+        <v>0.2726</v>
       </c>
       <c r="J145" t="n">
-        <v>6.094</v>
+        <v>5.452</v>
       </c>
     </row>
     <row r="146">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2229</v>
+        <v>0.1937</v>
       </c>
       <c r="J146" t="n">
-        <v>4.458</v>
+        <v>3.874</v>
       </c>
     </row>
     <row r="147">
@@ -9149,10 +9149,10 @@
         <v>1.7</v>
       </c>
       <c r="I147" t="n">
-        <v>1.12</v>
+        <v>1.1102</v>
       </c>
       <c r="J147" t="n">
-        <v>22.4</v>
+        <v>22.204</v>
       </c>
     </row>
     <row r="148">
@@ -9189,10 +9189,10 @@
         <v>1.21</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4409</v>
+        <v>0.3832</v>
       </c>
       <c r="J148" t="n">
-        <v>8.818</v>
+        <v>7.664</v>
       </c>
     </row>
     <row r="149">
@@ -9229,10 +9229,10 @@
         <v>0.96</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0759</v>
+        <v>-0.0608</v>
       </c>
       <c r="J149" t="n">
-        <v>-1.518</v>
+        <v>-1.216</v>
       </c>
     </row>
     <row r="150">
@@ -9269,10 +9269,10 @@
         <v>0.7</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3514</v>
+        <v>-0.3373</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.028</v>
+        <v>-6.746</v>
       </c>
     </row>
     <row r="151">
@@ -9309,10 +9309,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3966</v>
+        <v>-0.3866</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.932</v>
+        <v>-7.732</v>
       </c>
     </row>
     <row r="152">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.446</v>
+        <v>0.3908</v>
       </c>
       <c r="J152" t="n">
-        <v>9.811999999999999</v>
+        <v>8.5976</v>
       </c>
     </row>
     <row r="153">
@@ -9389,10 +9389,10 @@
         <v>0.93</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1042</v>
+        <v>-0.0892</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.2924</v>
+        <v>-1.9624</v>
       </c>
     </row>
     <row r="154">
@@ -9429,10 +9429,10 @@
         <v>0.92</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1163</v>
+        <v>-0.1004</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.5586</v>
+        <v>-2.2088</v>
       </c>
     </row>
     <row r="155">
@@ -9469,10 +9469,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2225</v>
+        <v>-0.2028</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.895</v>
+        <v>-4.4616</v>
       </c>
     </row>
     <row r="156">
@@ -9509,10 +9509,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4189</v>
+        <v>-0.4096</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.2158</v>
+        <v>-9.011200000000001</v>
       </c>
     </row>
     <row r="157">
@@ -9549,10 +9549,10 @@
         <v>1.7</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3648</v>
+        <v>1.3889</v>
       </c>
       <c r="J157" t="n">
-        <v>30.0256</v>
+        <v>30.5558</v>
       </c>
     </row>
     <row r="158">
@@ -9589,10 +9589,10 @@
         <v>1.62</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2603</v>
+        <v>1.278</v>
       </c>
       <c r="J158" t="n">
-        <v>27.7266</v>
+        <v>28.116</v>
       </c>
     </row>
     <row r="159">
@@ -9629,10 +9629,10 @@
         <v>1.32</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7886</v>
+        <v>0.7644</v>
       </c>
       <c r="J159" t="n">
-        <v>17.3492</v>
+        <v>16.8168</v>
       </c>
     </row>
     <row r="160">
@@ -9669,10 +9669,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.6926</v>
       </c>
       <c r="J160" t="n">
-        <v>-15.8246</v>
+        <v>-15.2372</v>
       </c>
     </row>
     <row r="161">
@@ -9709,10 +9709,10 @@
         <v>0.72</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8061</v>
+        <v>-0.7871</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.7342</v>
+        <v>-17.3162</v>
       </c>
     </row>
     <row r="162">
@@ -9749,10 +9749,10 @@
         <v>1.9</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5975</v>
+        <v>1.6393</v>
       </c>
       <c r="J162" t="n">
-        <v>33.5475</v>
+        <v>34.4253</v>
       </c>
     </row>
     <row r="163">
@@ -9789,10 +9789,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0998</v>
+        <v>1.1117</v>
       </c>
       <c r="J163" t="n">
-        <v>23.0958</v>
+        <v>23.3457</v>
       </c>
     </row>
     <row r="164">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6192</v>
+        <v>0.5914</v>
       </c>
       <c r="J164" t="n">
-        <v>13.0032</v>
+        <v>12.4194</v>
       </c>
     </row>
     <row r="165">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0495</v>
+        <v>-0.0449</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.0395</v>
+        <v>-0.9429</v>
       </c>
     </row>
     <row r="166">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.594</v>
+        <v>-0.5611</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.474</v>
+        <v>-11.7831</v>
       </c>
     </row>
     <row r="167">
@@ -9949,10 +9949,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.671</v>
+        <v>0.6209</v>
       </c>
       <c r="J167" t="n">
-        <v>14.091</v>
+        <v>13.0389</v>
       </c>
     </row>
     <row r="168">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1382</v>
+        <v>-0.1213</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.9022</v>
+        <v>-2.5473</v>
       </c>
     </row>
     <row r="169">
@@ -10029,10 +10029,10 @@
         <v>0.88</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1598</v>
+        <v>-0.1418</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.3558</v>
+        <v>-2.9778</v>
       </c>
     </row>
     <row r="170">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3454</v>
+        <v>-0.3298</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.2534</v>
+        <v>-6.9258</v>
       </c>
     </row>
     <row r="171">
@@ -10109,10 +10109,10 @@
         <v>0.61</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4175</v>
+        <v>-0.408</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.7675</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="172">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2937</v>
+        <v>0.2435</v>
       </c>
       <c r="J172" t="n">
-        <v>7.0488</v>
+        <v>5.844</v>
       </c>
     </row>
     <row r="173">
@@ -10189,10 +10189,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2746</v>
+        <v>0.2259</v>
       </c>
       <c r="J173" t="n">
-        <v>6.5904</v>
+        <v>5.4216</v>
       </c>
     </row>
     <row r="174">
@@ -10229,10 +10229,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.15</v>
+        <v>0.1153</v>
       </c>
       <c r="J174" t="n">
-        <v>3.6</v>
+        <v>2.7672</v>
       </c>
     </row>
     <row r="175">
@@ -10269,10 +10269,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1681</v>
+        <v>-0.1479</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.0344</v>
+        <v>-3.5496</v>
       </c>
     </row>
     <row r="176">
@@ -10309,10 +10309,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2805</v>
+        <v>-0.2616</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.732</v>
+        <v>-6.2784</v>
       </c>
     </row>
     <row r="177">
@@ -10349,10 +10349,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2387</v>
+        <v>1.2567</v>
       </c>
       <c r="J177" t="n">
-        <v>29.7288</v>
+        <v>30.1608</v>
       </c>
     </row>
     <row r="178">
@@ -10389,10 +10389,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9958</v>
+        <v>0.9918</v>
       </c>
       <c r="J178" t="n">
-        <v>23.8992</v>
+        <v>23.8032</v>
       </c>
     </row>
     <row r="179">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3926</v>
+        <v>0.3562</v>
       </c>
       <c r="J179" t="n">
-        <v>9.4224</v>
+        <v>8.5488</v>
       </c>
     </row>
     <row r="180">
@@ -10469,10 +10469,10 @@
         <v>0.87</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4491</v>
+        <v>-0.4075</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.7784</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -10509,10 +10509,10 @@
         <v>0.75</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7294</v>
+        <v>-0.7016</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.5056</v>
+        <v>-16.8384</v>
       </c>
     </row>
     <row r="182">
@@ -10549,10 +10549,10 @@
         <v>1.62</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2441</v>
+        <v>1.2607</v>
       </c>
       <c r="J182" t="n">
-        <v>24.882</v>
+        <v>25.214</v>
       </c>
     </row>
     <row r="183">
@@ -10589,10 +10589,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.218</v>
+        <v>1.2336</v>
       </c>
       <c r="J183" t="n">
-        <v>24.36</v>
+        <v>24.672</v>
       </c>
     </row>
     <row r="184">
@@ -10629,10 +10629,10 @@
         <v>1.28</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7002</v>
+        <v>0.6755</v>
       </c>
       <c r="J184" t="n">
-        <v>14.004</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="185">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1213</v>
+        <v>0.0975</v>
       </c>
       <c r="J185" t="n">
-        <v>2.426</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="186">
@@ -10709,10 +10709,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2538</v>
+        <v>-0.2191</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.076</v>
+        <v>-4.382</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +10749,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5144</v>
+        <v>0.4587</v>
       </c>
       <c r="J187" t="n">
-        <v>10.288</v>
+        <v>9.173999999999999</v>
       </c>
     </row>
     <row r="188">
@@ -10789,10 +10789,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3534</v>
+        <v>0.3007</v>
       </c>
       <c r="J188" t="n">
-        <v>7.068</v>
+        <v>6.014</v>
       </c>
     </row>
     <row r="189">
@@ -10829,10 +10829,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1906</v>
+        <v>0.1506</v>
       </c>
       <c r="J189" t="n">
-        <v>3.812</v>
+        <v>3.012</v>
       </c>
     </row>
     <row r="190">
@@ -10869,10 +10869,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3836</v>
+        <v>-0.371</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.672</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="191">
@@ -10909,10 +10909,10 @@
         <v>0.41</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5908</v>
+        <v>-0.605</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.816</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="192">
@@ -10949,10 +10949,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3937</v>
+        <v>0.3378</v>
       </c>
       <c r="J192" t="n">
-        <v>9.4488</v>
+        <v>8.107200000000001</v>
       </c>
     </row>
     <row r="193">
@@ -10989,10 +10989,10 @@
         <v>1.15</v>
       </c>
       <c r="I193" t="n">
-        <v>0.341</v>
+        <v>0.288</v>
       </c>
       <c r="J193" t="n">
-        <v>8.183999999999999</v>
+        <v>6.912</v>
       </c>
     </row>
     <row r="194">
@@ -11029,10 +11029,10 @@
         <v>1.07</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1878</v>
+        <v>0.149</v>
       </c>
       <c r="J194" t="n">
-        <v>4.5072</v>
+        <v>3.576</v>
       </c>
     </row>
     <row r="195">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1011</v>
+        <v>-0.0839</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.4264</v>
+        <v>-2.0136</v>
       </c>
     </row>
     <row r="196">
@@ -11109,10 +11109,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2646</v>
+        <v>-0.2452</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.3504</v>
+        <v>-5.8848</v>
       </c>
     </row>
     <row r="197">
@@ -11149,10 +11149,10 @@
         <v>1.36</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9157</v>
+        <v>0.9001</v>
       </c>
       <c r="J197" t="n">
-        <v>21.9768</v>
+        <v>21.6024</v>
       </c>
     </row>
     <row r="198">
@@ -11189,10 +11189,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7275</v>
+        <v>0.6956</v>
       </c>
       <c r="J198" t="n">
-        <v>17.46</v>
+        <v>16.6944</v>
       </c>
     </row>
     <row r="199">
@@ -11229,10 +11229,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3312</v>
+        <v>0.2914</v>
       </c>
       <c r="J199" t="n">
-        <v>7.9488</v>
+        <v>6.9936</v>
       </c>
     </row>
     <row r="200">
@@ -11269,10 +11269,10 @@
         <v>0.96</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1777</v>
+        <v>-0.1442</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.2648</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="201">
@@ -11309,10 +11309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.1069</v>
+        <v>-1.1188</v>
       </c>
       <c r="J201" t="n">
-        <v>-26.5656</v>
+        <v>-26.8512</v>
       </c>
     </row>
     <row r="202">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0169</v>
+        <v>-0.0091</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.3211</v>
+        <v>-0.1729</v>
       </c>
     </row>
     <row r="203">
@@ -11389,10 +11389,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.6986</v>
+        <v>-1.4402</v>
       </c>
     </row>
     <row r="204">
@@ -11429,10 +11429,10 @@
         <v>0.92</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1021</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.9399</v>
+        <v>-1.6701</v>
       </c>
     </row>
     <row r="205">
@@ -11469,10 +11469,10 @@
         <v>0.62</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3978</v>
+        <v>-0.3861</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.5582</v>
+        <v>-7.3359</v>
       </c>
     </row>
     <row r="206">
@@ -11509,10 +11509,10 @@
         <v>0.45</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5466</v>
+        <v>-0.552</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.3854</v>
+        <v>-10.488</v>
       </c>
     </row>
     <row r="207">
@@ -11549,10 +11549,10 @@
         <v>1.66</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2739</v>
+        <v>1.2929</v>
       </c>
       <c r="J207" t="n">
-        <v>24.2041</v>
+        <v>24.5651</v>
       </c>
     </row>
     <row r="208">
@@ -11589,10 +11589,10 @@
         <v>1.65</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2614</v>
+        <v>1.2799</v>
       </c>
       <c r="J208" t="n">
-        <v>23.9666</v>
+        <v>24.3181</v>
       </c>
     </row>
     <row r="209">
@@ -11629,10 +11629,10 @@
         <v>1.56</v>
       </c>
       <c r="I209" t="n">
-        <v>1.1471</v>
+        <v>1.1628</v>
       </c>
       <c r="J209" t="n">
-        <v>21.7949</v>
+        <v>22.0932</v>
       </c>
     </row>
     <row r="210">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4238</v>
+        <v>0.3926</v>
       </c>
       <c r="J210" t="n">
-        <v>8.052199999999999</v>
+        <v>7.4594</v>
       </c>
     </row>
     <row r="211">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1646</v>
+        <v>0.1351</v>
       </c>
       <c r="J211" t="n">
-        <v>3.1274</v>
+        <v>2.5669</v>
       </c>
     </row>
     <row r="212">
@@ -11749,10 +11749,10 @@
         <v>1.68</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1234</v>
+        <v>1.1192</v>
       </c>
       <c r="J212" t="n">
-        <v>23.5914</v>
+        <v>23.5032</v>
       </c>
     </row>
     <row r="213">
@@ -11789,10 +11789,10 @@
         <v>1.01</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J213" t="n">
-        <v>0.9786</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="214">
@@ -11829,10 +11829,10 @@
         <v>0.87</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1777</v>
+        <v>-0.1574</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.7317</v>
+        <v>-3.3054</v>
       </c>
     </row>
     <row r="215">
@@ -11869,10 +11869,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2984</v>
+        <v>-0.2803</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.2664</v>
+        <v>-5.8863</v>
       </c>
     </row>
     <row r="216">
@@ -11909,10 +11909,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4783</v>
+        <v>-0.4767</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.0443</v>
+        <v>-10.0107</v>
       </c>
     </row>
     <row r="217">
@@ -11949,10 +11949,10 @@
         <v>1.85</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5499</v>
+        <v>1.5889</v>
       </c>
       <c r="J217" t="n">
-        <v>32.5479</v>
+        <v>33.3669</v>
       </c>
     </row>
     <row r="218">
@@ -11989,10 +11989,10 @@
         <v>1.56</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1761</v>
+        <v>1.1901</v>
       </c>
       <c r="J218" t="n">
-        <v>24.6981</v>
+        <v>24.9921</v>
       </c>
     </row>
     <row r="219">
@@ -12029,10 +12029,10 @@
         <v>1.1</v>
       </c>
       <c r="I219" t="n">
-        <v>0.303</v>
+        <v>0.2711</v>
       </c>
       <c r="J219" t="n">
-        <v>6.363</v>
+        <v>5.6931</v>
       </c>
     </row>
     <row r="220">
@@ -12069,10 +12069,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3877</v>
+        <v>-0.3477</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.1417</v>
+        <v>-7.3017</v>
       </c>
     </row>
     <row r="221">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6095</v>
+        <v>-0.576</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.7995</v>
+        <v>-12.096</v>
       </c>
     </row>
     <row r="222">
@@ -12149,10 +12149,10 @@
         <v>2.21</v>
       </c>
       <c r="I222" t="n">
-        <v>1.9282</v>
+        <v>1.9818</v>
       </c>
       <c r="J222" t="n">
-        <v>30.8512</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="223">
@@ -12189,10 +12189,10 @@
         <v>1.69</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3108</v>
+        <v>1.3313</v>
       </c>
       <c r="J223" t="n">
-        <v>20.9728</v>
+        <v>21.3008</v>
       </c>
     </row>
     <row r="224">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3996</v>
+        <v>0.3678</v>
       </c>
       <c r="J224" t="n">
-        <v>6.3936</v>
+        <v>5.8848</v>
       </c>
     </row>
     <row r="225">
@@ -12269,10 +12269,10 @@
         <v>1.09</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2484</v>
+        <v>0.2164</v>
       </c>
       <c r="J225" t="n">
-        <v>3.9744</v>
+        <v>3.4624</v>
       </c>
     </row>
     <row r="226">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.207</v>
+        <v>-0.1803</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.312</v>
+        <v>-2.8848</v>
       </c>
     </row>
     <row r="227">
@@ -12349,10 +12349,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1419</v>
+        <v>0.1197</v>
       </c>
       <c r="J227" t="n">
-        <v>2.2704</v>
+        <v>1.9152</v>
       </c>
     </row>
     <row r="228">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.176</v>
+        <v>-0.1604</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.816</v>
+        <v>-2.5664</v>
       </c>
     </row>
     <row r="229">
@@ -12429,10 +12429,10 @@
         <v>0.85</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.176</v>
+        <v>-0.1604</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.816</v>
+        <v>-2.5664</v>
       </c>
     </row>
     <row r="230">
@@ -12469,10 +12469,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4017</v>
+        <v>-0.3905</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.4272</v>
+        <v>-6.248</v>
       </c>
     </row>
     <row r="231">
@@ -12509,10 +12509,10 @@
         <v>0.36</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6193</v>
+        <v>-0.6361</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.908799999999999</v>
+        <v>-10.1776</v>
       </c>
     </row>
     <row r="232">
@@ -12549,10 +12549,10 @@
         <v>1.17</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4039</v>
+        <v>0.3488</v>
       </c>
       <c r="J232" t="n">
-        <v>7.6741</v>
+        <v>6.6272</v>
       </c>
     </row>
     <row r="233">
@@ -12589,10 +12589,10 @@
         <v>1.1</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2713</v>
+        <v>0.2232</v>
       </c>
       <c r="J233" t="n">
-        <v>5.1547</v>
+        <v>4.2408</v>
       </c>
     </row>
     <row r="234">
@@ -12629,10 +12629,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1176</v>
+        <v>-0.1011</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.2344</v>
+        <v>-1.9209</v>
       </c>
     </row>
     <row r="235">
@@ -12669,10 +12669,10 @@
         <v>0.83</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2142</v>
+        <v>-0.1942</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.0698</v>
+        <v>-3.6898</v>
       </c>
     </row>
     <row r="236">
@@ -12709,10 +12709,10 @@
         <v>0.55</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4733</v>
+        <v>-0.4704</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.992699999999999</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="237">
@@ -12749,10 +12749,10 @@
         <v>1.96</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6913</v>
+        <v>1.7465</v>
       </c>
       <c r="J237" t="n">
-        <v>32.1347</v>
+        <v>33.1835</v>
       </c>
     </row>
     <row r="238">
@@ -12789,10 +12789,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9606</v>
+        <v>0.9516</v>
       </c>
       <c r="J238" t="n">
-        <v>18.2514</v>
+        <v>18.0804</v>
       </c>
     </row>
     <row r="239">
@@ -12829,10 +12829,10 @@
         <v>0.96</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2102</v>
+        <v>-0.1763</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.9938</v>
+        <v>-3.3497</v>
       </c>
     </row>
     <row r="240">
@@ -12869,10 +12869,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.358</v>
+        <v>-0.3179</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.802</v>
+        <v>-6.0401</v>
       </c>
     </row>
     <row r="241">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.385</v>
+        <v>-0.3446</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.315</v>
+        <v>-6.5474</v>
       </c>
     </row>
     <row r="242">
@@ -12949,10 +12949,10 @@
         <v>1.34</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7257</v>
+        <v>0.6841</v>
       </c>
       <c r="J242" t="n">
-        <v>13.7883</v>
+        <v>12.9979</v>
       </c>
     </row>
     <row r="243">
@@ -12989,10 +12989,10 @@
         <v>1.03</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1359</v>
+        <v>0.1055</v>
       </c>
       <c r="J243" t="n">
-        <v>2.5821</v>
+        <v>2.0045</v>
       </c>
     </row>
     <row r="244">
@@ -13029,10 +13029,10 @@
         <v>0.75</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2844</v>
+        <v>-0.2664</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.4036</v>
+        <v>-5.0616</v>
       </c>
     </row>
     <row r="245">
@@ -13069,10 +13069,10 @@
         <v>0.54</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4742</v>
+        <v>-0.4704</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.0098</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="246">
@@ -13109,10 +13109,10 @@
         <v>0.5</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5088</v>
+        <v>-0.5095</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.667199999999999</v>
+        <v>-9.6805</v>
       </c>
     </row>
     <row r="247">
@@ -13149,10 +13149,10 @@
         <v>1.89</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5778</v>
+        <v>1.6169</v>
       </c>
       <c r="J247" t="n">
-        <v>29.9782</v>
+        <v>30.7211</v>
       </c>
     </row>
     <row r="248">
@@ -13189,10 +13189,10 @@
         <v>1.41</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9433</v>
+        <v>0.9353</v>
       </c>
       <c r="J248" t="n">
-        <v>17.9227</v>
+        <v>17.7707</v>
       </c>
     </row>
     <row r="249">
@@ -13229,10 +13229,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5886</v>
       </c>
       <c r="J249" t="n">
-        <v>11.6926</v>
+        <v>11.1834</v>
       </c>
     </row>
     <row r="250">
@@ -13269,10 +13269,10 @@
         <v>1.21</v>
       </c>
       <c r="I250" t="n">
-        <v>0.5512</v>
+        <v>0.5223</v>
       </c>
       <c r="J250" t="n">
-        <v>10.4728</v>
+        <v>9.9237</v>
       </c>
     </row>
     <row r="251">
@@ -13309,10 +13309,10 @@
         <v>0.86</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5023</v>
+        <v>-0.4664</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.543699999999999</v>
+        <v>-8.861599999999999</v>
       </c>
     </row>
     <row r="252">
@@ -13349,10 +13349,10 @@
         <v>1.48</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1076</v>
+        <v>1.1212</v>
       </c>
       <c r="J252" t="n">
-        <v>26.5824</v>
+        <v>26.9088</v>
       </c>
     </row>
     <row r="253">
@@ -13389,10 +13389,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4742</v>
+        <v>0.4334</v>
       </c>
       <c r="J253" t="n">
-        <v>11.3808</v>
+        <v>10.4016</v>
       </c>
     </row>
     <row r="254">
@@ -13429,10 +13429,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2144</v>
+        <v>-0.1777</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.1456</v>
+        <v>-4.2648</v>
       </c>
     </row>
     <row r="255">
@@ -13469,10 +13469,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3301</v>
+        <v>-0.288</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.9224</v>
+        <v>-6.912</v>
       </c>
     </row>
     <row r="256">
@@ -13509,10 +13509,10 @@
         <v>0.88</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4093</v>
+        <v>-0.3663</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.8232</v>
+        <v>-8.7912</v>
       </c>
     </row>
     <row r="257">
@@ -13549,10 +13549,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3496</v>
+        <v>0.2957</v>
       </c>
       <c r="J257" t="n">
-        <v>8.3904</v>
+        <v>7.0968</v>
       </c>
     </row>
     <row r="258">
@@ -13589,10 +13589,10 @@
         <v>1.12</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2941</v>
+        <v>0.2438</v>
       </c>
       <c r="J258" t="n">
-        <v>7.0584</v>
+        <v>5.8512</v>
       </c>
     </row>
     <row r="259">
@@ -13629,10 +13629,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1503</v>
+        <v>0.1156</v>
       </c>
       <c r="J259" t="n">
-        <v>3.6072</v>
+        <v>2.7744</v>
       </c>
     </row>
     <row r="260">
@@ -13669,10 +13669,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1895</v>
+        <v>-0.169</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.548</v>
+        <v>-4.056</v>
       </c>
     </row>
     <row r="261">
@@ -13709,10 +13709,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.309</v>
+        <v>-0.2915</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.416</v>
+        <v>-6.996</v>
       </c>
     </row>
     <row r="262">
@@ -13749,10 +13749,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3394</v>
+        <v>1.3621</v>
       </c>
       <c r="J262" t="n">
-        <v>21.4304</v>
+        <v>21.7936</v>
       </c>
     </row>
     <row r="263">
@@ -13789,10 +13789,10 @@
         <v>1.66</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2656</v>
+        <v>1.2855</v>
       </c>
       <c r="J263" t="n">
-        <v>20.2496</v>
+        <v>20.568</v>
       </c>
     </row>
     <row r="264">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I264" t="n">
-        <v>1.0769</v>
+        <v>1.0925</v>
       </c>
       <c r="J264" t="n">
-        <v>17.2304</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="265">
@@ -13869,10 +13869,10 @@
         <v>1.46</v>
       </c>
       <c r="I265" t="n">
-        <v>1.0088</v>
+        <v>1.0169</v>
       </c>
       <c r="J265" t="n">
-        <v>16.1408</v>
+        <v>16.2704</v>
       </c>
     </row>
     <row r="266">
@@ -13909,10 +13909,10 @@
         <v>1.03</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0607</v>
+        <v>0.0363</v>
       </c>
       <c r="J266" t="n">
-        <v>0.9712</v>
+        <v>0.5808</v>
       </c>
     </row>
     <row r="267">
@@ -13949,10 +13949,10 @@
         <v>1.37</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8235</v>
+        <v>0.8052</v>
       </c>
       <c r="J267" t="n">
-        <v>13.176</v>
+        <v>12.8832</v>
       </c>
     </row>
     <row r="268">
@@ -13989,10 +13989,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.167</v>
+        <v>-0.1514</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.672</v>
+        <v>-2.4224</v>
       </c>
     </row>
     <row r="269">
@@ -14029,10 +14029,10 @@
         <v>0.72</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3039</v>
+        <v>-0.2882</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.8624</v>
+        <v>-4.6112</v>
       </c>
     </row>
     <row r="270">
@@ -14069,10 +14069,10 @@
         <v>0.4</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5864</v>
+        <v>-0.5976</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.382400000000001</v>
+        <v>-9.5616</v>
       </c>
     </row>
     <row r="271">
@@ -14109,10 +14109,10 @@
         <v>0.4</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5864</v>
+        <v>-0.5976</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.382400000000001</v>
+        <v>-9.5616</v>
       </c>
     </row>
     <row r="272">
@@ -14149,10 +14149,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3467</v>
+        <v>1.3693</v>
       </c>
       <c r="J272" t="n">
-        <v>26.934</v>
+        <v>27.386</v>
       </c>
     </row>
     <row r="273">
@@ -14189,10 +14189,10 @@
         <v>1.63</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2687</v>
+        <v>1.2867</v>
       </c>
       <c r="J273" t="n">
-        <v>25.374</v>
+        <v>25.734</v>
       </c>
     </row>
     <row r="274">
@@ -14229,10 +14229,10 @@
         <v>1.11</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3289</v>
+        <v>0.2965</v>
       </c>
       <c r="J274" t="n">
-        <v>6.578</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="275">
@@ -14269,10 +14269,10 @@
         <v>0.97</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1791</v>
+        <v>-0.1483</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.582</v>
+        <v>-2.966</v>
       </c>
     </row>
     <row r="276">
@@ -14309,10 +14309,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5514</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.724</v>
+        <v>-11.028</v>
       </c>
     </row>
     <row r="277">
@@ -14349,10 +14349,10 @@
         <v>1.28</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5911</v>
+        <v>0.5354</v>
       </c>
       <c r="J277" t="n">
-        <v>11.822</v>
+        <v>10.708</v>
       </c>
     </row>
     <row r="278">
@@ -14389,10 +14389,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5077</v>
+        <v>0.4509</v>
       </c>
       <c r="J278" t="n">
-        <v>10.154</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -14429,10 +14429,10 @@
         <v>0.98</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0371</v>
+        <v>-0.029</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.742</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="280">
@@ -14469,10 +14469,10 @@
         <v>0.74</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3027</v>
+        <v>-0.2847</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.054</v>
+        <v>-5.694</v>
       </c>
     </row>
     <row r="281">
@@ -14509,10 +14509,10 @@
         <v>0.36</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6335</v>
+        <v>-0.6556</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.67</v>
+        <v>-13.112</v>
       </c>
     </row>
     <row r="282">
@@ -14549,10 +14549,10 @@
         <v>1.46</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0535</v>
+        <v>1.0595</v>
       </c>
       <c r="J282" t="n">
-        <v>23.177</v>
+        <v>23.309</v>
       </c>
     </row>
     <row r="283">
@@ -14589,10 +14589,10 @@
         <v>1.38</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9177</v>
+        <v>0.9019</v>
       </c>
       <c r="J283" t="n">
-        <v>20.1894</v>
+        <v>19.8418</v>
       </c>
     </row>
     <row r="284">
@@ -14629,10 +14629,10 @@
         <v>1.28</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6871</v>
       </c>
       <c r="J284" t="n">
-        <v>15.7784</v>
+        <v>15.1162</v>
       </c>
     </row>
     <row r="285">
@@ -14669,10 +14669,10 @@
         <v>0.95</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2326</v>
+        <v>-0.1958</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.1172</v>
+        <v>-4.3076</v>
       </c>
     </row>
     <row r="286">
@@ -14709,10 +14709,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6209</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.6598</v>
+        <v>-12.8964</v>
       </c>
     </row>
     <row r="287">
@@ -14749,10 +14749,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2939</v>
+        <v>0.2443</v>
       </c>
       <c r="J287" t="n">
-        <v>6.4658</v>
+        <v>5.3746</v>
       </c>
     </row>
     <row r="288">
@@ -14789,10 +14789,10 @@
         <v>1.02</v>
       </c>
       <c r="I288" t="n">
-        <v>0.0895</v>
+        <v>0.0646</v>
       </c>
       <c r="J288" t="n">
-        <v>1.969</v>
+        <v>1.4212</v>
       </c>
     </row>
     <row r="289">
@@ -14829,10 +14829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0926</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.0372</v>
+        <v>-1.7226</v>
       </c>
     </row>
     <row r="290">
@@ -14869,10 +14869,10 @@
         <v>0.83</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2133</v>
+        <v>-0.1935</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.6926</v>
+        <v>-4.257</v>
       </c>
     </row>
     <row r="291">
@@ -14909,10 +14909,10 @@
         <v>0.62</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.411</v>
+        <v>-0.401</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.042</v>
+        <v>-8.821999999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14949,10 +14949,10 @@
         <v>1.46</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8105</v>
+        <v>0.7561</v>
       </c>
       <c r="J292" t="n">
-        <v>17.831</v>
+        <v>16.6342</v>
       </c>
     </row>
     <row r="293">
@@ -14989,10 +14989,10 @@
         <v>1.32</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6046</v>
+        <v>0.5448</v>
       </c>
       <c r="J293" t="n">
-        <v>13.3012</v>
+        <v>11.9856</v>
       </c>
     </row>
     <row r="294">
@@ -15029,10 +15029,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4476</v>
+        <v>0.3904</v>
       </c>
       <c r="J294" t="n">
-        <v>9.847200000000001</v>
+        <v>8.588800000000001</v>
       </c>
     </row>
     <row r="295">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2607</v>
+        <v>-0.2416</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.7354</v>
+        <v>-5.3152</v>
       </c>
     </row>
     <row r="296">
@@ -15109,10 +15109,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3738</v>
+        <v>-0.3621</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.223599999999999</v>
+        <v>-7.9662</v>
       </c>
     </row>
     <row r="297">
@@ -15149,10 +15149,10 @@
         <v>1.46</v>
       </c>
       <c r="I297" t="n">
-        <v>1.0873</v>
+        <v>1.1001</v>
       </c>
       <c r="J297" t="n">
-        <v>23.9206</v>
+        <v>24.2022</v>
       </c>
     </row>
     <row r="298">
@@ -15189,10 +15189,10 @@
         <v>1.37</v>
       </c>
       <c r="I298" t="n">
-        <v>0.9362</v>
+        <v>0.9235</v>
       </c>
       <c r="J298" t="n">
-        <v>20.5964</v>
+        <v>20.317</v>
       </c>
     </row>
     <row r="299">
@@ -15229,10 +15229,10 @@
         <v>0.91</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3246</v>
+        <v>-0.2827</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.1412</v>
+        <v>-6.2194</v>
       </c>
     </row>
     <row r="300">
@@ -15269,10 +15269,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3515</v>
+        <v>-0.309</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.733</v>
+        <v>-6.798</v>
       </c>
     </row>
     <row r="301">
@@ -15309,10 +15309,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0262</v>
+        <v>-1.027</v>
       </c>
       <c r="J301" t="n">
-        <v>-22.5764</v>
+        <v>-22.594</v>
       </c>
     </row>
     <row r="302">
@@ -15349,10 +15349,10 @@
         <v>0.83</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.1797</v>
+        <v>-0.1632</v>
       </c>
       <c r="J302" t="n">
-        <v>-3.0549</v>
+        <v>-2.7744</v>
       </c>
     </row>
     <row r="303">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1906</v>
+        <v>-0.1745</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.2402</v>
+        <v>-2.9665</v>
       </c>
     </row>
     <row r="304">
@@ -15429,10 +15429,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.4167</v>
+        <v>-0.4078</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.0839</v>
+        <v>-6.9326</v>
       </c>
     </row>
     <row r="305">
@@ -15469,10 +15469,10 @@
         <v>0.53</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4607</v>
+        <v>-0.4549</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.8319</v>
+        <v>-7.7333</v>
       </c>
     </row>
     <row r="306">
@@ -15509,10 +15509,10 @@
         <v>0.48</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5047</v>
+        <v>-0.5033</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.5799</v>
+        <v>-8.556100000000001</v>
       </c>
     </row>
     <row r="307">
@@ -15549,10 +15549,10 @@
         <v>1.9</v>
       </c>
       <c r="I307" t="n">
-        <v>1.5566</v>
+        <v>1.5922</v>
       </c>
       <c r="J307" t="n">
-        <v>26.4622</v>
+        <v>27.0674</v>
       </c>
     </row>
     <row r="308">
@@ -15589,10 +15589,10 @@
         <v>1.64</v>
       </c>
       <c r="I308" t="n">
-        <v>1.2413</v>
+        <v>1.2604</v>
       </c>
       <c r="J308" t="n">
-        <v>21.1021</v>
+        <v>21.4268</v>
       </c>
     </row>
     <row r="309">
@@ -15629,10 +15629,10 @@
         <v>1.52</v>
       </c>
       <c r="I309" t="n">
-        <v>1.09</v>
+        <v>1.1063</v>
       </c>
       <c r="J309" t="n">
-        <v>18.53</v>
+        <v>18.8071</v>
       </c>
     </row>
     <row r="310">
@@ -15669,10 +15669,10 @@
         <v>1.15</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3923</v>
+        <v>0.36</v>
       </c>
       <c r="J310" t="n">
-        <v>6.6691</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="311">
@@ -15709,10 +15709,10 @@
         <v>1.15</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3923</v>
+        <v>0.36</v>
       </c>
       <c r="J311" t="n">
-        <v>6.6691</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="312">
@@ -15749,10 +15749,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3593</v>
+        <v>1.3822</v>
       </c>
       <c r="J312" t="n">
-        <v>24.4674</v>
+        <v>24.8796</v>
       </c>
     </row>
     <row r="313">
@@ -15789,10 +15789,10 @@
         <v>1.58</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1714</v>
+        <v>1.1878</v>
       </c>
       <c r="J313" t="n">
-        <v>21.0852</v>
+        <v>21.3804</v>
       </c>
     </row>
     <row r="314">
@@ -15829,10 +15829,10 @@
         <v>1.58</v>
       </c>
       <c r="I314" t="n">
-        <v>1.1714</v>
+        <v>1.1878</v>
       </c>
       <c r="J314" t="n">
-        <v>21.0852</v>
+        <v>21.3804</v>
       </c>
     </row>
     <row r="315">
@@ -15869,10 +15869,10 @@
         <v>1.16</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4223</v>
+        <v>0.391</v>
       </c>
       <c r="J315" t="n">
-        <v>7.6014</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="316">
@@ -15909,10 +15909,10 @@
         <v>1.09</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2475</v>
+        <v>0.2154</v>
       </c>
       <c r="J316" t="n">
-        <v>4.455</v>
+        <v>3.8772</v>
       </c>
     </row>
     <row r="317">
@@ -15949,10 +15949,10 @@
         <v>1.18</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5108</v>
+        <v>0.4766</v>
       </c>
       <c r="J317" t="n">
-        <v>9.1944</v>
+        <v>8.578799999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15989,10 +15989,10 @@
         <v>0.65</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3628</v>
+        <v>-0.3498</v>
       </c>
       <c r="J318" t="n">
-        <v>-6.5304</v>
+        <v>-6.2964</v>
       </c>
     </row>
     <row r="319">
@@ -16029,10 +16029,10 @@
         <v>0.58</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.4251</v>
+        <v>-0.4159</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.6518</v>
+        <v>-7.4862</v>
       </c>
     </row>
     <row r="320">
@@ -16069,10 +16069,10 @@
         <v>0.58</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4251</v>
+        <v>-0.4159</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.6518</v>
+        <v>-7.4862</v>
       </c>
     </row>
     <row r="321">
@@ -16109,10 +16109,10 @@
         <v>0.57</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4339</v>
+        <v>-0.4255</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.8102</v>
+        <v>-7.659</v>
       </c>
     </row>
     <row r="322">
@@ -16149,10 +16149,10 @@
         <v>1.55</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1931</v>
+        <v>1.2095</v>
       </c>
       <c r="J322" t="n">
-        <v>27.4413</v>
+        <v>27.8185</v>
       </c>
     </row>
     <row r="323">
@@ -16189,10 +16189,10 @@
         <v>1.34</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8528</v>
+        <v>0.8305</v>
       </c>
       <c r="J323" t="n">
-        <v>19.6144</v>
+        <v>19.1015</v>
       </c>
     </row>
     <row r="324">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0404</v>
+        <v>0.0298</v>
       </c>
       <c r="J324" t="n">
-        <v>0.9292</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="325">
@@ -16269,10 +16269,10 @@
         <v>0.92</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3109</v>
+        <v>-0.2697</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.1507</v>
+        <v>-6.2031</v>
       </c>
     </row>
     <row r="326">
@@ -16309,10 +16309,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6569</v>
+        <v>-0.623</v>
       </c>
       <c r="J326" t="n">
-        <v>-15.1087</v>
+        <v>-14.329</v>
       </c>
     </row>
     <row r="327">
@@ -16349,10 +16349,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7399</v>
+        <v>0.6913</v>
       </c>
       <c r="J327" t="n">
-        <v>17.0177</v>
+        <v>15.8999</v>
       </c>
     </row>
     <row r="328">
@@ -16389,10 +16389,10 @@
         <v>0.9</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1396</v>
+        <v>-0.1219</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.2108</v>
+        <v>-2.8037</v>
       </c>
     </row>
     <row r="329">
@@ -16429,10 +16429,10 @@
         <v>0.89</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1505</v>
+        <v>-0.1323</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.4615</v>
+        <v>-3.0429</v>
       </c>
     </row>
     <row r="330">
@@ -16469,10 +16469,10 @@
         <v>0.78</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2631</v>
+        <v>-0.2438</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.0513</v>
+        <v>-5.6074</v>
       </c>
     </row>
     <row r="331">
@@ -16509,10 +16509,10 @@
         <v>0.59</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4377</v>
+        <v>-0.4305</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.0671</v>
+        <v>-9.9015</v>
       </c>
     </row>
     <row r="332">
@@ -16549,10 +16549,10 @@
         <v>2.18</v>
       </c>
       <c r="I332" t="n">
-        <v>1.8332</v>
+        <v>1.8935</v>
       </c>
       <c r="J332" t="n">
-        <v>25.6648</v>
+        <v>26.509</v>
       </c>
     </row>
     <row r="333">
@@ -16589,10 +16589,10 @@
         <v>2.02</v>
       </c>
       <c r="I333" t="n">
-        <v>1.6565</v>
+        <v>1.7018</v>
       </c>
       <c r="J333" t="n">
-        <v>23.191</v>
+        <v>23.8252</v>
       </c>
     </row>
     <row r="334">
@@ -16629,10 +16629,10 @@
         <v>1.96</v>
       </c>
       <c r="I334" t="n">
-        <v>1.5892</v>
+        <v>1.6299</v>
       </c>
       <c r="J334" t="n">
-        <v>22.2488</v>
+        <v>22.8186</v>
       </c>
     </row>
     <row r="335">
@@ -16669,10 +16669,10 @@
         <v>1.48</v>
       </c>
       <c r="I335" t="n">
-        <v>1.0157</v>
+        <v>1.0316</v>
       </c>
       <c r="J335" t="n">
-        <v>14.2198</v>
+        <v>14.4424</v>
       </c>
     </row>
     <row r="336">
@@ -16709,10 +16709,10 @@
         <v>0.92</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3953</v>
+        <v>-0.371</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.5342</v>
+        <v>-5.194</v>
       </c>
     </row>
     <row r="337">
@@ -16749,10 +16749,10 @@
         <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>0.1231</v>
+        <v>0.1342</v>
       </c>
       <c r="J337" t="n">
-        <v>1.7234</v>
+        <v>1.8788</v>
       </c>
     </row>
     <row r="338">
@@ -16789,10 +16789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.4312</v>
+        <v>-0.4237</v>
       </c>
       <c r="J338" t="n">
-        <v>-6.0368</v>
+        <v>-5.9318</v>
       </c>
     </row>
     <row r="339">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.44</v>
+        <v>-0.433</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.16</v>
+        <v>-6.062</v>
       </c>
     </row>
     <row r="340">
@@ -16869,10 +16869,10 @@
         <v>0.52</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4663</v>
+        <v>-0.4613</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.5282</v>
+        <v>-6.4582</v>
       </c>
     </row>
     <row r="341">
@@ -16909,10 +16909,10 @@
         <v>0.5</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4839</v>
+        <v>-0.4804</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.7746</v>
+        <v>-6.7256</v>
       </c>
     </row>
     <row r="342">
@@ -16949,10 +16949,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>0.9772</v>
+        <v>0.9709</v>
       </c>
       <c r="J342" t="n">
-        <v>19.544</v>
+        <v>19.418</v>
       </c>
     </row>
     <row r="343">
@@ -16989,10 +16989,10 @@
         <v>1.41</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9597</v>
+        <v>0.9507</v>
       </c>
       <c r="J343" t="n">
-        <v>19.194</v>
+        <v>19.014</v>
       </c>
     </row>
     <row r="344">
@@ -17029,10 +17029,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8462</v>
+        <v>0.826</v>
       </c>
       <c r="J344" t="n">
-        <v>16.924</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="345">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4522</v>
+        <v>0.4189</v>
       </c>
       <c r="J345" t="n">
-        <v>9.044</v>
+        <v>8.378</v>
       </c>
     </row>
     <row r="346">
@@ -17109,10 +17109,10 @@
         <v>0.82</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5843</v>
+        <v>-0.5491</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.686</v>
+        <v>-10.982</v>
       </c>
     </row>
     <row r="347">
@@ -17149,10 +17149,10 @@
         <v>1.05</v>
       </c>
       <c r="I347" t="n">
-        <v>0.1948</v>
+        <v>0.1584</v>
       </c>
       <c r="J347" t="n">
-        <v>3.896</v>
+        <v>3.168</v>
       </c>
     </row>
     <row r="348">
@@ -17189,10 +17189,10 @@
         <v>0.84</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1956</v>
+        <v>-0.1787</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.912</v>
+        <v>-3.574</v>
       </c>
     </row>
     <row r="349">
@@ -17229,10 +17229,10 @@
         <v>0.79</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.244</v>
+        <v>-0.2263</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.88</v>
+        <v>-4.526</v>
       </c>
     </row>
     <row r="350">
@@ -17269,10 +17269,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2629</v>
+        <v>-0.2452</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.258</v>
+        <v>-4.904</v>
       </c>
     </row>
     <row r="351">
@@ -17309,10 +17309,10 @@
         <v>0.58</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4363</v>
+        <v>-0.4281</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.726000000000001</v>
+        <v>-8.561999999999999</v>
       </c>
     </row>
     <row r="352">
@@ -17349,10 +17349,10 @@
         <v>1.58</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1953</v>
+        <v>1.21</v>
       </c>
       <c r="J352" t="n">
-        <v>21.5154</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="353">
@@ -17389,10 +17389,10 @@
         <v>1.54</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1424</v>
+        <v>1.1554</v>
       </c>
       <c r="J353" t="n">
-        <v>20.5632</v>
+        <v>20.7972</v>
       </c>
     </row>
     <row r="354">
@@ -17429,10 +17429,10 @@
         <v>1.5</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0887</v>
+        <v>1.0996</v>
       </c>
       <c r="J354" t="n">
-        <v>19.5966</v>
+        <v>19.7928</v>
       </c>
     </row>
     <row r="355">
@@ -17469,10 +17469,10 @@
         <v>1.06</v>
       </c>
       <c r="I355" t="n">
-        <v>0.1862</v>
+        <v>0.1585</v>
       </c>
       <c r="J355" t="n">
-        <v>3.3516</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="356">
@@ -17509,10 +17509,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.8144</v>
+        <v>-0.7978</v>
       </c>
       <c r="J356" t="n">
-        <v>-14.6592</v>
+        <v>-14.3604</v>
       </c>
     </row>
     <row r="357">
@@ -17549,10 +17549,10 @@
         <v>1.47</v>
       </c>
       <c r="I357" t="n">
-        <v>0.9141</v>
+        <v>0.8852</v>
       </c>
       <c r="J357" t="n">
-        <v>16.4538</v>
+        <v>15.9336</v>
       </c>
     </row>
     <row r="358">
@@ -17589,10 +17589,10 @@
         <v>1.12</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3255</v>
+        <v>0.2755</v>
       </c>
       <c r="J358" t="n">
-        <v>5.859</v>
+        <v>4.959</v>
       </c>
     </row>
     <row r="359">
@@ -17629,10 +17629,10 @@
         <v>0.8</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2395</v>
+        <v>-0.2203</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.311</v>
+        <v>-3.9654</v>
       </c>
     </row>
     <row r="360">
@@ -17669,10 +17669,10 @@
         <v>0.53</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.486</v>
+        <v>-0.4841</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.747999999999999</v>
+        <v>-8.713800000000001</v>
       </c>
     </row>
     <row r="361">
@@ -17709,10 +17709,10 @@
         <v>0.4</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5965</v>
+        <v>-0.6112</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.737</v>
+        <v>-11.0016</v>
       </c>
     </row>
     <row r="362">
@@ -17749,10 +17749,10 @@
         <v>1.21</v>
       </c>
       <c r="I362" t="n">
-        <v>0.4833</v>
+        <v>0.4281</v>
       </c>
       <c r="J362" t="n">
-        <v>10.1493</v>
+        <v>8.9901</v>
       </c>
     </row>
     <row r="363">
@@ -17789,10 +17789,10 @@
         <v>0.95</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.078</v>
+        <v>-0.0653</v>
       </c>
       <c r="J363" t="n">
-        <v>-1.638</v>
+        <v>-1.3713</v>
       </c>
     </row>
     <row r="364">
@@ -17829,10 +17829,10 @@
         <v>0.83</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2119</v>
+        <v>-0.1923</v>
       </c>
       <c r="J364" t="n">
-        <v>-4.4499</v>
+        <v>-4.0383</v>
       </c>
     </row>
     <row r="365">
@@ -17869,10 +17869,10 @@
         <v>0.77</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.271</v>
+        <v>-0.252</v>
       </c>
       <c r="J365" t="n">
-        <v>-5.691</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="366">
@@ -17909,10 +17909,10 @@
         <v>0.68</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3554</v>
+        <v>-0.3405</v>
       </c>
       <c r="J366" t="n">
-        <v>-7.4634</v>
+        <v>-7.1505</v>
       </c>
     </row>
     <row r="367">
@@ -17949,10 +17949,10 @@
         <v>1.58</v>
       </c>
       <c r="I367" t="n">
-        <v>1.2143</v>
+        <v>1.2301</v>
       </c>
       <c r="J367" t="n">
-        <v>25.5003</v>
+        <v>25.8321</v>
       </c>
     </row>
     <row r="368">
@@ -17989,10 +17989,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6513</v>
+        <v>0.6194</v>
       </c>
       <c r="J368" t="n">
-        <v>13.6773</v>
+        <v>13.0074</v>
       </c>
     </row>
     <row r="369">
@@ -18029,10 +18029,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.3867</v>
+        <v>0.3523</v>
       </c>
       <c r="J369" t="n">
-        <v>8.120699999999999</v>
+        <v>7.3983</v>
       </c>
     </row>
     <row r="370">
@@ -18069,10 +18069,10 @@
         <v>1.13</v>
       </c>
       <c r="I370" t="n">
-        <v>0.3867</v>
+        <v>0.3523</v>
       </c>
       <c r="J370" t="n">
-        <v>8.120699999999999</v>
+        <v>7.3983</v>
       </c>
     </row>
     <row r="371">
@@ -18109,10 +18109,10 @@
         <v>0.88</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4313</v>
+        <v>-0.3903</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.0573</v>
+        <v>-8.196300000000001</v>
       </c>
     </row>
     <row r="372">
@@ -18149,10 +18149,10 @@
         <v>1.03</v>
       </c>
       <c r="I372" t="n">
-        <v>0.1251</v>
+        <v>0.0948</v>
       </c>
       <c r="J372" t="n">
-        <v>2.502</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="373">
@@ -18189,10 +18189,10 @@
         <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>0.0216</v>
+        <v>0.0163</v>
       </c>
       <c r="J373" t="n">
-        <v>0.432</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="374">
@@ -18229,10 +18229,10 @@
         <v>0.96</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.0622</v>
+        <v>-0.0511</v>
       </c>
       <c r="J374" t="n">
-        <v>-1.244</v>
+        <v>-1.022</v>
       </c>
     </row>
     <row r="375">
@@ -18269,10 +18269,10 @@
         <v>0.72</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3166</v>
+        <v>-0.2994</v>
       </c>
       <c r="J375" t="n">
-        <v>-6.332</v>
+        <v>-5.988</v>
       </c>
     </row>
     <row r="376">
@@ -18309,10 +18309,10 @@
         <v>0.64</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.3897</v>
+        <v>-0.3775</v>
       </c>
       <c r="J376" t="n">
-        <v>-7.794</v>
+        <v>-7.55</v>
       </c>
     </row>
     <row r="377">
@@ -18349,10 +18349,10 @@
         <v>1.35</v>
       </c>
       <c r="I377" t="n">
-        <v>0.8477</v>
+        <v>0.8274</v>
       </c>
       <c r="J377" t="n">
-        <v>16.954</v>
+        <v>16.548</v>
       </c>
     </row>
     <row r="378">
@@ -18389,10 +18389,10 @@
         <v>1.32</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7886</v>
+        <v>0.7644</v>
       </c>
       <c r="J378" t="n">
-        <v>15.772</v>
+        <v>15.288</v>
       </c>
     </row>
     <row r="379">
@@ -18429,10 +18429,10 @@
         <v>1.28</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7083</v>
+        <v>0.68</v>
       </c>
       <c r="J379" t="n">
-        <v>14.166</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="380">
@@ -18469,10 +18469,10 @@
         <v>1.13</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3821</v>
+        <v>0.3486</v>
       </c>
       <c r="J380" t="n">
-        <v>7.642</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="381">
@@ -18509,10 +18509,10 @@
         <v>1.04</v>
       </c>
       <c r="I381" t="n">
-        <v>0.1337</v>
+        <v>0.1101</v>
       </c>
       <c r="J381" t="n">
-        <v>2.674</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="382">
@@ -18549,10 +18549,10 @@
         <v>1.52</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1167</v>
+        <v>1.129</v>
       </c>
       <c r="J382" t="n">
-        <v>21.2173</v>
+        <v>21.451</v>
       </c>
     </row>
     <row r="383">
@@ -18589,10 +18589,10 @@
         <v>1.46</v>
       </c>
       <c r="I383" t="n">
-        <v>1.0332</v>
+        <v>1.0371</v>
       </c>
       <c r="J383" t="n">
-        <v>19.6308</v>
+        <v>19.7049</v>
       </c>
     </row>
     <row r="384">
@@ -18629,10 +18629,10 @@
         <v>1.16</v>
       </c>
       <c r="I384" t="n">
-        <v>0.4459</v>
+        <v>0.4137</v>
       </c>
       <c r="J384" t="n">
-        <v>8.472099999999999</v>
+        <v>7.8603</v>
       </c>
     </row>
     <row r="385">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3742</v>
+        <v>0.3417</v>
       </c>
       <c r="J385" t="n">
-        <v>7.1098</v>
+        <v>6.4923</v>
       </c>
     </row>
     <row r="386">
@@ -18709,10 +18709,10 @@
         <v>1.1</v>
       </c>
       <c r="I386" t="n">
-        <v>0.2981</v>
+        <v>0.2665</v>
       </c>
       <c r="J386" t="n">
-        <v>5.6639</v>
+        <v>5.0635</v>
       </c>
     </row>
     <row r="387">
@@ -18749,10 +18749,10 @@
         <v>1.28</v>
       </c>
       <c r="I387" t="n">
-        <v>0.607</v>
+        <v>0.5546</v>
       </c>
       <c r="J387" t="n">
-        <v>11.533</v>
+        <v>10.5374</v>
       </c>
     </row>
     <row r="388">
@@ -18789,10 +18789,10 @@
         <v>1</v>
       </c>
       <c r="I388" t="n">
-        <v>0.0202</v>
+        <v>0.015</v>
       </c>
       <c r="J388" t="n">
-        <v>0.3838</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="389">
@@ -18829,10 +18829,10 @@
         <v>0.77</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2698</v>
+        <v>-0.2509</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.1262</v>
+        <v>-4.7671</v>
       </c>
     </row>
     <row r="390">
@@ -18869,10 +18869,10 @@
         <v>0.75</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2889</v>
+        <v>-0.2706</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.4891</v>
+        <v>-5.1414</v>
       </c>
     </row>
     <row r="391">
@@ -18909,10 +18909,10 @@
         <v>0.58</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4436</v>
+        <v>-0.4367</v>
       </c>
       <c r="J391" t="n">
-        <v>-8.4284</v>
+        <v>-8.2973</v>
       </c>
     </row>
     <row r="392">
@@ -18949,10 +18949,10 @@
         <v>1.36</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7689</v>
+        <v>0.7335</v>
       </c>
       <c r="J392" t="n">
-        <v>12.3024</v>
+        <v>11.736</v>
       </c>
     </row>
     <row r="393">
@@ -18989,10 +18989,10 @@
         <v>0.77</v>
       </c>
       <c r="I393" t="n">
-        <v>-0.2635</v>
+        <v>-0.2456</v>
       </c>
       <c r="J393" t="n">
-        <v>-4.216</v>
+        <v>-3.9296</v>
       </c>
     </row>
     <row r="394">
@@ -19029,10 +19029,10 @@
         <v>0.7</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.3289</v>
+        <v>-0.3127</v>
       </c>
       <c r="J394" t="n">
-        <v>-5.2624</v>
+        <v>-5.0032</v>
       </c>
     </row>
     <row r="395">
@@ -19069,10 +19069,10 @@
         <v>0.63</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.3925</v>
+        <v>-0.3803</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.28</v>
+        <v>-6.0848</v>
       </c>
     </row>
     <row r="396">
@@ -19109,10 +19109,10 @@
         <v>0.6</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4193</v>
+        <v>-0.4094</v>
       </c>
       <c r="J396" t="n">
-        <v>-6.7088</v>
+        <v>-6.5504</v>
       </c>
     </row>
     <row r="397">
@@ -19149,10 +19149,10 @@
         <v>1.74</v>
       </c>
       <c r="I397" t="n">
-        <v>1.383</v>
+        <v>1.4068</v>
       </c>
       <c r="J397" t="n">
-        <v>22.128</v>
+        <v>22.5088</v>
       </c>
     </row>
     <row r="398">
@@ -19189,10 +19189,10 @@
         <v>1.64</v>
       </c>
       <c r="I398" t="n">
-        <v>1.2572</v>
+        <v>1.2748</v>
       </c>
       <c r="J398" t="n">
-        <v>20.1152</v>
+        <v>20.3968</v>
       </c>
     </row>
     <row r="399">
@@ -19229,10 +19229,10 @@
         <v>1.22</v>
       </c>
       <c r="I399" t="n">
-        <v>0.5664</v>
+        <v>0.539</v>
       </c>
       <c r="J399" t="n">
-        <v>9.0624</v>
+        <v>8.624000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -19269,10 +19269,10 @@
         <v>1.14</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3841</v>
+        <v>0.3523</v>
       </c>
       <c r="J400" t="n">
-        <v>6.1456</v>
+        <v>5.6368</v>
       </c>
     </row>
     <row r="401">
@@ -19309,10 +19309,10 @@
         <v>1.09</v>
       </c>
       <c r="I401" t="n">
-        <v>0.2569</v>
+        <v>0.2256</v>
       </c>
       <c r="J401" t="n">
-        <v>4.1104</v>
+        <v>3.6096</v>
       </c>
     </row>
     <row r="402">
@@ -19349,10 +19349,10 @@
         <v>1.53</v>
       </c>
       <c r="I402" t="n">
-        <v>0.9552</v>
+        <v>0.9207</v>
       </c>
       <c r="J402" t="n">
-        <v>28.656</v>
+        <v>27.621</v>
       </c>
     </row>
     <row r="403">
@@ -19389,10 +19389,10 @@
         <v>1.18</v>
       </c>
       <c r="I403" t="n">
-        <v>0.4084</v>
+        <v>0.3521</v>
       </c>
       <c r="J403" t="n">
-        <v>12.252</v>
+        <v>10.563</v>
       </c>
     </row>
     <row r="404">
@@ -19429,10 +19429,10 @@
         <v>0.82</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2289</v>
+        <v>-0.2085</v>
       </c>
       <c r="J404" t="n">
-        <v>-6.867</v>
+        <v>-6.255</v>
       </c>
     </row>
     <row r="405">
@@ -19469,10 +19469,10 @@
         <v>0.76</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2879</v>
+        <v>-0.2692</v>
       </c>
       <c r="J405" t="n">
-        <v>-8.637</v>
+        <v>-8.076000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -19509,10 +19509,10 @@
         <v>0.52</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.5031</v>
+        <v>-0.5047</v>
       </c>
       <c r="J406" t="n">
-        <v>-15.093</v>
+        <v>-15.141</v>
       </c>
     </row>
     <row r="407">
@@ -19549,10 +19549,10 @@
         <v>1.64</v>
       </c>
       <c r="I407" t="n">
-        <v>1.3101</v>
+        <v>1.3331</v>
       </c>
       <c r="J407" t="n">
-        <v>39.303</v>
+        <v>39.993</v>
       </c>
     </row>
     <row r="408">
@@ -19589,10 +19589,10 @@
         <v>1.3</v>
       </c>
       <c r="I408" t="n">
-        <v>0.7664</v>
+        <v>0.7381</v>
       </c>
       <c r="J408" t="n">
-        <v>22.992</v>
+        <v>22.143</v>
       </c>
     </row>
     <row r="409">
@@ -19629,10 +19629,10 @@
         <v>1.07</v>
       </c>
       <c r="I409" t="n">
-        <v>0.2389</v>
+        <v>0.2076</v>
       </c>
       <c r="J409" t="n">
-        <v>7.167</v>
+        <v>6.228</v>
       </c>
     </row>
     <row r="410">
@@ -19669,10 +19669,10 @@
         <v>0.97</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1603</v>
+        <v>-0.1288</v>
       </c>
       <c r="J410" t="n">
-        <v>-4.809</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="411">
@@ -19709,10 +19709,10 @@
         <v>0.71</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.8136</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="J411" t="n">
-        <v>-24.408</v>
+        <v>-23.784</v>
       </c>
     </row>
     <row r="412">
@@ -19749,10 +19749,10 @@
         <v>1.23</v>
       </c>
       <c r="I412" t="n">
-        <v>0.6227</v>
+        <v>0.5866</v>
       </c>
       <c r="J412" t="n">
-        <v>18.0583</v>
+        <v>17.0114</v>
       </c>
     </row>
     <row r="413">
@@ -19789,10 +19789,10 @@
         <v>1.2</v>
       </c>
       <c r="I413" t="n">
-        <v>0.5568</v>
+        <v>0.5188</v>
       </c>
       <c r="J413" t="n">
-        <v>16.1472</v>
+        <v>15.0452</v>
       </c>
     </row>
     <row r="414">
@@ -19829,10 +19829,10 @@
         <v>1.07</v>
       </c>
       <c r="I414" t="n">
-        <v>0.2418</v>
+        <v>0.2097</v>
       </c>
       <c r="J414" t="n">
-        <v>7.0122</v>
+        <v>6.0813</v>
       </c>
     </row>
     <row r="415">
@@ -19869,10 +19869,10 @@
         <v>1.05</v>
       </c>
       <c r="I415" t="n">
-        <v>0.1831</v>
+        <v>0.1551</v>
       </c>
       <c r="J415" t="n">
-        <v>5.3099</v>
+        <v>4.4979</v>
       </c>
     </row>
     <row r="416">
@@ -19909,10 +19909,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.1831</v>
+        <v>0.1551</v>
       </c>
       <c r="J416" t="n">
-        <v>5.3099</v>
+        <v>4.4979</v>
       </c>
     </row>
     <row r="417">
@@ -19949,10 +19949,10 @@
         <v>1.31</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6131</v>
+        <v>0.5545</v>
       </c>
       <c r="J417" t="n">
-        <v>17.7799</v>
+        <v>16.0805</v>
       </c>
     </row>
     <row r="418">
@@ -19989,10 +19989,10 @@
         <v>1.21</v>
       </c>
       <c r="I418" t="n">
-        <v>0.4507</v>
+        <v>0.3927</v>
       </c>
       <c r="J418" t="n">
-        <v>13.0703</v>
+        <v>11.3883</v>
       </c>
     </row>
     <row r="419">
@@ -20069,10 +20069,10 @@
         <v>0.76</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2914</v>
+        <v>-0.2731</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.4506</v>
+        <v>-7.9199</v>
       </c>
     </row>
     <row r="421">
@@ -20109,10 +20109,10 @@
         <v>0.72</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3292</v>
+        <v>-0.313</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.546799999999999</v>
+        <v>-9.077</v>
       </c>
     </row>
     <row r="422">
@@ -20149,10 +20149,10 @@
         <v>1.77</v>
       </c>
       <c r="I422" t="n">
-        <v>1.4186</v>
+        <v>1.4446</v>
       </c>
       <c r="J422" t="n">
-        <v>26.9534</v>
+        <v>27.4474</v>
       </c>
     </row>
     <row r="423">
@@ -20189,10 +20189,10 @@
         <v>1.37</v>
       </c>
       <c r="I423" t="n">
-        <v>0.8645</v>
+        <v>0.8524</v>
       </c>
       <c r="J423" t="n">
-        <v>16.4255</v>
+        <v>16.1956</v>
       </c>
     </row>
     <row r="424">
@@ -20229,10 +20229,10 @@
         <v>1.36</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8461</v>
+        <v>0.8329</v>
       </c>
       <c r="J424" t="n">
-        <v>16.0759</v>
+        <v>15.8251</v>
       </c>
     </row>
     <row r="425">
@@ -20269,10 +20269,10 @@
         <v>1.26</v>
       </c>
       <c r="I425" t="n">
-        <v>0.6498</v>
+        <v>0.626</v>
       </c>
       <c r="J425" t="n">
-        <v>12.3462</v>
+        <v>11.894</v>
       </c>
     </row>
     <row r="426">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I426" t="n">
-        <v>0.3082</v>
+        <v>0.2761</v>
       </c>
       <c r="J426" t="n">
-        <v>5.8558</v>
+        <v>5.2459</v>
       </c>
     </row>
     <row r="427">
@@ -20349,10 +20349,10 @@
         <v>1.06</v>
       </c>
       <c r="I427" t="n">
-        <v>0.2696</v>
+        <v>0.2413</v>
       </c>
       <c r="J427" t="n">
-        <v>5.1224</v>
+        <v>4.5847</v>
       </c>
     </row>
     <row r="428">
@@ -20389,10 +20389,10 @@
         <v>0.82</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.2001</v>
+        <v>-0.1847</v>
       </c>
       <c r="J428" t="n">
-        <v>-3.8019</v>
+        <v>-3.5093</v>
       </c>
     </row>
     <row r="429">
@@ -20429,10 +20429,10 @@
         <v>0.67</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.3428</v>
+        <v>-0.3298</v>
       </c>
       <c r="J429" t="n">
-        <v>-6.5132</v>
+        <v>-6.2662</v>
       </c>
     </row>
     <row r="430">
@@ -20469,10 +20469,10 @@
         <v>0.51</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4842</v>
+        <v>-0.4807</v>
       </c>
       <c r="J430" t="n">
-        <v>-9.1998</v>
+        <v>-9.1333</v>
       </c>
     </row>
     <row r="431">
@@ -20509,10 +20509,10 @@
         <v>0.4</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5895</v>
       </c>
       <c r="J431" t="n">
-        <v>-11.0219</v>
+        <v>-11.2005</v>
       </c>
     </row>
   </sheetData>
